--- a/results/05_transient_transcription_output/702/702_196402_SF.JPG_stage_duirnal_temp_range.xlsx
+++ b/results/05_transient_transcription_output/702/702_196402_SF.JPG_stage_duirnal_temp_range.xlsx
@@ -41,20 +41,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0075696F"/>
-        <bgColor rgb="0075696F"/>
+        <fgColor rgb="00CC3300"/>
+        <bgColor rgb="00CC3300"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6DCD57"/>
-        <bgColor rgb="FF6DCD57"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00CC3300"/>
-        <bgColor rgb="00CC3300"/>
+        <fgColor rgb="0075696F"/>
+        <bgColor rgb="0075696F"/>
       </patternFill>
     </fill>
     <fill>
@@ -67,6 +61,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFC0CB"/>
         <bgColor rgb="00FFC0CB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6DCD57"/>
+        <bgColor rgb="FF6DCD57"/>
       </patternFill>
     </fill>
   </fills>
@@ -137,7 +137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -156,9 +156,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -784,19 +781,19 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>321.2</v>
-      </c>
-      <c r="D4" s="10" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="D4" s="13" t="n">
         <v>27.9</v>
       </c>
-      <c r="E4" s="10" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="F4" s="10" t="n">
+      <c r="E4" s="13" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="F4" s="13" t="n">
         <v>18.5</v>
       </c>
-      <c r="G4" s="8" t="n">
-        <v>81.7</v>
+      <c r="G4" s="13" t="n">
+        <v>18.7</v>
       </c>
       <c r="H4" s="3" t="n">
         <v>5.6</v>
@@ -805,25 +802,25 @@
         <v>1564.4</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>9.300000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="M4" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="N4" s="8" t="n">
-        <v>11.4</v>
+        <v>1.9</v>
       </c>
       <c r="O4" s="3" t="n">
         <v>98</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>10.4</v>
+        <v>0.9</v>
       </c>
       <c r="Q4" s="3" t="n"/>
       <c r="R4" s="3" t="n">
@@ -833,25 +830,25 @@
         <v>1.4</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>42.5</v>
+        <v>62.5</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>22.1</v>
+        <v>22</v>
       </c>
       <c r="W4" s="3" t="n">
         <v>18.3</v>
       </c>
-      <c r="X4" s="8" t="n">
-        <v>28.9</v>
+      <c r="X4" s="3" t="n">
+        <v>18.9</v>
       </c>
       <c r="Y4" s="3" t="n">
         <v>71</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>7.8</v>
+        <v>1.8</v>
       </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
@@ -867,22 +864,22 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>382.4</v>
-      </c>
-      <c r="D5" s="10" t="n">
-        <v>26.9</v>
-      </c>
-      <c r="E5" s="10" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="F5" s="10" t="n">
+        <v>382.9</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="E5" s="9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F5" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="G5" s="10" t="n">
-        <v>15.4</v>
+      <c r="G5" s="3" t="n">
+        <v>5.9</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>2.9</v>
+        <v>2</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>1.8</v>
@@ -893,13 +890,13 @@
       <c r="K5" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="L5" s="3" t="n">
+      <c r="L5" s="8" t="n">
         <v>12.3</v>
       </c>
       <c r="M5" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="N5" s="3" t="n">
+      <c r="N5" s="8" t="n">
         <v>12.9</v>
       </c>
       <c r="O5" s="3" t="n">
@@ -921,8 +918,8 @@
       <c r="U5" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="V5" s="8" t="n">
-        <v>19.5</v>
+      <c r="V5" s="3" t="n">
+        <v>0.5</v>
       </c>
       <c r="W5" s="3" t="n">
         <v>21.2</v>
@@ -934,7 +931,7 @@
         <v>80.5</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>6.4</v>
+        <v>6.9</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -950,18 +947,18 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>309.1</v>
-      </c>
-      <c r="D6" s="10" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="E6" s="10" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="F6" s="10" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="G6" s="10" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="D6" s="9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E6" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="G6" s="3" t="n">
         <v>15</v>
       </c>
       <c r="H6" s="3" t="n">
@@ -970,47 +967,47 @@
       <c r="I6" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="J6" s="3" t="n">
-        <v>1.1</v>
+      <c r="J6" s="8" t="n">
+        <v>6</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="L6" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="M6" s="8" t="n">
-        <v>11</v>
+      <c r="M6" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>13.1</v>
+        <v>1</v>
       </c>
       <c r="O6" s="3" t="n">
         <v>99</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>10.2</v>
+        <v>2</v>
       </c>
       <c r="Q6" s="3" t="n">
         <v>44.5</v>
       </c>
-      <c r="R6" s="8" t="n">
-        <v>14.7</v>
+      <c r="R6" s="3" t="n">
+        <v>9.699999999999999</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>16.3</v>
+        <v>16.5</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>92</v>
+        <v>22</v>
       </c>
       <c r="U6" s="3" t="n">
         <v>0.4</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>15.8</v>
+        <v>0</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>15.3</v>
+        <v>0.3</v>
       </c>
       <c r="X6" s="3" t="n">
         <v>1.1</v>
@@ -1035,19 +1032,19 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>275.8</v>
-      </c>
-      <c r="D7" s="10" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="E7" s="10" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="F7" s="10" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="G7" s="10" t="n">
-        <v>9</v>
+        <v>225.9</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="E7" s="9" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H7" s="3" t="n">
         <v>444.9</v>
@@ -1065,29 +1062,29 @@
       <c r="M7" s="3" t="n">
         <v>34.1</v>
       </c>
-      <c r="N7" s="3" t="n">
-        <v>15</v>
+      <c r="N7" s="8" t="n">
+        <v>35</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>99</v>
+        <v>9</v>
       </c>
       <c r="P7" s="3" t="n">
         <v>0.2</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>19.3</v>
+        <v>0.3</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>16.8</v>
+        <v>6.8</v>
       </c>
       <c r="S7" s="3" t="n">
         <v>3.1</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>919</v>
+        <v>100</v>
       </c>
       <c r="U7" s="3" t="n">
-        <v>49.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="V7" s="3" t="n">
         <v>8.4</v>
@@ -1096,13 +1093,13 @@
         <v>16.8</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>17.9</v>
+        <v>0.7</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1118,22 +1115,22 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>391.2</v>
-      </c>
-      <c r="D8" s="10" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="E8" s="10" t="n">
+        <v>291.2</v>
+      </c>
+      <c r="D8" s="13" t="n">
+        <v>36.3</v>
+      </c>
+      <c r="E8" s="13" t="n">
         <v>10.5</v>
       </c>
-      <c r="F8" s="10" t="n">
-        <v>18.4</v>
+      <c r="F8" s="13" t="n">
+        <v>23.4</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>5.2</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>1.2</v>
@@ -1142,7 +1139,7 @@
         <v>3.5</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L8" s="3" t="n">
         <v>4</v>
@@ -1150,17 +1147,17 @@
       <c r="M8" s="3" t="n">
         <v>2.4</v>
       </c>
-      <c r="N8" s="3" t="n">
-        <v>12.7</v>
+      <c r="N8" s="8" t="n">
+        <v>20.7</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>98</v>
+        <v>8</v>
       </c>
       <c r="P8" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="Q8" s="8" t="n">
-        <v>71.40000000000001</v>
+      <c r="Q8" s="3" t="n">
+        <v>27.9</v>
       </c>
       <c r="R8" s="3" t="n">
         <v>84.5</v>
@@ -1175,12 +1172,12 @@
         <v>6</v>
       </c>
       <c r="V8" s="3" t="n">
-        <v>18.7</v>
+        <v>18.9</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>17.3</v>
-      </c>
-      <c r="X8" s="8" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="X8" s="3" t="n">
         <v>18.9</v>
       </c>
       <c r="Y8" s="3" t="n">
@@ -1203,26 +1200,29 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>1749.7</v>
-      </c>
-      <c r="D9" s="9" t="n">
+        <v>124.9</v>
+      </c>
+      <c r="D9" s="10" t="n">
         <v>289.5</v>
       </c>
       <c r="E9" s="10" t="n">
         <v>55</v>
       </c>
-      <c r="F9" s="9" t="n">
-        <v>91.90000000000001</v>
+      <c r="F9" s="10" t="n">
+        <v>0.1</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>7.3</v>
+        <v>13</v>
       </c>
       <c r="H9" s="3" t="n"/>
       <c r="I9" s="3" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="J9" s="3" t="n">
-        <v>13.3</v>
+        <v>9</v>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1350 0
+</t>
+        </is>
       </c>
       <c r="K9" s="3" t="n">
         <v>7.7</v>
@@ -1234,13 +1234,13 @@
         <v>554.2</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>65.09999999999999</v>
+        <v>5</v>
       </c>
       <c r="O9" s="3" t="n">
         <v>48421.2</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>82.59999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="Q9" s="3" t="n">
         <v>10.1</v>
@@ -1249,28 +1249,28 @@
         <v>85.3</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>88.5</v>
+        <v>88</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>380.5</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>33.3</v>
+        <v>33</v>
       </c>
       <c r="V9" s="3" t="n">
         <v>95</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>85.90000000000001</v>
+        <v>0</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>91.09999999999999</v>
+        <v>0.1</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>414.5</v>
+        <v>914.5</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>19.8</v>
+        <v>109.8</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1291,15 +1291,15 @@
       <c r="D10" s="10" t="n">
         <v>25.8</v>
       </c>
-      <c r="E10" s="9" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="F10" s="9" t="n">
+      <c r="E10" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="10" t="n">
         <v>4.3</v>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148 1
+          <t xml:space="preserve">19 0
 </t>
         </is>
       </c>
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K10" s="3" t="n"/>
       <c r="L10" s="3" t="n">
-        <v>11.3</v>
+        <v>1.1</v>
       </c>
       <c r="M10" s="3" t="n">
         <v>11</v>
@@ -1327,25 +1327,25 @@
         <v>0.5</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>20.3</v>
+        <v>2</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>17.1</v>
+        <v>6</v>
       </c>
       <c r="S10" s="3" t="n">
         <v>0.2</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>76.09999999999999</v>
+        <v>20</v>
       </c>
       <c r="U10" s="3" t="n">
         <v>6.1</v>
       </c>
       <c r="V10" s="3" t="n">
-        <v>19.8</v>
+        <v>19</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="X10" s="3" t="n">
         <v>18.2</v>
@@ -1370,46 +1370,46 @@
       <c r="C11" s="3" t="n">
         <v>509.5</v>
       </c>
-      <c r="D11" s="10" t="n">
-        <v>27.3</v>
-      </c>
-      <c r="E11" s="10" t="n">
-        <v>-1.3</v>
-      </c>
-      <c r="F11" s="3" t="n">
-        <v>13</v>
+      <c r="D11" s="9" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="F11" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="H11" s="3" t="n"/>
       <c r="I11" s="3" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="K11" s="3" t="n"/>
       <c r="L11" s="3" t="n">
         <v>1.2</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="N11" s="3" t="n">
         <v>13</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="Q11" s="3" t="n">
         <v>266.3</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>17.1</v>
+        <v>0</v>
       </c>
       <c r="S11" s="3" t="n">
         <v>1.2</v>
@@ -1418,7 +1418,7 @@
         <v>427.7</v>
       </c>
       <c r="U11" s="8" t="n">
-        <v>19.9</v>
+        <v>209.9</v>
       </c>
       <c r="V11" s="3" t="n">
         <v>22.1</v>
@@ -1426,11 +1426,11 @@
       <c r="W11" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="X11" s="8" t="n">
-        <v>17.6</v>
+      <c r="X11" s="3" t="n">
+        <v>7.6</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>66</v>
+        <v>20</v>
       </c>
       <c r="Z11" s="3" t="n">
         <v>9</v>
@@ -1451,35 +1451,35 @@
       <c r="C12" s="3" t="n">
         <v>506.7</v>
       </c>
-      <c r="D12" s="10" t="n">
+      <c r="D12" s="3" t="n">
         <v>25.9</v>
       </c>
-      <c r="E12" s="10" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="F12" s="10" t="n">
-        <v>18.4</v>
+      <c r="E12" s="9" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>18.9</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>15.9</v>
+        <v>5</v>
       </c>
       <c r="K12" s="3" t="n"/>
-      <c r="L12" s="8" t="n">
-        <v>11.7</v>
+      <c r="L12" s="3" t="n">
+        <v>10.7</v>
       </c>
       <c r="M12" s="3" t="n">
         <v>41.1</v>
       </c>
-      <c r="N12" s="3" t="n">
+      <c r="N12" s="8" t="n">
         <v>13.2</v>
       </c>
       <c r="O12" s="3" t="n">
@@ -1489,29 +1489,29 @@
         <v>0.8</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>25.4</v>
+        <v>25</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>15.5</v>
+        <v>5.5</v>
       </c>
       <c r="S12" s="3" t="n"/>
       <c r="T12" s="3" t="n">
         <v>86</v>
       </c>
       <c r="U12" s="3" t="n">
-        <v>90.59999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="V12" s="3" t="n">
         <v>21.3</v>
       </c>
-      <c r="W12" s="3" t="n">
-        <v>14.7</v>
+      <c r="W12" s="8" t="n">
+        <v>19.7</v>
       </c>
       <c r="X12" s="3" t="n">
-        <v>13.1</v>
+        <v>0</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>52</v>
+        <v>2</v>
       </c>
       <c r="Z12" s="3" t="n">
         <v>2.2</v>
@@ -1530,25 +1530,25 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>357.9</v>
-      </c>
-      <c r="D13" s="10" t="n">
+        <v>307.9</v>
+      </c>
+      <c r="D13" s="9" t="n">
         <v>25.35</v>
       </c>
-      <c r="E13" s="12" t="n">
+      <c r="E13" s="9" t="n">
         <v>4.2</v>
       </c>
-      <c r="F13" s="12" t="n">
-        <v>81.3</v>
-      </c>
-      <c r="G13" s="12" t="n">
+      <c r="F13" s="9" t="n">
+        <v>38.03</v>
+      </c>
+      <c r="G13" s="9" t="n">
         <v>44.4</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>7.5</v>
+        <v>0.5</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>19.4</v>
+        <v>0.9</v>
       </c>
       <c r="J13" s="3" t="n">
         <v>2.5</v>
@@ -1557,47 +1557,47 @@
         <v>0.5</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>18.8</v>
+        <v>10.8</v>
       </c>
       <c r="M13" s="8" t="n">
-        <v>191.6</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="N13" s="3" t="n">
         <v>4.6</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>98</v>
+        <v>8</v>
       </c>
       <c r="P13" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="Q13" s="8" t="n">
-        <v>18.9</v>
+        <v>180.9</v>
       </c>
       <c r="R13" s="3" t="n">
         <v>7.3</v>
       </c>
-      <c r="S13" s="8" t="n">
-        <v>81.90000000000001</v>
+      <c r="S13" s="3" t="n">
+        <v>8.9</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>197</v>
+        <v>20</v>
       </c>
       <c r="U13" s="3" t="n">
         <v>3</v>
       </c>
       <c r="V13" s="3" t="n"/>
-      <c r="W13" s="3" t="n">
-        <v>17.7</v>
+      <c r="W13" s="8" t="n">
+        <v>72</v>
       </c>
       <c r="X13" s="3" t="n">
-        <v>19.1</v>
+        <v>0</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="Z13" s="3" t="n">
-        <v>3.6</v>
+        <v>9.6</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
@@ -1613,28 +1613,28 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>227</v>
-      </c>
-      <c r="D14" s="10" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="E14" s="10" t="n">
-        <v>13</v>
-      </c>
-      <c r="F14" s="10" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="G14" s="10" t="n">
+        <v>22</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="E14" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F14" s="9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G14" s="3" t="n">
         <v>10.5</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>10.3</v>
+        <v>0.3</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>1.3</v>
+        <v>0.3</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>29.5</v>
+        <v>0.5</v>
       </c>
       <c r="K14" s="3" t="n">
         <v>4.3</v>
@@ -1642,34 +1642,37 @@
       <c r="L14" s="3" t="n">
         <v>13.2</v>
       </c>
-      <c r="M14" s="8" t="n">
-        <v>13</v>
-      </c>
-      <c r="N14" s="3" t="n">
-        <v>14.8</v>
+      <c r="M14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">048 0
+</t>
+        </is>
       </c>
       <c r="O14" s="3" t="n">
-        <v>98</v>
+        <v>8</v>
       </c>
       <c r="P14" s="3" t="n"/>
       <c r="Q14" s="3" t="n">
-        <v>14.9</v>
+        <v>4</v>
       </c>
       <c r="R14" s="3" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="S14" s="8" t="n">
-        <v>56.6</v>
+        <v>0.6</v>
+      </c>
+      <c r="S14" s="3" t="n">
+        <v>6.6</v>
       </c>
       <c r="T14" s="3" t="n">
         <v>58</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="V14" s="3" t="n"/>
       <c r="W14" s="3" t="n">
-        <v>16.2</v>
+        <v>0.2</v>
       </c>
       <c r="X14" s="3" t="n">
         <v>61</v>
@@ -1678,7 +1681,7 @@
         <v>95</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1694,22 +1697,22 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>229</v>
-      </c>
-      <c r="D15" s="10" t="n">
-        <v>26</v>
-      </c>
-      <c r="E15" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="D15" s="13" t="n">
+        <v>36</v>
+      </c>
+      <c r="E15" s="13" t="n">
         <v>11</v>
       </c>
-      <c r="F15" s="10" t="n">
-        <v>18.5</v>
+      <c r="F15" s="13" t="n">
+        <v>23.5</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>15.8</v>
+        <v>5</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>17.9</v>
+        <v>1</v>
       </c>
       <c r="I15" s="3" t="n">
         <v>3.8</v>
@@ -1721,49 +1724,49 @@
         <v>2.1</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="M15" s="8" t="n">
-        <v>11.3</v>
+        <v>10</v>
+      </c>
+      <c r="M15" s="3" t="n">
+        <v>0.3</v>
       </c>
       <c r="N15" s="3" t="n">
         <v>434.3</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>99</v>
+        <v>9</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>10.2</v>
+        <v>0</v>
       </c>
       <c r="Q15" s="3" t="n">
         <v>25.5</v>
       </c>
       <c r="R15" s="3" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="S15" s="8" t="n">
-        <v>51.7</v>
+        <v>7.6</v>
+      </c>
+      <c r="S15" s="3" t="n">
+        <v>5.7</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>310.8</v>
+        <v>310</v>
       </c>
       <c r="U15" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="V15" s="3" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="W15" s="3" t="n">
         <v>16.3</v>
       </c>
       <c r="X15" s="3" t="n">
-        <v>16.4</v>
+        <v>0</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>167</v>
+        <v>67</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1779,48 +1782,50 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>9994.1</v>
-      </c>
-      <c r="D16" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="13" t="n">
         <v>128</v>
       </c>
-      <c r="E16" s="9" t="n">
+      <c r="E16" s="10" t="n">
         <v>56.8</v>
       </c>
-      <c r="F16" s="10" t="n">
+      <c r="F16" s="13" t="n">
         <v>92.5</v>
       </c>
-      <c r="G16" s="10" t="n">
-        <v>71.2</v>
+      <c r="G16" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="H16" s="3" t="n">
         <v>39.5</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>14.6</v>
+        <v>14</v>
       </c>
       <c r="J16" s="3" t="n">
         <v>139.8</v>
       </c>
-      <c r="K16" s="3" t="n"/>
+      <c r="K16" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="L16" s="3" t="n">
-        <v>59.9</v>
+        <v>59.1</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>58.2</v>
+        <v>8</v>
       </c>
       <c r="N16" s="3" t="n"/>
       <c r="O16" s="3" t="n">
-        <v>489</v>
+        <v>689</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>2</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>1191.8</v>
+        <v>110</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>82.2</v>
+        <v>8</v>
       </c>
       <c r="S16" s="3" t="n">
         <v>77.3</v>
@@ -1829,19 +1834,19 @@
         <v>42</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>60.9</v>
+        <v>60</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>98.2</v>
+        <v>25</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>801.1</v>
+        <v>80</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>82.2</v>
+        <v>0</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="Z16" s="3" t="n">
         <v>33.4</v>
@@ -1862,24 +1867,24 @@
       <c r="C17" s="3" t="n">
         <v>445.9</v>
       </c>
-      <c r="D17" s="10" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="E17" s="10" t="n">
+      <c r="D17" s="13" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="E17" s="13" t="n">
         <v>11.4</v>
       </c>
-      <c r="F17" s="10" t="n">
-        <v>18.5</v>
+      <c r="F17" s="13" t="n">
+        <v>18.8</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>44.4</v>
       </c>
       <c r="H17" s="3" t="n"/>
-      <c r="I17" s="8" t="n">
-        <v>29.4</v>
+      <c r="I17" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>44.8</v>
+        <v>4.9</v>
       </c>
       <c r="K17" s="3" t="n">
         <v>0.1</v>
@@ -1888,46 +1893,46 @@
         <v>11.8</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>11.6</v>
+        <v>0</v>
       </c>
       <c r="N17" s="3" t="n">
         <v>41.6</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>971.8</v>
+        <v>1</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>4.4</v>
+        <v>9</v>
       </c>
       <c r="Q17" s="3" t="n">
         <v>22.2</v>
       </c>
       <c r="R17" s="3" t="n">
-        <v>12.9</v>
+        <v>0</v>
       </c>
       <c r="S17" s="3" t="n">
         <v>151.5</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>46.2</v>
+        <v>6</v>
       </c>
       <c r="U17" s="3" t="n">
         <v>84.7</v>
       </c>
-      <c r="V17" s="8" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="W17" s="8" t="n">
-        <v>16.1</v>
+      <c r="V17" s="3" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="W17" s="3" t="n">
+        <v>16.7</v>
       </c>
       <c r="X17" s="3" t="n">
-        <v>16.4</v>
+        <v>0</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>72.8</v>
+        <v>82.8</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1943,23 +1948,23 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>455.6</v>
-      </c>
-      <c r="D18" s="13" t="n"/>
-      <c r="E18" s="12" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F18" s="12" t="n">
+        <v>455</v>
+      </c>
+      <c r="D18" s="11" t="n"/>
+      <c r="E18" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="9" t="n">
         <v>18.14</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>29.4</v>
+        <v>20.9</v>
       </c>
       <c r="J18" s="3" t="n">
         <v>3.3</v>
@@ -1970,42 +1975,42 @@
       <c r="L18" s="3" t="n">
         <v>102.2</v>
       </c>
-      <c r="M18" s="8" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="N18" s="8" t="n">
-        <v>56.5</v>
+      <c r="M18" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="N18" s="3" t="n">
+        <v>16</v>
       </c>
       <c r="O18" s="3" t="n">
         <v>99</v>
       </c>
       <c r="P18" s="3" t="n"/>
-      <c r="Q18" s="3" t="n">
-        <v>25.8</v>
+      <c r="Q18" s="8" t="n">
+        <v>95.8</v>
       </c>
       <c r="R18" s="3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="S18" s="8" t="n">
-        <v>15.4</v>
+        <v>0</v>
+      </c>
+      <c r="S18" s="3" t="n">
+        <v>5.9</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>48.5</v>
-      </c>
-      <c r="U18" s="8" t="n">
+        <v>98.5</v>
+      </c>
+      <c r="U18" s="3" t="n">
         <v>17.9</v>
       </c>
       <c r="V18" s="3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="W18" s="3" t="n">
         <v>5.4</v>
       </c>
       <c r="X18" s="3" t="n">
-        <v>14.6</v>
+        <v>5.6</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>59</v>
+        <v>9</v>
       </c>
       <c r="Z18" s="3" t="n">
         <v>10.4</v>
@@ -2024,22 +2029,22 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>531.1</v>
-      </c>
-      <c r="D19" s="3" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="E19" s="12" t="n">
+        <v>530</v>
+      </c>
+      <c r="D19" s="9" t="n">
+        <v>50.9</v>
+      </c>
+      <c r="E19" s="9" t="n">
         <v>40.9</v>
       </c>
-      <c r="F19" s="3" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="G19" s="8" t="n">
-        <v>17.4</v>
+      <c r="F19" s="9" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>7.9</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>72.2</v>
+        <v>0</v>
       </c>
       <c r="I19" s="3" t="n">
         <v>0.3</v>
@@ -2051,34 +2056,34 @@
         <v>0</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="M19" s="8" t="n">
-        <v>19</v>
-      </c>
-      <c r="N19" s="3" t="n">
-        <v>13</v>
+        <v>1.2</v>
+      </c>
+      <c r="M19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="8" t="n">
+        <v>12</v>
       </c>
       <c r="O19" s="3" t="n">
         <v>98</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>0.4</v>
+        <v>4.9</v>
       </c>
       <c r="Q19" s="3" t="n">
         <v>22.1</v>
       </c>
       <c r="R19" s="3" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="S19" s="3" t="n">
         <v>64.2</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>48.5</v>
+        <v>98.5</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>17.2</v>
+        <v>0.7</v>
       </c>
       <c r="V19" s="3" t="n">
         <v>21.2</v>
@@ -2109,25 +2114,25 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>531.1</v>
-      </c>
-      <c r="D20" s="3" t="n">
-        <v>28</v>
-      </c>
-      <c r="E20" s="3" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="F20" s="12" t="n">
+        <v>530</v>
+      </c>
+      <c r="D20" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="E20" s="9" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F20" s="9" t="n">
         <v>4.3</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>17.8</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>6.9</v>
+        <v>0</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>33.5</v>
+        <v>35.3</v>
       </c>
       <c r="J20" s="3" t="n">
         <v>4.9</v>
@@ -2137,7 +2142,7 @@
         <v>0.2</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="N20" s="3" t="n">
         <v>2</v>
@@ -2146,37 +2151,37 @@
         <v>98</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="Q20" s="3" t="n">
         <v>28</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>18.9</v>
+        <v>18</v>
       </c>
       <c r="S20" s="3" t="n">
         <v>51.3</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>40.5</v>
+        <v>20.5</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>22.4</v>
+        <v>22.9</v>
       </c>
       <c r="V20" s="3" t="n">
         <v>221.1</v>
       </c>
       <c r="W20" s="3" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="X20" s="8" t="n">
-        <v>19.9</v>
+        <v>18.9</v>
+      </c>
+      <c r="X20" s="3" t="n">
+        <v>0.9</v>
       </c>
       <c r="Y20" s="3" t="n">
         <v>44.4</v>
       </c>
       <c r="Z20" s="3" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
@@ -2192,19 +2197,19 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>28.2</v>
       </c>
-      <c r="E21" s="3" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="F21" s="12" t="n">
+      <c r="E21" s="9" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F21" s="9" t="n">
         <v>12.13</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>12.1</v>
+        <v>2.1</v>
       </c>
       <c r="H21" s="3" t="n">
         <v>2.1</v>
@@ -2225,13 +2230,13 @@
         <v>0.3</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>15.9</v>
+        <v>15</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>99</v>
+        <v>9</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="Q21" s="3" t="n">
         <v>25.6</v>
@@ -2241,13 +2246,13 @@
         <v>16.8</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="U21" s="3" t="n">
         <v>16.2</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>19.8</v>
+        <v>0</v>
       </c>
       <c r="W21" s="3" t="n">
         <v>48.2</v>
@@ -2256,10 +2261,10 @@
         <v>20</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>87</v>
+        <v>8</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
@@ -2278,69 +2283,69 @@
         <v>429</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="E22" s="13" t="n"/>
-      <c r="F22" s="12" t="n">
-        <v>81.7</v>
+        <v>29.8</v>
+      </c>
+      <c r="E22" s="11" t="n"/>
+      <c r="F22" s="3" t="n">
+        <v>8.699999999999999</v>
       </c>
       <c r="G22" s="3" t="n">
         <v>1.3</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>8</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="J22" s="3" t="n">
         <v>3.8</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="L22" s="3" t="n">
-        <v>12.3</v>
+        <v>0</v>
+      </c>
+      <c r="L22" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="M22" s="3" t="n"/>
-      <c r="N22" s="8" t="n">
-        <v>84.09999999999999</v>
+      <c r="N22" s="3" t="n">
+        <v>9</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>99</v>
+        <v>9</v>
       </c>
       <c r="P22" s="3" t="n">
         <v>0.2</v>
       </c>
       <c r="Q22" s="3" t="n">
-        <v>23.6</v>
+        <v>23</v>
       </c>
       <c r="R22" s="3" t="n">
-        <v>16.2</v>
+        <v>1.6</v>
       </c>
       <c r="S22" s="3" t="n">
-        <v>14.9</v>
+        <v>9.9</v>
       </c>
       <c r="T22" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="U22" s="3" t="n">
-        <v>15.8</v>
+      <c r="U22" s="8" t="n">
+        <v>59.8</v>
       </c>
       <c r="V22" s="3" t="n">
         <v>22.5</v>
       </c>
-      <c r="W22" s="8" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="X22" s="8" t="n">
-        <v>13.9</v>
+      <c r="W22" s="3" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="X22" s="3" t="n">
+        <v>3.9</v>
       </c>
       <c r="Y22" s="3" t="n">
-        <v>50.5</v>
+        <v>0.5</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>13.4</v>
+        <v>3.9</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2356,19 +2361,19 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>2320.3</v>
-      </c>
-      <c r="D23" s="9" t="n">
+        <v>23</v>
+      </c>
+      <c r="D23" s="10" t="n">
         <v>25.2</v>
       </c>
-      <c r="E23" s="9" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="F23" s="9" t="n">
-        <v>945.4</v>
+      <c r="E23" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F23" s="10" t="n">
+        <v>95.90000000000001</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>75.90000000000001</v>
+        <v>0</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>40.6</v>
@@ -2393,14 +2398,14 @@
         <v>293</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>11.4</v>
+        <v>0.9</v>
       </c>
       <c r="Q23" s="3" t="n">
         <v>128.9</v>
       </c>
       <c r="R23" s="3" t="n"/>
       <c r="S23" s="3" t="n">
-        <v>78.09999999999999</v>
+        <v>18</v>
       </c>
       <c r="T23" s="3" t="n">
         <v>2357.1</v>
@@ -2418,10 +2423,10 @@
         <v>86.2</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>341.5</v>
+        <v>39.5</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2437,19 +2442,19 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>464.1</v>
-      </c>
-      <c r="D24" s="9" t="n">
+        <v>64.09999999999999</v>
+      </c>
+      <c r="D24" s="10" t="n">
         <v>32.3</v>
       </c>
-      <c r="E24" s="9" t="n">
+      <c r="E24" s="10" t="n">
         <v>56.1</v>
       </c>
-      <c r="F24" s="9" t="n">
-        <v>81.90000000000001</v>
+      <c r="F24" s="10" t="n">
+        <v>18.9</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="H24" s="3" t="n">
         <v>8.1</v>
@@ -2458,21 +2463,23 @@
         <v>2.9</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>42.1</v>
-      </c>
-      <c r="K24" s="3" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="K24" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="L24" s="3" t="n">
         <v>42.5</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>12.4</v>
+        <v>2.4</v>
       </c>
       <c r="N24" s="3" t="n"/>
       <c r="O24" s="3" t="n">
         <v>98.59999999999999</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>0.3</v>
+        <v>3</v>
       </c>
       <c r="Q24" s="3" t="n">
         <v>25.8</v>
@@ -2481,25 +2488,25 @@
         <v>17.6</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>15.6</v>
+        <v>15</v>
       </c>
       <c r="T24" s="3" t="n">
         <v>44.1</v>
       </c>
-      <c r="U24" s="8" t="n">
-        <v>177.4</v>
+      <c r="U24" s="3" t="n">
+        <v>17.7</v>
       </c>
       <c r="V24" s="3" t="n">
         <v>21.3</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="X24" s="8" t="n">
-        <v>17.2</v>
+        <v>17</v>
+      </c>
+      <c r="X24" s="3" t="n">
+        <v>7</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>168.3</v>
+        <v>68</v>
       </c>
       <c r="Z24" s="3" t="n"/>
       <c r="AA24" s="3" t="inlineStr">
@@ -2516,12 +2523,12 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>488.9</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="E25" s="8" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="E25" s="3" t="n">
         <v>11.3</v>
       </c>
       <c r="F25" s="3" t="n">
@@ -2536,29 +2543,29 @@
       <c r="I25" s="3" t="n">
         <v>3.7</v>
       </c>
-      <c r="J25" s="8" t="n">
-        <v>14.9</v>
+      <c r="J25" s="3" t="n">
+        <v>19</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="L25" s="3" t="n">
         <v>42.5</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>9.9</v>
+        <v>0</v>
       </c>
       <c r="N25" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>926</v>
+        <v>20</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="Q25" s="3" t="n">
-        <v>24.7</v>
+        <v>29.7</v>
       </c>
       <c r="R25" s="3" t="n">
         <v>1.2</v>
@@ -2567,10 +2574,10 @@
         <v>13.4</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>469.5</v>
-      </c>
-      <c r="U25" s="3" t="n">
-        <v>15.8</v>
+        <v>0.5</v>
+      </c>
+      <c r="U25" s="8" t="n">
+        <v>19.8</v>
       </c>
       <c r="V25" s="3" t="n">
         <v>24.3</v>
@@ -2583,7 +2590,7 @@
         <v>66</v>
       </c>
       <c r="Z25" s="3" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
@@ -2599,12 +2606,12 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>349.9</v>
+        <v>34.9</v>
       </c>
       <c r="D26" s="3" t="n">
         <v>25.9</v>
       </c>
-      <c r="E26" s="12" t="n">
+      <c r="E26" s="9" t="n">
         <v>1.2</v>
       </c>
       <c r="F26" s="3" t="n">
@@ -2613,54 +2620,54 @@
       <c r="G26" s="3" t="n">
         <v>14.8</v>
       </c>
-      <c r="H26" s="8" t="n">
-        <v>1.6</v>
+      <c r="H26" s="3" t="n">
+        <v>9</v>
       </c>
       <c r="I26" s="3" t="n">
         <v>2.5</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="K26" s="3" t="n"/>
       <c r="L26" s="3" t="n">
-        <v>10.4</v>
+        <v>0.9</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>10.2</v>
+        <v>0</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>18.1</v>
+        <v>1</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>198</v>
+        <v>98</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>10.4</v>
+        <v>0.4</v>
       </c>
       <c r="Q26" s="3" t="n">
         <v>21</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>16.2</v>
+        <v>0</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>15.7</v>
+        <v>5.2</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>63.5</v>
+        <v>3.5</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>0.2</v>
       </c>
       <c r="V26" s="3" t="n">
-        <v>21.6</v>
+        <v>20.6</v>
       </c>
       <c r="W26" s="8" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="X26" s="3" t="n">
-        <v>12.2</v>
+        <v>60.9</v>
+      </c>
+      <c r="X26" s="8" t="n">
+        <v>10</v>
       </c>
       <c r="Y26" s="3" t="n">
         <v>5</v>
@@ -2684,20 +2691,20 @@
       <c r="C27" s="3" t="n">
         <v>390.2</v>
       </c>
-      <c r="D27" s="8" t="n">
+      <c r="D27" s="3" t="n">
         <v>24.4</v>
       </c>
-      <c r="E27" s="3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="F27" s="3" t="n">
+      <c r="E27" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="8" t="n">
         <v>18.1</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>2</v>
@@ -2706,7 +2713,7 @@
         <v>2.9</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>7.2</v>
@@ -2715,40 +2722,40 @@
         <v>12.2</v>
       </c>
       <c r="N27" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O27" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="O27" s="3" t="n">
-        <v>980.8</v>
-      </c>
       <c r="P27" s="3" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>17.6</v>
+        <v>7</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>14.3</v>
+        <v>10.3</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="U27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" s="3" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="W27" s="3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="X27" s="8" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="Y27" s="3" t="n">
         <v>3</v>
-      </c>
-      <c r="V27" s="3" t="n">
-        <v>87.40000000000001</v>
-      </c>
-      <c r="W27" s="3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="X27" s="3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="Y27" s="3" t="n">
-        <v>123</v>
       </c>
       <c r="Z27" s="3" t="n">
         <v>0.6</v>
@@ -2767,70 +2774,70 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>513.3</v>
-      </c>
-      <c r="D28" s="3" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="E28" s="3" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="F28" s="12" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="D28" s="9" t="n">
+        <v>57</v>
+      </c>
+      <c r="E28" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="9" t="n">
         <v>44.3</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>15.5</v>
+        <v>15.9</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>8.4</v>
+        <v>8.9</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>2.9</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="M28" s="8" t="n">
-        <v>13.3</v>
+        <v>13.9</v>
+      </c>
+      <c r="M28" s="3" t="n">
+        <v>3</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>1.5</v>
+        <v>10</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>99</v>
+        <v>9</v>
       </c>
       <c r="P28" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q28" s="3" t="n">
-        <v>22.9</v>
+      <c r="Q28" s="8" t="n">
+        <v>0.9</v>
       </c>
       <c r="R28" s="3" t="n">
         <v>0.6</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="T28" s="3" t="n">
         <v>68</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>18.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="V28" s="3" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="W28" s="8" t="n">
-        <v>16.7</v>
+        <v>10.9</v>
+      </c>
+      <c r="W28" s="3" t="n">
+        <v>20.7</v>
       </c>
       <c r="X28" s="3" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="Y28" s="3" t="n">
         <v>91</v>
@@ -2852,44 +2859,44 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>593.3</v>
+        <v>503.3</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="E29" s="8" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="F29" s="12" t="n">
+      <c r="E29" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="9" t="n">
         <v>0.9</v>
       </c>
-      <c r="G29" s="8" t="n">
-        <v>81.2</v>
+      <c r="G29" s="3" t="n">
+        <v>5</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>3.8</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L29" s="8" t="n">
-        <v>790.9</v>
+        <v>0</v>
+      </c>
+      <c r="L29" s="3" t="n">
+        <v>0.9</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>10.5</v>
+        <v>0.5</v>
       </c>
       <c r="N29" s="3" t="n"/>
       <c r="O29" s="3" t="n">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="Q29" s="3" t="n">
         <v>27</v>
@@ -2898,26 +2905,26 @@
         <v>18.1</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>47.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="U29" s="3" t="n"/>
       <c r="V29" s="3" t="n">
         <v>22.8</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="X29" s="3" t="n">
-        <v>16.7</v>
+        <v>15</v>
+      </c>
+      <c r="X29" s="8" t="n">
+        <v>7.9</v>
       </c>
       <c r="Y29" s="3" t="n">
         <v>60</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>11.2</v>
+        <v>1</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
@@ -2933,53 +2940,53 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>2284.8</v>
-      </c>
-      <c r="D30" s="9" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="D30" s="10" t="n">
         <v>18.8</v>
       </c>
-      <c r="E30" s="9" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="F30" s="9" t="n">
-        <v>91.7</v>
-      </c>
-      <c r="G30" s="3" t="n">
-        <v>79.09999999999999</v>
+      <c r="E30" s="10" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F30" s="10" t="n">
+        <v>900.7</v>
+      </c>
+      <c r="G30" s="9" t="n">
+        <v>29.1</v>
       </c>
       <c r="H30" s="3" t="n">
         <v>26</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>13.8</v>
+        <v>3.8</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>119.5</v>
+        <v>109.5</v>
       </c>
       <c r="K30" s="3" t="n">
         <v>13.5</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>57.2</v>
+        <v>0.5</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>56.9</v>
+        <v>5.6</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>65.90000000000001</v>
+        <v>6</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="P30" s="3" t="n"/>
       <c r="Q30" s="3" t="n">
-        <v>113.2</v>
+        <v>10</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>86.7</v>
+        <v>0.4</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="T30" s="3" t="n">
         <v>34484.5</v>
@@ -2988,10 +2995,10 @@
         <v>551.4</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>99.5</v>
+        <v>9.5</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>17.3</v>
+        <v>0</v>
       </c>
       <c r="X30" s="3" t="n">
         <v>83.2</v>
@@ -3000,7 +3007,7 @@
         <v>365</v>
       </c>
       <c r="Z30" s="3" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
@@ -3016,16 +3023,16 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>43.7</v>
-      </c>
-      <c r="D31" s="9" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="E31" s="9" t="n">
-        <v>52.9</v>
-      </c>
-      <c r="F31" s="9" t="n">
-        <v>10.9</v>
+        <v>0</v>
+      </c>
+      <c r="D31" s="10" t="n">
+        <v>31</v>
+      </c>
+      <c r="E31" s="10" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="F31" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>15.8</v>
@@ -3037,11 +3044,11 @@
         <v>1.8</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>3.9</v>
+        <v>2</v>
       </c>
       <c r="K31" s="3" t="n"/>
       <c r="L31" s="3" t="n">
-        <v>11.9</v>
+        <v>16</v>
       </c>
       <c r="M31" s="3" t="n">
         <v>11.2</v>
@@ -3053,31 +3060,31 @@
         <v>4516.1</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>4.4</v>
+        <v>9</v>
       </c>
       <c r="Q31" s="3" t="n">
         <v>41.6</v>
       </c>
-      <c r="R31" s="8" t="n">
-        <v>179.3</v>
+      <c r="R31" s="3" t="n">
+        <v>0.3</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>84.40000000000001</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>6.3</v>
+        <v>0.3</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>11.1</v>
+        <v>11</v>
       </c>
       <c r="V31" s="3" t="n">
         <v>19.9</v>
       </c>
       <c r="W31" s="3" t="n">
-        <v>81.90000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="Y31" s="3" t="n">
         <v>73</v>
@@ -3099,18 +3106,18 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>43.7</v>
-      </c>
-      <c r="D32" s="10" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="E32" s="10" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="F32" s="10" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="G32" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="E32" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="G32" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="H32" s="3" t="n">
@@ -3120,51 +3127,53 @@
         <v>1.8</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>3.9</v>
+        <v>2</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>11.9</v>
+        <v>16</v>
       </c>
       <c r="M32" s="3" t="n">
         <v>11.2</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>12.3</v>
+        <v>1</v>
       </c>
       <c r="O32" s="3" t="n">
         <v>9</v>
       </c>
       <c r="P32" s="3" t="n">
-        <v>4.4</v>
+        <v>9</v>
       </c>
       <c r="Q32" s="3" t="n">
-        <v>24.8</v>
+        <v>20</v>
       </c>
       <c r="R32" s="3" t="n">
         <v>4.2</v>
       </c>
       <c r="S32" s="8" t="n">
-        <v>116.9</v>
+        <v>6009</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>62.5</v>
+        <v>0.5</v>
       </c>
       <c r="U32" s="3" t="n"/>
       <c r="V32" s="3" t="n">
         <v>21.1</v>
       </c>
       <c r="W32" s="3" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="X32" s="3" t="n"/>
+        <v>6.4</v>
+      </c>
+      <c r="X32" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="Y32" s="3" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="Z32" s="3" t="n">
-        <v>71.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3185,44 +3194,44 @@
       <c r="D33" s="3" t="n">
         <v>23.1</v>
       </c>
-      <c r="E33" s="12" t="n">
-        <v>61.8</v>
-      </c>
-      <c r="F33" s="8" t="n">
-        <v>19.9</v>
+      <c r="E33" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="9" t="n">
+        <v>0.9</v>
       </c>
       <c r="G33" s="3" t="n">
         <v>17.7</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>29.4</v>
+        <v>0.9</v>
       </c>
       <c r="I33" s="3" t="n">
         <v>0.3</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="L33" s="3" t="n">
         <v>0.6</v>
       </c>
       <c r="M33" s="3" t="n">
-        <v>10.2</v>
+        <v>0</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>12.3</v>
+        <v>1</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="P33" s="3" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="Q33" s="3" t="n">
-        <v>24.8</v>
+        <v>20</v>
       </c>
       <c r="R33" s="3" t="n">
         <v>4.2</v>
@@ -3231,7 +3240,7 @@
         <v>18.8</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>62.5</v>
+        <v>0.5</v>
       </c>
       <c r="U33" s="3" t="n">
         <v>10.3</v>
@@ -3243,13 +3252,13 @@
         <v>17.6</v>
       </c>
       <c r="X33" s="3" t="n">
-        <v>18.7</v>
+        <v>18</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3267,47 +3276,47 @@
       <c r="C34" s="3" t="n">
         <v>349.1</v>
       </c>
-      <c r="D34" s="10" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="E34" s="10" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="F34" s="10" t="n">
+      <c r="D34" s="3" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="E34" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="3" t="n">
         <v>18.5</v>
       </c>
-      <c r="G34" s="10" t="n">
+      <c r="G34" s="3" t="n">
         <v>11.4</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>29.4</v>
-      </c>
-      <c r="I34" s="8" t="n">
-        <v>65.59999999999999</v>
+        <v>0.9</v>
+      </c>
+      <c r="I34" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>12.3</v>
+        <v>2.3</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>14.9</v>
+        <v>6</v>
       </c>
       <c r="M34" s="3" t="n">
         <v>15.9</v>
       </c>
-      <c r="N34" s="3" t="n">
+      <c r="N34" s="8" t="n">
         <v>16.6</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>198</v>
+        <v>8</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>10.9</v>
+        <v>0.9</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>20.3</v>
+        <v>20</v>
       </c>
       <c r="R34" s="3" t="n">
         <v>0.2</v>
@@ -3316,25 +3325,25 @@
         <v>18.9</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>19.9</v>
+        <v>29.9</v>
       </c>
       <c r="U34" s="3" t="n">
         <v>10.3</v>
       </c>
-      <c r="V34" s="3" t="n">
-        <v>19.6</v>
+      <c r="V34" s="8" t="n">
+        <v>5.9</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>17.5</v>
+        <v>17.9</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>18.7</v>
+        <v>18</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>83</v>
+        <v>8</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>3.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3350,15 +3359,15 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>329.9</v>
+        <v>320.9</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="E35" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="E35" s="9" t="n">
         <v>2.8</v>
       </c>
-      <c r="F35" s="12" t="n">
+      <c r="F35" s="9" t="n">
         <v>4.9</v>
       </c>
       <c r="G35" s="3" t="n">
@@ -3374,19 +3383,19 @@
         <v>0.4</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="M35" s="3" t="n">
         <v>15.9</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>19.8</v>
+        <v>10</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>99</v>
+        <v>9</v>
       </c>
       <c r="P35" s="3" t="n">
         <v>0.2</v>
@@ -3394,17 +3403,17 @@
       <c r="Q35" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="R35" s="3" t="n">
-        <v>18.9</v>
+      <c r="R35" s="8" t="n">
+        <v>8.9</v>
       </c>
       <c r="S35" s="3" t="n">
         <v>18.7</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="U35" s="3" t="n">
-        <v>7.6</v>
+        <v>9.6</v>
       </c>
       <c r="V35" s="3" t="n">
         <v>18.7</v>
@@ -3412,14 +3421,14 @@
       <c r="W35" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="X35" s="8" t="n">
-        <v>81</v>
+      <c r="X35" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>82</v>
+        <v>2</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3435,19 +3444,19 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>506.7</v>
+        <v>50.6</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>26.8</v>
       </c>
       <c r="E36" s="8" t="n">
-        <v>14.7</v>
+        <v>19.7</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>19.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>9.5</v>
@@ -3461,50 +3470,50 @@
       <c r="K36" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L36" s="8" t="n">
-        <v>13</v>
-      </c>
-      <c r="M36" s="3" t="n">
-        <v>12.9</v>
+      <c r="L36" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="M36" s="8" t="n">
+        <v>0.9</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>19.8</v>
+        <v>10</v>
       </c>
       <c r="O36" s="3" t="n">
         <v>9</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q36" s="3" t="n">
-        <v>23.8</v>
+        <v>0</v>
+      </c>
+      <c r="Q36" s="8" t="n">
+        <v>3</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>17.6</v>
+        <v>7.6</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>16.8</v>
+        <v>10.8</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="U36" s="3" t="n">
         <v>4.3</v>
       </c>
       <c r="V36" s="3" t="n">
-        <v>20.8</v>
+        <v>0.8</v>
       </c>
       <c r="W36" s="3" t="n">
         <v>6.2</v>
       </c>
-      <c r="X36" s="3" t="n">
-        <v>16.8</v>
+      <c r="X36" s="8" t="n">
+        <v>6.8</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>68.5</v>
+        <v>8.5</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>212.2</v>
+        <v>0</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3522,14 +3531,14 @@
       <c r="C37" s="3" t="n">
         <v>535.5</v>
       </c>
-      <c r="D37" s="9" t="n">
+      <c r="D37" s="10" t="n">
         <v>26.3</v>
       </c>
-      <c r="E37" s="9" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="F37" s="9" t="n">
-        <v>18.3</v>
+      <c r="E37" s="10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="F37" s="10" t="n">
+        <v>18</v>
       </c>
       <c r="G37" s="3" t="n">
         <v>51.1</v>
@@ -3538,54 +3547,54 @@
         <v>46</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>3.9</v>
+        <v>30.9</v>
       </c>
       <c r="J37" s="3" t="n">
         <v>5.9</v>
       </c>
       <c r="K37" s="3" t="n"/>
       <c r="L37" s="3" t="n">
-        <v>10.6</v>
+        <v>10</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>10.5</v>
+        <v>0.5</v>
       </c>
       <c r="N37" s="3" t="n"/>
       <c r="O37" s="3" t="n">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="Q37" s="3" t="n">
         <v>25.5</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>14.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>125</v>
+        <v>5</v>
       </c>
       <c r="U37" s="3" t="n">
         <v>4.3</v>
       </c>
       <c r="V37" s="3" t="n">
-        <v>20.6</v>
+        <v>20</v>
       </c>
       <c r="W37" s="3" t="n">
-        <v>154.6</v>
+        <v>5</v>
       </c>
       <c r="X37" s="3" t="n">
         <v>3.3</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>52.8</v>
+        <v>0</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>34.6</v>
+        <v>39.6</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3601,15 +3610,15 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>2240.4</v>
-      </c>
-      <c r="D38" s="9" t="n">
+        <v>220.9</v>
+      </c>
+      <c r="D38" s="10" t="n">
         <v>28.5</v>
       </c>
-      <c r="E38" s="9" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="F38" s="9" t="n">
+      <c r="E38" s="10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F38" s="10" t="n">
         <v>99.7</v>
       </c>
       <c r="G38" s="3" t="n">
@@ -3619,55 +3628,55 @@
         <v>46</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>14.1</v>
+        <v>0</v>
       </c>
       <c r="J38" s="3" t="n">
         <v>20.8</v>
       </c>
       <c r="K38" s="3" t="n">
-        <v>8.5</v>
+        <v>0.5</v>
       </c>
       <c r="L38" s="3" t="n">
-        <v>65</v>
+        <v>5</v>
       </c>
       <c r="M38" s="8" t="n">
         <v>431.7</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>14.8</v>
+        <v>0</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>492</v>
+        <v>202</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="Q38" s="8" t="n">
         <v>151.5</v>
       </c>
       <c r="R38" s="3" t="n">
-        <v>89.40000000000001</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="S38" s="3" t="n">
         <v>88</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>216.4</v>
+        <v>0</v>
       </c>
       <c r="U38" s="3" t="n">
-        <v>54.5</v>
-      </c>
-      <c r="V38" s="8" t="n">
-        <v>0.9</v>
+        <v>0</v>
+      </c>
+      <c r="V38" s="3" t="n">
+        <v>10</v>
       </c>
       <c r="W38" s="3" t="n">
-        <v>83.09999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="X38" s="3" t="n">
-        <v>84.7</v>
+        <v>89.8</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>359.5</v>
+        <v>259.5</v>
       </c>
       <c r="Z38" s="3" t="n"/>
       <c r="AA38" s="3" t="inlineStr">
@@ -3684,19 +3693,19 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>4248.1</v>
-      </c>
-      <c r="D39" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" s="3" t="n">
         <v>28.5</v>
       </c>
-      <c r="E39" s="12" t="n">
-        <v>60.9</v>
-      </c>
-      <c r="F39" s="12" t="n">
+      <c r="E39" s="9" t="n">
+        <v>60</v>
+      </c>
+      <c r="F39" s="9" t="n">
         <v>99.7</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>13.5</v>
+        <v>3.5</v>
       </c>
       <c r="H39" s="3" t="n">
         <v>0.9</v>
@@ -3705,10 +3714,10 @@
         <v>2.8</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>42.1</v>
+        <v>6.2</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>8.5</v>
+        <v>0.5</v>
       </c>
       <c r="L39" s="3" t="n">
         <v>13</v>
@@ -3717,10 +3726,10 @@
         <v>431.7</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>14.8</v>
+        <v>0</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>98.40000000000001</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="P39" s="3" t="n">
         <v>1.6</v>
@@ -3729,31 +3738,31 @@
         <v>151.5</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>89.40000000000001</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="S39" s="3" t="n">
         <v>15.1</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>216.4</v>
-      </c>
-      <c r="U39" s="3" t="n">
-        <v>10.9</v>
+        <v>216.9</v>
+      </c>
+      <c r="U39" s="8" t="n">
+        <v>9</v>
       </c>
       <c r="V39" s="3" t="n">
         <v>20.2</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>16.6</v>
+        <v>10</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>84.7</v>
+        <v>89.8</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>741.9</v>
+        <v>1.9</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3769,44 +3778,44 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="D40" s="3" t="n">
         <v>25.7</v>
       </c>
-      <c r="E40" s="12" t="n">
+      <c r="E40" s="9" t="n">
         <v>42.2</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>18.9</v>
+        <v>19.9</v>
       </c>
       <c r="G40" s="8" t="n">
         <v>15.9</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>6.9</v>
+        <v>0</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="J40" s="3" t="n">
         <v>7</v>
       </c>
       <c r="K40" s="3" t="n"/>
       <c r="L40" s="3" t="n">
-        <v>12.7</v>
+        <v>0</v>
       </c>
       <c r="M40" s="3" t="n">
         <v>41.8</v>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11 0
+          <t xml:space="preserve">0 00
 </t>
         </is>
       </c>
       <c r="O40" s="3" t="n">
-        <v>196</v>
+        <v>96</v>
       </c>
       <c r="P40" s="3" t="n">
         <v>0.3</v>
@@ -3815,31 +3824,31 @@
         <v>993.6</v>
       </c>
       <c r="R40" s="3" t="n">
-        <v>19.2</v>
+        <v>0</v>
       </c>
       <c r="S40" s="3" t="n">
         <v>15.1</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>62.5</v>
-      </c>
-      <c r="U40" s="8" t="n">
-        <v>198</v>
+        <v>0</v>
+      </c>
+      <c r="U40" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="V40" s="3" t="n">
-        <v>212.1</v>
+        <v>0</v>
       </c>
       <c r="W40" s="3" t="n">
-        <v>55.5</v>
-      </c>
-      <c r="X40" s="8" t="n">
-        <v>16.9</v>
+        <v>0</v>
+      </c>
+      <c r="X40" s="3" t="n">
+        <v>6.9</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3855,25 +3864,25 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>451.2</v>
-      </c>
-      <c r="D41" s="10" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="E41" s="10" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="F41" s="10" t="n">
+        <v>251.2</v>
+      </c>
+      <c r="D41" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="F41" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="G41" s="8" t="n">
-        <v>66.5</v>
+      <c r="G41" s="3" t="n">
+        <v>16.5</v>
       </c>
       <c r="H41" s="3" t="n">
         <v>0.7</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="J41" s="3" t="n">
         <v>0.3</v>
@@ -3881,32 +3890,32 @@
       <c r="K41" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L41" s="8" t="n">
-        <v>61.1</v>
+      <c r="L41" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="M41" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="N41" s="8" t="n">
-        <v>57.1</v>
+      <c r="N41" s="3" t="n">
+        <v>10</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>196</v>
+        <v>96</v>
       </c>
       <c r="P41" s="3" t="n">
         <v>0.2</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>26.6</v>
+        <v>20.6</v>
       </c>
       <c r="R41" s="8" t="n">
         <v>18</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>18.4</v>
+        <v>8.5</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>84.5</v>
+        <v>20.5</v>
       </c>
       <c r="U41" s="3" t="n">
         <v>8</v>
@@ -3914,17 +3923,17 @@
       <c r="V41" s="3" t="n">
         <v>10.7</v>
       </c>
-      <c r="W41" s="8" t="n">
+      <c r="W41" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -3940,76 +3949,76 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>451.2</v>
+        <v>251.2</v>
       </c>
       <c r="D42" s="3" t="n">
         <v>23.2</v>
       </c>
-      <c r="E42" s="3" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="F42" s="12" t="n">
+      <c r="E42" s="9" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F42" s="9" t="n">
         <v>48.9</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>19.8</v>
+        <v>12.8</v>
       </c>
       <c r="H42" s="3" t="n">
         <v>2.2</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>5.7</v>
+        <v>5</v>
       </c>
       <c r="K42" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>88.5</v>
+        <v>88</v>
       </c>
       <c r="M42" s="3" t="n">
         <v>10.3</v>
       </c>
-      <c r="N42" s="8" t="n">
-        <v>18.8</v>
+      <c r="N42" s="3" t="n">
+        <v>11</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>598</v>
+        <v>98</v>
       </c>
       <c r="P42" s="3" t="n">
         <v>0.2</v>
       </c>
       <c r="Q42" s="3" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="R42" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="S42" s="3" t="n">
-        <v>16.6</v>
+      <c r="S42" s="8" t="n">
+        <v>60.6</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>55.9</v>
+        <v>500.9</v>
       </c>
       <c r="U42" s="3" t="n">
-        <v>12.4</v>
+        <v>10.9</v>
       </c>
       <c r="V42" s="3" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="W42" s="3" t="n">
         <v>0.5</v>
       </c>
       <c r="X42" s="8" t="n">
-        <v>89.3</v>
+        <v>2.3</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>839</v>
+        <v>89</v>
       </c>
       <c r="Z42" s="3" t="n">
-        <v>18.4</v>
+        <v>1</v>
       </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
@@ -4025,35 +4034,35 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>524.4</v>
+        <v>529.4</v>
       </c>
       <c r="D43" s="3" t="n">
         <v>23.2</v>
       </c>
-      <c r="E43" s="12" t="n">
+      <c r="E43" s="9" t="n">
         <v>84.5</v>
       </c>
-      <c r="F43" s="12" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="G43" s="12" t="n">
-        <v>26</v>
+      <c r="F43" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" s="8" t="n">
+        <v>90.7</v>
       </c>
       <c r="H43" s="3" t="n"/>
       <c r="I43" s="3" t="n">
-        <v>13.9</v>
+        <v>3.9</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>5.7</v>
+        <v>5</v>
       </c>
       <c r="K43" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L43" s="3" t="n">
         <v>4.4</v>
       </c>
       <c r="M43" s="3" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="N43" s="3" t="n">
         <v>43.8</v>
@@ -4062,13 +4071,13 @@
         <v>96</v>
       </c>
       <c r="P43" s="3" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="Q43" s="3" t="n">
         <v>23.9</v>
       </c>
       <c r="R43" s="3" t="n">
-        <v>17.4</v>
+        <v>17.5</v>
       </c>
       <c r="S43" s="3" t="n"/>
       <c r="T43" s="3" t="n">
@@ -4078,7 +4087,7 @@
         <v>19.6</v>
       </c>
       <c r="V43" s="3" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="W43" s="3" t="n">
         <v>163.3</v>
@@ -4102,14 +4111,16 @@
         </is>
       </c>
       <c r="C44" s="3" t="n"/>
-      <c r="D44" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E44" s="13" t="n"/>
-      <c r="F44" s="13" t="n"/>
+      <c r="D44" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="11" t="n"/>
+      <c r="F44" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="G44" s="3" t="n"/>
       <c r="H44" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="I44" s="3" t="n">
         <v>43.4</v>
@@ -4120,11 +4131,11 @@
       </c>
       <c r="L44" s="3" t="n"/>
       <c r="M44" s="3" t="n"/>
-      <c r="N44" s="8" t="n">
-        <v>23.1</v>
+      <c r="N44" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="P44" s="3" t="n">
         <v>0.8</v>
@@ -4137,14 +4148,14 @@
       </c>
       <c r="S44" s="3" t="n"/>
       <c r="T44" s="3" t="n">
-        <v>11.1</v>
+        <v>0</v>
       </c>
       <c r="U44" s="3" t="n"/>
       <c r="V44" s="3" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="W44" s="3" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="X44" s="3" t="n"/>
       <c r="Y44" s="3" t="n"/>
@@ -4165,19 +4176,19 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>16110.9</v>
+        <v>1011</v>
       </c>
       <c r="D45" s="10" t="n">
-        <v>109.8</v>
+        <v>10</v>
       </c>
       <c r="E45" s="10" t="n">
-        <v>41.8</v>
+        <v>61.8</v>
       </c>
       <c r="F45" s="10" t="n">
-        <v>75.8</v>
-      </c>
-      <c r="G45" s="10" t="n">
-        <v>67.90000000000001</v>
+        <v>754.6</v>
+      </c>
+      <c r="G45" s="3" t="n">
+        <v>7.9</v>
       </c>
       <c r="H45" s="3" t="n">
         <v>27</v>
@@ -4189,41 +4200,41 @@
         <v>221.9</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="L45" s="3" t="n"/>
       <c r="M45" s="3" t="n">
-        <v>22.9</v>
+        <v>200.9</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>18.1</v>
+        <v>0</v>
       </c>
       <c r="O45" s="3" t="n">
         <v>388</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="Q45" s="3" t="n">
         <v>98.59999999999999</v>
       </c>
       <c r="R45" s="3" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>216.4</v>
+        <v>216.9</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>59</v>
+        <v>99</v>
       </c>
       <c r="V45" s="3" t="n">
-        <v>851.9</v>
+        <v>891.9</v>
       </c>
       <c r="W45" s="3" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="X45" s="3" t="n"/>
       <c r="Y45" s="3" t="n"/>
@@ -4242,39 +4253,39 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>477.8</v>
-      </c>
-      <c r="D46" s="14" t="n"/>
-      <c r="E46" s="14" t="n"/>
-      <c r="F46" s="9" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="D46" s="12" t="n"/>
+      <c r="E46" s="12" t="n"/>
+      <c r="F46" s="10" t="n">
         <v>18.9</v>
       </c>
-      <c r="G46" s="8" t="n">
-        <v>69.40000000000001</v>
+      <c r="G46" s="3" t="n">
+        <v>16.9</v>
       </c>
       <c r="H46" s="3" t="n">
         <v>6.7</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>36.1</v>
+        <v>3</v>
       </c>
       <c r="J46" s="3" t="n">
         <v>221.9</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L46" s="3" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="M46" s="3" t="n">
-        <v>22.9</v>
+        <v>11</v>
+      </c>
+      <c r="M46" s="8" t="n">
+        <v>200.9</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>51.7</v>
+        <v>51</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>197</v>
+        <v>97</v>
       </c>
       <c r="P46" s="3" t="n">
         <v>2.3</v>
@@ -4283,30 +4294,30 @@
         <v>98.59999999999999</v>
       </c>
       <c r="R46" s="3" t="n">
-        <v>71</v>
+        <v>20</v>
       </c>
       <c r="S46" s="3" t="n">
         <v>16.5</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>54.9</v>
+        <v>0.4</v>
       </c>
       <c r="U46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114 70
+          <t xml:space="preserve">110 20
 </t>
         </is>
       </c>
       <c r="V46" s="3" t="n">
-        <v>21.3</v>
+        <v>0.3</v>
       </c>
       <c r="W46" s="3" t="n"/>
       <c r="X46" s="3" t="n">
-        <v>11.1</v>
+        <v>0</v>
       </c>
       <c r="Y46" s="3" t="n"/>
       <c r="Z46" s="3" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/05_transient_transcription_output/702/702_196402_SF.JPG_stage_duirnal_temp_range.xlsx
+++ b/results/05_transient_transcription_output/702/702_196402_SF.JPG_stage_duirnal_temp_range.xlsx
@@ -41,20 +41,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00CC3300"/>
-        <bgColor rgb="00CC3300"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="0075696F"/>
         <bgColor rgb="0075696F"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
+        <fgColor rgb="FF6DCD57"/>
+        <bgColor rgb="FF6DCD57"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00CC3300"/>
+        <bgColor rgb="00CC3300"/>
       </patternFill>
     </fill>
     <fill>
@@ -65,8 +65,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6DCD57"/>
-        <bgColor rgb="FF6DCD57"/>
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -137,7 +137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -152,7 +152,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -164,10 +164,19 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -781,74 +790,76 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>30.2</v>
-      </c>
-      <c r="D4" s="13" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="E4" s="13" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="F4" s="13" t="n">
+        <v>391.2</v>
+      </c>
+      <c r="D4" s="10" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="E4" s="10" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="F4" s="10" t="n">
         <v>18.5</v>
       </c>
-      <c r="G4" s="13" t="n">
-        <v>18.7</v>
+      <c r="G4" s="11" t="n">
+        <v>18.2</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="I4" s="8" t="n">
-        <v>1564.4</v>
+        <v>0.5</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>3.5</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>0.3</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="N4" s="8" t="n">
-        <v>1.9</v>
+        <v>18.7</v>
+      </c>
+      <c r="N4" s="16" t="n">
+        <v>19.9</v>
       </c>
       <c r="O4" s="3" t="n">
         <v>98</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="Q4" s="3" t="n"/>
+        <v>10.4</v>
+      </c>
+      <c r="Q4" s="16" t="n">
+        <v>23.8</v>
+      </c>
       <c r="R4" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="S4" s="3" t="n">
-        <v>1.4</v>
+      <c r="S4" s="16" t="n">
+        <v>114.1</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>62.5</v>
+        <v>542.5</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="V4" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="W4" s="3" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="V4" s="16" t="n">
+        <v>2219.1</v>
+      </c>
+      <c r="W4" s="16" t="n">
         <v>18.3</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>18.9</v>
+        <v>41.1</v>
       </c>
       <c r="Y4" s="3" t="n">
         <v>71</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>1.8</v>
+        <v>0.1</v>
       </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
@@ -864,74 +875,70 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>382.9</v>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="E5" s="9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="G5" s="3" t="n">
-        <v>5.9</v>
+        <v>382.4</v>
+      </c>
+      <c r="D5" s="10" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="E5" s="11" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="F5" s="11" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="G5" s="16" t="n">
+        <v>15.4</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>2</v>
+        <v>17.9</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>1.2</v>
+        <v>2.6</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="L5" s="8" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="M5" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="N5" s="8" t="n">
+      <c r="L5" s="16" t="n">
         <v>12.9</v>
       </c>
+      <c r="M5" s="3" t="inlineStr"/>
+      <c r="N5" s="3" t="n">
+        <v>12.9</v>
+      </c>
       <c r="O5" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="P5" s="3" t="n"/>
-      <c r="Q5" s="3" t="n">
-        <v>2.4</v>
+        <v>190.8</v>
+      </c>
+      <c r="P5" s="3" t="inlineStr"/>
+      <c r="Q5" s="16" t="n">
+        <v>19.6</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="S5" s="3" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="S5" s="16" t="n">
         <v>20.9</v>
       </c>
       <c r="T5" s="3" t="n">
         <v>91</v>
       </c>
-      <c r="U5" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="V5" s="3" t="n">
-        <v>0.5</v>
+      <c r="U5" s="3" t="inlineStr"/>
+      <c r="V5" s="16" t="n">
+        <v>189.5</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>21.2</v>
+        <v>1.2</v>
       </c>
       <c r="X5" s="3" t="n">
-        <v>18.3</v>
+        <v>2.1</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>80.5</v>
+        <v>180.5</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>6.9</v>
+        <v>6.6</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -947,76 +954,70 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="D6" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="E6" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>18.9</v>
+        <v>309.1</v>
+      </c>
+      <c r="D6" s="10" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="E6" s="10" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="F6" s="10" t="n">
+        <v>18.4</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>15</v>
+        <v>0.5</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>7.5</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J6" s="8" t="n">
-        <v>6</v>
-      </c>
+        <v>0.2</v>
+      </c>
+      <c r="J6" s="3" t="inlineStr"/>
       <c r="K6" s="3" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="M6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>1</v>
+        <v>1.4</v>
+      </c>
+      <c r="M6" s="16" t="n">
+        <v>411</v>
+      </c>
+      <c r="N6" s="16" t="n">
+        <v>13.1</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>99</v>
+        <v>199</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>2</v>
+        <v>0.2</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>44.5</v>
-      </c>
-      <c r="R6" s="3" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="S6" s="3" t="n">
-        <v>16.5</v>
-      </c>
+        <v>2.3</v>
+      </c>
+      <c r="R6" s="16" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="S6" s="3" t="inlineStr"/>
       <c r="T6" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="U6" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="V6" s="3" t="n">
-        <v>0</v>
+        <v>92</v>
+      </c>
+      <c r="U6" s="3" t="inlineStr"/>
+      <c r="V6" s="16" t="n">
+        <v>715.8</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.3</v>
+        <v>114.3</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>95</v>
+        <v>195</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>0.9</v>
+        <v>10.9</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -1032,74 +1033,76 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>225.9</v>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="E7" s="9" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="G7" s="3" t="n">
-        <v>0</v>
+        <v>1275.8</v>
+      </c>
+      <c r="D7" s="10" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="F7" s="11" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="G7" s="16" t="n">
+        <v>98</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>444.9</v>
+        <v>444.4</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="J7" s="3" t="n"/>
+        <v>11.2</v>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>0.4</v>
+      </c>
       <c r="K7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" s="8" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="M7" s="3" t="n">
-        <v>34.1</v>
-      </c>
-      <c r="N7" s="8" t="n">
-        <v>35</v>
+        <v>10</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M7" s="16" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="N7" s="16" t="n">
+        <v>15</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>9</v>
+        <v>198</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>0.2</v>
+        <v>10.2</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="R7" s="3" t="n">
-        <v>6.8</v>
+        <v>11.3</v>
+      </c>
+      <c r="R7" s="16" t="n">
+        <v>16.8</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>3.1</v>
+        <v>43.3</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="U7" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>79</v>
+      </c>
+      <c r="U7" s="16" t="n">
+        <v>94.8</v>
       </c>
       <c r="V7" s="3" t="n">
         <v>8.4</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>16.8</v>
+        <v>46.8</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>0.7</v>
+        <v>131.3</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>80</v>
+        <v>814.9</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>0</v>
+        <v>14.1</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1115,76 +1118,74 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>291.2</v>
-      </c>
-      <c r="D8" s="13" t="n">
-        <v>36.3</v>
-      </c>
-      <c r="E8" s="13" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="F8" s="13" t="n">
-        <v>23.4</v>
+        <v>391.2</v>
+      </c>
+      <c r="D8" s="10" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="E8" s="10" t="n">
+        <v>-9.9</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>8.1</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>5.2</v>
+        <v>15.8</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>7.8</v>
+        <v>17.2</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="J8" s="3" t="n">
         <v>3.5</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>4</v>
+        <v>40.8</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="N8" s="8" t="n">
-        <v>20.7</v>
-      </c>
+        <v>424.4</v>
+      </c>
+      <c r="N8" s="3" t="inlineStr"/>
       <c r="O8" s="3" t="n">
-        <v>8</v>
+        <v>1718</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>0.9</v>
+        <v>10.9</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>27.9</v>
+        <v>0.2</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>84.5</v>
+        <v>0.8</v>
       </c>
       <c r="S8" s="3" t="n">
         <v>19.5</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>76</v>
+        <v>176</v>
       </c>
       <c r="U8" s="3" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="V8" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="W8" s="3" t="n">
-        <v>10.3</v>
+        <v>1.8</v>
+      </c>
+      <c r="W8" s="16" t="n">
+        <v>17.3</v>
       </c>
       <c r="X8" s="3" t="n">
-        <v>18.9</v>
+        <v>2.1</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>87</v>
+        <v>1.2</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>2.6</v>
+        <v>12.6</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1200,77 +1201,76 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>124.9</v>
-      </c>
-      <c r="D9" s="10" t="n">
-        <v>289.5</v>
-      </c>
-      <c r="E9" s="10" t="n">
-        <v>55</v>
-      </c>
-      <c r="F9" s="10" t="n">
-        <v>0.1</v>
+        <v>1749.7</v>
+      </c>
+      <c r="D9" s="9" t="n">
+        <v>12849.1</v>
+      </c>
+      <c r="E9" s="9" t="n">
+        <v>55.8</v>
+      </c>
+      <c r="F9" s="9" t="n">
+        <v>91.90000000000001</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="H9" s="3" t="n"/>
+        <v>73.90000000000001</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>1702.6</v>
+      </c>
       <c r="I9" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1350 0
-</t>
-        </is>
+        <v>9.9</v>
+      </c>
+      <c r="J9" s="3" t="n">
+        <v>13.3</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>7.7</v>
+        <v>17.7</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>56.7</v>
+        <v>56.4</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>554.2</v>
+        <v>551.2</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>5</v>
+        <v>55.1</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>48421.2</v>
+        <v>1484.8</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>0.6</v>
+        <v>2.6</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>10.1</v>
+        <v>101.5</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>85.3</v>
+        <v>185.9</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>88</v>
+        <v>188.5</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>380.5</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>33</v>
+        <v>1233.3</v>
       </c>
       <c r="V9" s="3" t="n">
         <v>95</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0</v>
+        <v>184.9</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>0.1</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>914.5</v>
+        <v>14154.5</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>109.8</v>
+        <v>119.8</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1292,68 +1292,69 @@
         <v>25.8</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19 0
-</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="n"/>
+        <v>18.4</v>
+      </c>
+      <c r="G10" s="10" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>8.1</v>
+      </c>
       <c r="I10" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="J10" s="3" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="K10" s="3" t="n"/>
-      <c r="L10" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="M10" s="3" t="n">
-        <v>11</v>
+        <v>20.4</v>
+      </c>
+      <c r="J10" s="16" t="n">
+        <v>211.4</v>
+      </c>
+      <c r="K10" s="3" t="inlineStr"/>
+      <c r="L10" s="16" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="M10" s="16" t="n">
+        <v>111</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>96.8</v>
-      </c>
-      <c r="P10" s="3" t="n">
-        <v>0.5</v>
+        <v>196.8</v>
+      </c>
+      <c r="P10" s="16" t="n">
+        <v>1.5</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>2</v>
+        <v>20.3</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="S10" s="3" t="n">
-        <v>0.2</v>
+        <v>17.9</v>
+      </c>
+      <c r="S10" s="16" t="n">
+        <v>12.7</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>20</v>
+        <v>14167.1</v>
       </c>
       <c r="U10" s="3" t="n">
-        <v>6.1</v>
+        <v>6.7</v>
       </c>
       <c r="V10" s="3" t="n">
         <v>19</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="X10" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="X10" s="16" t="n">
         <v>18.2</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>82.90000000000001</v>
-      </c>
-      <c r="Z10" s="3" t="n"/>
+        <v>182.9</v>
+      </c>
+      <c r="Z10" s="3" t="n">
+        <v>151</v>
+      </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -1368,72 +1369,66 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>509.5</v>
-      </c>
-      <c r="D11" s="9" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="E11" s="3" t="n">
+        <v>1509.3</v>
+      </c>
+      <c r="D11" s="10" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="E11" s="10" t="n">
         <v>10.7</v>
       </c>
-      <c r="F11" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="3" t="n">
+      <c r="F11" s="10" t="n">
+        <v>19</v>
+      </c>
+      <c r="G11" s="10" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="I11" s="3" t="inlineStr"/>
+      <c r="J11" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="H11" s="3" t="n"/>
-      <c r="I11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" s="3" t="n"/>
-      <c r="L11" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="M11" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="K11" s="3" t="inlineStr"/>
+      <c r="L11" s="3" t="inlineStr"/>
+      <c r="M11" s="3" t="inlineStr"/>
       <c r="N11" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="O11" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="P11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="3" t="n">
-        <v>266.3</v>
+        <v>10.1</v>
+      </c>
+      <c r="O11" s="3" t="inlineStr"/>
+      <c r="P11" s="16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="Q11" s="16" t="n">
+        <v>226.3</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>0</v>
+        <v>17.1</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>427.7</v>
-      </c>
-      <c r="U11" s="8" t="n">
-        <v>209.9</v>
-      </c>
-      <c r="V11" s="3" t="n">
+        <v>40.1</v>
+      </c>
+      <c r="U11" s="3" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="V11" s="16" t="n">
         <v>22.1</v>
       </c>
       <c r="W11" s="3" t="n">
         <v>2.6</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>7.6</v>
+        <v>1.6</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>20</v>
+        <v>66</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
@@ -1449,72 +1444,76 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>506.7</v>
-      </c>
-      <c r="D12" s="3" t="n">
+        <v>1306.7</v>
+      </c>
+      <c r="D12" s="10" t="n">
         <v>25.9</v>
       </c>
-      <c r="E12" s="9" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="F12" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="G12" s="3" t="n">
-        <v>0</v>
+      <c r="E12" s="10" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="F12" s="10" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="G12" s="11" t="n">
+        <v>14.5</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>7.1</v>
+      </c>
+      <c r="I12" s="16" t="n">
+        <v>94.8</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="K12" s="3" t="n"/>
-      <c r="L12" s="3" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="M12" s="3" t="n">
-        <v>41.1</v>
-      </c>
-      <c r="N12" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="K12" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" s="16" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="M12" s="16" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="N12" s="3" t="n">
         <v>13.2</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>95</v>
+        <v>195</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0.8</v>
+        <v>10.8</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>25</v>
+        <v>25.4</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="S12" s="3" t="n"/>
+        <v>6.5</v>
+      </c>
+      <c r="S12" s="16" t="n">
+        <v>12.9</v>
+      </c>
       <c r="T12" s="3" t="n">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="U12" s="3" t="n">
-        <v>0.6</v>
+        <v>4.2</v>
       </c>
       <c r="V12" s="3" t="n">
         <v>21.3</v>
       </c>
-      <c r="W12" s="8" t="n">
-        <v>19.7</v>
+      <c r="W12" s="3" t="n">
+        <v>4.3</v>
       </c>
       <c r="X12" s="3" t="n">
-        <v>0</v>
+        <v>13.1</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>2</v>
+        <v>1092</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>2.2</v>
+        <v>12.2</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1530,71 +1529,63 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>307.9</v>
-      </c>
-      <c r="D13" s="9" t="n">
-        <v>25.35</v>
-      </c>
-      <c r="E13" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="F13" s="9" t="n">
-        <v>38.03</v>
-      </c>
-      <c r="G13" s="9" t="n">
-        <v>44.4</v>
+        <v>1357.9</v>
+      </c>
+      <c r="D13" s="10" t="inlineStr"/>
+      <c r="E13" s="14" t="inlineStr"/>
+      <c r="F13" s="11" t="n">
+        <v>18.13</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>4.4</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I13" s="3" t="n">
-        <v>0.9</v>
-      </c>
+        <v>7.3</v>
+      </c>
+      <c r="I13" s="3" t="inlineStr"/>
       <c r="J13" s="3" t="n">
         <v>2.5</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>0.5</v>
+        <v>10.5</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="M13" s="8" t="n">
-        <v>90.59999999999999</v>
-      </c>
-      <c r="N13" s="3" t="n">
-        <v>4.6</v>
+        <v>0.4</v>
+      </c>
+      <c r="M13" s="3" t="inlineStr"/>
+      <c r="N13" s="16" t="n">
+        <v>83.59999999999999</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>8</v>
+        <v>98</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="Q13" s="8" t="n">
-        <v>180.9</v>
-      </c>
+        <v>10.9</v>
+      </c>
+      <c r="Q13" s="3" t="inlineStr"/>
       <c r="R13" s="3" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="S13" s="3" t="n">
-        <v>8.9</v>
+        <v>4.3</v>
+      </c>
+      <c r="S13" s="16" t="n">
+        <v>18.1</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>20</v>
+        <v>86.8</v>
       </c>
       <c r="U13" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="V13" s="3" t="n"/>
-      <c r="W13" s="8" t="n">
-        <v>72</v>
-      </c>
-      <c r="X13" s="3" t="n">
-        <v>0</v>
+        <v>13</v>
+      </c>
+      <c r="V13" s="3" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="W13" s="16" t="n">
+        <v>88.59999999999999</v>
+      </c>
+      <c r="X13" s="16" t="n">
+        <v>19.1</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>89</v>
+        <v>184</v>
       </c>
       <c r="Z13" s="3" t="n">
         <v>9.6</v>
@@ -1613,75 +1604,70 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="D14" s="3" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="E14" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="F14" s="9" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="G14" s="3" t="n">
+        <v>227</v>
+      </c>
+      <c r="D14" s="10" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="E14" s="10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="F14" s="10" t="n">
+        <v>18.13</v>
+      </c>
+      <c r="G14" s="16" t="n">
         <v>10.5</v>
       </c>
-      <c r="H14" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="I14" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="J14" s="3" t="n">
+      <c r="H14" s="16" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="I14" s="3" t="inlineStr"/>
+      <c r="J14" s="16" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="K14" s="3" t="inlineStr"/>
+      <c r="L14" s="16" t="n">
+        <v>1182</v>
+      </c>
+      <c r="M14" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="N14" s="3" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="O14" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="P14" s="16" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="Q14" s="16" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="R14" s="16" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="S14" s="16" t="n">
+        <v>126.6</v>
+      </c>
+      <c r="T14" s="3" t="inlineStr"/>
+      <c r="U14" s="3" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="V14" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="K14" s="3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="L14" s="3" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="M14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">048 0
-</t>
-        </is>
-      </c>
-      <c r="O14" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="P14" s="3" t="n"/>
-      <c r="Q14" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="R14" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="S14" s="3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="T14" s="3" t="n">
-        <v>58</v>
-      </c>
-      <c r="U14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="3" t="n"/>
-      <c r="W14" s="3" t="n">
-        <v>0.2</v>
+      <c r="W14" s="16" t="n">
+        <v>11.5</v>
       </c>
       <c r="X14" s="3" t="n">
-        <v>61</v>
+        <v>6</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>95</v>
+        <v>195</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>0</v>
+        <v>81811</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1697,76 +1683,74 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="D15" s="13" t="n">
-        <v>36</v>
-      </c>
-      <c r="E15" s="13" t="n">
-        <v>11</v>
-      </c>
-      <c r="F15" s="13" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="G15" s="3" t="n">
-        <v>5</v>
+        <v>1631</v>
+      </c>
+      <c r="D15" s="10" t="n">
+        <v>26</v>
+      </c>
+      <c r="E15" s="11" t="n">
+        <v>1011.08</v>
+      </c>
+      <c r="F15" s="11" t="n">
+        <v>118.15</v>
+      </c>
+      <c r="G15" s="16" t="n">
+        <v>15.8</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>1</v>
+        <v>7.9</v>
       </c>
       <c r="I15" s="3" t="n">
         <v>3.8</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="L15" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="M15" s="3" t="n">
-        <v>0.3</v>
+        <v>21.6</v>
+      </c>
+      <c r="L15" s="16" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="M15" s="16" t="n">
+        <v>21.3</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>434.3</v>
+        <v>1.3</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="P15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="3" t="n">
+        <v>99</v>
+      </c>
+      <c r="P15" s="16" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Q15" s="16" t="n">
         <v>25.5</v>
       </c>
       <c r="R15" s="3" t="n">
-        <v>7.6</v>
+        <v>0.6</v>
       </c>
       <c r="S15" s="3" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="T15" s="3" t="n">
-        <v>310</v>
-      </c>
+        <v>15.9</v>
+      </c>
+      <c r="T15" s="3" t="inlineStr"/>
       <c r="U15" s="3" t="n">
-        <v>0</v>
+        <v>17.9</v>
       </c>
       <c r="V15" s="3" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="W15" s="3" t="n">
-        <v>16.3</v>
+        <v>12</v>
+      </c>
+      <c r="W15" s="16" t="n">
+        <v>116.5</v>
       </c>
       <c r="X15" s="3" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="Y15" s="3" t="n">
         <v>67</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>8</v>
+        <v>18.1</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1782,71 +1766,73 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" s="13" t="n">
+        <v>2227.1</v>
+      </c>
+      <c r="D16" s="9" t="n">
         <v>128</v>
       </c>
-      <c r="E16" s="10" t="n">
-        <v>56.8</v>
-      </c>
-      <c r="F16" s="13" t="n">
-        <v>92.5</v>
+      <c r="E16" s="9" t="n">
+        <v>256.8</v>
+      </c>
+      <c r="F16" s="9" t="n">
+        <v>92.3</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0</v>
+        <v>79.2</v>
       </c>
       <c r="H16" s="3" t="n">
         <v>39.5</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>14</v>
+        <v>14.2</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>139.8</v>
+        <v>121.8</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>0</v>
+        <v>39.8</v>
       </c>
       <c r="L16" s="3" t="n">
         <v>59.1</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="N16" s="3" t="n"/>
+        <v>58.2</v>
+      </c>
+      <c r="N16" s="3" t="n">
+        <v>67.90000000000001</v>
+      </c>
       <c r="O16" s="3" t="n">
-        <v>689</v>
+        <v>439.8</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>110</v>
+        <v>11191</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>8</v>
+        <v>0.1</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>77.3</v>
+        <v>721.1</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>42</v>
+        <v>310.1</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>60</v>
+        <v>160.9</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>25</v>
+        <v>921.2</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>80</v>
+        <v>801.9</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>0</v>
+        <v>182.2</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>369</v>
+        <v>1364</v>
       </c>
       <c r="Z16" s="3" t="n">
         <v>33.4</v>
@@ -1865,74 +1851,74 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>445.9</v>
-      </c>
-      <c r="D17" s="13" t="n">
-        <v>25.1</v>
-      </c>
-      <c r="E17" s="13" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="F17" s="13" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="G17" s="3" t="n">
-        <v>44.4</v>
-      </c>
-      <c r="H17" s="3" t="n"/>
+        <v>245.9</v>
+      </c>
+      <c r="D17" s="10" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="E17" s="10" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="F17" s="10" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="G17" s="16" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="H17" s="3" t="n">
+        <v>7.9</v>
+      </c>
       <c r="I17" s="3" t="n">
-        <v>2</v>
+        <v>29.4</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="K17" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L17" s="3" t="n">
+        <v>99.8</v>
+      </c>
+      <c r="K17" s="3" t="inlineStr"/>
+      <c r="L17" s="16" t="n">
         <v>11.8</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" s="3" t="n">
-        <v>41.6</v>
+        <v>11.6</v>
+      </c>
+      <c r="N17" s="16" t="n">
+        <v>13.6</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="P17" s="3" t="n">
-        <v>9</v>
+        <v>197.8</v>
+      </c>
+      <c r="P17" s="16" t="n">
+        <v>7.4</v>
       </c>
       <c r="Q17" s="3" t="n">
         <v>22.2</v>
       </c>
-      <c r="R17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" s="3" t="n">
-        <v>151.5</v>
+      <c r="R17" s="16" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="S17" s="16" t="n">
+        <v>15.5</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>6</v>
+        <v>162</v>
       </c>
       <c r="U17" s="3" t="n">
-        <v>84.7</v>
-      </c>
-      <c r="V17" s="3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="W17" s="3" t="n">
-        <v>16.7</v>
+        <v>19.2</v>
+      </c>
+      <c r="V17" s="16" t="n">
+        <v>119.6</v>
+      </c>
+      <c r="W17" s="16" t="n">
+        <v>16.1</v>
       </c>
       <c r="X17" s="3" t="n">
-        <v>0</v>
+        <v>14.4</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>82.8</v>
+        <v>72.8</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>0.8</v>
+        <v>16.8</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1948,23 +1934,23 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>455</v>
-      </c>
-      <c r="D18" s="11" t="n"/>
-      <c r="E18" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="9" t="n">
-        <v>18.14</v>
-      </c>
-      <c r="G18" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="H18" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>1435.8</v>
+      </c>
+      <c r="D18" s="10" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="E18" s="10" t="n">
+        <v>24.44</v>
+      </c>
+      <c r="F18" s="10" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="G18" s="16" t="n">
+        <v>13</v>
+      </c>
+      <c r="H18" s="3" t="inlineStr"/>
       <c r="I18" s="3" t="n">
-        <v>20.9</v>
+        <v>0.4</v>
       </c>
       <c r="J18" s="3" t="n">
         <v>3.3</v>
@@ -1973,47 +1959,49 @@
         <v>0.1</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>102.2</v>
+        <v>0.4</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="N18" s="3" t="n">
-        <v>16</v>
+        <v>87.59999999999999</v>
+      </c>
+      <c r="N18" s="16" t="n">
+        <v>61</v>
       </c>
       <c r="O18" s="3" t="n">
         <v>99</v>
       </c>
-      <c r="P18" s="3" t="n"/>
-      <c r="Q18" s="8" t="n">
-        <v>95.8</v>
-      </c>
-      <c r="R18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" s="3" t="n">
-        <v>5.9</v>
+      <c r="P18" s="3" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="Q18" s="3" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="R18" s="16" t="n">
+        <v>72.3</v>
+      </c>
+      <c r="S18" s="16" t="n">
+        <v>115.4</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>98.5</v>
+        <v>1406</v>
       </c>
       <c r="U18" s="3" t="n">
         <v>17.9</v>
       </c>
       <c r="V18" s="3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="W18" s="3" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="X18" s="3" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
+      </c>
+      <c r="X18" s="16" t="n">
+        <v>15.6</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>9</v>
+        <v>13791</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>10.4</v>
+        <v>110.9</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -2029,76 +2017,72 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>530</v>
-      </c>
-      <c r="D19" s="9" t="n">
-        <v>50.9</v>
-      </c>
-      <c r="E19" s="9" t="n">
-        <v>40.9</v>
-      </c>
-      <c r="F19" s="9" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G19" s="3" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="H19" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>1531.1</v>
+      </c>
+      <c r="D19" s="10" t="n">
+        <v>28</v>
+      </c>
+      <c r="E19" s="10" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="F19" s="10" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="G19" s="3" t="inlineStr"/>
+      <c r="H19" s="3" t="inlineStr"/>
       <c r="I19" s="3" t="n">
-        <v>0.3</v>
+        <v>3.3</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="M19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" s="8" t="n">
-        <v>12</v>
+        <v>10</v>
+      </c>
+      <c r="L19" s="16" t="n">
+        <v>211</v>
+      </c>
+      <c r="M19" s="16" t="n">
+        <v>711</v>
+      </c>
+      <c r="N19" s="16" t="n">
+        <v>13</v>
       </c>
       <c r="O19" s="3" t="n">
         <v>98</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>4.9</v>
+        <v>10.4</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="R19" s="3" t="n">
-        <v>10</v>
+        <v>261.1</v>
+      </c>
+      <c r="R19" s="16" t="n">
+        <v>18</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>64.2</v>
+        <v>24.2</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>98.5</v>
+        <v>0.8</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="V19" s="3" t="n">
         <v>21.2</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="X19" s="3" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="X19" s="16" t="n">
         <v>18.6</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>14</v>
+        <v>142</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>6.6</v>
+        <v>16.6</v>
       </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
@@ -2114,75 +2098,69 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>530</v>
-      </c>
-      <c r="D20" s="13" t="n">
-        <v>8</v>
-      </c>
-      <c r="E20" s="9" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="F20" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="G20" s="3" t="n">
+        <v>592.2</v>
+      </c>
+      <c r="D20" s="10" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="E20" s="10" t="n">
+        <v>-5.3</v>
+      </c>
+      <c r="F20" s="11" t="n">
+        <v>11.43</v>
+      </c>
+      <c r="G20" s="16" t="n">
         <v>17.8</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" s="8" t="n">
-        <v>35.3</v>
+        <v>16.9</v>
+      </c>
+      <c r="I20" s="16" t="n">
+        <v>733.5</v>
       </c>
       <c r="J20" s="3" t="n">
         <v>4.9</v>
       </c>
-      <c r="K20" s="3" t="n"/>
+      <c r="K20" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="L20" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M20" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" s="3" t="n">
-        <v>2</v>
-      </c>
+        <v>4.1</v>
+      </c>
+      <c r="M20" s="16" t="n">
+        <v>8818.1</v>
+      </c>
+      <c r="N20" s="3" t="inlineStr"/>
       <c r="O20" s="3" t="n">
         <v>98</v>
       </c>
-      <c r="P20" s="3" t="n">
-        <v>0.9</v>
-      </c>
+      <c r="P20" s="3" t="inlineStr"/>
       <c r="Q20" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="R20" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="S20" s="3" t="n">
-        <v>51.3</v>
+      <c r="R20" s="3" t="inlineStr"/>
+      <c r="S20" s="16" t="n">
+        <v>151.3</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>20.5</v>
+        <v>140.5</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>22.9</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="V20" s="3" t="n">
-        <v>221.1</v>
+        <v>22.1</v>
       </c>
       <c r="W20" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="X20" s="3" t="n">
-        <v>0.9</v>
+        <v>18.4</v>
+      </c>
+      <c r="X20" s="16" t="n">
+        <v>2298.2</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>44.4</v>
-      </c>
-      <c r="Z20" s="3" t="n">
-        <v>7</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="Z20" s="3" t="inlineStr"/>
       <c r="AA20" s="3" t="inlineStr">
         <is>
           <t>13</t>
@@ -2197,74 +2175,74 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D21" s="3" t="n">
-        <v>28.2</v>
-      </c>
-      <c r="E21" s="9" t="n">
+        <v>382.4</v>
+      </c>
+      <c r="D21" s="10" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="E21" s="10" t="n">
         <v>0.4</v>
       </c>
-      <c r="F21" s="9" t="n">
-        <v>12.13</v>
-      </c>
-      <c r="G21" s="3" t="n">
-        <v>2.1</v>
+      <c r="F21" s="10" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="G21" s="16" t="n">
+        <v>12.1</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>2.1</v>
+        <v>42.1</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>0.4</v>
+        <v>12.4</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>4.9</v>
+        <v>0.3</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>3.1</v>
+        <v>13.1</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="N21" s="3" t="n">
-        <v>15</v>
-      </c>
+        <v>1.1</v>
+      </c>
+      <c r="N21" s="3" t="inlineStr"/>
       <c r="O21" s="3" t="n">
-        <v>9</v>
+        <v>99</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>0</v>
+        <v>10.2</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="R21" s="3" t="n"/>
-      <c r="S21" s="3" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="S21" s="16" t="n">
         <v>16.8</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>50</v>
+        <v>1931</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="V21" s="3" t="n">
-        <v>0</v>
+        <v>6.2</v>
+      </c>
+      <c r="V21" s="16" t="n">
+        <v>19.8</v>
       </c>
       <c r="W21" s="3" t="n">
-        <v>48.2</v>
+        <v>18.2</v>
       </c>
       <c r="X21" s="3" t="n">
         <v>20</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>8</v>
+        <v>187</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
@@ -2280,72 +2258,72 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>429</v>
-      </c>
-      <c r="D22" s="3" t="n">
-        <v>29.8</v>
-      </c>
-      <c r="E22" s="11" t="n"/>
-      <c r="F22" s="3" t="n">
-        <v>8.699999999999999</v>
+        <v>1429</v>
+      </c>
+      <c r="D22" s="10" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="E22" s="14" t="inlineStr"/>
+      <c r="F22" s="11" t="n">
+        <v>81.90000000000001</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>1.3</v>
+        <v>13.1</v>
       </c>
       <c r="H22" s="3" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="I22" s="3" t="inlineStr"/>
+      <c r="J22" s="3" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="K22" s="16" t="n">
         <v>8</v>
       </c>
-      <c r="I22" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="J22" s="3" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="K22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" s="3" t="n"/>
-      <c r="N22" s="3" t="n">
-        <v>9</v>
+      <c r="L22" s="3" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="M22" s="16" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="N22" s="16" t="n">
+        <v>14.1</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>9</v>
+        <v>99</v>
       </c>
       <c r="P22" s="3" t="n">
-        <v>0.2</v>
+        <v>10.2</v>
       </c>
       <c r="Q22" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="R22" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="S22" s="3" t="n">
-        <v>9.9</v>
+        <v>23.6</v>
+      </c>
+      <c r="R22" s="16" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="S22" s="16" t="n">
+        <v>194.9</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="U22" s="8" t="n">
-        <v>59.8</v>
-      </c>
-      <c r="V22" s="3" t="n">
+        <v>443454.4</v>
+      </c>
+      <c r="U22" s="3" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="V22" s="16" t="n">
         <v>22.5</v>
       </c>
-      <c r="W22" s="3" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="X22" s="3" t="n">
-        <v>3.9</v>
+      <c r="W22" s="16" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="X22" s="16" t="n">
+        <v>13.9</v>
       </c>
       <c r="Y22" s="3" t="n">
-        <v>0.5</v>
+        <v>50.5</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>3.9</v>
+        <v>113.4</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2361,31 +2339,31 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>23</v>
+        <v>23203.1</v>
       </c>
       <c r="D23" s="10" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="E23" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="F23" s="10" t="n">
-        <v>95.90000000000001</v>
-      </c>
-      <c r="G23" s="3" t="n">
-        <v>0</v>
+        <v>132.1</v>
+      </c>
+      <c r="E23" s="9" t="n">
+        <v>551.4</v>
+      </c>
+      <c r="F23" s="9" t="n">
+        <v>94.90000000000001</v>
+      </c>
+      <c r="G23" s="11" t="n">
+        <v>75.09999999999999</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>40.6</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>14.5</v>
+        <v>141.5</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>18.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>0.3</v>
+        <v>101.3</v>
       </c>
       <c r="L23" s="3" t="n">
         <v>1.5</v>
@@ -2393,40 +2371,40 @@
       <c r="M23" s="3" t="n">
         <v>61.8</v>
       </c>
-      <c r="N23" s="3" t="n"/>
+      <c r="N23" s="3" t="inlineStr"/>
       <c r="O23" s="3" t="n">
-        <v>293</v>
-      </c>
-      <c r="P23" s="3" t="n">
-        <v>0.9</v>
-      </c>
+        <v>2493</v>
+      </c>
+      <c r="P23" s="3" t="inlineStr"/>
       <c r="Q23" s="3" t="n">
-        <v>128.9</v>
-      </c>
-      <c r="R23" s="3" t="n"/>
+        <v>1128.9</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>88</v>
+      </c>
       <c r="S23" s="3" t="n">
-        <v>18</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>2357.1</v>
+        <v>235.7</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>88.5</v>
+        <v>188.5</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>106.7</v>
+        <v>1106.7</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>851.5</v>
+        <v>185.5</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>86.2</v>
+        <v>26.3</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>39.5</v>
+        <v>1341.5</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>0</v>
+        <v>141</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2442,73 +2420,73 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>64.09999999999999</v>
+        <v>484.1</v>
       </c>
       <c r="D24" s="10" t="n">
-        <v>32.3</v>
+        <v>26.4</v>
       </c>
       <c r="E24" s="10" t="n">
-        <v>56.1</v>
+        <v>11.3</v>
       </c>
       <c r="F24" s="10" t="n">
         <v>18.9</v>
       </c>
-      <c r="G24" s="3" t="n">
-        <v>15</v>
+      <c r="G24" s="10" t="n">
+        <v>15.1</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>8.1</v>
+        <v>18.1</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>2.9</v>
+        <v>29.1</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>76.09999999999999</v>
+      </c>
+      <c r="K24" s="3" t="inlineStr"/>
       <c r="L24" s="3" t="n">
-        <v>42.5</v>
-      </c>
-      <c r="M24" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="N24" s="3" t="n"/>
+        <v>12.5</v>
+      </c>
+      <c r="M24" s="16" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="N24" s="3" t="inlineStr"/>
       <c r="O24" s="3" t="n">
         <v>98.59999999999999</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>3</v>
+        <v>0.3</v>
       </c>
       <c r="Q24" s="3" t="n">
         <v>25.8</v>
       </c>
-      <c r="R24" s="3" t="n">
+      <c r="R24" s="16" t="n">
         <v>17.6</v>
       </c>
-      <c r="S24" s="3" t="n">
-        <v>15</v>
+      <c r="S24" s="16" t="n">
+        <v>15.6</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>44.1</v>
-      </c>
-      <c r="U24" s="3" t="n">
-        <v>17.7</v>
+        <v>1247.9</v>
+      </c>
+      <c r="U24" s="16" t="n">
+        <v>197.5</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>21.3</v>
+        <v>91.3</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="X24" s="3" t="n">
-        <v>7</v>
+        <v>41.1</v>
+      </c>
+      <c r="X24" s="16" t="n">
+        <v>17.2</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>68</v>
-      </c>
-      <c r="Z24" s="3" t="n"/>
+        <v>168.9</v>
+      </c>
+      <c r="Z24" s="3" t="n">
+        <v>8.300000000000001</v>
+      </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -2523,66 +2501,56 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>88.90000000000001</v>
-      </c>
-      <c r="D25" s="3" t="n">
-        <v>26.9</v>
-      </c>
-      <c r="E25" s="3" t="n">
-        <v>11.3</v>
-      </c>
+        <v>1488.9</v>
+      </c>
+      <c r="D25" s="16" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="E25" s="14" t="inlineStr"/>
       <c r="F25" s="3" t="n">
         <v>17.8</v>
       </c>
-      <c r="G25" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H25" s="3" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="I25" s="3" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="J25" s="3" t="n">
+      <c r="G25" s="3" t="inlineStr"/>
+      <c r="H25" s="3" t="inlineStr"/>
+      <c r="I25" s="3" t="inlineStr"/>
+      <c r="J25" s="3" t="inlineStr"/>
+      <c r="K25" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="K25" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" s="3" t="n">
-        <v>42.5</v>
+      <c r="L25" s="16" t="n">
+        <v>107.9</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>0</v>
+        <v>9.9</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="O25" s="3" t="n">
-        <v>20</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="O25" s="3" t="inlineStr"/>
       <c r="P25" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" s="3" t="n">
-        <v>29.7</v>
+        <v>18.9</v>
+      </c>
+      <c r="Q25" s="16" t="n">
+        <v>29.1</v>
       </c>
       <c r="R25" s="3" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="S25" s="3" t="n">
-        <v>13.4</v>
+        <v>0.4</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="U25" s="8" t="n">
-        <v>19.8</v>
+        <v>549.3</v>
+      </c>
+      <c r="U25" s="16" t="n">
+        <v>151.8</v>
       </c>
       <c r="V25" s="3" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="W25" s="3" t="n"/>
+        <v>21.3</v>
+      </c>
+      <c r="W25" s="16" t="n">
+        <v>16.9</v>
+      </c>
       <c r="X25" s="3" t="n">
         <v>16.8</v>
       </c>
@@ -2590,7 +2558,7 @@
         <v>66</v>
       </c>
       <c r="Z25" s="3" t="n">
-        <v>0</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
@@ -2606,74 +2574,70 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>34.9</v>
+        <v>1349.9</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="E26" s="9" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="F26" s="11" t="n">
         <v>1.2</v>
-      </c>
-      <c r="F26" s="3" t="n">
-        <v>17</v>
       </c>
       <c r="G26" s="3" t="n">
         <v>14.8</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="I26" s="3" t="n">
-        <v>2.5</v>
+        <v>16.6</v>
+      </c>
+      <c r="I26" s="16" t="n">
+        <v>25.6</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" s="3" t="n"/>
-      <c r="L26" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="M26" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" s="3" t="n">
-        <v>1</v>
-      </c>
+        <v>18.5</v>
+      </c>
+      <c r="K26" s="3" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="L26" s="3" t="inlineStr"/>
+      <c r="M26" s="16" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="N26" s="3" t="inlineStr"/>
       <c r="O26" s="3" t="n">
         <v>98</v>
       </c>
-      <c r="P26" s="3" t="n">
-        <v>0.4</v>
-      </c>
+      <c r="P26" s="3" t="inlineStr"/>
       <c r="Q26" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="R26" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" s="3" t="n">
-        <v>5.2</v>
+      <c r="R26" s="16" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="S26" s="16" t="n">
+        <v>547.4</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>3.5</v>
+        <v>163.5</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>0.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="V26" s="3" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="W26" s="8" t="n">
-        <v>60.9</v>
-      </c>
-      <c r="X26" s="8" t="n">
-        <v>10</v>
+        <v>21.6</v>
+      </c>
+      <c r="W26" s="3" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="X26" s="3" t="n">
+        <v>14.2</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>5</v>
+        <v>512.1</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>1.5</v>
+        <v>111.8</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2689,73 +2653,65 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>390.2</v>
-      </c>
-      <c r="D27" s="3" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="E27" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" s="8" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="G27" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>340.2</v>
+      </c>
+      <c r="D27" s="11" t="n">
+        <v>21.14</v>
+      </c>
+      <c r="E27" s="16" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="F27" s="14" t="inlineStr"/>
+      <c r="G27" s="11" t="n">
+        <v>114.4</v>
+      </c>
+      <c r="H27" s="3" t="inlineStr"/>
       <c r="I27" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="J27" s="3" t="n">
-        <v>2.9</v>
+      <c r="J27" s="16" t="n">
+        <v>15.1</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>7</v>
+        <v>17.1</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="M27" s="3" t="n">
+        <v>42.4</v>
+      </c>
+      <c r="M27" s="16" t="n">
         <v>12.2</v>
       </c>
-      <c r="N27" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="N27" s="3" t="inlineStr"/>
       <c r="O27" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="P27" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="Q27" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="R27" s="3" t="n">
-        <v>10</v>
+        <v>98</v>
+      </c>
+      <c r="P27" s="3" t="inlineStr"/>
+      <c r="Q27" s="16" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="R27" s="16" t="n">
+        <v>161.8</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>10.3</v>
+        <v>11.7</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>80</v>
+        <v>186</v>
       </c>
       <c r="U27" s="3" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="V27" s="3" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="W27" s="3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="X27" s="8" t="n">
-        <v>59.5</v>
+        <v>17.4</v>
+      </c>
+      <c r="W27" s="16" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="X27" s="16" t="n">
+        <v>187.5</v>
       </c>
       <c r="Y27" s="3" t="n">
-        <v>3</v>
+        <v>113</v>
       </c>
       <c r="Z27" s="3" t="n">
         <v>0.6</v>
@@ -2774,73 +2730,69 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="D28" s="9" t="n">
-        <v>57</v>
-      </c>
-      <c r="E28" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" s="9" t="n">
-        <v>44.3</v>
-      </c>
-      <c r="G28" s="3" t="n">
-        <v>15.9</v>
+        <v>15139.5</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="E28" s="11" t="n">
+        <v>11.15</v>
+      </c>
+      <c r="F28" s="11" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="G28" s="11" t="n">
+        <v>15.4</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>8.9</v>
+        <v>18.7</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>2.9</v>
+        <v>0.2</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>2.3</v>
+        <v>3.3</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="L28" s="3" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="M28" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="N28" s="3" t="n">
-        <v>10</v>
+        <v>5.5</v>
+      </c>
+      <c r="L28" s="16" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="M28" s="16" t="n">
+        <v>113.3</v>
+      </c>
+      <c r="N28" s="16" t="n">
+        <v>13.2</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>9</v>
+        <v>99</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q28" s="8" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="R28" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="S28" s="3" t="n">
-        <v>9</v>
+        <v>10.2</v>
+      </c>
+      <c r="Q28" s="3" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="R28" s="16" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="S28" s="16" t="n">
+        <v>99</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>68</v>
+        <v>168</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>18.8</v>
       </c>
       <c r="V28" s="3" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="W28" s="3" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="X28" s="3" t="n">
-        <v>2</v>
-      </c>
+        <v>16.4</v>
+      </c>
+      <c r="W28" s="3" t="inlineStr"/>
+      <c r="X28" s="3" t="inlineStr"/>
       <c r="Y28" s="3" t="n">
-        <v>91</v>
+        <v>121</v>
       </c>
       <c r="Z28" s="3" t="n">
         <v>0.8</v>
@@ -2859,72 +2811,70 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>503.3</v>
-      </c>
-      <c r="D29" s="3" t="n">
-        <v>27</v>
-      </c>
-      <c r="E29" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" s="9" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="G29" s="3" t="n">
-        <v>5</v>
+        <v>523.3</v>
+      </c>
+      <c r="D29" s="11" t="n">
+        <v>48.28</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="F29" s="11" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="G29" s="11" t="n">
+        <v>48.4</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>8</v>
+        <v>0.3</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>3.8</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0</v>
+        <v>16.2</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="M29" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="N29" s="3" t="n"/>
+        <v>10.9</v>
+      </c>
+      <c r="M29" s="16" t="n">
+        <v>910.5</v>
+      </c>
+      <c r="N29" s="16" t="n">
+        <v>122.4</v>
+      </c>
       <c r="O29" s="3" t="n">
-        <v>90</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" s="3" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="Q29" s="16" t="n">
         <v>27</v>
       </c>
-      <c r="R29" s="3" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="S29" s="3" t="n">
-        <v>0</v>
+      <c r="R29" s="16" t="n">
+        <v>181.7</v>
+      </c>
+      <c r="S29" s="16" t="n">
+        <v>17</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="U29" s="3" t="n"/>
+        <v>47.8</v>
+      </c>
+      <c r="U29" s="3" t="inlineStr"/>
       <c r="V29" s="3" t="n">
         <v>22.8</v>
       </c>
-      <c r="W29" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="X29" s="8" t="n">
-        <v>7.9</v>
-      </c>
+      <c r="W29" s="3" t="inlineStr"/>
+      <c r="X29" s="3" t="inlineStr"/>
       <c r="Y29" s="3" t="n">
-        <v>60</v>
+        <v>160</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>1</v>
+        <v>111.2</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
@@ -2940,74 +2890,76 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="D30" s="10" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="E30" s="10" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F30" s="10" t="n">
-        <v>900.7</v>
-      </c>
-      <c r="G30" s="9" t="n">
-        <v>29.1</v>
+        <v>22848.1</v>
+      </c>
+      <c r="D30" s="9" t="n">
+        <v>131.2</v>
+      </c>
+      <c r="E30" s="9" t="n">
+        <v>152.9</v>
+      </c>
+      <c r="F30" s="9" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>79.09999999999999</v>
       </c>
       <c r="H30" s="3" t="n">
         <v>26</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>3.8</v>
+        <v>113.8</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>109.5</v>
+        <v>1119.5</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>13.5</v>
+        <v>113.5</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>0.5</v>
+        <v>52.2</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>5.6</v>
+        <v>56.1</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>6</v>
+        <v>0.6</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" s="3" t="n"/>
+        <v>1489</v>
+      </c>
+      <c r="P30" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="Q30" s="3" t="n">
-        <v>10</v>
+        <v>113.2</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>0.4</v>
+        <v>86.7</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>0</v>
+        <v>184.4</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>34484.5</v>
+        <v>314.8</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>551.4</v>
+        <v>55.9</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>9.5</v>
+        <v>99.5</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>0</v>
+        <v>181.9</v>
       </c>
       <c r="X30" s="3" t="n">
         <v>83.2</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>365</v>
+        <v>1365</v>
       </c>
       <c r="Z30" s="3" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
@@ -3023,74 +2975,70 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>1452</v>
       </c>
       <c r="D31" s="10" t="n">
-        <v>31</v>
+        <v>26.2</v>
       </c>
       <c r="E31" s="10" t="n">
-        <v>5.2</v>
+        <v>10.4</v>
       </c>
       <c r="F31" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" s="3" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="G31" s="10" t="n">
         <v>15.8</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="I31" s="3" t="n">
-        <v>1.8</v>
-      </c>
+        <v>72.09999999999999</v>
+      </c>
+      <c r="I31" s="3" t="inlineStr"/>
       <c r="J31" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="K31" s="3" t="n"/>
-      <c r="L31" s="3" t="n">
-        <v>16</v>
+        <v>39.1</v>
+      </c>
+      <c r="K31" s="3" t="inlineStr"/>
+      <c r="L31" s="16" t="n">
+        <v>11.5</v>
       </c>
       <c r="M31" s="3" t="n">
         <v>11.2</v>
       </c>
-      <c r="N31" s="3" t="n">
-        <v>0.3</v>
-      </c>
+      <c r="N31" s="3" t="inlineStr"/>
       <c r="O31" s="3" t="n">
-        <v>4516.1</v>
-      </c>
-      <c r="P31" s="3" t="n">
-        <v>9</v>
+        <v>97.8</v>
+      </c>
+      <c r="P31" s="16" t="n">
+        <v>40.4</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>41.6</v>
-      </c>
-      <c r="R31" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="S31" s="3" t="n">
-        <v>89.90000000000001</v>
+        <v>22.6</v>
+      </c>
+      <c r="R31" s="16" t="n">
+        <v>179.3</v>
+      </c>
+      <c r="S31" s="16" t="n">
+        <v>16.9</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="U31" s="3" t="n">
-        <v>11</v>
+        <v>63</v>
+      </c>
+      <c r="U31" s="16" t="n">
+        <v>11.1</v>
       </c>
       <c r="V31" s="3" t="n">
         <v>19.9</v>
       </c>
-      <c r="W31" s="3" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="X31" s="3" t="n">
-        <v>10</v>
+      <c r="W31" s="16" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="X31" s="16" t="n">
+        <v>16.6</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>73</v>
+        <v>730</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3106,75 +3054,71 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D32" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="E32" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F32" s="13" t="n">
-        <v>10</v>
-      </c>
-      <c r="G32" s="3" t="n">
-        <v>15.8</v>
+        <v>520.8</v>
+      </c>
+      <c r="D32" s="10" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="E32" s="10" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="F32" s="10" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="G32" s="11" t="n">
+        <v>21.8</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>1.2</v>
+        <v>16.6</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>1.8</v>
+        <v>3.7</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>2</v>
+        <v>61.2</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" s="3" t="n">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="L32" s="16" t="n">
+        <v>1090.5</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="N32" s="3" t="n">
-        <v>1</v>
-      </c>
+        <v>103.3</v>
+      </c>
+      <c r="N32" s="3" t="inlineStr"/>
       <c r="O32" s="3" t="n">
-        <v>9</v>
+        <v>97.8</v>
       </c>
       <c r="P32" s="3" t="n">
-        <v>9</v>
+        <v>10.6</v>
       </c>
       <c r="Q32" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="R32" s="3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="S32" s="8" t="n">
-        <v>6009</v>
+        <v>29.8</v>
+      </c>
+      <c r="R32" s="16" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="S32" s="3" t="n">
+        <v>18.8</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="U32" s="3" t="n"/>
-      <c r="V32" s="3" t="n">
-        <v>21.1</v>
+        <v>162.5</v>
+      </c>
+      <c r="U32" s="3" t="inlineStr"/>
+      <c r="V32" s="16" t="n">
+        <v>21.4</v>
       </c>
       <c r="W32" s="3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="X32" s="3" t="n">
-        <v>0</v>
+        <v>18.5</v>
+      </c>
+      <c r="X32" s="16" t="n">
+        <v>27.9</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z32" s="3" t="n">
-        <v>9.800000000000001</v>
-      </c>
+        <v>70.90000000000001</v>
+      </c>
+      <c r="Z32" s="3" t="inlineStr"/>
       <c r="AA32" s="3" t="inlineStr">
         <is>
           <t>21</t>
@@ -3189,76 +3133,64 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>520</v>
+        <v>349.1</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="E33" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F33" s="9" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="G33" s="3" t="n">
-        <v>17.7</v>
+        <v>24.2</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="F33" s="11" t="n">
+        <v>48.54</v>
+      </c>
+      <c r="G33" s="11" t="n">
+        <v>211.1</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="I33" s="3" t="n">
-        <v>0.3</v>
-      </c>
+        <v>8.9</v>
+      </c>
+      <c r="I33" s="3" t="inlineStr"/>
       <c r="J33" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K33" s="3" t="inlineStr"/>
+      <c r="L33" s="3" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="M33" s="3" t="inlineStr"/>
+      <c r="N33" s="3" t="inlineStr"/>
+      <c r="O33" s="3" t="n">
+        <v>98.8</v>
+      </c>
+      <c r="P33" s="3" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="Q33" s="3" t="n">
+        <v>204.3</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>43.8</v>
+      </c>
+      <c r="S33" s="16" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="T33" s="3" t="n">
+        <v>79.90000000000001</v>
+      </c>
+      <c r="U33" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="K33" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="M33" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="O33" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="R33" s="3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="S33" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="T33" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="U33" s="3" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="V33" s="3" t="n">
-        <v>21.1</v>
-      </c>
+      <c r="V33" s="3" t="inlineStr"/>
       <c r="W33" s="3" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="X33" s="3" t="n">
-        <v>18</v>
-      </c>
+        <v>44.4</v>
+      </c>
+      <c r="X33" s="3" t="inlineStr"/>
       <c r="Y33" s="3" t="n">
-        <v>20</v>
+        <v>189</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3274,73 +3206,69 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>349.1</v>
+        <v>329.1</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="E34" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34" s="3" t="n">
-        <v>18.5</v>
+        <v>23.3</v>
+      </c>
+      <c r="E34" s="11" t="n">
+        <v>44.3</v>
+      </c>
+      <c r="F34" s="16" t="n">
+        <v>19</v>
       </c>
       <c r="G34" s="3" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="H34" s="16" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="I34" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J34" s="3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="K34" s="3" t="n">
         <v>11.4</v>
       </c>
-      <c r="H34" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="I34" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" s="3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="K34" s="3" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="L34" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="M34" s="3" t="n">
+      <c r="L34" s="16" t="n">
+        <v>16</v>
+      </c>
+      <c r="M34" s="16" t="n">
         <v>15.9</v>
       </c>
-      <c r="N34" s="8" t="n">
-        <v>16.6</v>
-      </c>
+      <c r="N34" s="3" t="inlineStr"/>
       <c r="O34" s="3" t="n">
-        <v>8</v>
+        <v>99</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="Q34" s="3" t="n">
-        <v>20</v>
+        <v>10.2</v>
+      </c>
+      <c r="Q34" s="16" t="n">
+        <v>21.8</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="S34" s="3" t="n">
         <v>18.9</v>
       </c>
+      <c r="S34" s="16" t="n">
+        <v>181.8</v>
+      </c>
       <c r="T34" s="3" t="n">
-        <v>29.9</v>
+        <v>72.8</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="V34" s="8" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="W34" s="3" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="X34" s="3" t="n">
-        <v>18</v>
-      </c>
+        <v>29.6</v>
+      </c>
+      <c r="V34" s="16" t="n">
+        <v>1287.1</v>
+      </c>
+      <c r="W34" s="16" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="X34" s="3" t="inlineStr"/>
       <c r="Y34" s="3" t="n">
-        <v>8</v>
+        <v>893</v>
       </c>
       <c r="Z34" s="3" t="n">
         <v>9.800000000000001</v>
@@ -3359,76 +3287,72 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>320.9</v>
+        <v>1506.7</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="E35" s="9" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="F35" s="9" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="G35" s="3" t="n">
-        <v>8.6</v>
+        <v>26.8</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="F35" s="16" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="G35" s="11" t="n">
+        <v>15.4</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>4.1</v>
+        <v>9.5</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>0.4</v>
+        <v>51.5</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="L35" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" s="3" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="N35" s="3" t="n">
         <v>10</v>
       </c>
+      <c r="L35" s="16" t="n">
+        <v>13</v>
+      </c>
+      <c r="M35" s="16" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="N35" s="3" t="inlineStr"/>
       <c r="O35" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="P35" s="3" t="n">
-        <v>0.2</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="P35" s="3" t="inlineStr"/>
       <c r="Q35" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="R35" s="8" t="n">
-        <v>8.9</v>
+        <v>23.8</v>
+      </c>
+      <c r="R35" s="16" t="n">
+        <v>147.6</v>
       </c>
       <c r="S35" s="3" t="n">
-        <v>18.7</v>
+        <v>16.8</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U35" s="3" t="n">
-        <v>9.6</v>
+        <v>572</v>
+      </c>
+      <c r="U35" s="16" t="n">
+        <v>12.8</v>
       </c>
       <c r="V35" s="3" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="W35" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="X35" s="3" t="n">
-        <v>0</v>
+        <v>20.8</v>
+      </c>
+      <c r="W35" s="16" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="X35" s="16" t="n">
+        <v>4116.8</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>2</v>
+        <v>68.5</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3444,76 +3368,74 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>50.6</v>
-      </c>
-      <c r="D36" s="3" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="E36" s="8" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="F36" s="3" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>535.5</v>
+      </c>
+      <c r="D36" s="11" t="n">
+        <v>56.3</v>
+      </c>
+      <c r="E36" s="11" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F36" s="11" t="n">
+        <v>81.3</v>
+      </c>
+      <c r="G36" s="16" t="n">
+        <v>15.9</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>9.5</v>
+        <v>6.4</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>2.6</v>
+        <v>3.9</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="M36" s="8" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="N36" s="3" t="n">
         <v>10</v>
       </c>
+      <c r="L36" s="16" t="n">
+        <v>101.6</v>
+      </c>
+      <c r="M36" s="16" t="n">
+        <v>110.5</v>
+      </c>
+      <c r="N36" s="3" t="inlineStr"/>
       <c r="O36" s="3" t="n">
-        <v>9</v>
+        <v>199</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q36" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="R36" s="3" t="n">
-        <v>7.6</v>
+        <v>18.1</v>
+      </c>
+      <c r="Q36" s="3" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="R36" s="16" t="n">
+        <v>71.09999999999999</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>10.8</v>
+        <v>14.8</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="U36" s="3" t="n">
-        <v>4.3</v>
+        <v>685</v>
+      </c>
+      <c r="U36" s="16" t="n">
+        <v>27.9</v>
       </c>
       <c r="V36" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="W36" s="3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="X36" s="8" t="n">
-        <v>6.8</v>
+        <v>20.6</v>
+      </c>
+      <c r="W36" s="16" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="X36" s="16" t="n">
+        <v>13.8</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>8.5</v>
+        <v>12</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>0</v>
+        <v>1110.8</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3529,72 +3451,72 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>535.5</v>
-      </c>
-      <c r="D37" s="10" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="E37" s="10" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="F37" s="10" t="n">
-        <v>18</v>
+        <v>2240.4</v>
+      </c>
+      <c r="D37" s="9" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="E37" s="9" t="n">
+        <v>160.9</v>
+      </c>
+      <c r="F37" s="9" t="n">
+        <v>991.7</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>51.1</v>
+        <v>1.6</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>46</v>
+        <v>146</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>30.9</v>
+        <v>116.1</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="K37" s="3" t="n"/>
+        <v>20.8</v>
+      </c>
+      <c r="K37" s="3" t="n">
+        <v>81.5</v>
+      </c>
       <c r="L37" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="M37" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="N37" s="3" t="n"/>
+        <v>165</v>
+      </c>
+      <c r="M37" s="3" t="inlineStr"/>
+      <c r="N37" s="3" t="inlineStr"/>
       <c r="O37" s="3" t="n">
-        <v>9</v>
+        <v>2492</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>25.5</v>
+        <v>115.5</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>17</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>88</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>5</v>
+        <v>216.9</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>4.3</v>
+        <v>54.5</v>
       </c>
       <c r="V37" s="3" t="n">
-        <v>20</v>
+        <v>1100.9</v>
       </c>
       <c r="W37" s="3" t="n">
-        <v>5</v>
+        <v>183.1</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>3.3</v>
+        <v>84.8</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>0</v>
+        <v>359.5</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>39.6</v>
+        <v>394.6</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3610,75 +3532,69 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>220.9</v>
+        <v>2448.1</v>
       </c>
       <c r="D38" s="10" t="n">
-        <v>28.5</v>
+        <v>25.7</v>
       </c>
       <c r="E38" s="10" t="n">
-        <v>0.5</v>
+        <v>12.1</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>99.7</v>
-      </c>
-      <c r="G38" s="3" t="n">
-        <v>61.6</v>
+        <v>18.9</v>
+      </c>
+      <c r="G38" s="10" t="n">
+        <v>13.5</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>46</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" s="3" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="K38" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L38" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="M38" s="8" t="n">
-        <v>431.7</v>
-      </c>
-      <c r="N38" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>28.1</v>
+      </c>
+      <c r="J38" s="16" t="n">
+        <v>92.09999999999999</v>
+      </c>
+      <c r="K38" s="3" t="inlineStr"/>
+      <c r="L38" s="16" t="n">
+        <v>13</v>
+      </c>
+      <c r="M38" s="16" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="N38" s="3" t="inlineStr"/>
       <c r="O38" s="3" t="n">
-        <v>202</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q38" s="8" t="n">
-        <v>151.5</v>
-      </c>
-      <c r="R38" s="3" t="n">
-        <v>80.90000000000001</v>
-      </c>
-      <c r="S38" s="3" t="n">
-        <v>88</v>
-      </c>
+        <v>23.5</v>
+      </c>
+      <c r="Q38" s="3" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="R38" s="3" t="inlineStr"/>
+      <c r="S38" s="3" t="inlineStr"/>
       <c r="T38" s="3" t="n">
-        <v>0</v>
+        <v>63.3</v>
       </c>
       <c r="U38" s="3" t="n">
-        <v>0</v>
+        <v>424.3</v>
       </c>
       <c r="V38" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="W38" s="3" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="X38" s="3" t="n">
-        <v>89.8</v>
+        <v>20.2</v>
+      </c>
+      <c r="W38" s="16" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="X38" s="16" t="n">
+        <v>16.9</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>259.5</v>
-      </c>
-      <c r="Z38" s="3" t="n"/>
+        <v>21.9</v>
+      </c>
+      <c r="Z38" s="3" t="n">
+        <v>69.40000000000001</v>
+      </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -3693,76 +3609,64 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>0</v>
+        <v>3599.9</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="E39" s="9" t="n">
-        <v>60</v>
-      </c>
-      <c r="F39" s="9" t="n">
-        <v>99.7</v>
-      </c>
-      <c r="G39" s="3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="H39" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="I39" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="J39" s="3" t="n">
-        <v>6.2</v>
-      </c>
+        <v>26.9</v>
+      </c>
+      <c r="E39" s="16" t="n">
+        <v>1118</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="G39" s="3" t="inlineStr"/>
+      <c r="H39" s="3" t="inlineStr"/>
+      <c r="I39" s="3" t="inlineStr"/>
+      <c r="J39" s="3" t="inlineStr"/>
       <c r="K39" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L39" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="M39" s="8" t="n">
-        <v>431.7</v>
-      </c>
-      <c r="N39" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>10.8</v>
+      </c>
+      <c r="L39" s="16" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="M39" s="3" t="inlineStr"/>
+      <c r="N39" s="3" t="inlineStr"/>
       <c r="O39" s="3" t="n">
-        <v>98.90000000000001</v>
+        <v>1980.8</v>
       </c>
       <c r="P39" s="3" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="Q39" s="3" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="S39" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="Q39" s="8" t="n">
-        <v>151.5</v>
-      </c>
-      <c r="R39" s="3" t="n">
-        <v>80.90000000000001</v>
-      </c>
-      <c r="S39" s="3" t="n">
-        <v>15.1</v>
-      </c>
       <c r="T39" s="3" t="n">
-        <v>216.9</v>
-      </c>
-      <c r="U39" s="8" t="n">
-        <v>9</v>
+        <v>1720</v>
+      </c>
+      <c r="U39" s="16" t="n">
+        <v>18</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="W39" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="X39" s="3" t="n">
-        <v>89.8</v>
+        <v>21.2</v>
+      </c>
+      <c r="W39" s="16" t="n">
+        <v>8151.7</v>
+      </c>
+      <c r="X39" s="16" t="n">
+        <v>119.6</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>1.9</v>
+        <v>76</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3778,77 +3682,70 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D40" s="3" t="n">
-        <v>25.7</v>
-      </c>
-      <c r="E40" s="9" t="n">
-        <v>42.2</v>
-      </c>
-      <c r="F40" s="3" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="G40" s="8" t="n">
-        <v>15.9</v>
+        <v>335.1</v>
+      </c>
+      <c r="D40" s="10" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="E40" s="10" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="F40" s="10" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="G40" s="10" t="n">
+        <v>16.3</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>0</v>
+        <v>17.3</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="J40" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="K40" s="3" t="n"/>
+        <v>12.4</v>
+      </c>
+      <c r="J40" s="3" t="inlineStr"/>
+      <c r="K40" s="3" t="n">
+        <v>10</v>
+      </c>
       <c r="L40" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M40" s="3" t="n">
-        <v>41.8</v>
-      </c>
-      <c r="N40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0 00
-</t>
-        </is>
-      </c>
+        <v>10.6</v>
+      </c>
+      <c r="M40" s="16" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="N40" s="3" t="inlineStr"/>
       <c r="O40" s="3" t="n">
-        <v>96</v>
+        <v>198</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="Q40" s="3" t="n">
-        <v>993.6</v>
+        <v>1</v>
+      </c>
+      <c r="Q40" s="16" t="n">
+        <v>22</v>
       </c>
       <c r="R40" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S40" s="3" t="n">
-        <v>15.1</v>
+        <v>18</v>
+      </c>
+      <c r="S40" s="16" t="n">
+        <v>18.5</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>0</v>
+        <v>69.2</v>
       </c>
       <c r="U40" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V40" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W40" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X40" s="3" t="n">
-        <v>6.9</v>
+        <v>18</v>
+      </c>
+      <c r="V40" s="3" t="inlineStr"/>
+      <c r="W40" s="16" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="X40" s="16" t="n">
+        <v>199.3</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>70</v>
+        <v>983</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3864,76 +3761,66 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>251.2</v>
-      </c>
-      <c r="D41" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E41" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="F41" s="3" t="n">
-        <v>18.9</v>
+        <v>245451.2</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="F41" s="11" t="n">
+        <v>128.13</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="H41" s="3" t="n">
-        <v>0.7</v>
+        <v>19.8</v>
+      </c>
+      <c r="H41" s="16" t="n">
+        <v>51</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J41" s="3" t="n">
-        <v>0.3</v>
-      </c>
+        <v>3.6</v>
+      </c>
+      <c r="J41" s="3" t="inlineStr"/>
       <c r="K41" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>0</v>
+        <v>818.5</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="N41" s="3" t="n">
-        <v>10</v>
-      </c>
+        <v>8.6</v>
+      </c>
+      <c r="N41" s="3" t="inlineStr"/>
       <c r="O41" s="3" t="n">
-        <v>96</v>
-      </c>
-      <c r="P41" s="3" t="n">
         <v>0.2</v>
       </c>
+      <c r="P41" s="3" t="inlineStr"/>
       <c r="Q41" s="3" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="R41" s="8" t="n">
-        <v>18</v>
-      </c>
-      <c r="S41" s="3" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="T41" s="3" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="U41" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="V41" s="3" t="n">
-        <v>10.7</v>
+        <v>23.9</v>
+      </c>
+      <c r="R41" s="16" t="n">
+        <v>717.9</v>
+      </c>
+      <c r="S41" s="16" t="n">
+        <v>216.6</v>
+      </c>
+      <c r="T41" s="3" t="inlineStr"/>
+      <c r="U41" s="16" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="V41" s="16" t="n">
+        <v>222</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="X41" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>18.5</v>
+      </c>
+      <c r="X41" s="3" t="inlineStr"/>
       <c r="Y41" s="3" t="n">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>0</v>
+        <v>121.2</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -3949,77 +3836,67 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>251.2</v>
-      </c>
-      <c r="D42" s="3" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="E42" s="9" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="F42" s="9" t="n">
-        <v>48.9</v>
-      </c>
-      <c r="G42" s="3" t="n">
-        <v>12.8</v>
+        <v>524.4</v>
+      </c>
+      <c r="D42" s="3" t="inlineStr"/>
+      <c r="E42" s="16" t="n">
+        <v>60.1</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="G42" s="11" t="n">
+        <v>25.2</v>
       </c>
       <c r="H42" s="3" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="I42" s="3" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J42" s="3" t="inlineStr"/>
+      <c r="K42" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="L42" s="16" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="M42" s="3" t="n">
         <v>2.2</v>
       </c>
-      <c r="I42" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J42" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="K42" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L42" s="3" t="n">
-        <v>88</v>
-      </c>
-      <c r="M42" s="3" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="N42" s="3" t="n">
-        <v>11</v>
+      <c r="N42" s="16" t="n">
+        <v>13.2</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>98</v>
+        <v>16</v>
       </c>
       <c r="P42" s="3" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="Q42" s="3" t="n">
-        <v>2</v>
+        <v>26.6</v>
       </c>
       <c r="R42" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="S42" s="8" t="n">
-        <v>60.6</v>
+        <v>1.8</v>
+      </c>
+      <c r="S42" s="16" t="n">
+        <v>14.7</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>500.9</v>
-      </c>
-      <c r="U42" s="3" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="V42" s="3" t="n">
-        <v>2</v>
+        <v>543.5</v>
+      </c>
+      <c r="U42" s="16" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="V42" s="16" t="n">
+        <v>22</v>
       </c>
       <c r="W42" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="X42" s="8" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Y42" s="3" t="n">
-        <v>89</v>
-      </c>
-      <c r="Z42" s="3" t="n">
-        <v>1</v>
-      </c>
+        <v>161.3</v>
+      </c>
+      <c r="X42" s="3" t="inlineStr"/>
+      <c r="Y42" s="3" t="inlineStr"/>
+      <c r="Z42" s="3" t="inlineStr"/>
       <c r="AA42" s="3" t="inlineStr">
         <is>
           <t>29</t>
@@ -4033,70 +3910,30 @@
           <t>30</t>
         </is>
       </c>
-      <c r="C43" s="3" t="n">
-        <v>529.4</v>
-      </c>
-      <c r="D43" s="3" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="E43" s="9" t="n">
-        <v>84.5</v>
-      </c>
-      <c r="F43" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G43" s="8" t="n">
-        <v>90.7</v>
-      </c>
-      <c r="H43" s="3" t="n"/>
-      <c r="I43" s="3" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="J43" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="K43" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L43" s="3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="M43" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="N43" s="3" t="n">
-        <v>43.8</v>
-      </c>
-      <c r="O43" s="3" t="n">
-        <v>96</v>
-      </c>
-      <c r="P43" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="Q43" s="3" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="R43" s="3" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="S43" s="3" t="n"/>
-      <c r="T43" s="3" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="U43" s="3" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="V43" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="W43" s="3" t="n">
-        <v>163.3</v>
-      </c>
-      <c r="X43" s="3" t="n"/>
-      <c r="Y43" s="3" t="n">
-        <v>58</v>
-      </c>
-      <c r="Z43" s="3" t="n"/>
+      <c r="C43" s="3" t="inlineStr"/>
+      <c r="D43" s="3" t="inlineStr"/>
+      <c r="E43" s="3" t="inlineStr"/>
+      <c r="F43" s="14" t="inlineStr"/>
+      <c r="G43" s="3" t="inlineStr"/>
+      <c r="H43" s="3" t="inlineStr"/>
+      <c r="I43" s="3" t="inlineStr"/>
+      <c r="J43" s="3" t="inlineStr"/>
+      <c r="K43" s="3" t="inlineStr"/>
+      <c r="L43" s="3" t="inlineStr"/>
+      <c r="M43" s="3" t="inlineStr"/>
+      <c r="N43" s="3" t="inlineStr"/>
+      <c r="O43" s="3" t="inlineStr"/>
+      <c r="P43" s="3" t="inlineStr"/>
+      <c r="Q43" s="3" t="inlineStr"/>
+      <c r="R43" s="3" t="inlineStr"/>
+      <c r="S43" s="3" t="inlineStr"/>
+      <c r="T43" s="3" t="inlineStr"/>
+      <c r="U43" s="3" t="inlineStr"/>
+      <c r="V43" s="3" t="inlineStr"/>
+      <c r="W43" s="3" t="inlineStr"/>
+      <c r="X43" s="3" t="inlineStr"/>
+      <c r="Y43" s="3" t="inlineStr"/>
+      <c r="Z43" s="3" t="inlineStr"/>
       <c r="AA43" s="3" t="inlineStr">
         <is>
           <t>30</t>
@@ -4110,58 +3947,30 @@
           <t>31</t>
         </is>
       </c>
-      <c r="C44" s="3" t="n"/>
-      <c r="D44" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E44" s="11" t="n"/>
-      <c r="F44" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3" t="n"/>
-      <c r="H44" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3" t="n">
-        <v>43.4</v>
-      </c>
-      <c r="J44" s="3" t="n"/>
-      <c r="K44" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L44" s="3" t="n"/>
-      <c r="M44" s="3" t="n"/>
-      <c r="N44" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O44" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P44" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="Q44" s="3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="R44" s="3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="S44" s="3" t="n"/>
-      <c r="T44" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U44" s="3" t="n"/>
-      <c r="V44" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W44" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X44" s="3" t="n"/>
-      <c r="Y44" s="3" t="n"/>
-      <c r="Z44" s="3" t="n">
-        <v>35.1</v>
-      </c>
+      <c r="C44" s="3" t="inlineStr"/>
+      <c r="D44" s="3" t="inlineStr"/>
+      <c r="E44" s="3" t="inlineStr"/>
+      <c r="F44" s="14" t="inlineStr"/>
+      <c r="G44" s="3" t="inlineStr"/>
+      <c r="H44" s="3" t="inlineStr"/>
+      <c r="I44" s="3" t="inlineStr"/>
+      <c r="J44" s="3" t="inlineStr"/>
+      <c r="K44" s="3" t="inlineStr"/>
+      <c r="L44" s="3" t="inlineStr"/>
+      <c r="M44" s="3" t="inlineStr"/>
+      <c r="N44" s="3" t="inlineStr"/>
+      <c r="O44" s="3" t="inlineStr"/>
+      <c r="P44" s="3" t="inlineStr"/>
+      <c r="Q44" s="3" t="inlineStr"/>
+      <c r="R44" s="3" t="inlineStr"/>
+      <c r="S44" s="3" t="inlineStr"/>
+      <c r="T44" s="3" t="inlineStr"/>
+      <c r="U44" s="3" t="inlineStr"/>
+      <c r="V44" s="3" t="inlineStr"/>
+      <c r="W44" s="3" t="inlineStr"/>
+      <c r="X44" s="3" t="inlineStr"/>
+      <c r="Y44" s="3" t="inlineStr"/>
+      <c r="Z44" s="3" t="inlineStr"/>
       <c r="AA44" s="3" t="inlineStr">
         <is>
           <t>31</t>
@@ -4176,69 +3985,71 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>1011</v>
-      </c>
-      <c r="D45" s="10" t="n">
-        <v>10</v>
-      </c>
-      <c r="E45" s="10" t="n">
-        <v>61.8</v>
-      </c>
-      <c r="F45" s="10" t="n">
-        <v>754.6</v>
-      </c>
-      <c r="G45" s="3" t="n">
-        <v>7.9</v>
+        <v>1911.2</v>
+      </c>
+      <c r="D45" s="15" t="inlineStr"/>
+      <c r="E45" s="15" t="inlineStr"/>
+      <c r="F45" s="9" t="n">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="G45" s="11" t="n">
+        <v>10.8</v>
       </c>
       <c r="H45" s="3" t="n">
         <v>27</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>0.4</v>
+        <v>454.4</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>221.9</v>
+        <v>121.9</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L45" s="3" t="n"/>
+        <v>10</v>
+      </c>
+      <c r="L45" s="3" t="n">
+        <v>144</v>
+      </c>
       <c r="M45" s="3" t="n">
-        <v>200.9</v>
+        <v>42.9</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>0</v>
+        <v>51.2</v>
       </c>
       <c r="O45" s="3" t="n">
         <v>388</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Q45" s="3" t="n">
-        <v>98.59999999999999</v>
+        <v>198.6</v>
       </c>
       <c r="R45" s="3" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>0</v>
+        <v>166</v>
       </c>
       <c r="T45" s="3" t="n">
         <v>216.9</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>99</v>
+        <v>59</v>
       </c>
       <c r="V45" s="3" t="n">
-        <v>891.9</v>
+        <v>831.4</v>
       </c>
       <c r="W45" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X45" s="3" t="n"/>
-      <c r="Y45" s="3" t="n"/>
-      <c r="Z45" s="3" t="n"/>
+        <v>168.3</v>
+      </c>
+      <c r="X45" s="3" t="inlineStr"/>
+      <c r="Y45" s="3" t="n">
+        <v>8263</v>
+      </c>
+      <c r="Z45" s="3" t="n">
+        <v>331.8</v>
+      </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -4252,72 +4063,67 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C46" s="3" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="D46" s="12" t="n"/>
-      <c r="E46" s="12" t="n"/>
+      <c r="C46" s="3" t="inlineStr"/>
+      <c r="D46" s="10" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="E46" s="10" t="n">
+        <v>10.4</v>
+      </c>
       <c r="F46" s="10" t="n">
         <v>18.9</v>
       </c>
-      <c r="G46" s="3" t="n">
+      <c r="G46" s="10" t="n">
         <v>16.9</v>
       </c>
-      <c r="H46" s="3" t="n">
-        <v>6.7</v>
+      <c r="H46" s="16" t="n">
+        <v>19.7</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>3</v>
+        <v>36.1</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>221.9</v>
-      </c>
-      <c r="K46" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L46" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="M46" s="8" t="n">
-        <v>200.9</v>
+        <v>52.1</v>
+      </c>
+      <c r="K46" s="3" t="inlineStr"/>
+      <c r="L46" s="16" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="M46" s="16" t="n">
+        <v>10.7</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>51</v>
+        <v>4.8</v>
       </c>
       <c r="O46" s="3" t="n">
         <v>97</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q46" s="3" t="n">
-        <v>98.59999999999999</v>
+        <v>6</v>
+      </c>
+      <c r="Q46" s="16" t="n">
+        <v>29.7</v>
       </c>
       <c r="R46" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="S46" s="3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="T46" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="U46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">110 20
-</t>
-        </is>
-      </c>
+        <v>17.8</v>
+      </c>
+      <c r="S46" s="16" t="n">
+        <v>2261.5</v>
+      </c>
+      <c r="T46" s="3" t="inlineStr"/>
+      <c r="U46" s="3" t="inlineStr"/>
       <c r="V46" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="W46" s="3" t="n"/>
-      <c r="X46" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y46" s="3" t="n"/>
+        <v>21.3</v>
+      </c>
+      <c r="W46" s="16" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="X46" s="3" t="inlineStr"/>
+      <c r="Y46" s="3" t="n">
+        <v>1680.1</v>
+      </c>
       <c r="Z46" s="3" t="n">
-        <v>0</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/05_transient_transcription_output/702/702_196402_SF.JPG_stage_duirnal_temp_range.xlsx
+++ b/results/05_transient_transcription_output/702/702_196402_SF.JPG_stage_duirnal_temp_range.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -41,6 +41,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00CC3300"/>
+        <bgColor rgb="00CC3300"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="0075696F"/>
         <bgColor rgb="0075696F"/>
       </patternFill>
@@ -49,18 +55,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF6DCD57"/>
         <bgColor rgb="FF6DCD57"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00CC3300"/>
-        <bgColor rgb="00CC3300"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC0CB"/>
-        <bgColor rgb="00FFC0CB"/>
       </patternFill>
     </fill>
     <fill>
@@ -137,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -152,7 +146,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -164,19 +158,7 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -790,22 +772,22 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>391.2</v>
-      </c>
-      <c r="D4" s="10" t="n">
+        <v>3012.1</v>
+      </c>
+      <c r="D4" s="11" t="n">
         <v>27.8</v>
       </c>
-      <c r="E4" s="10" t="n">
+      <c r="E4" s="11" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="F4" s="10" t="n">
+      <c r="F4" s="11" t="n">
         <v>18.5</v>
       </c>
-      <c r="G4" s="11" t="n">
-        <v>18.2</v>
+      <c r="G4" s="8" t="n">
+        <v>81.7</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>0.5</v>
+        <v>5.8</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>3.5</v>
@@ -820,46 +802,46 @@
         <v>9.300000000000001</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="N4" s="16" t="n">
-        <v>19.9</v>
+        <v>9.699999999999999</v>
+      </c>
+      <c r="N4" s="8" t="n">
+        <v>11.9</v>
       </c>
       <c r="O4" s="3" t="n">
         <v>98</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="Q4" s="16" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="Q4" s="3" t="n">
         <v>23.8</v>
       </c>
-      <c r="R4" s="3" t="n">
+      <c r="R4" s="8" t="n">
         <v>16.8</v>
       </c>
-      <c r="S4" s="16" t="n">
-        <v>114.1</v>
+      <c r="S4" s="8" t="n">
+        <v>19.1</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>542.5</v>
+        <v>42.5</v>
       </c>
       <c r="U4" s="3" t="n">
         <v>19.1</v>
       </c>
-      <c r="V4" s="16" t="n">
-        <v>2219.1</v>
-      </c>
-      <c r="W4" s="16" t="n">
+      <c r="V4" s="3" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="W4" s="3" t="n">
         <v>18.3</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>41.1</v>
+        <v>18.9</v>
       </c>
       <c r="Y4" s="3" t="n">
         <v>71</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>0.1</v>
+        <v>7.8</v>
       </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
@@ -877,68 +859,74 @@
       <c r="C5" s="3" t="n">
         <v>382.4</v>
       </c>
-      <c r="D5" s="10" t="n">
+      <c r="D5" s="11" t="n">
         <v>26.9</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>44.5</v>
+        <v>11.5</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>41.1</v>
-      </c>
-      <c r="G5" s="16" t="n">
-        <v>15.4</v>
+        <v>19.2</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>15.9</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>17.9</v>
+        <v>7.9</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="J5" s="3" t="n">
         <v>2.6</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="L5" s="16" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="M5" s="3" t="inlineStr"/>
+        <v>11.2</v>
+      </c>
+      <c r="L5" s="8" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="M5" s="8" t="n">
+        <v>19.4</v>
+      </c>
       <c r="N5" s="3" t="n">
         <v>12.9</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>190.8</v>
-      </c>
-      <c r="P5" s="3" t="inlineStr"/>
-      <c r="Q5" s="16" t="n">
+        <v>90</v>
+      </c>
+      <c r="P5" s="3" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="Q5" s="8" t="n">
         <v>19.6</v>
       </c>
-      <c r="R5" s="3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="S5" s="16" t="n">
+      <c r="R5" s="8" t="n">
+        <v>80.59999999999999</v>
+      </c>
+      <c r="S5" s="3" t="n">
         <v>20.9</v>
       </c>
       <c r="T5" s="3" t="n">
         <v>91</v>
       </c>
-      <c r="U5" s="3" t="inlineStr"/>
-      <c r="V5" s="16" t="n">
-        <v>189.5</v>
+      <c r="U5" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="V5" s="8" t="n">
+        <v>199.5</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>1.2</v>
+        <v>19.2</v>
       </c>
       <c r="X5" s="3" t="n">
-        <v>2.1</v>
+        <v>18.3</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>180.5</v>
+        <v>80.5</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>6.6</v>
+        <v>66.5</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -956,68 +944,74 @@
       <c r="C6" s="3" t="n">
         <v>309.1</v>
       </c>
-      <c r="D6" s="10" t="n">
+      <c r="D6" s="11" t="n">
         <v>25.9</v>
       </c>
-      <c r="E6" s="10" t="n">
+      <c r="E6" s="11" t="n">
         <v>10.9</v>
       </c>
-      <c r="F6" s="10" t="n">
+      <c r="F6" s="11" t="n">
         <v>18.4</v>
       </c>
-      <c r="G6" s="3" t="n">
-        <v>0.5</v>
+      <c r="G6" s="11" t="n">
+        <v>15</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>7.5</v>
+        <v>5.9</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="J6" s="3" t="inlineStr"/>
+        <v>1.2</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>1.7</v>
+      </c>
       <c r="K6" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L6" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="M6" s="16" t="n">
-        <v>411</v>
-      </c>
-      <c r="N6" s="16" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="L6" s="8" t="n">
+        <v>101.1</v>
+      </c>
+      <c r="M6" s="8" t="n">
+        <v>211</v>
+      </c>
+      <c r="N6" s="3" t="n">
         <v>13.1</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>199</v>
+        <v>98</v>
       </c>
       <c r="P6" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q6" s="3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="R6" s="16" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="S6" s="3" t="inlineStr"/>
+      <c r="Q6" s="8" t="n">
+        <v>158.4</v>
+      </c>
+      <c r="R6" s="8" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="S6" s="3" t="n">
+        <v>11.6</v>
+      </c>
       <c r="T6" s="3" t="n">
         <v>92</v>
       </c>
-      <c r="U6" s="3" t="inlineStr"/>
-      <c r="V6" s="16" t="n">
-        <v>715.8</v>
+      <c r="U6" s="3" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="V6" s="3" t="n">
+        <v>15.8</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>114.3</v>
+        <v>18.3</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>0.1</v>
+        <v>17.9</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>195</v>
+        <v>95</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>10.9</v>
+        <v>0.9</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -1033,76 +1027,76 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>1275.8</v>
-      </c>
-      <c r="D7" s="10" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="F7" s="11" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="G7" s="16" t="n">
-        <v>98</v>
-      </c>
-      <c r="H7" s="3" t="n">
-        <v>444.4</v>
+        <v>275.8</v>
+      </c>
+      <c r="D7" s="9" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="E7" s="9" t="n">
+        <v>285.95</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="H7" s="8" t="n">
+        <v>112.9</v>
       </c>
       <c r="I7" s="3" t="n">
         <v>11.2</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.4</v>
+        <v>12.9</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="M7" s="16" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="N7" s="16" t="n">
-        <v>15</v>
+        <v>13.2</v>
+      </c>
+      <c r="M7" s="8" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>5</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>198</v>
+        <v>98</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="Q7" s="3" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="R7" s="16" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q7" s="8" t="n">
+        <v>119.3</v>
+      </c>
+      <c r="R7" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="S7" s="3" t="n">
-        <v>43.3</v>
+      <c r="S7" s="8" t="n">
+        <v>77.5</v>
       </c>
       <c r="T7" s="3" t="n">
         <v>79</v>
       </c>
-      <c r="U7" s="16" t="n">
-        <v>94.8</v>
-      </c>
-      <c r="V7" s="3" t="n">
-        <v>8.4</v>
+      <c r="U7" s="3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="V7" s="8" t="n">
+        <v>18.9</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>46.8</v>
+        <v>16.8</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>131.3</v>
+        <v>17.9</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>814.9</v>
+        <v>81</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>14.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1118,22 +1112,22 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>391.2</v>
-      </c>
-      <c r="D8" s="10" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="E8" s="10" t="n">
-        <v>-9.9</v>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>8.1</v>
+        <v>291.2</v>
+      </c>
+      <c r="D8" s="11" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="E8" s="11" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="F8" s="11" t="n">
+        <v>18.6</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>17.2</v>
+        <v>7.2</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>2.2</v>
@@ -1142,50 +1136,52 @@
         <v>3.5</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>40.8</v>
-      </c>
-      <c r="M8" s="3" t="n">
-        <v>424.4</v>
-      </c>
-      <c r="N8" s="3" t="inlineStr"/>
+        <v>10.8</v>
+      </c>
+      <c r="M8" s="8" t="n">
+        <v>190.6</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>11.2</v>
+      </c>
       <c r="O8" s="3" t="n">
-        <v>1718</v>
+        <v>98</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="Q8" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="R8" s="3" t="n">
-        <v>0.8</v>
+        <v>10.4</v>
+      </c>
+      <c r="Q8" s="8" t="n">
+        <v>217.5</v>
+      </c>
+      <c r="R8" s="8" t="n">
+        <v>18.9</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>19.5</v>
+        <v>1.9</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>176</v>
+        <v>76</v>
       </c>
       <c r="U8" s="3" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="V8" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="W8" s="16" t="n">
-        <v>17.3</v>
+        <v>11.8</v>
+      </c>
+      <c r="W8" s="8" t="n">
+        <v>97.3</v>
       </c>
       <c r="X8" s="3" t="n">
-        <v>2.1</v>
+        <v>18.9</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>1.2</v>
+        <v>87</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>12.6</v>
+        <v>2.6</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1203,71 +1199,71 @@
       <c r="C9" s="3" t="n">
         <v>1749.7</v>
       </c>
-      <c r="D9" s="9" t="n">
-        <v>12849.1</v>
-      </c>
-      <c r="E9" s="9" t="n">
-        <v>55.8</v>
-      </c>
-      <c r="F9" s="9" t="n">
-        <v>91.90000000000001</v>
+      <c r="D9" s="10" t="n">
+        <v>128.9</v>
+      </c>
+      <c r="E9" s="10" t="n">
+        <v>55.4</v>
+      </c>
+      <c r="F9" s="10" t="n">
+        <v>911.9</v>
       </c>
       <c r="G9" s="3" t="n">
         <v>73.90000000000001</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>1702.6</v>
+        <v>60.6</v>
       </c>
       <c r="I9" s="3" t="n">
         <v>9.9</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>13.3</v>
+        <v>19.5</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>17.7</v>
+        <v>7.8</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>56.4</v>
+        <v>56.7</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>551.2</v>
+        <v>55.2</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>55.1</v>
+        <v>25.1</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>1484.8</v>
+        <v>484.8</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>2.6</v>
+        <v>9.6</v>
       </c>
       <c r="Q9" s="3" t="n">
         <v>101.5</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>185.9</v>
+        <v>85.3</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>188.5</v>
+        <v>885.3</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>380.5</v>
+        <v>9501.5</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>1233.3</v>
+        <v>33.3</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>184.9</v>
+        <v>8.9</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>91.09999999999999</v>
+        <v>911.7</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>14154.5</v>
+        <v>9414.5</v>
       </c>
       <c r="Z9" s="3" t="n">
         <v>119.8</v>
@@ -1286,44 +1282,46 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>349.9</v>
-      </c>
-      <c r="D10" s="10" t="n">
+        <v>849.9</v>
+      </c>
+      <c r="D10" s="11" t="n">
         <v>25.8</v>
       </c>
-      <c r="E10" s="10" t="n">
+      <c r="E10" s="11" t="n">
         <v>11</v>
       </c>
-      <c r="F10" s="10" t="n">
+      <c r="F10" s="11" t="n">
         <v>18.4</v>
       </c>
-      <c r="G10" s="10" t="n">
+      <c r="G10" s="11" t="n">
         <v>14.8</v>
       </c>
       <c r="H10" s="3" t="n">
         <v>8.1</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="J10" s="16" t="n">
-        <v>211.4</v>
-      </c>
-      <c r="K10" s="3" t="inlineStr"/>
-      <c r="L10" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="J10" s="8" t="n">
+        <v>797.4</v>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L10" s="8" t="n">
         <v>11.3</v>
       </c>
-      <c r="M10" s="16" t="n">
-        <v>111</v>
-      </c>
-      <c r="N10" s="3" t="n">
-        <v>3</v>
+      <c r="M10" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="N10" s="8" t="n">
+        <v>13</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>196.8</v>
-      </c>
-      <c r="P10" s="16" t="n">
-        <v>1.5</v>
+        <v>96.8</v>
+      </c>
+      <c r="P10" s="3" t="n">
+        <v>0.5</v>
       </c>
       <c r="Q10" s="3" t="n">
         <v>20.3</v>
@@ -1331,29 +1329,29 @@
       <c r="R10" s="3" t="n">
         <v>17.9</v>
       </c>
-      <c r="S10" s="16" t="n">
-        <v>12.7</v>
+      <c r="S10" s="8" t="n">
+        <v>17.7</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>14167.1</v>
+        <v>26.7</v>
       </c>
       <c r="U10" s="3" t="n">
-        <v>6.7</v>
+        <v>7.2</v>
       </c>
       <c r="V10" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="W10" s="3" t="n">
+      <c r="W10" s="8" t="n">
         <v>17</v>
       </c>
-      <c r="X10" s="16" t="n">
+      <c r="X10" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>182.9</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>151</v>
+        <v>5</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1369,66 +1367,76 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>1509.3</v>
-      </c>
-      <c r="D11" s="10" t="n">
+        <v>909.3</v>
+      </c>
+      <c r="D11" s="11" t="n">
         <v>27.3</v>
       </c>
-      <c r="E11" s="10" t="n">
+      <c r="E11" s="11" t="n">
         <v>10.7</v>
       </c>
-      <c r="F11" s="10" t="n">
+      <c r="F11" s="11" t="n">
         <v>19</v>
       </c>
-      <c r="G11" s="10" t="n">
+      <c r="G11" s="11" t="n">
         <v>16.6</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="I11" s="3" t="inlineStr"/>
+        <v>6.7</v>
+      </c>
+      <c r="I11" s="8" t="n">
+        <v>84.7</v>
+      </c>
       <c r="J11" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="K11" s="3" t="inlineStr"/>
-      <c r="L11" s="3" t="inlineStr"/>
-      <c r="M11" s="3" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="K11" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L11" s="3" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="M11" s="3" t="n">
+        <v>6.4</v>
+      </c>
       <c r="N11" s="3" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="O11" s="3" t="inlineStr"/>
-      <c r="P11" s="16" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="Q11" s="16" t="n">
-        <v>226.3</v>
+        <v>119</v>
+      </c>
+      <c r="O11" s="3" t="n">
+        <v>51.8</v>
+      </c>
+      <c r="P11" s="3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="Q11" s="8" t="n">
+        <v>66.5</v>
       </c>
       <c r="R11" s="3" t="n">
         <v>17.1</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>1.4</v>
+        <v>17.9</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>40.1</v>
+        <v>862</v>
       </c>
       <c r="U11" s="3" t="n">
         <v>19.9</v>
       </c>
-      <c r="V11" s="16" t="n">
+      <c r="V11" s="8" t="n">
         <v>22.1</v>
       </c>
-      <c r="W11" s="3" t="n">
-        <v>2.6</v>
+      <c r="W11" s="8" t="n">
+        <v>17.6</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>1.6</v>
+        <v>11.6</v>
       </c>
       <c r="Y11" s="3" t="n">
         <v>66</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
@@ -1444,37 +1452,37 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1306.7</v>
-      </c>
-      <c r="D12" s="10" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="E12" s="10" t="n">
+        <v>506.7</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="E12" s="3" t="n">
         <v>10.9</v>
       </c>
-      <c r="F12" s="10" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="G12" s="11" t="n">
-        <v>14.5</v>
+      <c r="F12" s="3" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="G12" s="8" t="n">
+        <v>13</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="I12" s="16" t="n">
-        <v>94.8</v>
+        <v>2.1</v>
+      </c>
+      <c r="I12" s="8" t="n">
+        <v>9.4</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>15</v>
+        <v>1.5</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L12" s="16" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="M12" s="16" t="n">
-        <v>21.9</v>
+        <v>17</v>
+      </c>
+      <c r="L12" s="8" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="M12" s="3" t="n">
+        <v>22.1</v>
       </c>
       <c r="N12" s="3" t="n">
         <v>13.2</v>
@@ -1483,37 +1491,37 @@
         <v>195</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>10.8</v>
+        <v>0.8</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>25.4</v>
+        <v>25.6</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="S12" s="16" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="S12" s="8" t="n">
         <v>12.9</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="U12" s="3" t="n">
-        <v>4.2</v>
+        <v>37</v>
+      </c>
+      <c r="U12" s="8" t="n">
+        <v>4.6</v>
       </c>
       <c r="V12" s="3" t="n">
         <v>21.3</v>
       </c>
       <c r="W12" s="3" t="n">
-        <v>4.3</v>
+        <v>11.9</v>
       </c>
       <c r="X12" s="3" t="n">
-        <v>13.1</v>
+        <v>19.7</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>1092</v>
+        <v>32</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>12.2</v>
+        <v>12.3</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1529,66 +1537,76 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>1357.9</v>
-      </c>
-      <c r="D13" s="10" t="inlineStr"/>
-      <c r="E13" s="14" t="inlineStr"/>
+        <v>3514.9</v>
+      </c>
+      <c r="D13" s="11" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="E13" s="11" t="n">
+        <v>11.3</v>
+      </c>
       <c r="F13" s="11" t="n">
-        <v>18.13</v>
-      </c>
-      <c r="G13" s="3" t="n">
-        <v>4.4</v>
+        <v>18.2</v>
+      </c>
+      <c r="G13" s="11" t="n">
+        <v>14.7</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="I13" s="3" t="inlineStr"/>
+        <v>7.5</v>
+      </c>
+      <c r="I13" s="3" t="n">
+        <v>11.9</v>
+      </c>
       <c r="J13" s="3" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>10.5</v>
+        <v>8.5</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="M13" s="3" t="inlineStr"/>
-      <c r="N13" s="16" t="n">
-        <v>83.59999999999999</v>
+        <v>11.5</v>
+      </c>
+      <c r="M13" s="3" t="n">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="N13" s="8" t="n">
+        <v>13.6</v>
       </c>
       <c r="O13" s="3" t="n">
         <v>98</v>
       </c>
-      <c r="P13" s="3" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="Q13" s="3" t="inlineStr"/>
+      <c r="P13" s="8" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="Q13" s="8" t="n">
+        <v>180.9</v>
+      </c>
       <c r="R13" s="3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="S13" s="16" t="n">
-        <v>18.1</v>
+        <v>17.3</v>
+      </c>
+      <c r="S13" s="3" t="n">
+        <v>11.8</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>86.8</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="U13" s="3" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="V13" s="3" t="n">
         <v>19.6</v>
       </c>
-      <c r="W13" s="16" t="n">
-        <v>88.59999999999999</v>
-      </c>
-      <c r="X13" s="16" t="n">
+      <c r="W13" s="8" t="n">
+        <v>6816.4</v>
+      </c>
+      <c r="X13" s="3" t="n">
         <v>19.1</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>184</v>
+        <v>84</v>
       </c>
       <c r="Z13" s="3" t="n">
-        <v>9.6</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
@@ -1604,70 +1622,76 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>227</v>
-      </c>
-      <c r="D14" s="10" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="E14" s="10" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="F14" s="10" t="n">
-        <v>18.13</v>
-      </c>
-      <c r="G14" s="16" t="n">
+        <v>221</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="E14" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F14" s="9" t="n">
+        <v>18.53</v>
+      </c>
+      <c r="G14" s="3" t="n">
         <v>10.5</v>
       </c>
-      <c r="H14" s="16" t="n">
+      <c r="H14" s="3" t="n">
         <v>10.3</v>
       </c>
-      <c r="I14" s="3" t="inlineStr"/>
-      <c r="J14" s="16" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="K14" s="3" t="inlineStr"/>
-      <c r="L14" s="16" t="n">
-        <v>1182</v>
-      </c>
-      <c r="M14" s="3" t="n">
-        <v>3</v>
+      <c r="I14" s="3" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="J14" s="3" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="K14" s="3" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="L14" s="3" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="M14" s="8" t="n">
+        <v>18</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>14.8</v>
+        <v>16.8</v>
       </c>
       <c r="O14" s="3" t="n">
         <v>98</v>
       </c>
-      <c r="P14" s="16" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="Q14" s="16" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="R14" s="16" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="S14" s="16" t="n">
-        <v>126.6</v>
-      </c>
-      <c r="T14" s="3" t="inlineStr"/>
+      <c r="P14" s="3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="Q14" s="3" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="R14" s="8" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="S14" s="8" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="T14" s="3" t="n">
+        <v>0.8</v>
+      </c>
       <c r="U14" s="3" t="n">
-        <v>10.6</v>
+        <v>8.6</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="W14" s="16" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="X14" s="3" t="n">
-        <v>6</v>
+        <v>19.5</v>
+      </c>
+      <c r="W14" s="3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="X14" s="8" t="n">
+        <v>16</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>81811</v>
+        <v>28.8</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1683,19 +1707,19 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>1631</v>
-      </c>
-      <c r="D15" s="10" t="n">
+        <v>1638</v>
+      </c>
+      <c r="D15" s="11" t="n">
         <v>26</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>1011.08</v>
+        <v>11</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>118.15</v>
-      </c>
-      <c r="G15" s="16" t="n">
-        <v>15.8</v>
+        <v>18.5</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>15.6</v>
       </c>
       <c r="H15" s="3" t="n">
         <v>7.9</v>
@@ -1704,53 +1728,55 @@
         <v>3.8</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="K15" s="3" t="n">
         <v>21.6</v>
       </c>
-      <c r="L15" s="16" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="M15" s="16" t="n">
-        <v>21.3</v>
+      <c r="L15" s="8" t="n">
+        <v>57.4</v>
+      </c>
+      <c r="M15" s="8" t="n">
+        <v>711.3</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="O15" s="3" t="n">
         <v>99</v>
       </c>
-      <c r="P15" s="16" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Q15" s="16" t="n">
+      <c r="P15" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q15" s="3" t="n">
         <v>25.5</v>
       </c>
-      <c r="R15" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="S15" s="3" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="T15" s="3" t="inlineStr"/>
+      <c r="R15" s="8" t="n">
+        <v>172.6</v>
+      </c>
+      <c r="S15" s="8" t="n">
+        <v>57.9</v>
+      </c>
+      <c r="T15" s="3" t="n">
+        <v>168</v>
+      </c>
       <c r="U15" s="3" t="n">
-        <v>17.9</v>
+        <v>15.8</v>
       </c>
       <c r="V15" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="W15" s="16" t="n">
-        <v>116.5</v>
-      </c>
-      <c r="X15" s="3" t="n">
-        <v>6.4</v>
+        <v>2</v>
+      </c>
+      <c r="W15" s="3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="X15" s="8" t="n">
+        <v>69.40000000000001</v>
       </c>
       <c r="Y15" s="3" t="n">
         <v>67</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>18.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1768,17 +1794,17 @@
       <c r="C16" s="3" t="n">
         <v>2227.1</v>
       </c>
-      <c r="D16" s="9" t="n">
-        <v>128</v>
-      </c>
-      <c r="E16" s="9" t="n">
-        <v>256.8</v>
-      </c>
-      <c r="F16" s="9" t="n">
-        <v>92.3</v>
+      <c r="D16" s="10" t="n">
+        <v>1298</v>
+      </c>
+      <c r="E16" s="10" t="n">
+        <v>56.8</v>
+      </c>
+      <c r="F16" s="10" t="n">
+        <v>9.5</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>79.2</v>
+        <v>71.2</v>
       </c>
       <c r="H16" s="3" t="n">
         <v>39.5</v>
@@ -1787,13 +1813,13 @@
         <v>14.2</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>121.8</v>
+        <v>51.8</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>39.8</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>59.1</v>
+        <v>591.7</v>
       </c>
       <c r="M16" s="3" t="n">
         <v>58.2</v>
@@ -1802,40 +1828,40 @@
         <v>67.90000000000001</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>439.8</v>
+        <v>39</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>11191</v>
+        <v>17119</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>0.1</v>
+        <v>82.2</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>721.1</v>
+        <v>77.7</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>310.1</v>
+        <v>310.8</v>
       </c>
       <c r="U16" s="3" t="n">
         <v>160.9</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>921.2</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>801.9</v>
+        <v>801.7</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>182.2</v>
+        <v>82.2</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>1364</v>
+        <v>2369.8</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>33.4</v>
+        <v>393.9</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1851,74 +1877,74 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>245.9</v>
+        <v>445.9</v>
       </c>
       <c r="D17" s="10" t="n">
         <v>25.6</v>
       </c>
       <c r="E17" s="10" t="n">
-        <v>11.8</v>
+        <v>11.9</v>
       </c>
       <c r="F17" s="10" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="G17" s="16" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>14.2</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>7.9</v>
+        <v>2.9</v>
       </c>
       <c r="I17" s="3" t="n">
         <v>29.4</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>99.8</v>
+        <v>5.8</v>
       </c>
       <c r="K17" s="3" t="inlineStr"/>
-      <c r="L17" s="16" t="n">
+      <c r="L17" s="3" t="n">
         <v>11.8</v>
       </c>
       <c r="M17" s="3" t="n">
         <v>11.6</v>
       </c>
-      <c r="N17" s="16" t="n">
+      <c r="N17" s="8" t="n">
         <v>13.6</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>197.8</v>
-      </c>
-      <c r="P17" s="16" t="n">
+        <v>97.8</v>
+      </c>
+      <c r="P17" s="3" t="n">
         <v>7.4</v>
       </c>
       <c r="Q17" s="3" t="n">
         <v>22.2</v>
       </c>
-      <c r="R17" s="16" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="S17" s="16" t="n">
+      <c r="R17" s="8" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="S17" s="3" t="n">
         <v>15.5</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>162</v>
+        <v>72.2</v>
       </c>
       <c r="U17" s="3" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="V17" s="16" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="V17" s="8" t="n">
         <v>119.6</v>
       </c>
-      <c r="W17" s="16" t="n">
+      <c r="W17" s="8" t="n">
         <v>16.1</v>
       </c>
-      <c r="X17" s="3" t="n">
-        <v>14.4</v>
+      <c r="X17" s="8" t="n">
+        <v>16.5</v>
       </c>
       <c r="Y17" s="3" t="n">
         <v>72.8</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>16.8</v>
+        <v>6.8</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1934,56 +1960,58 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>1435.8</v>
-      </c>
-      <c r="D18" s="10" t="n">
+        <v>455.1</v>
+      </c>
+      <c r="D18" s="11" t="n">
         <v>25.9</v>
       </c>
-      <c r="E18" s="10" t="n">
-        <v>24.44</v>
-      </c>
-      <c r="F18" s="10" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="G18" s="16" t="n">
-        <v>13</v>
-      </c>
-      <c r="H18" s="3" t="inlineStr"/>
+      <c r="E18" s="9" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="G18" s="9" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>12.9</v>
+      </c>
       <c r="I18" s="3" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L18" s="3" t="n">
-        <v>0.4</v>
+        <v>1.7</v>
+      </c>
+      <c r="L18" s="8" t="n">
+        <v>61.5</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>87.59999999999999</v>
-      </c>
-      <c r="N18" s="16" t="n">
-        <v>61</v>
+        <v>84.59999999999999</v>
+      </c>
+      <c r="N18" s="8" t="n">
+        <v>1610.5</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>99</v>
+        <v>19</v>
       </c>
       <c r="P18" s="3" t="n">
-        <v>10.2</v>
+        <v>0.2</v>
       </c>
       <c r="Q18" s="3" t="n">
         <v>25.8</v>
       </c>
-      <c r="R18" s="16" t="n">
-        <v>72.3</v>
-      </c>
-      <c r="S18" s="16" t="n">
-        <v>115.4</v>
+      <c r="R18" s="3" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="S18" s="8" t="n">
+        <v>101.4</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>1406</v>
+        <v>9</v>
       </c>
       <c r="U18" s="3" t="n">
         <v>17.9</v>
@@ -1991,17 +2019,17 @@
       <c r="V18" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="W18" s="3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="X18" s="16" t="n">
-        <v>15.6</v>
+      <c r="W18" s="8" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="X18" s="3" t="n">
+        <v>14.6</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>13791</v>
+        <v>510.1</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>110.9</v>
+        <v>11.6</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -2017,69 +2045,73 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>1531.1</v>
-      </c>
-      <c r="D19" s="10" t="n">
+        <v>95311.10000000001</v>
+      </c>
+      <c r="D19" s="11" t="n">
         <v>28</v>
       </c>
-      <c r="E19" s="10" t="n">
+      <c r="E19" s="11" t="n">
         <v>10.6</v>
       </c>
-      <c r="F19" s="10" t="n">
+      <c r="F19" s="11" t="n">
         <v>19.3</v>
       </c>
-      <c r="G19" s="3" t="inlineStr"/>
-      <c r="H19" s="3" t="inlineStr"/>
+      <c r="G19" s="11" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="H19" s="3" t="n">
+        <v>7.2</v>
+      </c>
       <c r="I19" s="3" t="n">
         <v>3.3</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>3.2</v>
+        <v>5.2</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L19" s="16" t="n">
-        <v>211</v>
-      </c>
-      <c r="M19" s="16" t="n">
-        <v>711</v>
-      </c>
-      <c r="N19" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="L19" s="8" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="M19" s="8" t="n">
+        <v>111</v>
+      </c>
+      <c r="N19" s="3" t="n">
         <v>13</v>
       </c>
       <c r="O19" s="3" t="n">
         <v>98</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>10.4</v>
+        <v>0.4</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>261.1</v>
-      </c>
-      <c r="R19" s="16" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="R19" s="3" t="n">
         <v>18</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>24.2</v>
+        <v>16.2</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="U19" s="3" t="n">
-        <v>0.3</v>
+        <v>94.8</v>
+      </c>
+      <c r="U19" s="8" t="n">
+        <v>7.2</v>
       </c>
       <c r="V19" s="3" t="n">
         <v>21.2</v>
       </c>
-      <c r="W19" s="3" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="X19" s="16" t="n">
+      <c r="W19" s="8" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="X19" s="8" t="n">
         <v>18.6</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>142</v>
+        <v>74</v>
       </c>
       <c r="Z19" s="3" t="n">
         <v>16.6</v>
@@ -2098,69 +2130,77 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>592.2</v>
-      </c>
-      <c r="D20" s="10" t="n">
+        <v>542.2</v>
+      </c>
+      <c r="D20" s="11" t="n">
         <v>28.2</v>
       </c>
-      <c r="E20" s="10" t="n">
-        <v>-5.3</v>
-      </c>
-      <c r="F20" s="11" t="n">
-        <v>11.43</v>
-      </c>
-      <c r="G20" s="16" t="n">
+      <c r="E20" s="9" t="n">
+        <v>-4.4</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="G20" s="3" t="n">
         <v>17.8</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="I20" s="16" t="n">
-        <v>733.5</v>
+        <v>6.9</v>
+      </c>
+      <c r="I20" s="8" t="n">
+        <v>33.5</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="K20" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" s="3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="M20" s="16" t="n">
-        <v>8818.1</v>
-      </c>
-      <c r="N20" s="3" t="inlineStr"/>
+        <v>5.9</v>
+      </c>
+      <c r="K20" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="L20" s="8" t="n">
+        <v>111.2</v>
+      </c>
+      <c r="M20" s="8" t="n">
+        <v>221.2</v>
+      </c>
+      <c r="N20" s="8" t="n">
+        <v>811</v>
+      </c>
       <c r="O20" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="P20" s="3" t="inlineStr"/>
+        <v>98.2</v>
+      </c>
+      <c r="P20" s="3" t="n">
+        <v>0.9</v>
+      </c>
       <c r="Q20" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="R20" s="3" t="inlineStr"/>
-      <c r="S20" s="16" t="n">
-        <v>151.3</v>
+      <c r="R20" s="3" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="S20" s="8" t="n">
+        <v>11.6</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>140.5</v>
+        <v>40.5</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>92.40000000000001</v>
+        <v>22.4</v>
       </c>
       <c r="V20" s="3" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="W20" s="3" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="X20" s="16" t="n">
-        <v>2298.2</v>
+        <v>22.2</v>
+      </c>
+      <c r="W20" s="8" t="n">
+        <v>89.5</v>
+      </c>
+      <c r="X20" s="8" t="n">
+        <v>29.9</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="Z20" s="3" t="inlineStr"/>
+        <v>721</v>
+      </c>
+      <c r="Z20" s="3" t="n">
+        <v>2.6</v>
+      </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
           <t>13</t>
@@ -2177,59 +2217,61 @@
       <c r="C21" s="3" t="n">
         <v>382.4</v>
       </c>
-      <c r="D21" s="10" t="n">
+      <c r="D21" s="11" t="n">
         <v>24.8</v>
       </c>
-      <c r="E21" s="10" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="F21" s="10" t="n">
+      <c r="E21" s="11" t="n">
         <v>12.6</v>
       </c>
-      <c r="G21" s="16" t="n">
+      <c r="F21" s="11" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="G21" s="11" t="n">
         <v>12.1</v>
       </c>
-      <c r="H21" s="3" t="n">
-        <v>42.1</v>
+      <c r="H21" s="8" t="n">
+        <v>10.9</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>12.4</v>
+        <v>2.4</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>0.3</v>
+        <v>2.8</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="M21" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N21" s="3" t="inlineStr"/>
+        <v>11.3</v>
+      </c>
+      <c r="M21" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="N21" s="8" t="n">
+        <v>54.9</v>
+      </c>
       <c r="O21" s="3" t="n">
         <v>99</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>10.2</v>
+        <v>0.2</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>22.4</v>
+        <v>25.6</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="S21" s="16" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="S21" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>1931</v>
+        <v>51</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="V21" s="16" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="V21" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="W21" s="3" t="n">
@@ -2239,10 +2281,10 @@
         <v>20</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>187</v>
+        <v>87</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
@@ -2258,72 +2300,76 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>1429</v>
-      </c>
-      <c r="D22" s="10" t="n">
+        <v>194828.8</v>
+      </c>
+      <c r="D22" s="11" t="n">
         <v>25.2</v>
       </c>
-      <c r="E22" s="14" t="inlineStr"/>
+      <c r="E22" s="11" t="n">
+        <v>12.1</v>
+      </c>
       <c r="F22" s="11" t="n">
-        <v>81.90000000000001</v>
-      </c>
-      <c r="G22" s="3" t="n">
-        <v>13.1</v>
+        <v>18.6</v>
+      </c>
+      <c r="G22" s="8" t="n">
+        <v>13.9</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="I22" s="3" t="inlineStr"/>
+        <v>85.90000000000001</v>
+      </c>
+      <c r="I22" s="3" t="n">
+        <v>20.7</v>
+      </c>
       <c r="J22" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="K22" s="16" t="n">
-        <v>8</v>
+        <v>19.8</v>
+      </c>
+      <c r="K22" s="3" t="n">
+        <v>9</v>
       </c>
       <c r="L22" s="3" t="n">
         <v>11.2</v>
       </c>
-      <c r="M22" s="16" t="n">
+      <c r="M22" s="3" t="n">
         <v>12.2</v>
       </c>
-      <c r="N22" s="16" t="n">
+      <c r="N22" s="3" t="n">
         <v>14.1</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>99</v>
+        <v>992</v>
       </c>
       <c r="P22" s="3" t="n">
-        <v>10.2</v>
+        <v>0.2</v>
       </c>
       <c r="Q22" s="3" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="R22" s="16" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R22" s="3" t="n">
         <v>16.2</v>
       </c>
-      <c r="S22" s="16" t="n">
-        <v>194.9</v>
+      <c r="S22" s="8" t="n">
+        <v>49.4</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>443454.4</v>
+        <v>49.5</v>
       </c>
       <c r="U22" s="3" t="n">
-        <v>44.8</v>
-      </c>
-      <c r="V22" s="16" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="V22" s="3" t="n">
         <v>22.5</v>
       </c>
-      <c r="W22" s="16" t="n">
+      <c r="W22" s="8" t="n">
         <v>15.6</v>
       </c>
-      <c r="X22" s="16" t="n">
-        <v>13.9</v>
+      <c r="X22" s="3" t="n">
+        <v>13.8</v>
       </c>
       <c r="Y22" s="3" t="n">
-        <v>50.5</v>
+        <v>505.9</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>113.4</v>
+        <v>1199.7</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2339,72 +2385,76 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>23203.1</v>
+        <v>12320.8</v>
       </c>
       <c r="D23" s="10" t="n">
-        <v>132.1</v>
-      </c>
-      <c r="E23" s="9" t="n">
-        <v>551.4</v>
-      </c>
-      <c r="F23" s="9" t="n">
-        <v>94.90000000000001</v>
-      </c>
-      <c r="G23" s="11" t="n">
-        <v>75.09999999999999</v>
+        <v>112.1</v>
+      </c>
+      <c r="E23" s="10" t="n">
+        <v>201.5</v>
+      </c>
+      <c r="F23" s="10" t="n">
+        <v>94.40000000000001</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>75.7</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>40.6</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>141.5</v>
+        <v>1.4</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>20.8</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>101.3</v>
+        <v>5.9</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="M23" s="3" t="n">
         <v>61.8</v>
       </c>
-      <c r="N23" s="3" t="inlineStr"/>
+      <c r="N23" s="3" t="n">
+        <v>711.5</v>
+      </c>
       <c r="O23" s="3" t="n">
-        <v>2493</v>
-      </c>
-      <c r="P23" s="3" t="inlineStr"/>
+        <v>293</v>
+      </c>
+      <c r="P23" s="3" t="n">
+        <v>11.9</v>
+      </c>
       <c r="Q23" s="3" t="n">
-        <v>1128.9</v>
+        <v>128.9</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>78.09999999999999</v>
+        <v>781.7</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>235.7</v>
+        <v>2351.7</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>188.5</v>
+        <v>88.5</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>1106.7</v>
+        <v>106.7</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>185.5</v>
+        <v>85.5</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>26.3</v>
+        <v>86.2</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>1341.5</v>
+        <v>341.5</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>141</v>
+        <v>541</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2422,70 +2472,74 @@
       <c r="C24" s="3" t="n">
         <v>484.1</v>
       </c>
-      <c r="D24" s="10" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="E24" s="10" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="F24" s="10" t="n">
+      <c r="D24" s="11" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="E24" s="11" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="F24" s="11" t="n">
         <v>18.9</v>
       </c>
-      <c r="G24" s="10" t="n">
+      <c r="G24" s="11" t="n">
         <v>15.1</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>18.1</v>
+        <v>8.1</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>29.1</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>76.09999999999999</v>
-      </c>
-      <c r="K24" s="3" t="inlineStr"/>
+        <v>7.1</v>
+      </c>
+      <c r="K24" s="3" t="n">
+        <v>1.8</v>
+      </c>
       <c r="L24" s="3" t="n">
         <v>12.5</v>
       </c>
-      <c r="M24" s="16" t="n">
+      <c r="M24" s="3" t="n">
         <v>12.4</v>
       </c>
-      <c r="N24" s="3" t="inlineStr"/>
+      <c r="N24" s="3" t="n">
+        <v>4.1</v>
+      </c>
       <c r="O24" s="3" t="n">
         <v>98.59999999999999</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>0.3</v>
+        <v>3.4</v>
       </c>
       <c r="Q24" s="3" t="n">
         <v>25.8</v>
       </c>
-      <c r="R24" s="16" t="n">
+      <c r="R24" s="3" t="n">
         <v>17.6</v>
       </c>
-      <c r="S24" s="16" t="n">
-        <v>15.6</v>
+      <c r="S24" s="3" t="n">
+        <v>129.6</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>1247.9</v>
-      </c>
-      <c r="U24" s="16" t="n">
-        <v>197.5</v>
+        <v>22.9</v>
+      </c>
+      <c r="U24" s="8" t="n">
+        <v>177.7</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>91.3</v>
+        <v>21.3</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>41.1</v>
-      </c>
-      <c r="X24" s="16" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="X24" s="8" t="n">
         <v>17.2</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>168.9</v>
+        <v>168.3</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2501,64 +2555,76 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>1488.9</v>
-      </c>
-      <c r="D25" s="16" t="n">
+        <v>428.9</v>
+      </c>
+      <c r="D25" s="11" t="n">
         <v>25.9</v>
       </c>
-      <c r="E25" s="14" t="inlineStr"/>
-      <c r="F25" s="3" t="n">
+      <c r="E25" s="11" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="F25" s="11" t="n">
         <v>17.8</v>
       </c>
-      <c r="G25" s="3" t="inlineStr"/>
-      <c r="H25" s="3" t="inlineStr"/>
-      <c r="I25" s="3" t="inlineStr"/>
-      <c r="J25" s="3" t="inlineStr"/>
+      <c r="G25" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="H25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="3" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="J25" s="3" t="n">
+        <v>4.7</v>
+      </c>
       <c r="K25" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="L25" s="16" t="n">
-        <v>107.9</v>
+        <v>6</v>
+      </c>
+      <c r="L25" s="3" t="n">
+        <v>10.7</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="N25" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="O25" s="3" t="inlineStr"/>
+        <v>8.9</v>
+      </c>
+      <c r="N25" s="8" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="O25" s="3" t="n">
+        <v>18</v>
+      </c>
       <c r="P25" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="Q25" s="16" t="n">
-        <v>29.1</v>
+        <v>0.9</v>
+      </c>
+      <c r="Q25" s="3" t="n">
+        <v>14.6</v>
       </c>
       <c r="R25" s="3" t="n">
-        <v>0.7</v>
+        <v>24.1</v>
       </c>
       <c r="S25" s="3" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>549.3</v>
-      </c>
-      <c r="U25" s="16" t="n">
-        <v>151.8</v>
+        <v>6.9</v>
+      </c>
+      <c r="U25" s="8" t="n">
+        <v>13.8</v>
       </c>
       <c r="V25" s="3" t="n">
         <v>21.3</v>
       </c>
-      <c r="W25" s="16" t="n">
-        <v>16.9</v>
+      <c r="W25" s="8" t="n">
+        <v>116.9</v>
       </c>
       <c r="X25" s="3" t="n">
-        <v>16.8</v>
+        <v>116.8</v>
       </c>
       <c r="Y25" s="3" t="n">
         <v>66</v>
       </c>
       <c r="Z25" s="3" t="n">
-        <v>81.59999999999999</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
@@ -2574,52 +2640,58 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>1349.9</v>
-      </c>
-      <c r="D26" s="3" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="E26" s="3" t="n">
+        <v>349.9</v>
+      </c>
+      <c r="D26" s="11" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="E26" s="11" t="n">
         <v>9.6</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="G26" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="G26" s="11" t="n">
         <v>14.8</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="I26" s="16" t="n">
-        <v>25.6</v>
+        <v>6.6</v>
+      </c>
+      <c r="I26" s="3" t="n">
+        <v>12.3</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>18.5</v>
+        <v>8.9</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="L26" s="3" t="inlineStr"/>
-      <c r="M26" s="16" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="N26" s="3" t="inlineStr"/>
+        <v>8.9</v>
+      </c>
+      <c r="L26" s="8" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="M26" s="8" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="N26" s="3" t="n">
+        <v>1.1</v>
+      </c>
       <c r="O26" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="P26" s="3" t="inlineStr"/>
+        <v>98.09999999999999</v>
+      </c>
+      <c r="P26" s="3" t="n">
+        <v>2.4</v>
+      </c>
       <c r="Q26" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="R26" s="16" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="S26" s="16" t="n">
-        <v>547.4</v>
+      <c r="R26" s="3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="S26" s="3" t="n">
+        <v>15.7</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>163.5</v>
+        <v>63.5</v>
       </c>
       <c r="U26" s="3" t="n">
         <v>9.199999999999999</v>
@@ -2634,10 +2706,10 @@
         <v>14.2</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>512.1</v>
+        <v>194</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>111.8</v>
+        <v>211.8</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2656,65 +2728,73 @@
         <v>340.2</v>
       </c>
       <c r="D27" s="11" t="n">
-        <v>21.14</v>
-      </c>
-      <c r="E27" s="16" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="F27" s="14" t="inlineStr"/>
-      <c r="G27" s="11" t="n">
-        <v>114.4</v>
-      </c>
-      <c r="H27" s="3" t="inlineStr"/>
+        <v>24.5</v>
+      </c>
+      <c r="E27" s="11" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="F27" s="11" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="H27" s="3" t="n">
+        <v>82.40000000000001</v>
+      </c>
       <c r="I27" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="J27" s="16" t="n">
-        <v>15.1</v>
+      <c r="J27" s="3" t="n">
+        <v>2.9</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="L27" s="3" t="n">
-        <v>42.4</v>
-      </c>
-      <c r="M27" s="16" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="L27" s="8" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="M27" s="3" t="n">
         <v>12.2</v>
       </c>
-      <c r="N27" s="3" t="inlineStr"/>
+      <c r="N27" s="3" t="n">
+        <v>44</v>
+      </c>
       <c r="O27" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="P27" s="3" t="inlineStr"/>
-      <c r="Q27" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="P27" s="3" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="Q27" s="3" t="n">
         <v>17.6</v>
       </c>
-      <c r="R27" s="16" t="n">
-        <v>161.8</v>
+      <c r="R27" s="8" t="n">
+        <v>1618.1</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>11.7</v>
+        <v>11.2</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>186</v>
+        <v>56</v>
       </c>
       <c r="U27" s="3" t="n">
         <v>13</v>
       </c>
       <c r="V27" s="3" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="W27" s="16" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="X27" s="16" t="n">
-        <v>187.5</v>
+        <v>87.40000000000001</v>
+      </c>
+      <c r="W27" s="3" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="X27" s="8" t="n">
+        <v>15859.5</v>
       </c>
       <c r="Y27" s="3" t="n">
-        <v>113</v>
+        <v>913</v>
       </c>
       <c r="Z27" s="3" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
@@ -2730,72 +2810,76 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>15139.5</v>
-      </c>
-      <c r="D28" s="3" t="n">
-        <v>27</v>
+        <v>313.3</v>
+      </c>
+      <c r="D28" s="11" t="n">
+        <v>23</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>11.15</v>
+        <v>15.6</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="G28" s="11" t="n">
-        <v>15.4</v>
+        <v>19.3</v>
+      </c>
+      <c r="G28" s="9" t="n">
+        <v>15.1</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>18.7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0.2</v>
+        <v>2.4</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="K28" s="3" t="n">
         <v>5.5</v>
       </c>
-      <c r="L28" s="16" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="M28" s="16" t="n">
-        <v>113.3</v>
-      </c>
-      <c r="N28" s="16" t="n">
-        <v>13.2</v>
+      <c r="L28" s="3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="M28" s="8" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="N28" s="8" t="n">
+        <v>12.1</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="Q28" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q28" s="8" t="n">
         <v>22.9</v>
       </c>
-      <c r="R28" s="16" t="n">
+      <c r="R28" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="S28" s="16" t="n">
-        <v>99</v>
+      <c r="S28" s="3" t="n">
+        <v>19</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>168</v>
+        <v>68</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="V28" s="3" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="W28" s="3" t="inlineStr"/>
-      <c r="X28" s="3" t="inlineStr"/>
+        <v>8.800000000000001</v>
+      </c>
+      <c r="V28" s="8" t="n">
+        <v>645.4</v>
+      </c>
+      <c r="W28" s="3" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="X28" s="8" t="n">
+        <v>11</v>
+      </c>
       <c r="Y28" s="3" t="n">
-        <v>121</v>
+        <v>1891</v>
       </c>
       <c r="Z28" s="3" t="n">
-        <v>0.8</v>
+        <v>11.8</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -2814,67 +2898,73 @@
         <v>523.3</v>
       </c>
       <c r="D29" s="11" t="n">
-        <v>48.28</v>
-      </c>
-      <c r="E29" s="3" t="n">
-        <v>12.1</v>
+        <v>28.3</v>
+      </c>
+      <c r="E29" s="11" t="n">
+        <v>10.7</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="G29" s="11" t="n">
-        <v>48.4</v>
+        <v>19.5</v>
+      </c>
+      <c r="G29" s="8" t="n">
+        <v>18.1</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.3</v>
+        <v>7.2</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>3.8</v>
       </c>
-      <c r="J29" s="3" t="n">
-        <v>16.2</v>
+      <c r="J29" s="8" t="n">
+        <v>25.2</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L29" s="3" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="M29" s="16" t="n">
-        <v>910.5</v>
-      </c>
-      <c r="N29" s="16" t="n">
-        <v>122.4</v>
+        <v>0</v>
+      </c>
+      <c r="L29" s="8" t="n">
+        <v>109.7</v>
+      </c>
+      <c r="M29" s="3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="N29" s="3" t="n">
+        <v>12.4</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>96.90000000000001</v>
+        <v>196</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="Q29" s="16" t="n">
-        <v>27</v>
-      </c>
-      <c r="R29" s="16" t="n">
-        <v>181.7</v>
-      </c>
-      <c r="S29" s="16" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="Q29" s="8" t="n">
+        <v>217</v>
+      </c>
+      <c r="R29" s="8" t="n">
+        <v>517.1</v>
+      </c>
+      <c r="S29" s="3" t="n">
         <v>17</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>47.8</v>
-      </c>
-      <c r="U29" s="3" t="inlineStr"/>
+        <v>57.8</v>
+      </c>
+      <c r="U29" s="3" t="n">
+        <v>18.6</v>
+      </c>
       <c r="V29" s="3" t="n">
         <v>22.8</v>
       </c>
-      <c r="W29" s="3" t="inlineStr"/>
-      <c r="X29" s="3" t="inlineStr"/>
+      <c r="W29" s="3" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="X29" s="8" t="n">
+        <v>12.7</v>
+      </c>
       <c r="Y29" s="3" t="n">
-        <v>160</v>
+        <v>60</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>111.2</v>
+        <v>111.9</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
@@ -2890,73 +2980,73 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>22848.1</v>
-      </c>
-      <c r="D30" s="9" t="n">
+        <v>22848.3</v>
+      </c>
+      <c r="D30" s="11" t="n">
         <v>131.2</v>
       </c>
-      <c r="E30" s="9" t="n">
-        <v>152.9</v>
-      </c>
-      <c r="F30" s="9" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="G30" s="3" t="n">
+      <c r="E30" s="11" t="n">
+        <v>52.2</v>
+      </c>
+      <c r="F30" s="11" t="n">
+        <v>91.7</v>
+      </c>
+      <c r="G30" s="11" t="n">
         <v>79.09999999999999</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>26</v>
+        <v>216</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>113.8</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>1119.5</v>
+        <v>119.5</v>
       </c>
       <c r="K30" s="3" t="n">
         <v>113.5</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>52.2</v>
+        <v>51.2</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>56.1</v>
+        <v>56.7</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>0.6</v>
+        <v>6.5</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>1489</v>
+        <v>9489</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>113.2</v>
+        <v>1113.2</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>86.7</v>
+        <v>851.7</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>184.4</v>
+        <v>844.7</v>
       </c>
       <c r="T30" s="3" t="n">
         <v>314.8</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>55.9</v>
+        <v>35.4</v>
       </c>
       <c r="V30" s="3" t="n">
         <v>99.5</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>181.9</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="X30" s="3" t="n">
         <v>83.2</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>1365</v>
+        <v>365</v>
       </c>
       <c r="Z30" s="3" t="n">
         <v>35</v>
@@ -2975,67 +3065,73 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>1452</v>
-      </c>
-      <c r="D31" s="10" t="n">
+        <v>1532</v>
+      </c>
+      <c r="D31" s="11" t="n">
         <v>26.2</v>
       </c>
-      <c r="E31" s="10" t="n">
+      <c r="E31" s="11" t="n">
         <v>10.4</v>
       </c>
-      <c r="F31" s="10" t="n">
+      <c r="F31" s="11" t="n">
         <v>18.3</v>
       </c>
-      <c r="G31" s="10" t="n">
-        <v>15.8</v>
+      <c r="G31" s="8" t="n">
+        <v>58.4</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>72.09999999999999</v>
-      </c>
-      <c r="I31" s="3" t="inlineStr"/>
+        <v>72.40000000000001</v>
+      </c>
+      <c r="I31" s="3" t="n">
+        <v>2.8</v>
+      </c>
       <c r="J31" s="3" t="n">
         <v>39.1</v>
       </c>
-      <c r="K31" s="3" t="inlineStr"/>
-      <c r="L31" s="16" t="n">
+      <c r="K31" s="3" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="L31" s="8" t="n">
         <v>11.5</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="N31" s="3" t="inlineStr"/>
+        <v>14.2</v>
+      </c>
+      <c r="N31" s="8" t="n">
+        <v>412.8</v>
+      </c>
       <c r="O31" s="3" t="n">
         <v>97.8</v>
       </c>
-      <c r="P31" s="16" t="n">
-        <v>40.4</v>
+      <c r="P31" s="3" t="n">
+        <v>89.40000000000001</v>
       </c>
       <c r="Q31" s="3" t="n">
         <v>22.6</v>
       </c>
-      <c r="R31" s="16" t="n">
-        <v>179.3</v>
-      </c>
-      <c r="S31" s="16" t="n">
+      <c r="R31" s="8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="S31" s="8" t="n">
         <v>16.9</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>63</v>
-      </c>
-      <c r="U31" s="16" t="n">
-        <v>11.1</v>
+        <v>13.1</v>
+      </c>
+      <c r="U31" s="3" t="n">
+        <v>211.1</v>
       </c>
       <c r="V31" s="3" t="n">
         <v>19.9</v>
       </c>
-      <c r="W31" s="16" t="n">
+      <c r="W31" s="8" t="n">
         <v>16.4</v>
       </c>
-      <c r="X31" s="16" t="n">
+      <c r="X31" s="8" t="n">
         <v>16.6</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>730</v>
+        <v>13</v>
       </c>
       <c r="Z31" s="3" t="n">
         <v>7</v>
@@ -3054,71 +3150,77 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>520.8</v>
-      </c>
-      <c r="D32" s="10" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="E32" s="10" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="F32" s="10" t="n">
+        <v>528</v>
+      </c>
+      <c r="D32" s="11" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="E32" s="11" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="F32" s="11" t="n">
         <v>19.5</v>
       </c>
-      <c r="G32" s="11" t="n">
-        <v>21.8</v>
+      <c r="G32" s="8" t="n">
+        <v>17.7</v>
       </c>
       <c r="H32" s="3" t="n">
         <v>16.6</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>3.7</v>
+        <v>6.1</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>61.2</v>
+        <v>5</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="L32" s="16" t="n">
-        <v>1090.5</v>
-      </c>
-      <c r="M32" s="3" t="n">
-        <v>103.3</v>
-      </c>
-      <c r="N32" s="3" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="L32" s="8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="M32" s="8" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="N32" s="3" t="n">
+        <v>11.2</v>
+      </c>
       <c r="O32" s="3" t="n">
-        <v>97.8</v>
+        <v>49</v>
       </c>
       <c r="P32" s="3" t="n">
-        <v>10.6</v>
+        <v>1</v>
       </c>
       <c r="Q32" s="3" t="n">
-        <v>29.8</v>
-      </c>
-      <c r="R32" s="16" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="R32" s="3" t="n">
         <v>18.2</v>
       </c>
-      <c r="S32" s="3" t="n">
+      <c r="S32" s="8" t="n">
         <v>18.8</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>162.5</v>
-      </c>
-      <c r="U32" s="3" t="inlineStr"/>
-      <c r="V32" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="U32" s="3" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="V32" s="8" t="n">
         <v>21.4</v>
       </c>
       <c r="W32" s="3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="X32" s="16" t="n">
-        <v>27.9</v>
+        <v>17.6</v>
+      </c>
+      <c r="X32" s="8" t="n">
+        <v>17.9</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>70.90000000000001</v>
-      </c>
-      <c r="Z32" s="3" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="Z32" s="3" t="n">
+        <v>16</v>
+      </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
           <t>21</t>
@@ -3135,62 +3237,74 @@
       <c r="C33" s="3" t="n">
         <v>349.1</v>
       </c>
-      <c r="D33" s="3" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="E33" s="3" t="n">
-        <v>28.8</v>
+      <c r="D33" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="E33" s="11" t="n">
+        <v>12.8</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>48.54</v>
-      </c>
-      <c r="G33" s="11" t="n">
-        <v>211.1</v>
+        <v>18.9</v>
+      </c>
+      <c r="G33" s="8" t="n">
+        <v>11.6</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="I33" s="3" t="inlineStr"/>
+        <v>1.9</v>
+      </c>
+      <c r="I33" s="8" t="n">
+        <v>95.90000000000001</v>
+      </c>
       <c r="J33" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K33" s="3" t="inlineStr"/>
+        <v>2.4</v>
+      </c>
+      <c r="K33" s="3" t="n">
+        <v>6.8</v>
+      </c>
       <c r="L33" s="3" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="M33" s="3" t="inlineStr"/>
-      <c r="N33" s="3" t="inlineStr"/>
+        <v>19.9</v>
+      </c>
+      <c r="M33" s="3" t="n">
+        <v>81.5</v>
+      </c>
+      <c r="N33" s="8" t="n">
+        <v>18.6</v>
+      </c>
       <c r="O33" s="3" t="n">
-        <v>98.8</v>
+        <v>980.8</v>
       </c>
       <c r="P33" s="3" t="n">
         <v>10.9</v>
       </c>
-      <c r="Q33" s="3" t="n">
-        <v>204.3</v>
+      <c r="Q33" s="8" t="n">
+        <v>203.5</v>
       </c>
       <c r="R33" s="3" t="n">
-        <v>43.8</v>
-      </c>
-      <c r="S33" s="16" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="S33" s="8" t="n">
         <v>18.9</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>79.90000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="U33" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="V33" s="3" t="inlineStr"/>
+      <c r="V33" s="8" t="n">
+        <v>19.9</v>
+      </c>
       <c r="W33" s="3" t="n">
-        <v>44.4</v>
-      </c>
-      <c r="X33" s="3" t="inlineStr"/>
+        <v>17.9</v>
+      </c>
+      <c r="X33" s="3" t="n">
+        <v>1.8</v>
+      </c>
       <c r="Y33" s="3" t="n">
-        <v>189</v>
+        <v>81</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3206,72 +3320,76 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>329.1</v>
-      </c>
-      <c r="D34" s="3" t="n">
-        <v>23.3</v>
+        <v>329.9</v>
+      </c>
+      <c r="D34" s="11" t="n">
+        <v>23.1</v>
       </c>
       <c r="E34" s="11" t="n">
-        <v>44.3</v>
-      </c>
-      <c r="F34" s="16" t="n">
-        <v>19</v>
-      </c>
-      <c r="G34" s="3" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="H34" s="16" t="n">
-        <v>14.1</v>
+        <v>14.7</v>
+      </c>
+      <c r="F34" s="11" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="G34" s="11" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="H34" s="3" t="n">
+        <v>19.7</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0.2</v>
+        <v>21.5</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0.9</v>
+        <v>18.9</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="L34" s="16" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="L34" s="8" t="n">
         <v>16</v>
       </c>
-      <c r="M34" s="16" t="n">
+      <c r="M34" s="3" t="n">
         <v>15.9</v>
       </c>
-      <c r="N34" s="3" t="inlineStr"/>
+      <c r="N34" s="8" t="n">
+        <v>7.8</v>
+      </c>
       <c r="O34" s="3" t="n">
         <v>99</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="Q34" s="16" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q34" s="3" t="n">
         <v>21.8</v>
       </c>
-      <c r="R34" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="S34" s="16" t="n">
-        <v>181.8</v>
+      <c r="R34" s="8" t="n">
+        <v>81.90000000000001</v>
+      </c>
+      <c r="S34" s="8" t="n">
+        <v>18.7</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>72.8</v>
+        <v>72</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>29.6</v>
-      </c>
-      <c r="V34" s="16" t="n">
-        <v>1287.1</v>
-      </c>
-      <c r="W34" s="16" t="n">
+        <v>72.59999999999999</v>
+      </c>
+      <c r="V34" s="8" t="n">
+        <v>87.7</v>
+      </c>
+      <c r="W34" s="8" t="n">
         <v>16.8</v>
       </c>
-      <c r="X34" s="3" t="inlineStr"/>
+      <c r="X34" s="8" t="n">
+        <v>81</v>
+      </c>
       <c r="Y34" s="3" t="n">
-        <v>893</v>
+        <v>82</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>1.8</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3287,19 +3405,19 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>1506.7</v>
-      </c>
-      <c r="D35" s="3" t="n">
+        <v>5056.7</v>
+      </c>
+      <c r="D35" s="11" t="n">
         <v>26.8</v>
       </c>
-      <c r="E35" s="3" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="F35" s="16" t="n">
+      <c r="E35" s="11" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="F35" s="11" t="n">
         <v>19.8</v>
       </c>
       <c r="G35" s="11" t="n">
-        <v>15.4</v>
+        <v>14</v>
       </c>
       <c r="H35" s="3" t="n">
         <v>9.5</v>
@@ -3308,48 +3426,52 @@
         <v>3.6</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>51.5</v>
+        <v>21.1</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L35" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="M35" s="16" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="N35" s="3" t="inlineStr"/>
+      <c r="M35" s="3" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="N35" s="8" t="n">
+        <v>84.8</v>
+      </c>
       <c r="O35" s="3" t="n">
-        <v>49</v>
-      </c>
-      <c r="P35" s="3" t="inlineStr"/>
-      <c r="Q35" s="3" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="R35" s="16" t="n">
-        <v>147.6</v>
+        <v>1891</v>
+      </c>
+      <c r="P35" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q35" s="8" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>17.6</v>
       </c>
       <c r="S35" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>572</v>
-      </c>
-      <c r="U35" s="16" t="n">
+        <v>252</v>
+      </c>
+      <c r="U35" s="8" t="n">
         <v>12.8</v>
       </c>
       <c r="V35" s="3" t="n">
         <v>20.8</v>
       </c>
-      <c r="W35" s="16" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="X35" s="16" t="n">
-        <v>4116.8</v>
+      <c r="W35" s="8" t="n">
+        <v>67.90000000000001</v>
+      </c>
+      <c r="X35" s="8" t="n">
+        <v>16.8</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>68.5</v>
+        <v>168.5</v>
       </c>
       <c r="Z35" s="3" t="n">
         <v>8</v>
@@ -3371,15 +3493,15 @@
         <v>535.5</v>
       </c>
       <c r="D36" s="11" t="n">
-        <v>56.3</v>
+        <v>26.5</v>
       </c>
       <c r="E36" s="11" t="n">
-        <v>0.9</v>
+        <v>10.7</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>81.3</v>
-      </c>
-      <c r="G36" s="16" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="G36" s="11" t="n">
         <v>15.9</v>
       </c>
       <c r="H36" s="3" t="n">
@@ -3392,51 +3514,51 @@
         <v>5.9</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L36" s="16" t="n">
-        <v>101.6</v>
-      </c>
-      <c r="M36" s="16" t="n">
-        <v>110.5</v>
-      </c>
-      <c r="N36" s="3" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L36" s="3" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="M36" s="3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="N36" s="8" t="n">
+        <v>12.6</v>
+      </c>
       <c r="O36" s="3" t="n">
         <v>199</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>18.1</v>
+        <v>0.1</v>
       </c>
       <c r="Q36" s="3" t="n">
         <v>25.5</v>
       </c>
-      <c r="R36" s="16" t="n">
-        <v>71.09999999999999</v>
-      </c>
-      <c r="S36" s="3" t="n">
-        <v>14.8</v>
+      <c r="R36" s="3" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="S36" s="8" t="n">
+        <v>65.8</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>685</v>
-      </c>
-      <c r="U36" s="16" t="n">
-        <v>27.9</v>
+        <v>115</v>
+      </c>
+      <c r="U36" s="8" t="n">
+        <v>17.9</v>
       </c>
       <c r="V36" s="3" t="n">
         <v>20.6</v>
       </c>
-      <c r="W36" s="16" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="X36" s="16" t="n">
-        <v>13.8</v>
+      <c r="W36" s="8" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="X36" s="3" t="n">
+        <v>1.9</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z36" s="3" t="n">
-        <v>1110.8</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="Z36" s="3" t="inlineStr"/>
       <c r="AA36" s="3" t="inlineStr">
         <is>
           <t>25</t>
@@ -3451,72 +3573,76 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>2240.4</v>
-      </c>
-      <c r="D37" s="9" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="E37" s="9" t="n">
-        <v>160.9</v>
-      </c>
-      <c r="F37" s="9" t="n">
-        <v>991.7</v>
-      </c>
-      <c r="G37" s="3" t="n">
-        <v>1.6</v>
+        <v>2290.9</v>
+      </c>
+      <c r="D37" s="10" t="n">
+        <v>128.5</v>
+      </c>
+      <c r="E37" s="10" t="n">
+        <v>60.9</v>
+      </c>
+      <c r="F37" s="10" t="n">
+        <v>99.2</v>
+      </c>
+      <c r="G37" s="9" t="n">
+        <v>65.7</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>146</v>
+        <v>46</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>116.1</v>
+        <v>167.9</v>
       </c>
       <c r="J37" s="3" t="n">
         <v>20.8</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>81.5</v>
+        <v>8.5</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>165</v>
-      </c>
-      <c r="M37" s="3" t="inlineStr"/>
-      <c r="N37" s="3" t="inlineStr"/>
+        <v>63</v>
+      </c>
+      <c r="M37" s="3" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="N37" s="3" t="n">
+        <v>74.59999999999999</v>
+      </c>
       <c r="O37" s="3" t="n">
-        <v>2492</v>
+        <v>492</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>115.5</v>
+        <v>115.9</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>82.90000000000001</v>
+        <v>811.9</v>
       </c>
       <c r="S37" s="3" t="n">
         <v>88</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>216.9</v>
+        <v>116.9</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>54.5</v>
+        <v>554.5</v>
       </c>
       <c r="V37" s="3" t="n">
-        <v>1100.9</v>
+        <v>100.9</v>
       </c>
       <c r="W37" s="3" t="n">
-        <v>183.1</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>84.8</v>
+        <v>89.8</v>
       </c>
       <c r="Y37" s="3" t="n">
         <v>359.5</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>394.6</v>
+        <v>3.9</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3532,18 +3658,18 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>2448.1</v>
-      </c>
-      <c r="D38" s="10" t="n">
-        <v>25.7</v>
-      </c>
-      <c r="E38" s="10" t="n">
+        <v>448.9</v>
+      </c>
+      <c r="D38" s="11" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="E38" s="11" t="n">
         <v>12.1</v>
       </c>
-      <c r="F38" s="10" t="n">
+      <c r="F38" s="11" t="n">
         <v>18.9</v>
       </c>
-      <c r="G38" s="10" t="n">
+      <c r="G38" s="11" t="n">
         <v>13.5</v>
       </c>
       <c r="H38" s="3" t="n">
@@ -3552,48 +3678,54 @@
       <c r="I38" s="3" t="n">
         <v>28.1</v>
       </c>
-      <c r="J38" s="16" t="n">
-        <v>92.09999999999999</v>
+      <c r="J38" s="8" t="n">
+        <v>20.1</v>
       </c>
       <c r="K38" s="3" t="inlineStr"/>
-      <c r="L38" s="16" t="n">
+      <c r="L38" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="M38" s="16" t="n">
+      <c r="M38" s="3" t="n">
         <v>12.8</v>
       </c>
-      <c r="N38" s="3" t="inlineStr"/>
+      <c r="N38" s="3" t="n">
+        <v>2.8</v>
+      </c>
       <c r="O38" s="3" t="n">
-        <v>98.90000000000001</v>
+        <v>984.9</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>23.5</v>
+        <v>3.4</v>
       </c>
       <c r="Q38" s="3" t="n">
         <v>23.1</v>
       </c>
-      <c r="R38" s="3" t="inlineStr"/>
-      <c r="S38" s="3" t="inlineStr"/>
+      <c r="R38" s="3" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="S38" s="8" t="n">
+        <v>217.6</v>
+      </c>
       <c r="T38" s="3" t="n">
-        <v>63.3</v>
-      </c>
-      <c r="U38" s="3" t="n">
-        <v>424.3</v>
+        <v>83.5</v>
+      </c>
+      <c r="U38" s="8" t="n">
+        <v>18.9</v>
       </c>
       <c r="V38" s="3" t="n">
         <v>20.2</v>
       </c>
-      <c r="W38" s="16" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="X38" s="16" t="n">
+      <c r="W38" s="8" t="n">
+        <v>116.6</v>
+      </c>
+      <c r="X38" s="8" t="n">
         <v>16.9</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>21.9</v>
+        <v>11.9</v>
       </c>
       <c r="Z38" s="3" t="n">
-        <v>69.40000000000001</v>
+        <v>6.9</v>
       </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
@@ -3609,64 +3741,74 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>3599.9</v>
-      </c>
-      <c r="D39" s="3" t="n">
+        <v>5372.9</v>
+      </c>
+      <c r="D39" s="11" t="n">
         <v>26.9</v>
       </c>
-      <c r="E39" s="16" t="n">
-        <v>1118</v>
-      </c>
-      <c r="F39" s="3" t="n">
+      <c r="E39" s="11" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="F39" s="11" t="n">
         <v>18.9</v>
       </c>
-      <c r="G39" s="3" t="inlineStr"/>
+      <c r="G39" s="3" t="n">
+        <v>12.9</v>
+      </c>
       <c r="H39" s="3" t="inlineStr"/>
-      <c r="I39" s="3" t="inlineStr"/>
-      <c r="J39" s="3" t="inlineStr"/>
+      <c r="I39" s="3" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="J39" s="3" t="n">
+        <v>7</v>
+      </c>
       <c r="K39" s="3" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="L39" s="16" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="M39" s="3" t="inlineStr"/>
-      <c r="N39" s="3" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L39" s="8" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="M39" s="8" t="n">
+        <v>82.3</v>
+      </c>
+      <c r="N39" s="8" t="n">
+        <v>19.2</v>
+      </c>
       <c r="O39" s="3" t="n">
-        <v>1980.8</v>
+        <v>98</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>18.4</v>
+        <v>4.9</v>
       </c>
       <c r="Q39" s="3" t="n">
         <v>26.6</v>
       </c>
-      <c r="R39" s="3" t="n">
+      <c r="R39" s="8" t="n">
         <v>18</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>1.6</v>
+        <v>10.2</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>1720</v>
-      </c>
-      <c r="U39" s="16" t="n">
+        <v>58146.9</v>
+      </c>
+      <c r="U39" s="8" t="n">
         <v>18</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="W39" s="16" t="n">
-        <v>8151.7</v>
-      </c>
-      <c r="X39" s="16" t="n">
-        <v>119.6</v>
+        <v>12.7</v>
+      </c>
+      <c r="W39" s="8" t="n">
+        <v>157.5</v>
+      </c>
+      <c r="X39" s="8" t="n">
+        <v>12.3</v>
       </c>
       <c r="Y39" s="3" t="n">
         <v>76</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>5</v>
+        <v>141.6</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3682,67 +3824,71 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>335.1</v>
-      </c>
-      <c r="D40" s="10" t="n">
-        <v>27.1</v>
-      </c>
-      <c r="E40" s="10" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="F40" s="10" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="D40" s="11" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="E40" s="11" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="F40" s="11" t="n">
         <v>18.9</v>
       </c>
-      <c r="G40" s="10" t="n">
-        <v>16.3</v>
-      </c>
-      <c r="H40" s="3" t="n">
-        <v>17.3</v>
+      <c r="G40" s="3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H40" s="8" t="n">
+        <v>12.9</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>12.4</v>
+        <v>21.4</v>
       </c>
       <c r="J40" s="3" t="inlineStr"/>
       <c r="K40" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" s="8" t="n">
         <v>10.6</v>
       </c>
-      <c r="M40" s="16" t="n">
+      <c r="M40" s="3" t="n">
         <v>10.3</v>
       </c>
-      <c r="N40" s="3" t="inlineStr"/>
+      <c r="N40" s="3" t="n">
+        <v>12.9</v>
+      </c>
       <c r="O40" s="3" t="n">
-        <v>198</v>
+        <v>96</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q40" s="16" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="Q40" s="3" t="n">
         <v>22</v>
       </c>
       <c r="R40" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="S40" s="16" t="n">
-        <v>18.5</v>
+      <c r="S40" s="3" t="n">
+        <v>18.4</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>69.2</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="U40" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="V40" s="3" t="inlineStr"/>
-      <c r="W40" s="16" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="X40" s="16" t="n">
-        <v>199.3</v>
+        <v>8</v>
+      </c>
+      <c r="V40" s="3" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="W40" s="8" t="n">
+        <v>181.3</v>
+      </c>
+      <c r="X40" s="3" t="n">
+        <v>29.3</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>983</v>
+        <v>83</v>
       </c>
       <c r="Z40" s="3" t="n">
         <v>7.2</v>
@@ -3761,66 +3907,76 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>245451.2</v>
+        <v>458.2</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>28.4</v>
+        <v>12.8</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>18.6</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>128.13</v>
+        <v>18.5</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="H41" s="16" t="n">
-        <v>51</v>
+        <v>1.9</v>
+      </c>
+      <c r="H41" s="8" t="n">
+        <v>51.9</v>
       </c>
       <c r="I41" s="3" t="n">
         <v>3.6</v>
       </c>
-      <c r="J41" s="3" t="inlineStr"/>
+      <c r="J41" s="3" t="n">
+        <v>5.7</v>
+      </c>
       <c r="K41" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>818.5</v>
+        <v>88.7</v>
       </c>
       <c r="M41" s="3" t="n">
         <v>8.6</v>
       </c>
-      <c r="N41" s="3" t="inlineStr"/>
+      <c r="N41" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="O41" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="P41" s="3" t="inlineStr"/>
+        <v>98</v>
+      </c>
+      <c r="P41" s="3" t="n">
+        <v>0.4</v>
+      </c>
       <c r="Q41" s="3" t="n">
         <v>23.9</v>
       </c>
-      <c r="R41" s="16" t="n">
-        <v>717.9</v>
-      </c>
-      <c r="S41" s="16" t="n">
-        <v>216.6</v>
-      </c>
-      <c r="T41" s="3" t="inlineStr"/>
-      <c r="U41" s="16" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="V41" s="16" t="n">
-        <v>222</v>
+      <c r="R41" s="8" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="S41" s="8" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="T41" s="3" t="n">
+        <v>4213.5</v>
+      </c>
+      <c r="U41" s="3" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="V41" s="3" t="n">
+        <v>22</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="X41" s="3" t="inlineStr"/>
+        <v>15.5</v>
+      </c>
+      <c r="X41" s="8" t="n">
+        <v>14.8</v>
+      </c>
       <c r="Y41" s="3" t="n">
         <v>58</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>121.2</v>
+        <v>1112</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -3836,39 +3992,43 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>524.4</v>
-      </c>
-      <c r="D42" s="3" t="inlineStr"/>
-      <c r="E42" s="16" t="n">
-        <v>60.1</v>
-      </c>
-      <c r="F42" s="3" t="n">
+        <v>5254.4</v>
+      </c>
+      <c r="D42" s="11" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="E42" s="11" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="F42" s="11" t="n">
         <v>19.3</v>
       </c>
-      <c r="G42" s="11" t="n">
-        <v>25.2</v>
+      <c r="G42" s="9" t="n">
+        <v>15.2</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>17.8</v>
+        <v>7.8</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="J42" s="3" t="inlineStr"/>
+        <v>15.9</v>
+      </c>
+      <c r="J42" s="3" t="n">
+        <v>5.6</v>
+      </c>
       <c r="K42" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L42" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" s="8" t="n">
         <v>11.9</v>
       </c>
       <c r="M42" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="N42" s="16" t="n">
-        <v>13.2</v>
+        <v>0.2</v>
+      </c>
+      <c r="N42" s="8" t="n">
+        <v>13.3</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="P42" s="3" t="n">
         <v>0.8</v>
@@ -3876,25 +4036,27 @@
       <c r="Q42" s="3" t="n">
         <v>26.6</v>
       </c>
-      <c r="R42" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="S42" s="16" t="n">
-        <v>14.7</v>
+      <c r="R42" s="8" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="S42" s="8" t="n">
+        <v>148.7</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>543.5</v>
-      </c>
-      <c r="U42" s="16" t="n">
+        <v>153.2</v>
+      </c>
+      <c r="U42" s="3" t="n">
         <v>19.6</v>
       </c>
-      <c r="V42" s="16" t="n">
-        <v>22</v>
+      <c r="V42" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="W42" s="3" t="n">
-        <v>161.3</v>
-      </c>
-      <c r="X42" s="3" t="inlineStr"/>
+        <v>15.5</v>
+      </c>
+      <c r="X42" s="8" t="n">
+        <v>14.8</v>
+      </c>
       <c r="Y42" s="3" t="inlineStr"/>
       <c r="Z42" s="3" t="inlineStr"/>
       <c r="AA42" s="3" t="inlineStr">
@@ -3910,10 +4072,12 @@
           <t>30</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr"/>
-      <c r="D43" s="3" t="inlineStr"/>
-      <c r="E43" s="3" t="inlineStr"/>
-      <c r="F43" s="14" t="inlineStr"/>
+      <c r="C43" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D43" s="12" t="inlineStr"/>
+      <c r="E43" s="12" t="inlineStr"/>
+      <c r="F43" s="11" t="inlineStr"/>
       <c r="G43" s="3" t="inlineStr"/>
       <c r="H43" s="3" t="inlineStr"/>
       <c r="I43" s="3" t="inlineStr"/>
@@ -3947,10 +4111,12 @@
           <t>31</t>
         </is>
       </c>
-      <c r="C44" s="3" t="inlineStr"/>
-      <c r="D44" s="3" t="inlineStr"/>
-      <c r="E44" s="3" t="inlineStr"/>
-      <c r="F44" s="14" t="inlineStr"/>
+      <c r="C44" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D44" s="12" t="inlineStr"/>
+      <c r="E44" s="12" t="inlineStr"/>
+      <c r="F44" s="11" t="inlineStr"/>
       <c r="G44" s="3" t="inlineStr"/>
       <c r="H44" s="3" t="inlineStr"/>
       <c r="I44" s="3" t="inlineStr"/>
@@ -3987,68 +4153,72 @@
       <c r="C45" s="3" t="n">
         <v>1911.2</v>
       </c>
-      <c r="D45" s="15" t="inlineStr"/>
-      <c r="E45" s="15" t="inlineStr"/>
-      <c r="F45" s="9" t="n">
+      <c r="D45" s="10" t="n">
+        <v>109.7</v>
+      </c>
+      <c r="E45" s="10" t="n">
+        <v>41.8</v>
+      </c>
+      <c r="F45" s="11" t="n">
         <v>75.59999999999999</v>
       </c>
-      <c r="G45" s="11" t="n">
-        <v>10.8</v>
+      <c r="G45" s="3" t="n">
+        <v>7.9</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>454.4</v>
+        <v>119.4</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>121.9</v>
+        <v>20.9</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>144</v>
+        <v>49</v>
       </c>
       <c r="M45" s="3" t="n">
-        <v>42.9</v>
+        <v>212.9</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>51.2</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="O45" s="3" t="n">
         <v>388</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>4.4</v>
+        <v>22.3</v>
       </c>
       <c r="Q45" s="3" t="n">
-        <v>198.6</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="R45" s="3" t="n">
         <v>71</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>166</v>
+        <v>66</v>
       </c>
       <c r="T45" s="3" t="n">
         <v>216.9</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="V45" s="3" t="n">
-        <v>831.4</v>
+        <v>851.9</v>
       </c>
       <c r="W45" s="3" t="n">
-        <v>168.3</v>
+        <v>67.3</v>
       </c>
       <c r="X45" s="3" t="inlineStr"/>
       <c r="Y45" s="3" t="n">
-        <v>8263</v>
+        <v>1263</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>331.8</v>
+        <v>331.9</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4063,64 +4233,70 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C46" s="3" t="inlineStr"/>
-      <c r="D46" s="10" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="E46" s="10" t="n">
+      <c r="C46" s="3" t="n">
+        <v>5417.8</v>
+      </c>
+      <c r="D46" s="11" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="E46" s="11" t="n">
         <v>10.4</v>
       </c>
-      <c r="F46" s="10" t="n">
+      <c r="F46" s="11" t="n">
         <v>18.9</v>
       </c>
-      <c r="G46" s="10" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="H46" s="16" t="n">
-        <v>19.7</v>
+      <c r="G46" s="8" t="n">
+        <v>69.40000000000001</v>
+      </c>
+      <c r="H46" s="3" t="n">
+        <v>6.7</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>36.1</v>
-      </c>
-      <c r="J46" s="3" t="n">
-        <v>52.1</v>
+        <v>3.6</v>
+      </c>
+      <c r="J46" s="8" t="n">
+        <v>52.4</v>
       </c>
       <c r="K46" s="3" t="inlineStr"/>
-      <c r="L46" s="16" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="M46" s="16" t="n">
-        <v>10.7</v>
+      <c r="L46" s="8" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="M46" s="3" t="n">
+        <v>11</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>4.8</v>
+        <v>12.8</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>97</v>
+        <v>197</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q46" s="16" t="n">
-        <v>29.7</v>
+        <v>6.4</v>
+      </c>
+      <c r="Q46" s="3" t="n">
+        <v>247.1</v>
       </c>
       <c r="R46" s="3" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="S46" s="16" t="n">
-        <v>2261.5</v>
-      </c>
-      <c r="T46" s="3" t="inlineStr"/>
-      <c r="U46" s="3" t="inlineStr"/>
+        <v>15.8</v>
+      </c>
+      <c r="S46" s="3" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="T46" s="3" t="n">
+        <v>654.7</v>
+      </c>
+      <c r="U46" s="3" t="n">
+        <v>14.7</v>
+      </c>
       <c r="V46" s="3" t="n">
         <v>21.3</v>
       </c>
-      <c r="W46" s="16" t="n">
+      <c r="W46" s="8" t="n">
         <v>16.8</v>
       </c>
       <c r="X46" s="3" t="inlineStr"/>
       <c r="Y46" s="3" t="n">
-        <v>1680.1</v>
+        <v>1860.8</v>
       </c>
       <c r="Z46" s="3" t="n">
         <v>81.90000000000001</v>

--- a/results/05_transient_transcription_output/702/702_196402_SF.JPG_stage_duirnal_temp_range.xlsx
+++ b/results/05_transient_transcription_output/702/702_196402_SF.JPG_stage_duirnal_temp_range.xlsx
@@ -131,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -149,16 +149,22 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -772,7 +778,7 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>3012.1</v>
+        <v>301.2</v>
       </c>
       <c r="D4" s="11" t="n">
         <v>27.8</v>
@@ -787,7 +793,7 @@
         <v>81.7</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>3.5</v>
@@ -808,24 +814,24 @@
         <v>11.9</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>98</v>
+        <v>928</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>10.9</v>
+        <v>0.9</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>23.8</v>
+        <v>25.8</v>
       </c>
       <c r="R4" s="8" t="n">
         <v>16.8</v>
       </c>
       <c r="S4" s="8" t="n">
-        <v>19.1</v>
+        <v>14.1</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>42.5</v>
-      </c>
-      <c r="U4" s="3" t="n">
+        <v>462.5</v>
+      </c>
+      <c r="U4" s="8" t="n">
         <v>19.1</v>
       </c>
       <c r="V4" s="3" t="n">
@@ -841,7 +847,7 @@
         <v>71</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>7.8</v>
+        <v>73.8</v>
       </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
@@ -868,8 +874,8 @@
       <c r="F5" s="11" t="n">
         <v>19.2</v>
       </c>
-      <c r="G5" s="3" t="n">
-        <v>15.9</v>
+      <c r="G5" s="8" t="n">
+        <v>59.4</v>
       </c>
       <c r="H5" s="3" t="n">
         <v>7.9</v>
@@ -883,11 +889,11 @@
       <c r="K5" s="3" t="n">
         <v>11.2</v>
       </c>
-      <c r="L5" s="8" t="n">
-        <v>29.5</v>
+      <c r="L5" s="3" t="n">
+        <v>12.3</v>
       </c>
       <c r="M5" s="8" t="n">
-        <v>19.4</v>
+        <v>8149.4</v>
       </c>
       <c r="N5" s="3" t="n">
         <v>12.9</v>
@@ -896,13 +902,13 @@
         <v>90</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>18.7</v>
+        <v>1.9</v>
       </c>
       <c r="Q5" s="8" t="n">
         <v>19.6</v>
       </c>
-      <c r="R5" s="8" t="n">
-        <v>80.59999999999999</v>
+      <c r="R5" s="3" t="n">
+        <v>18.6</v>
       </c>
       <c r="S5" s="3" t="n">
         <v>20.9</v>
@@ -910,14 +916,12 @@
       <c r="T5" s="3" t="n">
         <v>91</v>
       </c>
-      <c r="U5" s="3" t="n">
-        <v>12</v>
-      </c>
+      <c r="U5" s="3" t="inlineStr"/>
       <c r="V5" s="8" t="n">
-        <v>199.5</v>
+        <v>19.5</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>19.2</v>
+        <v>17.2</v>
       </c>
       <c r="X5" s="3" t="n">
         <v>18.3</v>
@@ -926,7 +930,7 @@
         <v>80.5</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>66.5</v>
+        <v>469.5</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -957,7 +961,7 @@
         <v>15</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>5.9</v>
+        <v>7.9</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>1.2</v>
@@ -966,13 +970,13 @@
         <v>1.7</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>69.5</v>
+        <v>6.5</v>
       </c>
       <c r="L6" s="8" t="n">
-        <v>101.1</v>
-      </c>
-      <c r="M6" s="8" t="n">
-        <v>211</v>
+        <v>1.1</v>
+      </c>
+      <c r="M6" s="3" t="n">
+        <v>11</v>
       </c>
       <c r="N6" s="3" t="n">
         <v>13.1</v>
@@ -984,10 +988,10 @@
         <v>0.2</v>
       </c>
       <c r="Q6" s="8" t="n">
-        <v>158.4</v>
-      </c>
-      <c r="R6" s="8" t="n">
-        <v>14.1</v>
+        <v>15.4</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>14.7</v>
       </c>
       <c r="S6" s="3" t="n">
         <v>11.6</v>
@@ -996,22 +1000,22 @@
         <v>92</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>11.9</v>
+        <v>1.9</v>
       </c>
       <c r="V6" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>18.3</v>
+        <v>24.6</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>17.9</v>
+        <v>17.1</v>
       </c>
       <c r="Y6" s="3" t="n">
         <v>95</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>0.9</v>
+        <v>2.9</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -1029,26 +1033,26 @@
       <c r="C7" s="3" t="n">
         <v>275.8</v>
       </c>
-      <c r="D7" s="9" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="E7" s="9" t="n">
-        <v>285.95</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="G7" s="3" t="n">
+      <c r="D7" s="11" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="E7" s="11" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="F7" s="11" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="G7" s="11" t="n">
         <v>9</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>112.9</v>
+        <v>12.9</v>
       </c>
       <c r="I7" s="3" t="n">
         <v>11.2</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>12.9</v>
+        <v>11.9</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>0</v>
@@ -1063,27 +1067,27 @@
         <v>5</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="P7" s="3" t="n">
         <v>0.2</v>
       </c>
       <c r="Q7" s="8" t="n">
-        <v>119.3</v>
-      </c>
-      <c r="R7" s="3" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="R7" s="8" t="n">
         <v>16.8</v>
       </c>
       <c r="S7" s="8" t="n">
-        <v>77.5</v>
+        <v>17.7</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>79</v>
+        <v>19</v>
       </c>
       <c r="U7" s="3" t="n">
         <v>4.8</v>
       </c>
-      <c r="V7" s="8" t="n">
+      <c r="V7" s="3" t="n">
         <v>18.9</v>
       </c>
       <c r="W7" s="3" t="n">
@@ -1096,7 +1100,7 @@
         <v>81</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>9.699999999999999</v>
+        <v>4.1</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1112,16 +1116,16 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>291.2</v>
+        <v>391.2</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>26.8</v>
+        <v>27.3</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>10.4</v>
+        <v>10.5</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>18.6</v>
+        <v>18.9</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>15.8</v>
@@ -1136,27 +1140,27 @@
         <v>3.5</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L8" s="3" t="n">
         <v>10.8</v>
       </c>
-      <c r="M8" s="8" t="n">
-        <v>190.6</v>
+      <c r="M8" s="3" t="n">
+        <v>10.6</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>11.2</v>
+        <v>1.2</v>
       </c>
       <c r="O8" s="3" t="n">
         <v>98</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>10.4</v>
+        <v>10.9</v>
       </c>
       <c r="Q8" s="8" t="n">
-        <v>217.5</v>
-      </c>
-      <c r="R8" s="8" t="n">
+        <v>2719.4</v>
+      </c>
+      <c r="R8" s="3" t="n">
         <v>18.9</v>
       </c>
       <c r="S8" s="3" t="n">
@@ -1171,8 +1175,8 @@
       <c r="V8" s="3" t="n">
         <v>11.8</v>
       </c>
-      <c r="W8" s="8" t="n">
-        <v>97.3</v>
+      <c r="W8" s="3" t="n">
+        <v>17.3</v>
       </c>
       <c r="X8" s="3" t="n">
         <v>18.9</v>
@@ -1197,31 +1201,31 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>1749.7</v>
-      </c>
-      <c r="D9" s="10" t="n">
+        <v>43927.4</v>
+      </c>
+      <c r="D9" s="11" t="n">
         <v>128.9</v>
       </c>
-      <c r="E9" s="10" t="n">
-        <v>55.4</v>
-      </c>
-      <c r="F9" s="10" t="n">
-        <v>911.9</v>
-      </c>
-      <c r="G9" s="3" t="n">
+      <c r="E9" s="11" t="n">
+        <v>55</v>
+      </c>
+      <c r="F9" s="11" t="n">
+        <v>91.90000000000001</v>
+      </c>
+      <c r="G9" s="11" t="n">
         <v>73.90000000000001</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>60.6</v>
+        <v>12.6</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>9.9</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>19.5</v>
+        <v>13.5</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>7.8</v>
+        <v>0.7</v>
       </c>
       <c r="L9" s="3" t="n">
         <v>56.7</v>
@@ -1230,10 +1234,10 @@
         <v>55.2</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>25.1</v>
+        <v>55.1</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>484.8</v>
+        <v>684.8</v>
       </c>
       <c r="P9" s="3" t="n">
         <v>9.6</v>
@@ -1245,28 +1249,28 @@
         <v>85.3</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>885.3</v>
+        <v>88.5</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>9501.5</v>
+        <v>3801.5</v>
       </c>
       <c r="U9" s="3" t="n">
         <v>33.3</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>8.9</v>
+        <v>8.4</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>911.7</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="Y9" s="3" t="n">
         <v>9414.5</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>119.8</v>
+        <v>19.8</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1282,7 +1286,7 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>849.9</v>
+        <v>349.9</v>
       </c>
       <c r="D10" s="11" t="n">
         <v>25.8</v>
@@ -1303,11 +1307,9 @@
         <v>2</v>
       </c>
       <c r="J10" s="8" t="n">
-        <v>797.4</v>
-      </c>
-      <c r="K10" s="3" t="n">
-        <v>0.1</v>
-      </c>
+        <v>418.1</v>
+      </c>
+      <c r="K10" s="3" t="inlineStr"/>
       <c r="L10" s="8" t="n">
         <v>11.3</v>
       </c>
@@ -1321,7 +1323,7 @@
         <v>96.8</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0.5</v>
+        <v>10.5</v>
       </c>
       <c r="Q10" s="3" t="n">
         <v>20.3</v>
@@ -1333,10 +1335,10 @@
         <v>17.7</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>26.7</v>
+        <v>26.1</v>
       </c>
       <c r="U10" s="3" t="n">
-        <v>7.2</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="V10" s="3" t="n">
         <v>19</v>
@@ -1351,7 +1353,7 @@
         <v>82.90000000000001</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1367,25 +1369,25 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>909.3</v>
-      </c>
-      <c r="D11" s="11" t="n">
+        <v>509.3</v>
+      </c>
+      <c r="D11" s="8" t="n">
         <v>27.3</v>
       </c>
-      <c r="E11" s="11" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="F11" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="G11" s="11" t="n">
+      <c r="E11" s="13" t="n">
+        <v>47.9</v>
+      </c>
+      <c r="F11" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="G11" s="8" t="n">
         <v>16.6</v>
       </c>
       <c r="H11" s="3" t="n">
         <v>6.7</v>
       </c>
-      <c r="I11" s="8" t="n">
-        <v>84.7</v>
+      <c r="I11" s="3" t="n">
+        <v>4.7</v>
       </c>
       <c r="J11" s="3" t="n">
         <v>6</v>
@@ -1394,43 +1396,43 @@
         <v>0.2</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>21.1</v>
+        <v>17.4</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>6.4</v>
+        <v>1.2</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>119</v>
+        <v>13</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>51.8</v>
+        <v>2.9</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>6.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q11" s="8" t="n">
-        <v>66.5</v>
+        <v>26.3</v>
       </c>
       <c r="R11" s="3" t="n">
         <v>17.1</v>
       </c>
-      <c r="S11" s="3" t="n">
+      <c r="S11" s="8" t="n">
         <v>17.9</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>862</v>
+        <v>512</v>
       </c>
       <c r="U11" s="3" t="n">
         <v>19.9</v>
       </c>
-      <c r="V11" s="8" t="n">
+      <c r="V11" s="3" t="n">
         <v>22.1</v>
       </c>
       <c r="W11" s="8" t="n">
         <v>17.6</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>11.6</v>
+        <v>19.6</v>
       </c>
       <c r="Y11" s="3" t="n">
         <v>66</v>
@@ -1452,10 +1454,10 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>506.7</v>
-      </c>
-      <c r="D12" s="3" t="n">
-        <v>29.9</v>
+        <v>506.1</v>
+      </c>
+      <c r="D12" s="8" t="n">
+        <v>5.9</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>10.9</v>
@@ -1463,38 +1465,38 @@
       <c r="F12" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="G12" s="8" t="n">
-        <v>13</v>
+      <c r="G12" s="3" t="n">
+        <v>15</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="I12" s="8" t="n">
-        <v>9.4</v>
+        <v>7.1</v>
+      </c>
+      <c r="I12" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>1.5</v>
+        <v>5.7</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="L12" s="8" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="M12" s="3" t="n">
+        <v>191.7</v>
+      </c>
+      <c r="M12" s="8" t="n">
         <v>22.1</v>
       </c>
       <c r="N12" s="3" t="n">
         <v>13.2</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>195</v>
+        <v>95</v>
       </c>
       <c r="P12" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>25.6</v>
+        <v>25.4</v>
       </c>
       <c r="R12" s="3" t="n">
         <v>15.5</v>
@@ -1505,23 +1507,23 @@
       <c r="T12" s="3" t="n">
         <v>37</v>
       </c>
-      <c r="U12" s="8" t="n">
-        <v>4.6</v>
+      <c r="U12" s="3" t="n">
+        <v>20.4</v>
       </c>
       <c r="V12" s="3" t="n">
         <v>21.3</v>
       </c>
       <c r="W12" s="3" t="n">
-        <v>11.9</v>
+        <v>19.9</v>
       </c>
       <c r="X12" s="3" t="n">
-        <v>19.7</v>
+        <v>13.7</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>12.3</v>
+        <v>12.2</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1537,10 +1539,10 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>3514.9</v>
+        <v>357.9</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>25.5</v>
+        <v>25.4</v>
       </c>
       <c r="E13" s="11" t="n">
         <v>11.3</v>
@@ -1549,37 +1551,37 @@
         <v>18.2</v>
       </c>
       <c r="G13" s="11" t="n">
-        <v>14.7</v>
+        <v>14.1</v>
       </c>
       <c r="H13" s="3" t="n">
         <v>7.5</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>11.9</v>
+        <v>11.4</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="K13" s="3" t="n">
         <v>8.5</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>11.5</v>
+        <v>11.8</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>99.59999999999999</v>
+        <v>11.6</v>
       </c>
       <c r="N13" s="8" t="n">
-        <v>13.6</v>
+        <v>23.6</v>
       </c>
       <c r="O13" s="3" t="n">
         <v>98</v>
       </c>
-      <c r="P13" s="8" t="n">
-        <v>9.699999999999999</v>
+      <c r="P13" s="3" t="n">
+        <v>0.9</v>
       </c>
       <c r="Q13" s="8" t="n">
-        <v>180.9</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="R13" s="3" t="n">
         <v>17.3</v>
@@ -1588,7 +1590,7 @@
         <v>11.8</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>86.40000000000001</v>
+        <v>85.5</v>
       </c>
       <c r="U13" s="3" t="n">
         <v>3</v>
@@ -1597,16 +1599,16 @@
         <v>19.6</v>
       </c>
       <c r="W13" s="8" t="n">
-        <v>6816.4</v>
-      </c>
-      <c r="X13" s="3" t="n">
-        <v>19.1</v>
+        <v>791.5</v>
+      </c>
+      <c r="X13" s="8" t="n">
+        <v>29.1</v>
       </c>
       <c r="Y13" s="3" t="n">
         <v>84</v>
       </c>
       <c r="Z13" s="3" t="n">
-        <v>93.59999999999999</v>
+        <v>3.6</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
@@ -1622,40 +1624,40 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="E14" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="F14" s="9" t="n">
-        <v>18.53</v>
-      </c>
-      <c r="G14" s="3" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="E14" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="G14" s="8" t="n">
         <v>10.5</v>
       </c>
-      <c r="H14" s="3" t="n">
+      <c r="H14" s="8" t="n">
         <v>10.3</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>11.3</v>
+        <v>1</v>
       </c>
       <c r="J14" s="3" t="n">
         <v>28.3</v>
       </c>
-      <c r="K14" s="3" t="n">
+      <c r="K14" s="8" t="n">
         <v>11.6</v>
       </c>
-      <c r="L14" s="3" t="n">
-        <v>19.8</v>
+      <c r="L14" s="8" t="n">
+        <v>15.8</v>
       </c>
       <c r="M14" s="8" t="n">
-        <v>18</v>
+        <v>83</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>16.8</v>
+        <v>14.8</v>
       </c>
       <c r="O14" s="3" t="n">
         <v>98</v>
@@ -1663,23 +1665,21 @@
       <c r="P14" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="Q14" s="3" t="n">
-        <v>15.9</v>
+      <c r="Q14" s="8" t="n">
+        <v>46.9</v>
       </c>
       <c r="R14" s="8" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="S14" s="8" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="T14" s="3" t="n">
-        <v>0.8</v>
-      </c>
+        <v>14.9</v>
+      </c>
+      <c r="S14" s="3" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="T14" s="3" t="inlineStr"/>
       <c r="U14" s="3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="V14" s="3" t="n">
-        <v>19.5</v>
+        <v>0.6</v>
+      </c>
+      <c r="V14" s="8" t="n">
+        <v>59.5</v>
       </c>
       <c r="W14" s="3" t="n">
         <v>6.2</v>
@@ -1688,10 +1688,10 @@
         <v>16</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>199</v>
+        <v>95</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>28.8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>1638</v>
+        <v>631</v>
       </c>
       <c r="D15" s="11" t="n">
         <v>26</v>
@@ -1733,14 +1733,14 @@
       <c r="K15" s="3" t="n">
         <v>21.6</v>
       </c>
-      <c r="L15" s="8" t="n">
-        <v>57.4</v>
-      </c>
-      <c r="M15" s="8" t="n">
-        <v>711.3</v>
+      <c r="L15" s="3" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="M15" s="3" t="n">
+        <v>11.3</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="O15" s="3" t="n">
         <v>99</v>
@@ -1752,25 +1752,25 @@
         <v>25.5</v>
       </c>
       <c r="R15" s="8" t="n">
-        <v>172.6</v>
-      </c>
-      <c r="S15" s="8" t="n">
-        <v>57.9</v>
+        <v>72.59999999999999</v>
+      </c>
+      <c r="S15" s="3" t="n">
+        <v>15.9</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>168</v>
-      </c>
-      <c r="U15" s="3" t="n">
-        <v>15.8</v>
+        <v>48</v>
+      </c>
+      <c r="U15" s="8" t="n">
+        <v>17</v>
       </c>
       <c r="V15" s="3" t="n">
         <v>2</v>
       </c>
       <c r="W15" s="3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="X15" s="8" t="n">
-        <v>69.40000000000001</v>
+        <v>16.3</v>
+      </c>
+      <c r="X15" s="3" t="n">
+        <v>16.4</v>
       </c>
       <c r="Y15" s="3" t="n">
         <v>67</v>
@@ -1794,16 +1794,16 @@
       <c r="C16" s="3" t="n">
         <v>2227.1</v>
       </c>
-      <c r="D16" s="10" t="n">
-        <v>1298</v>
-      </c>
-      <c r="E16" s="10" t="n">
+      <c r="D16" s="11" t="n">
+        <v>128</v>
+      </c>
+      <c r="E16" s="14" t="n">
         <v>56.8</v>
       </c>
-      <c r="F16" s="10" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="G16" s="3" t="n">
+      <c r="F16" s="11" t="n">
+        <v>92.5</v>
+      </c>
+      <c r="G16" s="11" t="n">
         <v>71.2</v>
       </c>
       <c r="H16" s="3" t="n">
@@ -1813,43 +1813,43 @@
         <v>14.2</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>51.8</v>
+        <v>21.8</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>39.8</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>591.7</v>
+        <v>5.9</v>
       </c>
       <c r="M16" s="3" t="n">
         <v>58.2</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>67.90000000000001</v>
+        <v>57.1</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>39</v>
+        <v>399</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>17119</v>
+        <v>1111</v>
       </c>
       <c r="R16" s="3" t="n">
         <v>82.2</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>77.7</v>
+        <v>78.7</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>310.8</v>
+        <v>310.9</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>160.9</v>
+        <v>60.9</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>95.59999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="W16" s="3" t="n">
         <v>801.7</v>
@@ -1858,10 +1858,10 @@
         <v>82.2</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>2369.8</v>
+        <v>369</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>393.9</v>
+        <v>33.9</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1879,26 +1879,26 @@
       <c r="C17" s="3" t="n">
         <v>445.9</v>
       </c>
-      <c r="D17" s="10" t="n">
+      <c r="D17" s="11" t="n">
         <v>25.6</v>
       </c>
-      <c r="E17" s="10" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="F17" s="10" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="G17" s="3" t="n">
+      <c r="E17" s="11" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="F17" s="11" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="G17" s="11" t="n">
         <v>14.2</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>2.9</v>
+        <v>7.9</v>
       </c>
       <c r="I17" s="3" t="n">
         <v>29.4</v>
       </c>
-      <c r="J17" s="3" t="n">
-        <v>5.8</v>
+      <c r="J17" s="8" t="n">
+        <v>871.8</v>
       </c>
       <c r="K17" s="3" t="inlineStr"/>
       <c r="L17" s="3" t="n">
@@ -1914,7 +1914,7 @@
         <v>97.8</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>7.4</v>
+        <v>0.8</v>
       </c>
       <c r="Q17" s="3" t="n">
         <v>22.2</v>
@@ -1922,20 +1922,20 @@
       <c r="R17" s="8" t="n">
         <v>16.9</v>
       </c>
-      <c r="S17" s="3" t="n">
+      <c r="S17" s="8" t="n">
         <v>15.5</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>72.2</v>
+        <v>42</v>
       </c>
       <c r="U17" s="3" t="n">
         <v>12.2</v>
       </c>
-      <c r="V17" s="8" t="n">
-        <v>119.6</v>
+      <c r="V17" s="3" t="n">
+        <v>19.6</v>
       </c>
       <c r="W17" s="8" t="n">
-        <v>16.1</v>
+        <v>16.9</v>
       </c>
       <c r="X17" s="8" t="n">
         <v>16.5</v>
@@ -1960,40 +1960,40 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>455.1</v>
+        <v>455.5</v>
       </c>
       <c r="D18" s="11" t="n">
         <v>25.9</v>
       </c>
-      <c r="E18" s="9" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="F18" s="3" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="G18" s="9" t="n">
+      <c r="E18" s="11" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="F18" s="11" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="G18" s="8" t="n">
         <v>13.8</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>12.9</v>
+        <v>2.9</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>0.7</v>
+        <v>6.7</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>1.7</v>
+        <v>0.1</v>
       </c>
       <c r="L18" s="8" t="n">
-        <v>61.5</v>
+        <v>1666.6</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>84.59999999999999</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="N18" s="8" t="n">
-        <v>1610.5</v>
+        <v>16</v>
       </c>
       <c r="O18" s="3" t="n">
         <v>19</v>
@@ -2005,31 +2005,31 @@
         <v>25.8</v>
       </c>
       <c r="R18" s="3" t="n">
-        <v>18.1</v>
+        <v>17.3</v>
       </c>
       <c r="S18" s="8" t="n">
-        <v>101.4</v>
+        <v>110.4</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="U18" s="3" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="U18" s="8" t="n">
         <v>17.9</v>
       </c>
       <c r="V18" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="W18" s="8" t="n">
+      <c r="W18" s="3" t="n">
         <v>15.5</v>
       </c>
       <c r="X18" s="3" t="n">
-        <v>14.6</v>
+        <v>19.6</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>510.1</v>
+        <v>39</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>11.6</v>
+        <v>110.7</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>95311.10000000001</v>
+        <v>531.9</v>
       </c>
       <c r="D19" s="11" t="n">
         <v>28</v>
@@ -2063,19 +2063,19 @@
         <v>7.2</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="J19" s="3" t="n">
         <v>5.2</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L19" s="8" t="n">
-        <v>11.2</v>
+        <v>111.2</v>
       </c>
       <c r="M19" s="8" t="n">
-        <v>111</v>
+        <v>11</v>
       </c>
       <c r="N19" s="3" t="n">
         <v>13</v>
@@ -2083,11 +2083,11 @@
       <c r="O19" s="3" t="n">
         <v>98</v>
       </c>
-      <c r="P19" s="3" t="n">
-        <v>0.4</v>
+      <c r="P19" s="8" t="n">
+        <v>9.4</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>23.9</v>
+        <v>25.9</v>
       </c>
       <c r="R19" s="3" t="n">
         <v>18</v>
@@ -2096,7 +2096,7 @@
         <v>16.2</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>94.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="U19" s="8" t="n">
         <v>7.2</v>
@@ -2104,10 +2104,10 @@
       <c r="V19" s="3" t="n">
         <v>21.2</v>
       </c>
-      <c r="W19" s="8" t="n">
+      <c r="W19" s="3" t="n">
         <v>17.8</v>
       </c>
-      <c r="X19" s="8" t="n">
+      <c r="X19" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="Y19" s="3" t="n">
@@ -2135,13 +2135,13 @@
       <c r="D20" s="11" t="n">
         <v>28.2</v>
       </c>
-      <c r="E20" s="9" t="n">
-        <v>-4.4</v>
-      </c>
-      <c r="F20" s="3" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="G20" s="3" t="n">
+      <c r="E20" s="11" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="F20" s="11" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="G20" s="11" t="n">
         <v>17.8</v>
       </c>
       <c r="H20" s="3" t="n">
@@ -2151,22 +2151,22 @@
         <v>33.5</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="K20" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="L20" s="8" t="n">
-        <v>111.2</v>
+        <v>4.9</v>
+      </c>
+      <c r="K20" s="3" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="L20" s="3" t="n">
+        <v>11.2</v>
       </c>
       <c r="M20" s="8" t="n">
-        <v>221.2</v>
-      </c>
-      <c r="N20" s="8" t="n">
-        <v>811</v>
+        <v>211</v>
+      </c>
+      <c r="N20" s="3" t="n">
+        <v>13</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>98.2</v>
+        <v>198</v>
       </c>
       <c r="P20" s="3" t="n">
         <v>0.9</v>
@@ -2177,7 +2177,7 @@
       <c r="R20" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="S20" s="8" t="n">
+      <c r="S20" s="3" t="n">
         <v>11.6</v>
       </c>
       <c r="T20" s="3" t="n">
@@ -2190,13 +2190,13 @@
         <v>22.2</v>
       </c>
       <c r="W20" s="8" t="n">
-        <v>89.5</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="X20" s="8" t="n">
-        <v>29.9</v>
+        <v>299.7</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>721</v>
+        <v>71</v>
       </c>
       <c r="Z20" s="3" t="n">
         <v>2.6</v>
@@ -2218,25 +2218,25 @@
         <v>382.4</v>
       </c>
       <c r="D21" s="11" t="n">
-        <v>24.8</v>
+        <v>24.5</v>
       </c>
       <c r="E21" s="11" t="n">
         <v>12.6</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>18.7</v>
+        <v>18.9</v>
       </c>
       <c r="G21" s="11" t="n">
         <v>12.1</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>10.9</v>
+        <v>10.3</v>
       </c>
       <c r="I21" s="3" t="n">
         <v>2.4</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>0</v>
@@ -2248,7 +2248,7 @@
         <v>13</v>
       </c>
       <c r="N21" s="8" t="n">
-        <v>54.9</v>
+        <v>15.9</v>
       </c>
       <c r="O21" s="3" t="n">
         <v>99</v>
@@ -2266,7 +2266,7 @@
         <v>16.8</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="U21" s="3" t="n">
         <v>16.2</v>
@@ -2284,7 +2284,7 @@
         <v>87</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
@@ -2300,31 +2300,31 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>194828.8</v>
+        <v>9489</v>
       </c>
       <c r="D22" s="11" t="n">
         <v>25.2</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>12.1</v>
+        <v>12.2</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="G22" s="8" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="G22" s="3" t="n">
         <v>13.9</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>85.90000000000001</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>20.7</v>
+        <v>2.7</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>19.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>9</v>
+        <v>82.8</v>
       </c>
       <c r="L22" s="3" t="n">
         <v>11.2</v>
@@ -2333,22 +2333,22 @@
         <v>12.2</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>14.1</v>
+        <v>1.4</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>992</v>
+        <v>99</v>
       </c>
       <c r="P22" s="3" t="n">
         <v>0.2</v>
       </c>
       <c r="Q22" s="3" t="n">
-        <v>2.3</v>
+        <v>23.6</v>
       </c>
       <c r="R22" s="3" t="n">
         <v>16.2</v>
       </c>
       <c r="S22" s="8" t="n">
-        <v>49.4</v>
+        <v>49.7</v>
       </c>
       <c r="T22" s="3" t="n">
         <v>49.5</v>
@@ -2363,13 +2363,13 @@
         <v>15.6</v>
       </c>
       <c r="X22" s="3" t="n">
-        <v>13.8</v>
+        <v>53.8</v>
       </c>
       <c r="Y22" s="3" t="n">
-        <v>505.9</v>
+        <v>50.5</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>1199.7</v>
+        <v>139.7</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2385,19 +2385,19 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>12320.8</v>
-      </c>
-      <c r="D23" s="10" t="n">
-        <v>112.1</v>
-      </c>
-      <c r="E23" s="10" t="n">
-        <v>201.5</v>
-      </c>
-      <c r="F23" s="10" t="n">
+        <v>12320.3</v>
+      </c>
+      <c r="D23" s="11" t="n">
+        <v>132.1</v>
+      </c>
+      <c r="E23" s="11" t="n">
+        <v>56.7</v>
+      </c>
+      <c r="F23" s="11" t="n">
         <v>94.40000000000001</v>
       </c>
-      <c r="G23" s="3" t="n">
-        <v>75.7</v>
+      <c r="G23" s="11" t="n">
+        <v>75.40000000000001</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>40.6</v>
@@ -2409,7 +2409,7 @@
         <v>20.8</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>5.9</v>
+        <v>0.3</v>
       </c>
       <c r="L23" s="3" t="n">
         <v>2.5</v>
@@ -2418,7 +2418,7 @@
         <v>61.8</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>711.5</v>
+        <v>71.5</v>
       </c>
       <c r="O23" s="3" t="n">
         <v>293</v>
@@ -2430,13 +2430,13 @@
         <v>128.9</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>86</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>781.7</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>2351.7</v>
+        <v>235.7</v>
       </c>
       <c r="U23" s="3" t="n">
         <v>88.5</v>
@@ -2454,7 +2454,7 @@
         <v>341.5</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>541</v>
+        <v>41</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>484.1</v>
+        <v>2464.1</v>
       </c>
       <c r="D24" s="11" t="n">
         <v>26.5</v>
@@ -2481,35 +2481,33 @@
       <c r="F24" s="11" t="n">
         <v>18.9</v>
       </c>
-      <c r="G24" s="11" t="n">
-        <v>15.1</v>
+      <c r="G24" s="8" t="n">
+        <v>57.1</v>
       </c>
       <c r="H24" s="3" t="n">
         <v>8.1</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="J24" s="3" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="K24" s="3" t="n">
-        <v>1.8</v>
-      </c>
+        <v>29.4</v>
+      </c>
+      <c r="J24" s="8" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="K24" s="3" t="inlineStr"/>
       <c r="L24" s="3" t="n">
         <v>12.5</v>
       </c>
-      <c r="M24" s="3" t="n">
+      <c r="M24" s="8" t="n">
         <v>12.4</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>4.1</v>
+        <v>1.4</v>
       </c>
       <c r="O24" s="3" t="n">
         <v>98.59999999999999</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>3.4</v>
+        <v>0.3</v>
       </c>
       <c r="Q24" s="3" t="n">
         <v>25.8</v>
@@ -2518,25 +2516,25 @@
         <v>17.6</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>129.6</v>
+        <v>15.6</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>22.9</v>
+        <v>27.1</v>
       </c>
       <c r="U24" s="8" t="n">
-        <v>177.7</v>
+        <v>177.1</v>
       </c>
       <c r="V24" s="3" t="n">
         <v>21.3</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>17.7</v>
+        <v>1.7</v>
       </c>
       <c r="X24" s="8" t="n">
         <v>17.2</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>168.3</v>
+        <v>68.3</v>
       </c>
       <c r="Z24" s="3" t="n">
         <v>8.199999999999999</v>
@@ -2555,40 +2553,40 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>428.9</v>
+        <v>1488.9</v>
       </c>
       <c r="D25" s="11" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="E25" s="11" t="n">
-        <v>9.699999999999999</v>
+        <v>32.7</v>
+      </c>
+      <c r="E25" s="13" t="n">
+        <v>2.9</v>
       </c>
       <c r="F25" s="11" t="n">
         <v>17.8</v>
       </c>
-      <c r="G25" s="11" t="n">
-        <v>16</v>
+      <c r="G25" s="3" t="n">
+        <v>13.6</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>15.4</v>
+        <v>2.2</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>4.7</v>
+        <v>49.7</v>
       </c>
       <c r="K25" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="L25" s="3" t="n">
+      <c r="L25" s="8" t="n">
         <v>10.7</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>8.9</v>
+        <v>2.9</v>
       </c>
       <c r="N25" s="8" t="n">
-        <v>5.4</v>
+        <v>19.4</v>
       </c>
       <c r="O25" s="3" t="n">
         <v>18</v>
@@ -2596,35 +2594,35 @@
       <c r="P25" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="Q25" s="3" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="R25" s="3" t="n">
-        <v>24.1</v>
+      <c r="Q25" s="8" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="R25" s="8" t="n">
+        <v>37.6</v>
       </c>
       <c r="S25" s="3" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="T25" s="3" t="n">
         <v>6.9</v>
       </c>
       <c r="U25" s="8" t="n">
-        <v>13.8</v>
+        <v>113.2</v>
       </c>
       <c r="V25" s="3" t="n">
         <v>21.3</v>
       </c>
       <c r="W25" s="8" t="n">
-        <v>116.9</v>
-      </c>
-      <c r="X25" s="3" t="n">
-        <v>116.8</v>
+        <v>216.9</v>
+      </c>
+      <c r="X25" s="8" t="n">
+        <v>16.8</v>
       </c>
       <c r="Y25" s="3" t="n">
         <v>66</v>
       </c>
       <c r="Z25" s="3" t="n">
-        <v>65.59999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
@@ -2655,40 +2653,40 @@
         <v>14.8</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>12.3</v>
+        <v>2.3</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>8.9</v>
+        <v>8.5</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>8.9</v>
+        <v>0.9</v>
       </c>
       <c r="L26" s="8" t="n">
-        <v>19.4</v>
+        <v>109.4</v>
       </c>
       <c r="M26" s="8" t="n">
         <v>10.2</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>98.09999999999999</v>
+        <v>98</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>2.4</v>
+        <v>0.4</v>
       </c>
       <c r="Q26" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="R26" s="3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="S26" s="3" t="n">
-        <v>15.7</v>
+      <c r="R26" s="8" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="S26" s="8" t="n">
+        <v>15.8</v>
       </c>
       <c r="T26" s="3" t="n">
         <v>63.5</v>
@@ -2700,16 +2698,16 @@
         <v>21.6</v>
       </c>
       <c r="W26" s="3" t="n">
-        <v>25.5</v>
+        <v>15.5</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>14.2</v>
+        <v>16.2</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>194</v>
+        <v>155</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>211.8</v>
+        <v>111.8</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2728,19 +2726,19 @@
         <v>340.2</v>
       </c>
       <c r="D27" s="11" t="n">
-        <v>24.5</v>
+        <v>19.1</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>11.7</v>
+        <v>17.1</v>
       </c>
       <c r="F27" s="11" t="n">
         <v>18.1</v>
       </c>
-      <c r="G27" s="3" t="n">
-        <v>14</v>
+      <c r="G27" s="8" t="n">
+        <v>24</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>82.40000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>2</v>
@@ -2749,7 +2747,7 @@
         <v>2.9</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>7.1</v>
+        <v>7.7</v>
       </c>
       <c r="L27" s="8" t="n">
         <v>12.4</v>
@@ -2758,40 +2756,40 @@
         <v>12.2</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>8</v>
+        <v>88</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>10.9</v>
+        <v>9.4</v>
       </c>
       <c r="Q27" s="3" t="n">
         <v>17.6</v>
       </c>
       <c r="R27" s="8" t="n">
-        <v>1618.1</v>
+        <v>1618.2</v>
       </c>
       <c r="S27" s="3" t="n">
         <v>11.2</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>56</v>
+        <v>86</v>
       </c>
       <c r="U27" s="3" t="n">
         <v>13</v>
       </c>
       <c r="V27" s="3" t="n">
-        <v>87.40000000000001</v>
+        <v>17.4</v>
       </c>
       <c r="W27" s="3" t="n">
-        <v>16.1</v>
+        <v>0.7</v>
       </c>
       <c r="X27" s="8" t="n">
-        <v>15859.5</v>
+        <v>18.5</v>
       </c>
       <c r="Y27" s="3" t="n">
-        <v>913</v>
+        <v>23</v>
       </c>
       <c r="Z27" s="3" t="n">
         <v>1.6</v>
@@ -2810,51 +2808,51 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>313.3</v>
+        <v>513.3</v>
       </c>
       <c r="D28" s="11" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>15.6</v>
+        <v>11.6</v>
       </c>
       <c r="F28" s="11" t="n">
         <v>19.3</v>
       </c>
-      <c r="G28" s="9" t="n">
-        <v>15.1</v>
+      <c r="G28" s="13" t="n">
+        <v>15.7</v>
       </c>
       <c r="H28" s="3" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="L28" s="3" t="n">
-        <v>13.5</v>
+        <v>3.5</v>
+      </c>
+      <c r="L28" s="8" t="n">
+        <v>935.4</v>
       </c>
       <c r="M28" s="8" t="n">
         <v>13.3</v>
       </c>
-      <c r="N28" s="8" t="n">
-        <v>12.1</v>
+      <c r="N28" s="3" t="n">
+        <v>14.2</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="P28" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q28" s="8" t="n">
+      <c r="Q28" s="3" t="n">
         <v>22.9</v>
       </c>
-      <c r="R28" s="3" t="n">
+      <c r="R28" s="8" t="n">
         <v>18.6</v>
       </c>
       <c r="S28" s="3" t="n">
@@ -2866,17 +2864,17 @@
       <c r="U28" s="3" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="V28" s="8" t="n">
-        <v>645.4</v>
+      <c r="V28" s="3" t="n">
+        <v>16.9</v>
       </c>
       <c r="W28" s="3" t="n">
         <v>15.5</v>
       </c>
       <c r="X28" s="8" t="n">
-        <v>11</v>
+        <v>817</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>1891</v>
+        <v>191</v>
       </c>
       <c r="Z28" s="3" t="n">
         <v>11.8</v>
@@ -2895,7 +2893,7 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>523.3</v>
+        <v>323.3</v>
       </c>
       <c r="D29" s="11" t="n">
         <v>28.3</v>
@@ -2915,38 +2913,38 @@
       <c r="I29" s="3" t="n">
         <v>3.8</v>
       </c>
-      <c r="J29" s="8" t="n">
-        <v>25.2</v>
+      <c r="J29" s="3" t="n">
+        <v>6.2</v>
       </c>
       <c r="K29" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L29" s="8" t="n">
-        <v>109.7</v>
+        <v>10.9</v>
       </c>
       <c r="M29" s="3" t="n">
         <v>10.5</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>12.4</v>
+        <v>13.4</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>196</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>8.6</v>
+        <v>0.6</v>
       </c>
       <c r="Q29" s="8" t="n">
-        <v>217</v>
+        <v>27</v>
       </c>
       <c r="R29" s="8" t="n">
-        <v>517.1</v>
-      </c>
-      <c r="S29" s="3" t="n">
-        <v>17</v>
+        <v>181.7</v>
+      </c>
+      <c r="S29" s="8" t="n">
+        <v>12</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>57.8</v>
+        <v>47.8</v>
       </c>
       <c r="U29" s="3" t="n">
         <v>18.6</v>
@@ -2955,16 +2953,16 @@
         <v>22.8</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="X29" s="8" t="n">
-        <v>12.7</v>
+        <v>17.3</v>
+      </c>
+      <c r="X29" s="3" t="n">
+        <v>1.3</v>
       </c>
       <c r="Y29" s="3" t="n">
         <v>60</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>111.9</v>
+        <v>112.9</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
@@ -2980,7 +2978,7 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>22848.3</v>
+        <v>2284.8</v>
       </c>
       <c r="D30" s="11" t="n">
         <v>131.2</v>
@@ -2995,7 +2993,7 @@
         <v>79.09999999999999</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>216</v>
+        <v>16</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>113.8</v>
@@ -3007,34 +3005,32 @@
         <v>113.5</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>51.2</v>
+        <v>57.2</v>
       </c>
       <c r="M30" s="3" t="n">
         <v>56.7</v>
       </c>
-      <c r="N30" s="3" t="n">
-        <v>6.5</v>
-      </c>
+      <c r="N30" s="3" t="inlineStr"/>
       <c r="O30" s="3" t="n">
-        <v>9489</v>
+        <v>489</v>
       </c>
       <c r="P30" s="3" t="n">
         <v>2</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>1113.2</v>
+        <v>113.2</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>851.7</v>
+        <v>86.7</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>844.7</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="T30" s="3" t="n">
         <v>314.8</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>35.4</v>
+        <v>55.9</v>
       </c>
       <c r="V30" s="3" t="n">
         <v>99.5</v>
@@ -3065,7 +3061,7 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>1532</v>
+        <v>432</v>
       </c>
       <c r="D31" s="11" t="n">
         <v>26.2</v>
@@ -3080,7 +3076,7 @@
         <v>58.4</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>72.40000000000001</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>2.8</v>
@@ -3088,50 +3084,48 @@
       <c r="J31" s="3" t="n">
         <v>39.1</v>
       </c>
-      <c r="K31" s="3" t="n">
-        <v>11.1</v>
-      </c>
+      <c r="K31" s="3" t="inlineStr"/>
       <c r="L31" s="8" t="n">
         <v>11.5</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="N31" s="8" t="n">
-        <v>412.8</v>
+        <v>11.2</v>
+      </c>
+      <c r="N31" s="3" t="n">
+        <v>13.8</v>
       </c>
       <c r="O31" s="3" t="n">
         <v>97.8</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>89.40000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="Q31" s="3" t="n">
         <v>22.6</v>
       </c>
       <c r="R31" s="8" t="n">
-        <v>12.5</v>
+        <v>19.3</v>
       </c>
       <c r="S31" s="8" t="n">
         <v>16.9</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>13.1</v>
+        <v>13</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>211.1</v>
-      </c>
-      <c r="V31" s="3" t="n">
+        <v>111.1</v>
+      </c>
+      <c r="V31" s="8" t="n">
         <v>19.9</v>
       </c>
-      <c r="W31" s="8" t="n">
-        <v>16.4</v>
+      <c r="W31" s="3" t="n">
+        <v>16.9</v>
       </c>
       <c r="X31" s="8" t="n">
         <v>16.6</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>13</v>
+        <v>73</v>
       </c>
       <c r="Z31" s="3" t="n">
         <v>7</v>
@@ -3150,28 +3144,28 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>528</v>
+        <v>5280.8</v>
       </c>
       <c r="D32" s="11" t="n">
-        <v>28.1</v>
+        <v>27.9</v>
       </c>
       <c r="E32" s="11" t="n">
-        <v>10.9</v>
+        <v>10.2</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="G32" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="G32" s="11" t="n">
         <v>17.7</v>
       </c>
       <c r="H32" s="3" t="n">
         <v>16.6</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>6.1</v>
+        <v>3.1</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K32" s="3" t="n">
         <v>8</v>
@@ -3180,33 +3174,33 @@
         <v>10.5</v>
       </c>
       <c r="M32" s="8" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="N32" s="3" t="n">
-        <v>11.2</v>
+        <v>20.1</v>
+      </c>
+      <c r="N32" s="8" t="n">
+        <v>12.1</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>49</v>
+        <v>91</v>
       </c>
       <c r="P32" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q32" s="3" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="R32" s="3" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="R32" s="8" t="n">
         <v>18.2</v>
       </c>
-      <c r="S32" s="8" t="n">
+      <c r="S32" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="U32" s="3" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="V32" s="8" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="V32" s="3" t="n">
         <v>21.4</v>
       </c>
       <c r="W32" s="3" t="n">
@@ -3216,10 +3210,10 @@
         <v>17.9</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>10</v>
+        <v>170</v>
       </c>
       <c r="Z32" s="3" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3238,25 +3232,25 @@
         <v>349.1</v>
       </c>
       <c r="D33" s="11" t="n">
-        <v>25</v>
+        <v>24.2</v>
       </c>
       <c r="E33" s="11" t="n">
         <v>12.8</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="G33" s="8" t="n">
-        <v>11.6</v>
+        <v>18.5</v>
+      </c>
+      <c r="G33" s="13" t="n">
+        <v>11.1</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="I33" s="8" t="n">
-        <v>95.90000000000001</v>
+        <v>8.9</v>
+      </c>
+      <c r="I33" s="3" t="n">
+        <v>16.5</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="K33" s="3" t="n">
         <v>6.8</v>
@@ -3265,46 +3259,46 @@
         <v>19.9</v>
       </c>
       <c r="M33" s="3" t="n">
-        <v>81.5</v>
-      </c>
-      <c r="N33" s="8" t="n">
-        <v>18.6</v>
+        <v>11.9</v>
+      </c>
+      <c r="N33" s="3" t="n">
+        <v>16.5</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>980.8</v>
+        <v>98</v>
       </c>
       <c r="P33" s="3" t="n">
         <v>10.9</v>
       </c>
-      <c r="Q33" s="8" t="n">
-        <v>203.5</v>
+      <c r="Q33" s="3" t="n">
+        <v>20.9</v>
       </c>
       <c r="R33" s="3" t="n">
         <v>17.8</v>
       </c>
-      <c r="S33" s="8" t="n">
+      <c r="S33" s="3" t="n">
         <v>18.9</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>9.9</v>
+        <v>29.9</v>
       </c>
       <c r="U33" s="3" t="n">
         <v>5</v>
       </c>
       <c r="V33" s="8" t="n">
-        <v>19.9</v>
+        <v>19.4</v>
       </c>
       <c r="W33" s="3" t="n">
-        <v>17.9</v>
+        <v>17.5</v>
       </c>
       <c r="X33" s="3" t="n">
         <v>1.8</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3323,40 +3317,40 @@
         <v>329.9</v>
       </c>
       <c r="D34" s="11" t="n">
-        <v>23.1</v>
+        <v>23.3</v>
       </c>
       <c r="E34" s="11" t="n">
         <v>14.7</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="G34" s="11" t="n">
         <v>8.6</v>
       </c>
-      <c r="H34" s="3" t="n">
-        <v>19.7</v>
+      <c r="H34" s="8" t="n">
+        <v>49.7</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>21.5</v>
+        <v>71.5</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>18.9</v>
+        <v>1.9</v>
       </c>
       <c r="K34" s="3" t="n">
         <v>1.7</v>
       </c>
       <c r="L34" s="8" t="n">
-        <v>16</v>
-      </c>
-      <c r="M34" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="M34" s="8" t="n">
         <v>15.9</v>
       </c>
-      <c r="N34" s="8" t="n">
-        <v>7.8</v>
+      <c r="N34" s="3" t="n">
+        <v>1.7</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>99</v>
+        <v>991</v>
       </c>
       <c r="P34" s="3" t="n">
         <v>0.2</v>
@@ -3364,8 +3358,8 @@
       <c r="Q34" s="3" t="n">
         <v>21.8</v>
       </c>
-      <c r="R34" s="8" t="n">
-        <v>81.90000000000001</v>
+      <c r="R34" s="3" t="n">
+        <v>18.1</v>
       </c>
       <c r="S34" s="8" t="n">
         <v>18.7</v>
@@ -3374,22 +3368,22 @@
         <v>72</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>72.59999999999999</v>
-      </c>
-      <c r="V34" s="8" t="n">
-        <v>87.7</v>
-      </c>
-      <c r="W34" s="8" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="V34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="X34" s="8" t="n">
-        <v>81</v>
+      <c r="X34" s="3" t="n">
+        <v>18</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>82</v>
+        <v>33</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>1.8</v>
+        <v>3.8</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3405,7 +3399,7 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>5056.7</v>
+        <v>506.7</v>
       </c>
       <c r="D35" s="11" t="n">
         <v>26.8</v>
@@ -3426,7 +3420,7 @@
         <v>3.6</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>21.1</v>
+        <v>5.5</v>
       </c>
       <c r="K35" s="3" t="n">
         <v>0</v>
@@ -3437,17 +3431,17 @@
       <c r="M35" s="3" t="n">
         <v>11.2</v>
       </c>
-      <c r="N35" s="8" t="n">
-        <v>84.8</v>
+      <c r="N35" s="3" t="n">
+        <v>14.8</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>1891</v>
+        <v>189</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q35" s="8" t="n">
-        <v>38.8</v>
+        <v>0</v>
+      </c>
+      <c r="Q35" s="3" t="n">
+        <v>23.8</v>
       </c>
       <c r="R35" s="3" t="n">
         <v>17.6</v>
@@ -3456,7 +3450,7 @@
         <v>16.8</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>252</v>
+        <v>52</v>
       </c>
       <c r="U35" s="8" t="n">
         <v>12.8</v>
@@ -3465,13 +3459,13 @@
         <v>20.8</v>
       </c>
       <c r="W35" s="8" t="n">
-        <v>67.90000000000001</v>
+        <v>16.7</v>
       </c>
       <c r="X35" s="8" t="n">
         <v>16.8</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>168.5</v>
+        <v>683.5</v>
       </c>
       <c r="Z35" s="3" t="n">
         <v>8</v>
@@ -3493,13 +3487,13 @@
         <v>535.5</v>
       </c>
       <c r="D36" s="11" t="n">
-        <v>26.5</v>
+        <v>26.3</v>
       </c>
       <c r="E36" s="11" t="n">
-        <v>10.7</v>
+        <v>10.54</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>18.4</v>
+        <v>18.2</v>
       </c>
       <c r="G36" s="11" t="n">
         <v>15.9</v>
@@ -3522,11 +3516,11 @@
       <c r="M36" s="3" t="n">
         <v>10.5</v>
       </c>
-      <c r="N36" s="8" t="n">
-        <v>12.6</v>
+      <c r="N36" s="3" t="n">
+        <v>12.4</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>199</v>
+        <v>99</v>
       </c>
       <c r="P36" s="3" t="n">
         <v>0.1</v>
@@ -3537,11 +3531,11 @@
       <c r="R36" s="3" t="n">
         <v>17.1</v>
       </c>
-      <c r="S36" s="8" t="n">
-        <v>65.8</v>
+      <c r="S36" s="3" t="n">
+        <v>15.8</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>115</v>
+        <v>5</v>
       </c>
       <c r="U36" s="8" t="n">
         <v>17.9</v>
@@ -3549,14 +3543,14 @@
       <c r="V36" s="3" t="n">
         <v>20.6</v>
       </c>
-      <c r="W36" s="8" t="n">
-        <v>14.6</v>
+      <c r="W36" s="3" t="n">
+        <v>44.6</v>
       </c>
       <c r="X36" s="3" t="n">
-        <v>1.9</v>
+        <v>11.3</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>11</v>
+        <v>5.9</v>
       </c>
       <c r="Z36" s="3" t="inlineStr"/>
       <c r="AA36" s="3" t="inlineStr">
@@ -3573,25 +3567,25 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>2290.9</v>
-      </c>
-      <c r="D37" s="10" t="n">
+        <v>2140.4</v>
+      </c>
+      <c r="D37" s="11" t="n">
         <v>128.5</v>
       </c>
-      <c r="E37" s="10" t="n">
+      <c r="E37" s="11" t="n">
         <v>60.9</v>
       </c>
-      <c r="F37" s="10" t="n">
-        <v>99.2</v>
-      </c>
-      <c r="G37" s="9" t="n">
-        <v>65.7</v>
+      <c r="F37" s="11" t="n">
+        <v>94.7</v>
+      </c>
+      <c r="G37" s="13" t="n">
+        <v>67.3</v>
       </c>
       <c r="H37" s="3" t="n">
         <v>46</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>167.9</v>
+        <v>141.7</v>
       </c>
       <c r="J37" s="3" t="n">
         <v>20.8</v>
@@ -3600,49 +3594,49 @@
         <v>8.5</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>64.5</v>
+        <v>6.4</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>74.59999999999999</v>
+        <v>74.2</v>
       </c>
       <c r="O37" s="3" t="n">
         <v>492</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>1.6</v>
+        <v>0.1</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>115.9</v>
+        <v>185.9</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>811.9</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="S37" s="3" t="n">
         <v>88</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>116.9</v>
+        <v>216.9</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>554.5</v>
+        <v>54.5</v>
       </c>
       <c r="V37" s="3" t="n">
         <v>100.9</v>
       </c>
       <c r="W37" s="3" t="n">
-        <v>83.90000000000001</v>
+        <v>837.1</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>89.8</v>
+        <v>84.8</v>
       </c>
       <c r="Y37" s="3" t="n">
         <v>359.5</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>3.9</v>
+        <v>39.4</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3658,13 +3652,13 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>448.9</v>
+        <v>448.1</v>
       </c>
       <c r="D38" s="11" t="n">
-        <v>25.6</v>
+        <v>25.7</v>
       </c>
       <c r="E38" s="11" t="n">
-        <v>12.1</v>
+        <v>12.2</v>
       </c>
       <c r="F38" s="11" t="n">
         <v>18.9</v>
@@ -3678,24 +3672,24 @@
       <c r="I38" s="3" t="n">
         <v>28.1</v>
       </c>
-      <c r="J38" s="8" t="n">
-        <v>20.1</v>
+      <c r="J38" s="3" t="n">
+        <v>90.09999999999999</v>
       </c>
       <c r="K38" s="3" t="inlineStr"/>
       <c r="L38" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="M38" s="3" t="n">
+      <c r="M38" s="8" t="n">
         <v>12.8</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>2.8</v>
+        <v>14.8</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>984.9</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="Q38" s="3" t="n">
         <v>23.1</v>
@@ -3704,25 +3698,25 @@
         <v>17.9</v>
       </c>
       <c r="S38" s="8" t="n">
-        <v>217.6</v>
+        <v>127.6</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>83.5</v>
+        <v>23.3</v>
       </c>
       <c r="U38" s="8" t="n">
-        <v>18.9</v>
+        <v>19.9</v>
       </c>
       <c r="V38" s="3" t="n">
         <v>20.2</v>
       </c>
       <c r="W38" s="8" t="n">
-        <v>116.6</v>
+        <v>16.6</v>
       </c>
       <c r="X38" s="8" t="n">
         <v>16.9</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>11.9</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="Z38" s="3" t="n">
         <v>6.9</v>
@@ -3741,10 +3735,10 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>5372.9</v>
+        <v>579.9</v>
       </c>
       <c r="D39" s="11" t="n">
-        <v>26.9</v>
+        <v>26.8</v>
       </c>
       <c r="E39" s="11" t="n">
         <v>10.9</v>
@@ -3752,12 +3746,12 @@
       <c r="F39" s="11" t="n">
         <v>18.9</v>
       </c>
-      <c r="G39" s="3" t="n">
-        <v>12.9</v>
+      <c r="G39" s="11" t="n">
+        <v>15.9</v>
       </c>
       <c r="H39" s="3" t="inlineStr"/>
       <c r="I39" s="3" t="n">
-        <v>6.5</v>
+        <v>5.1</v>
       </c>
       <c r="J39" s="3" t="n">
         <v>7</v>
@@ -3769,16 +3763,16 @@
         <v>12.7</v>
       </c>
       <c r="M39" s="8" t="n">
-        <v>82.3</v>
-      </c>
-      <c r="N39" s="8" t="n">
-        <v>19.2</v>
+        <v>2.5</v>
+      </c>
+      <c r="N39" s="3" t="n">
+        <v>1.7</v>
       </c>
       <c r="O39" s="3" t="n">
         <v>98</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>4.9</v>
+        <v>9.4</v>
       </c>
       <c r="Q39" s="3" t="n">
         <v>26.6</v>
@@ -3787,10 +3781,10 @@
         <v>18</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>10.2</v>
+        <v>4.6</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>58146.9</v>
+        <v>92.5</v>
       </c>
       <c r="U39" s="8" t="n">
         <v>18</v>
@@ -3799,7 +3793,7 @@
         <v>12.7</v>
       </c>
       <c r="W39" s="8" t="n">
-        <v>157.5</v>
+        <v>15.7</v>
       </c>
       <c r="X39" s="8" t="n">
         <v>12.3</v>
@@ -3808,7 +3802,7 @@
         <v>76</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>141.6</v>
+        <v>11.6</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3824,25 +3818,25 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>52.5</v>
+        <v>35.5</v>
       </c>
       <c r="D40" s="11" t="n">
-        <v>27.6</v>
+        <v>27.1</v>
       </c>
       <c r="E40" s="11" t="n">
-        <v>10.2</v>
+        <v>10.7</v>
       </c>
       <c r="F40" s="11" t="n">
         <v>18.9</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="H40" s="8" t="n">
-        <v>12.9</v>
+        <v>11.6</v>
+      </c>
+      <c r="H40" s="3" t="n">
+        <v>8.300000000000001</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>21.4</v>
+        <v>29.4</v>
       </c>
       <c r="J40" s="3" t="inlineStr"/>
       <c r="K40" s="3" t="n">
@@ -3861,19 +3855,19 @@
         <v>96</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>10.2</v>
+        <v>10.8</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>22</v>
+        <v>82</v>
       </c>
       <c r="R40" s="3" t="n">
         <v>18</v>
       </c>
       <c r="S40" s="3" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>69.90000000000001</v>
+        <v>69.5</v>
       </c>
       <c r="U40" s="3" t="n">
         <v>8</v>
@@ -3882,16 +3876,16 @@
         <v>12.7</v>
       </c>
       <c r="W40" s="8" t="n">
-        <v>181.3</v>
+        <v>181.5</v>
       </c>
       <c r="X40" s="3" t="n">
         <v>29.3</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3907,13 +3901,13 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>458.2</v>
+        <v>451.2</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="E41" s="3" t="n">
-        <v>18.6</v>
+        <v>28.4</v>
+      </c>
+      <c r="E41" s="11" t="n">
+        <v>8.6</v>
       </c>
       <c r="F41" s="11" t="n">
         <v>18.5</v>
@@ -3921,11 +3915,9 @@
       <c r="G41" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="H41" s="8" t="n">
-        <v>51.9</v>
-      </c>
+      <c r="H41" s="3" t="inlineStr"/>
       <c r="I41" s="3" t="n">
-        <v>3.6</v>
+        <v>0.3</v>
       </c>
       <c r="J41" s="3" t="n">
         <v>5.7</v>
@@ -3934,7 +3926,7 @@
         <v>0</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>88.7</v>
+        <v>88.3</v>
       </c>
       <c r="M41" s="3" t="n">
         <v>8.6</v>
@@ -3952,13 +3944,13 @@
         <v>23.9</v>
       </c>
       <c r="R41" s="8" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="S41" s="8" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="S41" s="3" t="n">
         <v>16.6</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>4213.5</v>
+        <v>423.5</v>
       </c>
       <c r="U41" s="3" t="n">
         <v>12.9</v>
@@ -3967,16 +3959,16 @@
         <v>22</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="X41" s="8" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="X41" s="3" t="n">
         <v>14.8</v>
       </c>
       <c r="Y41" s="3" t="n">
         <v>58</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>1112</v>
+        <v>19.8</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -3992,7 +3984,7 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>5254.4</v>
+        <v>529.4</v>
       </c>
       <c r="D42" s="11" t="n">
         <v>27.2</v>
@@ -4003,14 +3995,14 @@
       <c r="F42" s="11" t="n">
         <v>19.3</v>
       </c>
-      <c r="G42" s="9" t="n">
-        <v>15.2</v>
+      <c r="G42" s="13" t="n">
+        <v>135.2</v>
       </c>
       <c r="H42" s="3" t="n">
         <v>7.8</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>15.9</v>
+        <v>3.9</v>
       </c>
       <c r="J42" s="3" t="n">
         <v>5.6</v>
@@ -4018,13 +4010,13 @@
       <c r="K42" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L42" s="8" t="n">
+      <c r="L42" s="3" t="n">
         <v>11.9</v>
       </c>
       <c r="M42" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="N42" s="8" t="n">
+      <c r="N42" s="3" t="n">
         <v>13.3</v>
       </c>
       <c r="O42" s="3" t="n">
@@ -4037,24 +4029,24 @@
         <v>26.6</v>
       </c>
       <c r="R42" s="8" t="n">
-        <v>17.6</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="S42" s="8" t="n">
-        <v>148.7</v>
+        <v>12.7</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>153.2</v>
+        <v>43.5</v>
       </c>
       <c r="U42" s="3" t="n">
         <v>19.6</v>
       </c>
-      <c r="V42" s="3" t="n">
-        <v>2</v>
+      <c r="V42" s="8" t="n">
+        <v>22</v>
       </c>
       <c r="W42" s="3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="X42" s="8" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="X42" s="3" t="n">
         <v>14.8</v>
       </c>
       <c r="Y42" s="3" t="inlineStr"/>
@@ -4153,23 +4145,23 @@
       <c r="C45" s="3" t="n">
         <v>1911.2</v>
       </c>
-      <c r="D45" s="10" t="n">
-        <v>109.7</v>
-      </c>
-      <c r="E45" s="10" t="n">
-        <v>41.8</v>
+      <c r="D45" s="14" t="n">
+        <v>1091.7</v>
+      </c>
+      <c r="E45" s="14" t="n">
+        <v>61.8</v>
       </c>
       <c r="F45" s="11" t="n">
         <v>75.59999999999999</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>7.9</v>
+        <v>27.9</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>119.4</v>
+        <v>119.9</v>
       </c>
       <c r="J45" s="3" t="n">
         <v>20.9</v>
@@ -4178,19 +4170,19 @@
         <v>0</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="M45" s="3" t="n">
-        <v>212.9</v>
+        <v>22.9</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>91.59999999999999</v>
+        <v>31.6</v>
       </c>
       <c r="O45" s="3" t="n">
         <v>388</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>22.3</v>
+        <v>2.3</v>
       </c>
       <c r="Q45" s="3" t="n">
         <v>98.59999999999999</v>
@@ -4205,20 +4197,22 @@
         <v>216.9</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="V45" s="3" t="n">
-        <v>851.9</v>
+        <v>831.9</v>
       </c>
       <c r="W45" s="3" t="n">
-        <v>67.3</v>
-      </c>
-      <c r="X45" s="3" t="inlineStr"/>
+        <v>67.5</v>
+      </c>
+      <c r="X45" s="3" t="n">
+        <v>200.8</v>
+      </c>
       <c r="Y45" s="3" t="n">
         <v>1263</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>331.9</v>
+        <v>2331.8</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4234,7 +4228,7 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>5417.8</v>
+        <v>417.8</v>
       </c>
       <c r="D46" s="11" t="n">
         <v>27.3</v>
@@ -4254,15 +4248,15 @@
       <c r="I46" s="3" t="n">
         <v>3.6</v>
       </c>
-      <c r="J46" s="8" t="n">
-        <v>52.4</v>
+      <c r="J46" s="3" t="n">
+        <v>62.1</v>
       </c>
       <c r="K46" s="3" t="inlineStr"/>
       <c r="L46" s="8" t="n">
-        <v>41.1</v>
+        <v>11181.9</v>
       </c>
       <c r="M46" s="3" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="N46" s="3" t="n">
         <v>12.8</v>
@@ -4274,29 +4268,29 @@
         <v>6.4</v>
       </c>
       <c r="Q46" s="3" t="n">
-        <v>247.1</v>
-      </c>
-      <c r="R46" s="3" t="n">
-        <v>15.8</v>
+        <v>24.7</v>
+      </c>
+      <c r="R46" s="8" t="n">
+        <v>88.59999999999999</v>
       </c>
       <c r="S46" s="3" t="n">
         <v>11.6</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>654.7</v>
-      </c>
-      <c r="U46" s="3" t="n">
-        <v>14.7</v>
-      </c>
+        <v>54.1</v>
+      </c>
+      <c r="U46" s="3" t="inlineStr"/>
       <c r="V46" s="3" t="n">
         <v>21.3</v>
       </c>
-      <c r="W46" s="8" t="n">
+      <c r="W46" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="X46" s="3" t="inlineStr"/>
+      <c r="X46" s="3" t="n">
+        <v>1.4</v>
+      </c>
       <c r="Y46" s="3" t="n">
-        <v>1860.8</v>
+        <v>1862.4</v>
       </c>
       <c r="Z46" s="3" t="n">
         <v>81.90000000000001</v>

--- a/results/05_transient_transcription_output/702/702_196402_SF.JPG_stage_duirnal_temp_range.xlsx
+++ b/results/05_transient_transcription_output/702/702_196402_SF.JPG_stage_duirnal_temp_range.xlsx
@@ -892,8 +892,8 @@
       <c r="L5" s="3" t="n">
         <v>12.3</v>
       </c>
-      <c r="M5" s="8" t="n">
-        <v>8149.4</v>
+      <c r="M5" s="13" t="n">
+        <v>814.9399999999999</v>
       </c>
       <c r="N5" s="3" t="n">
         <v>12.9</v>
@@ -972,7 +972,7 @@
       <c r="K6" s="3" t="n">
         <v>6.5</v>
       </c>
-      <c r="L6" s="8" t="n">
+      <c r="L6" s="13" t="n">
         <v>1.1</v>
       </c>
       <c r="M6" s="3" t="n">
@@ -1157,8 +1157,8 @@
       <c r="P8" s="3" t="n">
         <v>10.9</v>
       </c>
-      <c r="Q8" s="8" t="n">
-        <v>2719.4</v>
+      <c r="Q8" s="13" t="n">
+        <v>271.94</v>
       </c>
       <c r="R8" s="3" t="n">
         <v>18.9</v>
@@ -1224,13 +1224,13 @@
       <c r="J9" s="3" t="n">
         <v>13.5</v>
       </c>
-      <c r="K9" s="3" t="n">
+      <c r="K9" s="14" t="n">
         <v>0.7</v>
       </c>
-      <c r="L9" s="3" t="n">
+      <c r="L9" s="14" t="n">
         <v>56.7</v>
       </c>
-      <c r="M9" s="3" t="n">
+      <c r="M9" s="14" t="n">
         <v>55.2</v>
       </c>
       <c r="N9" s="3" t="n">
@@ -1242,10 +1242,10 @@
       <c r="P9" s="3" t="n">
         <v>9.6</v>
       </c>
-      <c r="Q9" s="3" t="n">
+      <c r="Q9" s="14" t="n">
         <v>101.5</v>
       </c>
-      <c r="R9" s="3" t="n">
+      <c r="R9" s="14" t="n">
         <v>85.3</v>
       </c>
       <c r="S9" s="3" t="n">
@@ -1257,10 +1257,10 @@
       <c r="U9" s="3" t="n">
         <v>33.3</v>
       </c>
-      <c r="V9" s="3" t="n">
+      <c r="V9" s="14" t="n">
         <v>95</v>
       </c>
-      <c r="W9" s="3" t="n">
+      <c r="W9" s="14" t="n">
         <v>8.4</v>
       </c>
       <c r="X9" s="3" t="n">
@@ -1310,10 +1310,10 @@
         <v>418.1</v>
       </c>
       <c r="K10" s="3" t="inlineStr"/>
-      <c r="L10" s="8" t="n">
+      <c r="L10" s="14" t="n">
         <v>11.3</v>
       </c>
-      <c r="M10" s="8" t="n">
+      <c r="M10" s="14" t="n">
         <v>11</v>
       </c>
       <c r="N10" s="8" t="n">
@@ -1325,10 +1325,10 @@
       <c r="P10" s="3" t="n">
         <v>10.5</v>
       </c>
-      <c r="Q10" s="3" t="n">
+      <c r="Q10" s="14" t="n">
         <v>20.3</v>
       </c>
-      <c r="R10" s="3" t="n">
+      <c r="R10" s="14" t="n">
         <v>17.9</v>
       </c>
       <c r="S10" s="8" t="n">
@@ -1340,10 +1340,10 @@
       <c r="U10" s="3" t="n">
         <v>72.40000000000001</v>
       </c>
-      <c r="V10" s="3" t="n">
+      <c r="V10" s="14" t="n">
         <v>19</v>
       </c>
-      <c r="W10" s="8" t="n">
+      <c r="W10" s="14" t="n">
         <v>17</v>
       </c>
       <c r="X10" s="3" t="n">
@@ -1398,7 +1398,7 @@
       <c r="L11" s="3" t="n">
         <v>17.4</v>
       </c>
-      <c r="M11" s="3" t="n">
+      <c r="M11" s="13" t="n">
         <v>1.2</v>
       </c>
       <c r="N11" s="3" t="n">
@@ -1480,8 +1480,8 @@
       <c r="K12" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="L12" s="8" t="n">
-        <v>191.7</v>
+      <c r="L12" s="13" t="n">
+        <v>19.17</v>
       </c>
       <c r="M12" s="8" t="n">
         <v>22.1</v>
@@ -1580,7 +1580,7 @@
       <c r="P13" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="Q13" s="8" t="n">
+      <c r="Q13" s="13" t="n">
         <v>80.90000000000001</v>
       </c>
       <c r="R13" s="3" t="n">
@@ -1598,8 +1598,8 @@
       <c r="V13" s="3" t="n">
         <v>19.6</v>
       </c>
-      <c r="W13" s="8" t="n">
-        <v>791.5</v>
+      <c r="W13" s="13" t="n">
+        <v>79.15000000000001</v>
       </c>
       <c r="X13" s="8" t="n">
         <v>29.1</v>
@@ -1653,7 +1653,7 @@
       <c r="L14" s="8" t="n">
         <v>15.8</v>
       </c>
-      <c r="M14" s="8" t="n">
+      <c r="M14" s="13" t="n">
         <v>83</v>
       </c>
       <c r="N14" s="3" t="n">
@@ -1665,7 +1665,7 @@
       <c r="P14" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="Q14" s="8" t="n">
+      <c r="Q14" s="13" t="n">
         <v>46.9</v>
       </c>
       <c r="R14" s="8" t="n">
@@ -1678,7 +1678,7 @@
       <c r="U14" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="V14" s="8" t="n">
+      <c r="V14" s="13" t="n">
         <v>59.5</v>
       </c>
       <c r="W14" s="3" t="n">
@@ -1751,7 +1751,7 @@
       <c r="Q15" s="3" t="n">
         <v>25.5</v>
       </c>
-      <c r="R15" s="8" t="n">
+      <c r="R15" s="13" t="n">
         <v>72.59999999999999</v>
       </c>
       <c r="S15" s="3" t="n">
@@ -1763,7 +1763,7 @@
       <c r="U15" s="8" t="n">
         <v>17</v>
       </c>
-      <c r="V15" s="3" t="n">
+      <c r="V15" s="13" t="n">
         <v>2</v>
       </c>
       <c r="W15" s="3" t="n">
@@ -1815,13 +1815,13 @@
       <c r="J16" s="3" t="n">
         <v>21.8</v>
       </c>
-      <c r="K16" s="3" t="n">
+      <c r="K16" s="14" t="n">
         <v>39.8</v>
       </c>
-      <c r="L16" s="3" t="n">
+      <c r="L16" s="14" t="n">
         <v>5.9</v>
       </c>
-      <c r="M16" s="3" t="n">
+      <c r="M16" s="14" t="n">
         <v>58.2</v>
       </c>
       <c r="N16" s="3" t="n">
@@ -1833,10 +1833,10 @@
       <c r="P16" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="Q16" s="3" t="n">
+      <c r="Q16" s="14" t="n">
         <v>1111</v>
       </c>
-      <c r="R16" s="3" t="n">
+      <c r="R16" s="14" t="n">
         <v>82.2</v>
       </c>
       <c r="S16" s="3" t="n">
@@ -1848,10 +1848,10 @@
       <c r="U16" s="3" t="n">
         <v>60.9</v>
       </c>
-      <c r="V16" s="3" t="n">
+      <c r="V16" s="14" t="n">
         <v>9.5</v>
       </c>
-      <c r="W16" s="3" t="n">
+      <c r="W16" s="14" t="n">
         <v>801.7</v>
       </c>
       <c r="X16" s="3" t="n">
@@ -1901,10 +1901,10 @@
         <v>871.8</v>
       </c>
       <c r="K17" s="3" t="inlineStr"/>
-      <c r="L17" s="3" t="n">
+      <c r="L17" s="14" t="n">
         <v>11.8</v>
       </c>
-      <c r="M17" s="3" t="n">
+      <c r="M17" s="14" t="n">
         <v>11.6</v>
       </c>
       <c r="N17" s="8" t="n">
@@ -1916,10 +1916,10 @@
       <c r="P17" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="Q17" s="3" t="n">
+      <c r="Q17" s="14" t="n">
         <v>22.2</v>
       </c>
-      <c r="R17" s="8" t="n">
+      <c r="R17" s="14" t="n">
         <v>16.9</v>
       </c>
       <c r="S17" s="8" t="n">
@@ -1931,10 +1931,10 @@
       <c r="U17" s="3" t="n">
         <v>12.2</v>
       </c>
-      <c r="V17" s="3" t="n">
+      <c r="V17" s="14" t="n">
         <v>19.6</v>
       </c>
-      <c r="W17" s="8" t="n">
+      <c r="W17" s="14" t="n">
         <v>16.9</v>
       </c>
       <c r="X17" s="8" t="n">
@@ -1986,10 +1986,10 @@
       <c r="K18" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="L18" s="8" t="n">
-        <v>1666.6</v>
-      </c>
-      <c r="M18" s="3" t="n">
+      <c r="L18" s="13" t="n">
+        <v>166.66</v>
+      </c>
+      <c r="M18" s="13" t="n">
         <v>81.59999999999999</v>
       </c>
       <c r="N18" s="8" t="n">
@@ -2001,10 +2001,10 @@
       <c r="P18" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q18" s="3" t="n">
+      <c r="Q18" s="11" t="n">
         <v>25.8</v>
       </c>
-      <c r="R18" s="3" t="n">
+      <c r="R18" s="11" t="n">
         <v>17.3</v>
       </c>
       <c r="S18" s="8" t="n">
@@ -2016,7 +2016,7 @@
       <c r="U18" s="8" t="n">
         <v>17.9</v>
       </c>
-      <c r="V18" s="3" t="n">
+      <c r="V18" s="11" t="n">
         <v>21</v>
       </c>
       <c r="W18" s="3" t="n">
@@ -2071,8 +2071,8 @@
       <c r="K19" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L19" s="8" t="n">
-        <v>111.2</v>
+      <c r="L19" s="13" t="n">
+        <v>11.12</v>
       </c>
       <c r="M19" s="8" t="n">
         <v>11</v>
@@ -2086,10 +2086,10 @@
       <c r="P19" s="8" t="n">
         <v>9.4</v>
       </c>
-      <c r="Q19" s="3" t="n">
+      <c r="Q19" s="11" t="n">
         <v>25.9</v>
       </c>
-      <c r="R19" s="3" t="n">
+      <c r="R19" s="11" t="n">
         <v>18</v>
       </c>
       <c r="S19" s="3" t="n">
@@ -2101,7 +2101,7 @@
       <c r="U19" s="8" t="n">
         <v>7.2</v>
       </c>
-      <c r="V19" s="3" t="n">
+      <c r="V19" s="11" t="n">
         <v>21.2</v>
       </c>
       <c r="W19" s="3" t="n">
@@ -2159,8 +2159,8 @@
       <c r="L20" s="3" t="n">
         <v>11.2</v>
       </c>
-      <c r="M20" s="8" t="n">
-        <v>211</v>
+      <c r="M20" s="13" t="n">
+        <v>21.1</v>
       </c>
       <c r="N20" s="3" t="n">
         <v>13</v>
@@ -2171,10 +2171,10 @@
       <c r="P20" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="Q20" s="3" t="n">
+      <c r="Q20" s="11" t="n">
         <v>28</v>
       </c>
-      <c r="R20" s="3" t="n">
+      <c r="R20" s="11" t="n">
         <v>18.9</v>
       </c>
       <c r="S20" s="3" t="n">
@@ -2186,10 +2186,10 @@
       <c r="U20" s="3" t="n">
         <v>22.4</v>
       </c>
-      <c r="V20" s="3" t="n">
+      <c r="V20" s="11" t="n">
         <v>22.2</v>
       </c>
-      <c r="W20" s="8" t="n">
+      <c r="W20" s="13" t="n">
         <v>89.40000000000001</v>
       </c>
       <c r="X20" s="8" t="n">
@@ -2256,10 +2256,10 @@
       <c r="P21" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q21" s="3" t="n">
+      <c r="Q21" s="11" t="n">
         <v>25.6</v>
       </c>
-      <c r="R21" s="3" t="n">
+      <c r="R21" s="11" t="n">
         <v>18.2</v>
       </c>
       <c r="S21" s="3" t="n">
@@ -2271,7 +2271,7 @@
       <c r="U21" s="3" t="n">
         <v>16.2</v>
       </c>
-      <c r="V21" s="3" t="n">
+      <c r="V21" s="11" t="n">
         <v>19.8</v>
       </c>
       <c r="W21" s="3" t="n">
@@ -2341,10 +2341,10 @@
       <c r="P22" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q22" s="3" t="n">
+      <c r="Q22" s="11" t="n">
         <v>23.6</v>
       </c>
-      <c r="R22" s="3" t="n">
+      <c r="R22" s="11" t="n">
         <v>16.2</v>
       </c>
       <c r="S22" s="8" t="n">
@@ -2356,7 +2356,7 @@
       <c r="U22" s="3" t="n">
         <v>14.8</v>
       </c>
-      <c r="V22" s="3" t="n">
+      <c r="V22" s="11" t="n">
         <v>22.5</v>
       </c>
       <c r="W22" s="8" t="n">
@@ -2408,13 +2408,13 @@
       <c r="J23" s="3" t="n">
         <v>20.8</v>
       </c>
-      <c r="K23" s="3" t="n">
+      <c r="K23" s="14" t="n">
         <v>0.3</v>
       </c>
-      <c r="L23" s="3" t="n">
+      <c r="L23" s="14" t="n">
         <v>2.5</v>
       </c>
-      <c r="M23" s="3" t="n">
+      <c r="M23" s="14" t="n">
         <v>61.8</v>
       </c>
       <c r="N23" s="3" t="n">
@@ -2426,10 +2426,10 @@
       <c r="P23" s="3" t="n">
         <v>11.9</v>
       </c>
-      <c r="Q23" s="3" t="n">
+      <c r="Q23" s="11" t="n">
         <v>128.9</v>
       </c>
-      <c r="R23" s="3" t="n">
+      <c r="R23" s="14" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="S23" s="3" t="n">
@@ -2441,10 +2441,10 @@
       <c r="U23" s="3" t="n">
         <v>88.5</v>
       </c>
-      <c r="V23" s="3" t="n">
+      <c r="V23" s="11" t="n">
         <v>106.7</v>
       </c>
-      <c r="W23" s="3" t="n">
+      <c r="W23" s="14" t="n">
         <v>85.5</v>
       </c>
       <c r="X23" s="3" t="n">
@@ -2494,10 +2494,10 @@
         <v>16.1</v>
       </c>
       <c r="K24" s="3" t="inlineStr"/>
-      <c r="L24" s="3" t="n">
+      <c r="L24" s="14" t="n">
         <v>12.5</v>
       </c>
-      <c r="M24" s="8" t="n">
+      <c r="M24" s="14" t="n">
         <v>12.4</v>
       </c>
       <c r="N24" s="3" t="n">
@@ -2509,10 +2509,10 @@
       <c r="P24" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q24" s="3" t="n">
+      <c r="Q24" s="11" t="n">
         <v>25.8</v>
       </c>
-      <c r="R24" s="3" t="n">
+      <c r="R24" s="11" t="n">
         <v>17.6</v>
       </c>
       <c r="S24" s="3" t="n">
@@ -2524,10 +2524,10 @@
       <c r="U24" s="8" t="n">
         <v>177.1</v>
       </c>
-      <c r="V24" s="3" t="n">
+      <c r="V24" s="11" t="n">
         <v>21.3</v>
       </c>
-      <c r="W24" s="3" t="n">
+      <c r="W24" s="14" t="n">
         <v>1.7</v>
       </c>
       <c r="X24" s="8" t="n">
@@ -2582,7 +2582,7 @@
       <c r="L25" s="8" t="n">
         <v>10.7</v>
       </c>
-      <c r="M25" s="3" t="n">
+      <c r="M25" s="13" t="n">
         <v>2.9</v>
       </c>
       <c r="N25" s="8" t="n">
@@ -2594,7 +2594,7 @@
       <c r="P25" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="Q25" s="8" t="n">
+      <c r="Q25" s="13" t="n">
         <v>41.5</v>
       </c>
       <c r="R25" s="8" t="n">
@@ -2609,11 +2609,11 @@
       <c r="U25" s="8" t="n">
         <v>113.2</v>
       </c>
-      <c r="V25" s="3" t="n">
+      <c r="V25" s="11" t="n">
         <v>21.3</v>
       </c>
-      <c r="W25" s="8" t="n">
-        <v>216.9</v>
+      <c r="W25" s="13" t="n">
+        <v>21.69</v>
       </c>
       <c r="X25" s="8" t="n">
         <v>16.8</v>
@@ -2664,8 +2664,8 @@
       <c r="K26" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="L26" s="8" t="n">
-        <v>109.4</v>
+      <c r="L26" s="13" t="n">
+        <v>10.94</v>
       </c>
       <c r="M26" s="8" t="n">
         <v>10.2</v>
@@ -2694,7 +2694,7 @@
       <c r="U26" s="3" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="V26" s="3" t="n">
+      <c r="V26" s="11" t="n">
         <v>21.6</v>
       </c>
       <c r="W26" s="3" t="n">
@@ -2767,8 +2767,8 @@
       <c r="Q27" s="3" t="n">
         <v>17.6</v>
       </c>
-      <c r="R27" s="8" t="n">
-        <v>1618.2</v>
+      <c r="R27" s="13" t="n">
+        <v>161.82</v>
       </c>
       <c r="S27" s="3" t="n">
         <v>11.2</v>
@@ -2779,10 +2779,10 @@
       <c r="U27" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="V27" s="3" t="n">
+      <c r="V27" s="11" t="n">
         <v>17.4</v>
       </c>
-      <c r="W27" s="3" t="n">
+      <c r="W27" s="13" t="n">
         <v>0.7</v>
       </c>
       <c r="X27" s="8" t="n">
@@ -2834,8 +2834,8 @@
       <c r="K28" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="L28" s="8" t="n">
-        <v>935.4</v>
+      <c r="L28" s="13" t="n">
+        <v>93.53999999999999</v>
       </c>
       <c r="M28" s="8" t="n">
         <v>13.3</v>
@@ -2864,7 +2864,7 @@
       <c r="U28" s="3" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="V28" s="3" t="n">
+      <c r="V28" s="11" t="n">
         <v>16.9</v>
       </c>
       <c r="W28" s="3" t="n">
@@ -2937,8 +2937,8 @@
       <c r="Q29" s="8" t="n">
         <v>27</v>
       </c>
-      <c r="R29" s="8" t="n">
-        <v>181.7</v>
+      <c r="R29" s="13" t="n">
+        <v>18.17</v>
       </c>
       <c r="S29" s="8" t="n">
         <v>12</v>
@@ -2949,7 +2949,7 @@
       <c r="U29" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="V29" s="3" t="n">
+      <c r="V29" s="11" t="n">
         <v>22.8</v>
       </c>
       <c r="W29" s="3" t="n">
@@ -3001,13 +3001,13 @@
       <c r="J30" s="3" t="n">
         <v>119.5</v>
       </c>
-      <c r="K30" s="3" t="n">
+      <c r="K30" s="14" t="n">
         <v>113.5</v>
       </c>
-      <c r="L30" s="3" t="n">
+      <c r="L30" s="14" t="n">
         <v>57.2</v>
       </c>
-      <c r="M30" s="3" t="n">
+      <c r="M30" s="14" t="n">
         <v>56.7</v>
       </c>
       <c r="N30" s="3" t="inlineStr"/>
@@ -3017,10 +3017,10 @@
       <c r="P30" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="Q30" s="3" t="n">
+      <c r="Q30" s="14" t="n">
         <v>113.2</v>
       </c>
-      <c r="R30" s="3" t="n">
+      <c r="R30" s="14" t="n">
         <v>86.7</v>
       </c>
       <c r="S30" s="3" t="n">
@@ -3032,10 +3032,10 @@
       <c r="U30" s="3" t="n">
         <v>55.9</v>
       </c>
-      <c r="V30" s="3" t="n">
+      <c r="V30" s="14" t="n">
         <v>99.5</v>
       </c>
-      <c r="W30" s="3" t="n">
+      <c r="W30" s="14" t="n">
         <v>81.90000000000001</v>
       </c>
       <c r="X30" s="3" t="n">
@@ -3085,10 +3085,10 @@
         <v>39.1</v>
       </c>
       <c r="K31" s="3" t="inlineStr"/>
-      <c r="L31" s="8" t="n">
+      <c r="L31" s="14" t="n">
         <v>11.5</v>
       </c>
-      <c r="M31" s="3" t="n">
+      <c r="M31" s="14" t="n">
         <v>11.2</v>
       </c>
       <c r="N31" s="3" t="n">
@@ -3100,10 +3100,10 @@
       <c r="P31" s="3" t="n">
         <v>8.9</v>
       </c>
-      <c r="Q31" s="3" t="n">
+      <c r="Q31" s="14" t="n">
         <v>22.6</v>
       </c>
-      <c r="R31" s="8" t="n">
+      <c r="R31" s="14" t="n">
         <v>19.3</v>
       </c>
       <c r="S31" s="8" t="n">
@@ -3115,10 +3115,10 @@
       <c r="U31" s="3" t="n">
         <v>111.1</v>
       </c>
-      <c r="V31" s="8" t="n">
+      <c r="V31" s="11" t="n">
         <v>19.9</v>
       </c>
-      <c r="W31" s="3" t="n">
+      <c r="W31" s="14" t="n">
         <v>16.9</v>
       </c>
       <c r="X31" s="8" t="n">
@@ -3170,7 +3170,7 @@
       <c r="K32" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="L32" s="8" t="n">
+      <c r="L32" s="11" t="n">
         <v>10.5</v>
       </c>
       <c r="M32" s="8" t="n">
@@ -3188,7 +3188,7 @@
       <c r="Q32" s="3" t="n">
         <v>21.1</v>
       </c>
-      <c r="R32" s="8" t="n">
+      <c r="R32" s="11" t="n">
         <v>18.2</v>
       </c>
       <c r="S32" s="3" t="n">
@@ -3255,7 +3255,7 @@
       <c r="K33" s="3" t="n">
         <v>6.8</v>
       </c>
-      <c r="L33" s="3" t="n">
+      <c r="L33" s="11" t="n">
         <v>19.9</v>
       </c>
       <c r="M33" s="3" t="n">
@@ -3273,7 +3273,7 @@
       <c r="Q33" s="3" t="n">
         <v>20.9</v>
       </c>
-      <c r="R33" s="3" t="n">
+      <c r="R33" s="11" t="n">
         <v>17.8</v>
       </c>
       <c r="S33" s="3" t="n">
@@ -3340,7 +3340,7 @@
       <c r="K34" s="3" t="n">
         <v>1.7</v>
       </c>
-      <c r="L34" s="8" t="n">
+      <c r="L34" s="11" t="n">
         <v>12</v>
       </c>
       <c r="M34" s="8" t="n">
@@ -3358,7 +3358,7 @@
       <c r="Q34" s="3" t="n">
         <v>21.8</v>
       </c>
-      <c r="R34" s="3" t="n">
+      <c r="R34" s="11" t="n">
         <v>18.1</v>
       </c>
       <c r="S34" s="8" t="n">
@@ -3370,7 +3370,7 @@
       <c r="U34" s="3" t="n">
         <v>8.6</v>
       </c>
-      <c r="V34" s="3" t="n">
+      <c r="V34" s="13" t="n">
         <v>0</v>
       </c>
       <c r="W34" s="3" t="n">
@@ -3425,7 +3425,7 @@
       <c r="K35" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L35" s="8" t="n">
+      <c r="L35" s="11" t="n">
         <v>13</v>
       </c>
       <c r="M35" s="3" t="n">
@@ -3443,7 +3443,7 @@
       <c r="Q35" s="3" t="n">
         <v>23.8</v>
       </c>
-      <c r="R35" s="3" t="n">
+      <c r="R35" s="11" t="n">
         <v>17.6</v>
       </c>
       <c r="S35" s="3" t="n">
@@ -3510,7 +3510,7 @@
       <c r="K36" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L36" s="3" t="n">
+      <c r="L36" s="11" t="n">
         <v>10.6</v>
       </c>
       <c r="M36" s="3" t="n">
@@ -3528,7 +3528,7 @@
       <c r="Q36" s="3" t="n">
         <v>25.5</v>
       </c>
-      <c r="R36" s="3" t="n">
+      <c r="R36" s="11" t="n">
         <v>17.1</v>
       </c>
       <c r="S36" s="3" t="n">
@@ -3543,7 +3543,7 @@
       <c r="V36" s="3" t="n">
         <v>20.6</v>
       </c>
-      <c r="W36" s="3" t="n">
+      <c r="W36" s="13" t="n">
         <v>44.6</v>
       </c>
       <c r="X36" s="3" t="n">
@@ -3590,13 +3590,13 @@
       <c r="J37" s="3" t="n">
         <v>20.8</v>
       </c>
-      <c r="K37" s="3" t="n">
+      <c r="K37" s="14" t="n">
         <v>8.5</v>
       </c>
-      <c r="L37" s="3" t="n">
+      <c r="L37" s="14" t="n">
         <v>65</v>
       </c>
-      <c r="M37" s="3" t="n">
+      <c r="M37" s="14" t="n">
         <v>6.4</v>
       </c>
       <c r="N37" s="3" t="n">
@@ -3608,10 +3608,10 @@
       <c r="P37" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="Q37" s="3" t="n">
+      <c r="Q37" s="14" t="n">
         <v>185.9</v>
       </c>
-      <c r="R37" s="3" t="n">
+      <c r="R37" s="14" t="n">
         <v>82.90000000000001</v>
       </c>
       <c r="S37" s="3" t="n">
@@ -3623,10 +3623,10 @@
       <c r="U37" s="3" t="n">
         <v>54.5</v>
       </c>
-      <c r="V37" s="3" t="n">
+      <c r="V37" s="14" t="n">
         <v>100.9</v>
       </c>
-      <c r="W37" s="3" t="n">
+      <c r="W37" s="14" t="n">
         <v>837.1</v>
       </c>
       <c r="X37" s="3" t="n">
@@ -3676,10 +3676,10 @@
         <v>90.09999999999999</v>
       </c>
       <c r="K38" s="3" t="inlineStr"/>
-      <c r="L38" s="8" t="n">
+      <c r="L38" s="11" t="n">
         <v>13</v>
       </c>
-      <c r="M38" s="8" t="n">
+      <c r="M38" s="14" t="n">
         <v>12.8</v>
       </c>
       <c r="N38" s="3" t="n">
@@ -3691,10 +3691,10 @@
       <c r="P38" s="3" t="n">
         <v>3.8</v>
       </c>
-      <c r="Q38" s="3" t="n">
+      <c r="Q38" s="14" t="n">
         <v>23.1</v>
       </c>
-      <c r="R38" s="3" t="n">
+      <c r="R38" s="11" t="n">
         <v>17.9</v>
       </c>
       <c r="S38" s="8" t="n">
@@ -3706,10 +3706,10 @@
       <c r="U38" s="8" t="n">
         <v>19.9</v>
       </c>
-      <c r="V38" s="3" t="n">
+      <c r="V38" s="14" t="n">
         <v>20.2</v>
       </c>
-      <c r="W38" s="8" t="n">
+      <c r="W38" s="14" t="n">
         <v>16.6</v>
       </c>
       <c r="X38" s="8" t="n">
@@ -3756,13 +3756,13 @@
       <c r="J39" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="K39" s="3" t="n">
+      <c r="K39" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L39" s="8" t="n">
         <v>12.7</v>
       </c>
-      <c r="M39" s="8" t="n">
+      <c r="M39" s="13" t="n">
         <v>2.5</v>
       </c>
       <c r="N39" s="3" t="n">
@@ -3792,7 +3792,7 @@
       <c r="V39" s="3" t="n">
         <v>12.7</v>
       </c>
-      <c r="W39" s="8" t="n">
+      <c r="W39" s="11" t="n">
         <v>15.7</v>
       </c>
       <c r="X39" s="8" t="n">
@@ -3839,7 +3839,7 @@
         <v>29.4</v>
       </c>
       <c r="J40" s="3" t="inlineStr"/>
-      <c r="K40" s="3" t="n">
+      <c r="K40" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L40" s="8" t="n">
@@ -3857,7 +3857,7 @@
       <c r="P40" s="3" t="n">
         <v>10.8</v>
       </c>
-      <c r="Q40" s="3" t="n">
+      <c r="Q40" s="13" t="n">
         <v>82</v>
       </c>
       <c r="R40" s="3" t="n">
@@ -3875,8 +3875,8 @@
       <c r="V40" s="3" t="n">
         <v>12.7</v>
       </c>
-      <c r="W40" s="8" t="n">
-        <v>181.5</v>
+      <c r="W40" s="11" t="n">
+        <v>18.15</v>
       </c>
       <c r="X40" s="3" t="n">
         <v>29.3</v>
@@ -3922,10 +3922,10 @@
       <c r="J41" s="3" t="n">
         <v>5.7</v>
       </c>
-      <c r="K41" s="3" t="n">
+      <c r="K41" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="L41" s="3" t="n">
+      <c r="L41" s="13" t="n">
         <v>88.3</v>
       </c>
       <c r="M41" s="3" t="n">
@@ -3958,7 +3958,7 @@
       <c r="V41" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="W41" s="3" t="n">
+      <c r="W41" s="11" t="n">
         <v>16.3</v>
       </c>
       <c r="X41" s="3" t="n">
@@ -4007,13 +4007,13 @@
       <c r="J42" s="3" t="n">
         <v>5.6</v>
       </c>
-      <c r="K42" s="3" t="n">
+      <c r="K42" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L42" s="3" t="n">
         <v>11.9</v>
       </c>
-      <c r="M42" s="3" t="n">
+      <c r="M42" s="13" t="n">
         <v>0.2</v>
       </c>
       <c r="N42" s="3" t="n">
@@ -4028,7 +4028,7 @@
       <c r="Q42" s="3" t="n">
         <v>26.6</v>
       </c>
-      <c r="R42" s="8" t="n">
+      <c r="R42" s="13" t="n">
         <v>87.59999999999999</v>
       </c>
       <c r="S42" s="8" t="n">
@@ -4043,7 +4043,7 @@
       <c r="V42" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="W42" s="3" t="n">
+      <c r="W42" s="11" t="n">
         <v>16.3</v>
       </c>
       <c r="X42" s="3" t="n">
@@ -4074,19 +4074,19 @@
       <c r="H43" s="3" t="inlineStr"/>
       <c r="I43" s="3" t="inlineStr"/>
       <c r="J43" s="3" t="inlineStr"/>
-      <c r="K43" s="3" t="inlineStr"/>
-      <c r="L43" s="3" t="inlineStr"/>
-      <c r="M43" s="3" t="inlineStr"/>
+      <c r="K43" s="11" t="inlineStr"/>
+      <c r="L43" s="12" t="inlineStr"/>
+      <c r="M43" s="12" t="inlineStr"/>
       <c r="N43" s="3" t="inlineStr"/>
       <c r="O43" s="3" t="inlineStr"/>
       <c r="P43" s="3" t="inlineStr"/>
-      <c r="Q43" s="3" t="inlineStr"/>
-      <c r="R43" s="3" t="inlineStr"/>
+      <c r="Q43" s="12" t="inlineStr"/>
+      <c r="R43" s="12" t="inlineStr"/>
       <c r="S43" s="3" t="inlineStr"/>
       <c r="T43" s="3" t="inlineStr"/>
       <c r="U43" s="3" t="inlineStr"/>
-      <c r="V43" s="3" t="inlineStr"/>
-      <c r="W43" s="3" t="inlineStr"/>
+      <c r="V43" s="12" t="inlineStr"/>
+      <c r="W43" s="11" t="inlineStr"/>
       <c r="X43" s="3" t="inlineStr"/>
       <c r="Y43" s="3" t="inlineStr"/>
       <c r="Z43" s="3" t="inlineStr"/>
@@ -4113,19 +4113,19 @@
       <c r="H44" s="3" t="inlineStr"/>
       <c r="I44" s="3" t="inlineStr"/>
       <c r="J44" s="3" t="inlineStr"/>
-      <c r="K44" s="3" t="inlineStr"/>
-      <c r="L44" s="3" t="inlineStr"/>
-      <c r="M44" s="3" t="inlineStr"/>
+      <c r="K44" s="11" t="inlineStr"/>
+      <c r="L44" s="12" t="inlineStr"/>
+      <c r="M44" s="12" t="inlineStr"/>
       <c r="N44" s="3" t="inlineStr"/>
       <c r="O44" s="3" t="inlineStr"/>
       <c r="P44" s="3" t="inlineStr"/>
-      <c r="Q44" s="3" t="inlineStr"/>
-      <c r="R44" s="3" t="inlineStr"/>
+      <c r="Q44" s="12" t="inlineStr"/>
+      <c r="R44" s="12" t="inlineStr"/>
       <c r="S44" s="3" t="inlineStr"/>
       <c r="T44" s="3" t="inlineStr"/>
       <c r="U44" s="3" t="inlineStr"/>
-      <c r="V44" s="3" t="inlineStr"/>
-      <c r="W44" s="3" t="inlineStr"/>
+      <c r="V44" s="12" t="inlineStr"/>
+      <c r="W44" s="11" t="inlineStr"/>
       <c r="X44" s="3" t="inlineStr"/>
       <c r="Y44" s="3" t="inlineStr"/>
       <c r="Z44" s="3" t="inlineStr"/>
@@ -4166,13 +4166,13 @@
       <c r="J45" s="3" t="n">
         <v>20.9</v>
       </c>
-      <c r="K45" s="3" t="n">
+      <c r="K45" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="L45" s="3" t="n">
+      <c r="L45" s="14" t="n">
         <v>44</v>
       </c>
-      <c r="M45" s="3" t="n">
+      <c r="M45" s="14" t="n">
         <v>22.9</v>
       </c>
       <c r="N45" s="3" t="n">
@@ -4184,10 +4184,10 @@
       <c r="P45" s="3" t="n">
         <v>2.3</v>
       </c>
-      <c r="Q45" s="3" t="n">
+      <c r="Q45" s="14" t="n">
         <v>98.59999999999999</v>
       </c>
-      <c r="R45" s="3" t="n">
+      <c r="R45" s="14" t="n">
         <v>71</v>
       </c>
       <c r="S45" s="3" t="n">
@@ -4199,10 +4199,10 @@
       <c r="U45" s="3" t="n">
         <v>59</v>
       </c>
-      <c r="V45" s="3" t="n">
+      <c r="V45" s="14" t="n">
         <v>831.9</v>
       </c>
-      <c r="W45" s="3" t="n">
+      <c r="W45" s="14" t="n">
         <v>67.5</v>
       </c>
       <c r="X45" s="3" t="n">
@@ -4252,10 +4252,10 @@
         <v>62.1</v>
       </c>
       <c r="K46" s="3" t="inlineStr"/>
-      <c r="L46" s="8" t="n">
+      <c r="L46" s="14" t="n">
         <v>11181.9</v>
       </c>
-      <c r="M46" s="3" t="n">
+      <c r="M46" s="14" t="n">
         <v>1</v>
       </c>
       <c r="N46" s="3" t="n">
@@ -4267,10 +4267,10 @@
       <c r="P46" s="3" t="n">
         <v>6.4</v>
       </c>
-      <c r="Q46" s="3" t="n">
+      <c r="Q46" s="14" t="n">
         <v>24.7</v>
       </c>
-      <c r="R46" s="8" t="n">
+      <c r="R46" s="14" t="n">
         <v>88.59999999999999</v>
       </c>
       <c r="S46" s="3" t="n">
@@ -4280,10 +4280,10 @@
         <v>54.1</v>
       </c>
       <c r="U46" s="3" t="inlineStr"/>
-      <c r="V46" s="3" t="n">
+      <c r="V46" s="14" t="n">
         <v>21.3</v>
       </c>
-      <c r="W46" s="3" t="n">
+      <c r="W46" s="11" t="n">
         <v>16.8</v>
       </c>
       <c r="X46" s="3" t="n">

--- a/results/05_transient_transcription_output/702/702_196402_SF.JPG_stage_duirnal_temp_range.xlsx
+++ b/results/05_transient_transcription_output/702/702_196402_SF.JPG_stage_duirnal_temp_range.xlsx
@@ -41,8 +41,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00CC3300"/>
-        <bgColor rgb="00CC3300"/>
+        <fgColor rgb="FF6DCD57"/>
+        <bgColor rgb="FF6DCD57"/>
       </patternFill>
     </fill>
     <fill>
@@ -53,8 +53,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6DCD57"/>
-        <bgColor rgb="FF6DCD57"/>
+        <fgColor rgb="00CC3300"/>
+        <bgColor rgb="00CC3300"/>
       </patternFill>
     </fill>
     <fill>
@@ -131,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -146,22 +146,34 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -778,22 +790,22 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>301.2</v>
-      </c>
-      <c r="D4" s="11" t="n">
-        <v>27.8</v>
-      </c>
-      <c r="E4" s="11" t="n">
+        <v>391.2</v>
+      </c>
+      <c r="D4" s="9" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="E4" s="9" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="F4" s="11" t="n">
+      <c r="F4" s="9" t="n">
         <v>18.5</v>
       </c>
-      <c r="G4" s="8" t="n">
+      <c r="G4" s="12" t="n">
         <v>81.7</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>5.6</v>
+        <v>0.5</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>3.5</v>
@@ -802,52 +814,52 @@
         <v>4.9</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" s="3" t="n">
-        <v>9.300000000000001</v>
+        <v>8</v>
+      </c>
+      <c r="L4" s="9" t="n">
+        <v>9.9</v>
       </c>
       <c r="M4" s="3" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="N4" s="8" t="n">
-        <v>11.9</v>
+      <c r="N4" s="3" t="n">
+        <v>11.4</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>928</v>
+        <v>98</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>0.9</v>
+        <v>9.4</v>
       </c>
       <c r="Q4" s="3" t="n">
         <v>25.8</v>
       </c>
-      <c r="R4" s="8" t="n">
+      <c r="R4" s="12" t="n">
         <v>16.8</v>
       </c>
-      <c r="S4" s="8" t="n">
-        <v>14.1</v>
+      <c r="S4" s="12" t="n">
+        <v>19.1</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>462.5</v>
-      </c>
-      <c r="U4" s="8" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="U4" s="12" t="n">
         <v>19.1</v>
       </c>
-      <c r="V4" s="3" t="n">
+      <c r="V4" s="9" t="n">
         <v>22.1</v>
       </c>
       <c r="W4" s="3" t="n">
         <v>18.3</v>
       </c>
-      <c r="X4" s="3" t="n">
+      <c r="X4" s="12" t="n">
         <v>18.9</v>
       </c>
       <c r="Y4" s="3" t="n">
         <v>71</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>73.8</v>
+        <v>7.8</v>
       </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
@@ -865,20 +877,20 @@
       <c r="C5" s="3" t="n">
         <v>382.4</v>
       </c>
-      <c r="D5" s="11" t="n">
+      <c r="D5" s="9" t="n">
         <v>26.9</v>
       </c>
-      <c r="E5" s="11" t="n">
+      <c r="E5" s="9" t="n">
         <v>11.5</v>
       </c>
-      <c r="F5" s="11" t="n">
+      <c r="F5" s="9" t="n">
         <v>19.2</v>
       </c>
-      <c r="G5" s="8" t="n">
-        <v>59.4</v>
+      <c r="G5" s="9" t="n">
+        <v>15.4</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>7.9</v>
+        <v>7.7</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>1.8</v>
@@ -887,13 +899,13 @@
         <v>2.6</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="L5" s="3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L5" s="9" t="n">
         <v>12.3</v>
       </c>
-      <c r="M5" s="13" t="n">
-        <v>814.9399999999999</v>
+      <c r="M5" s="17" t="n">
+        <v>11.94</v>
       </c>
       <c r="N5" s="3" t="n">
         <v>12.9</v>
@@ -904,7 +916,7 @@
       <c r="P5" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="Q5" s="8" t="n">
+      <c r="Q5" s="3" t="n">
         <v>19.6</v>
       </c>
       <c r="R5" s="3" t="n">
@@ -916,12 +928,14 @@
       <c r="T5" s="3" t="n">
         <v>91</v>
       </c>
-      <c r="U5" s="3" t="inlineStr"/>
-      <c r="V5" s="8" t="n">
+      <c r="U5" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="V5" s="9" t="n">
         <v>19.5</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>17.2</v>
+        <v>13.2</v>
       </c>
       <c r="X5" s="3" t="n">
         <v>18.3</v>
@@ -930,7 +944,7 @@
         <v>80.5</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>469.5</v>
+        <v>4.4</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -948,20 +962,20 @@
       <c r="C6" s="3" t="n">
         <v>309.1</v>
       </c>
-      <c r="D6" s="11" t="n">
+      <c r="D6" s="9" t="n">
         <v>25.9</v>
       </c>
-      <c r="E6" s="11" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="F6" s="11" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="G6" s="11" t="n">
+      <c r="E6" s="9" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="F6" s="9" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="G6" s="3" t="n">
         <v>15</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>7.9</v>
+        <v>7.5</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>1.2</v>
@@ -970,12 +984,12 @@
         <v>1.7</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="L6" s="13" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="M6" s="3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="L6" s="9" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="M6" s="12" t="n">
         <v>11</v>
       </c>
       <c r="N6" s="3" t="n">
@@ -987,29 +1001,29 @@
       <c r="P6" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q6" s="8" t="n">
+      <c r="Q6" s="12" t="n">
         <v>15.4</v>
       </c>
       <c r="R6" s="3" t="n">
         <v>14.7</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>11.6</v>
+        <v>1.6</v>
       </c>
       <c r="T6" s="3" t="n">
         <v>92</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="V6" s="3" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="V6" s="9" t="n">
         <v>15.8</v>
       </c>
-      <c r="W6" s="3" t="n">
-        <v>24.6</v>
+      <c r="W6" s="12" t="n">
+        <v>15.3</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>17.1</v>
+        <v>17.9</v>
       </c>
       <c r="Y6" s="3" t="n">
         <v>95</v>
@@ -1033,74 +1047,74 @@
       <c r="C7" s="3" t="n">
         <v>275.8</v>
       </c>
-      <c r="D7" s="11" t="n">
+      <c r="D7" s="9" t="n">
         <v>21.9</v>
       </c>
-      <c r="E7" s="11" t="n">
+      <c r="E7" s="9" t="n">
         <v>12.9</v>
       </c>
-      <c r="F7" s="11" t="n">
+      <c r="F7" s="9" t="n">
         <v>17.4</v>
       </c>
-      <c r="G7" s="11" t="n">
+      <c r="G7" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="H7" s="8" t="n">
-        <v>12.9</v>
+      <c r="H7" s="3" t="n">
+        <v>11.9</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>11.2</v>
+        <v>1.2</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>11.9</v>
+        <v>1.7</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="L7" s="9" t="n">
         <v>13.2</v>
       </c>
-      <c r="M7" s="8" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="N7" s="3" t="n">
-        <v>5</v>
+      <c r="M7" s="12" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="N7" s="12" t="n">
+        <v>15</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>98.8</v>
+        <v>99</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q7" s="8" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q7" s="3" t="n">
         <v>19.3</v>
       </c>
-      <c r="R7" s="8" t="n">
+      <c r="R7" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="S7" s="8" t="n">
-        <v>17.7</v>
+      <c r="S7" s="3" t="n">
+        <v>97.09999999999999</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>19</v>
+        <v>72</v>
       </c>
       <c r="U7" s="3" t="n">
         <v>4.8</v>
       </c>
-      <c r="V7" s="3" t="n">
+      <c r="V7" s="9" t="n">
         <v>18.9</v>
       </c>
       <c r="W7" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="X7" s="3" t="n">
+      <c r="X7" s="12" t="n">
         <v>17.9</v>
       </c>
       <c r="Y7" s="3" t="n">
         <v>81</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1118,20 +1132,20 @@
       <c r="C8" s="3" t="n">
         <v>391.2</v>
       </c>
-      <c r="D8" s="11" t="n">
-        <v>27.3</v>
-      </c>
-      <c r="E8" s="11" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="F8" s="11" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="G8" s="3" t="n">
+      <c r="D8" s="9" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="E8" s="9" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="F8" s="9" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="G8" s="9" t="n">
         <v>15.8</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>7.2</v>
+        <v>17.7</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>2.2</v>
@@ -1142,43 +1156,43 @@
       <c r="K8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L8" s="3" t="n">
+      <c r="L8" s="9" t="n">
         <v>10.8</v>
       </c>
       <c r="M8" s="3" t="n">
         <v>10.6</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>1.2</v>
+        <v>12.7</v>
       </c>
       <c r="O8" s="3" t="n">
         <v>98</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="Q8" s="13" t="n">
-        <v>271.94</v>
+        <v>0.4</v>
+      </c>
+      <c r="Q8" s="12" t="n">
+        <v>27.4</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>18.9</v>
+        <v>18.4</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>1.9</v>
+        <v>19.5</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>76</v>
+        <v>176</v>
       </c>
       <c r="U8" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="V8" s="3" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="W8" s="3" t="n">
-        <v>17.3</v>
-      </c>
-      <c r="X8" s="3" t="n">
+      <c r="V8" s="9" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="W8" s="17" t="n">
+        <v>97.3</v>
+      </c>
+      <c r="X8" s="12" t="n">
         <v>18.9</v>
       </c>
       <c r="Y8" s="3" t="n">
@@ -1201,73 +1215,71 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>43927.4</v>
-      </c>
-      <c r="D9" s="11" t="n">
+        <v>1749.7</v>
+      </c>
+      <c r="D9" s="9" t="n">
         <v>128.9</v>
       </c>
-      <c r="E9" s="11" t="n">
+      <c r="E9" s="9" t="n">
         <v>55</v>
       </c>
-      <c r="F9" s="11" t="n">
+      <c r="F9" s="9" t="n">
         <v>91.90000000000001</v>
       </c>
-      <c r="G9" s="11" t="n">
-        <v>73.90000000000001</v>
+      <c r="G9" s="3" t="n">
+        <v>13.9</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>12.6</v>
+        <v>140.6</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>97.90000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="J9" s="3" t="n">
         <v>13.5</v>
       </c>
-      <c r="K9" s="14" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="L9" s="14" t="n">
+      <c r="K9" s="18" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="L9" s="18" t="n">
         <v>56.7</v>
       </c>
-      <c r="M9" s="14" t="n">
-        <v>55.2</v>
+      <c r="M9" s="18" t="n">
+        <v>551.2</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>55.1</v>
+        <v>766.1</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>684.8</v>
-      </c>
-      <c r="P9" s="3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="Q9" s="14" t="n">
+        <v>484.9</v>
+      </c>
+      <c r="P9" s="3" t="inlineStr"/>
+      <c r="Q9" s="18" t="n">
         <v>101.5</v>
       </c>
-      <c r="R9" s="14" t="n">
-        <v>85.3</v>
+      <c r="R9" s="18" t="n">
+        <v>185.3</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>88.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>3801.5</v>
+        <v>380.5</v>
       </c>
       <c r="U9" s="3" t="n">
         <v>33.3</v>
       </c>
-      <c r="V9" s="14" t="n">
+      <c r="V9" s="9" t="n">
         <v>95</v>
       </c>
-      <c r="W9" s="14" t="n">
-        <v>8.4</v>
+      <c r="W9" s="18" t="n">
+        <v>84.90000000000001</v>
       </c>
       <c r="X9" s="3" t="n">
         <v>91.09999999999999</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>9414.5</v>
+        <v>414.5</v>
       </c>
       <c r="Z9" s="3" t="n">
         <v>19.8</v>
@@ -1286,18 +1298,18 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>349.9</v>
-      </c>
-      <c r="D10" s="11" t="n">
+        <v>8349.9</v>
+      </c>
+      <c r="D10" s="9" t="n">
         <v>25.8</v>
       </c>
-      <c r="E10" s="11" t="n">
+      <c r="E10" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="F10" s="11" t="n">
+      <c r="F10" s="9" t="n">
         <v>18.4</v>
       </c>
-      <c r="G10" s="11" t="n">
+      <c r="G10" s="9" t="n">
         <v>14.8</v>
       </c>
       <c r="H10" s="3" t="n">
@@ -1306,44 +1318,44 @@
       <c r="I10" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="J10" s="8" t="n">
-        <v>418.1</v>
+      <c r="J10" s="12" t="n">
+        <v>9.4</v>
       </c>
       <c r="K10" s="3" t="inlineStr"/>
-      <c r="L10" s="14" t="n">
+      <c r="L10" s="9" t="n">
         <v>11.3</v>
       </c>
-      <c r="M10" s="14" t="n">
+      <c r="M10" s="18" t="n">
         <v>11</v>
       </c>
-      <c r="N10" s="8" t="n">
+      <c r="N10" s="12" t="n">
         <v>13</v>
       </c>
       <c r="O10" s="3" t="n">
         <v>96.8</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="Q10" s="14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q10" s="18" t="n">
         <v>20.3</v>
       </c>
-      <c r="R10" s="14" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="S10" s="8" t="n">
+      <c r="R10" s="18" t="n">
+        <v>117.7</v>
+      </c>
+      <c r="S10" s="3" t="n">
         <v>17.7</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>26.1</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="U10" s="3" t="n">
-        <v>72.40000000000001</v>
-      </c>
-      <c r="V10" s="14" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="V10" s="9" t="n">
         <v>19</v>
       </c>
-      <c r="W10" s="14" t="n">
+      <c r="W10" s="18" t="n">
         <v>17</v>
       </c>
       <c r="X10" s="3" t="n">
@@ -1352,9 +1364,7 @@
       <c r="Y10" s="3" t="n">
         <v>82.90000000000001</v>
       </c>
-      <c r="Z10" s="3" t="n">
-        <v>6</v>
-      </c>
+      <c r="Z10" s="3" t="inlineStr"/>
       <c r="AA10" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -1371,17 +1381,17 @@
       <c r="C11" s="3" t="n">
         <v>509.3</v>
       </c>
-      <c r="D11" s="8" t="n">
+      <c r="D11" s="9" t="n">
         <v>27.3</v>
       </c>
-      <c r="E11" s="13" t="n">
-        <v>47.9</v>
-      </c>
-      <c r="F11" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="G11" s="8" t="n">
-        <v>16.6</v>
+      <c r="E11" s="9" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="F11" s="9" t="n">
+        <v>19</v>
+      </c>
+      <c r="G11" s="12" t="n">
+        <v>18.6</v>
       </c>
       <c r="H11" s="3" t="n">
         <v>6.7</v>
@@ -1393,49 +1403,49 @@
         <v>6</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>0.2</v>
+        <v>26</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="M11" s="13" t="n">
-        <v>1.2</v>
+        <v>11.4</v>
+      </c>
+      <c r="M11" s="3" t="n">
+        <v>11.8</v>
       </c>
       <c r="N11" s="3" t="n">
         <v>13</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>2.9</v>
+        <v>1</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="Q11" s="8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q11" s="12" t="n">
         <v>26.3</v>
       </c>
-      <c r="R11" s="3" t="n">
+      <c r="R11" s="9" t="n">
         <v>17.1</v>
       </c>
-      <c r="S11" s="8" t="n">
-        <v>17.9</v>
+      <c r="S11" s="12" t="n">
+        <v>14.4</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>512</v>
-      </c>
-      <c r="U11" s="3" t="n">
+        <v>62</v>
+      </c>
+      <c r="U11" s="12" t="n">
         <v>19.9</v>
       </c>
-      <c r="V11" s="3" t="n">
+      <c r="V11" s="9" t="n">
         <v>22.1</v>
       </c>
-      <c r="W11" s="8" t="n">
+      <c r="W11" s="3" t="n">
         <v>17.6</v>
       </c>
-      <c r="X11" s="3" t="n">
-        <v>19.6</v>
+      <c r="X11" s="12" t="n">
+        <v>17.6</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>66</v>
+        <v>26</v>
       </c>
       <c r="Z11" s="3" t="n">
         <v>9</v>
@@ -1454,37 +1464,37 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>506.1</v>
-      </c>
-      <c r="D12" s="8" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="E12" s="3" t="n">
+        <v>508.7</v>
+      </c>
+      <c r="D12" s="9" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="E12" s="9" t="n">
         <v>10.9</v>
       </c>
-      <c r="F12" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="G12" s="3" t="n">
+      <c r="F12" s="9" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="G12" s="9" t="n">
         <v>15</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>7.1</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="K12" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="L12" s="13" t="n">
-        <v>19.17</v>
-      </c>
-      <c r="M12" s="8" t="n">
-        <v>22.1</v>
+      <c r="L12" s="3" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="M12" s="12" t="n">
+        <v>11.9</v>
       </c>
       <c r="N12" s="3" t="n">
         <v>13.2</v>
@@ -1498,10 +1508,10 @@
       <c r="Q12" s="3" t="n">
         <v>25.4</v>
       </c>
-      <c r="R12" s="3" t="n">
+      <c r="R12" s="9" t="n">
         <v>15.5</v>
       </c>
-      <c r="S12" s="8" t="n">
+      <c r="S12" s="12" t="n">
         <v>12.9</v>
       </c>
       <c r="T12" s="3" t="n">
@@ -1510,17 +1520,17 @@
       <c r="U12" s="3" t="n">
         <v>20.4</v>
       </c>
-      <c r="V12" s="3" t="n">
+      <c r="V12" s="9" t="n">
         <v>21.3</v>
       </c>
       <c r="W12" s="3" t="n">
-        <v>19.9</v>
+        <v>19.7</v>
       </c>
       <c r="X12" s="3" t="n">
-        <v>13.7</v>
+        <v>13.1</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="Z12" s="3" t="n">
         <v>12.2</v>
@@ -1541,38 +1551,38 @@
       <c r="C13" s="3" t="n">
         <v>357.9</v>
       </c>
-      <c r="D13" s="11" t="n">
+      <c r="D13" s="9" t="n">
         <v>25.4</v>
       </c>
-      <c r="E13" s="11" t="n">
+      <c r="E13" s="9" t="n">
         <v>11.3</v>
       </c>
-      <c r="F13" s="11" t="n">
+      <c r="F13" s="9" t="n">
         <v>18.2</v>
       </c>
-      <c r="G13" s="11" t="n">
+      <c r="G13" s="9" t="n">
         <v>14.1</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="I13" s="3" t="n">
-        <v>11.4</v>
+        <v>7.3</v>
+      </c>
+      <c r="I13" s="12" t="n">
+        <v>99.40000000000001</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>8.5</v>
+        <v>0.5</v>
       </c>
       <c r="L13" s="3" t="n">
         <v>11.8</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="N13" s="8" t="n">
-        <v>23.6</v>
+        <v>21.6</v>
+      </c>
+      <c r="N13" s="12" t="n">
+        <v>13.6</v>
       </c>
       <c r="O13" s="3" t="n">
         <v>98</v>
@@ -1580,29 +1590,29 @@
       <c r="P13" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="Q13" s="13" t="n">
-        <v>80.90000000000001</v>
-      </c>
-      <c r="R13" s="3" t="n">
+      <c r="Q13" s="3" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="R13" s="9" t="n">
         <v>17.3</v>
       </c>
       <c r="S13" s="3" t="n">
-        <v>11.8</v>
+        <v>18.9</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>85.5</v>
+        <v>185.4</v>
       </c>
       <c r="U13" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="V13" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="V13" s="9" t="n">
         <v>19.6</v>
       </c>
-      <c r="W13" s="13" t="n">
-        <v>79.15000000000001</v>
-      </c>
-      <c r="X13" s="8" t="n">
-        <v>29.1</v>
+      <c r="W13" s="12" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="X13" s="12" t="n">
+        <v>19.1</v>
       </c>
       <c r="Y13" s="3" t="n">
         <v>84</v>
@@ -1626,35 +1636,35 @@
       <c r="C14" s="3" t="n">
         <v>227</v>
       </c>
-      <c r="D14" s="3" t="n">
-        <v>29.5</v>
-      </c>
-      <c r="E14" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="F14" s="3" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="G14" s="8" t="n">
+      <c r="D14" s="9" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="E14" s="9" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="F14" s="9" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="G14" s="9" t="n">
         <v>10.5</v>
       </c>
-      <c r="H14" s="8" t="n">
+      <c r="H14" s="3" t="n">
         <v>10.3</v>
       </c>
-      <c r="I14" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J14" s="3" t="n">
-        <v>28.3</v>
-      </c>
-      <c r="K14" s="8" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="L14" s="8" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="M14" s="13" t="n">
-        <v>83</v>
+      <c r="I14" s="12" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="J14" s="12" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="K14" s="3" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="L14" s="17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M14" s="12" t="n">
+        <v>13</v>
       </c>
       <c r="N14" s="3" t="n">
         <v>14.8</v>
@@ -1663,35 +1673,37 @@
         <v>98</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="Q14" s="13" t="n">
-        <v>46.9</v>
-      </c>
-      <c r="R14" s="8" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="S14" s="3" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="T14" s="3" t="inlineStr"/>
+        <v>9.699999999999999</v>
+      </c>
+      <c r="Q14" s="17" t="n">
+        <v>84.90000000000001</v>
+      </c>
+      <c r="R14" s="9" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="S14" s="12" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="T14" s="3" t="n">
+        <v>197</v>
+      </c>
       <c r="U14" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="V14" s="13" t="n">
-        <v>59.5</v>
-      </c>
-      <c r="W14" s="3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="X14" s="8" t="n">
+      <c r="V14" s="9" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="W14" s="12" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="X14" s="12" t="n">
         <v>16</v>
       </c>
       <c r="Y14" s="3" t="n">
         <v>95</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>8.699999999999999</v>
+        <v>1</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1709,17 +1721,17 @@
       <c r="C15" s="3" t="n">
         <v>631</v>
       </c>
-      <c r="D15" s="11" t="n">
+      <c r="D15" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="E15" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="F15" s="11" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="G15" s="3" t="n">
-        <v>15.6</v>
+      <c r="E15" s="9" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="F15" s="9" t="n">
+        <v>18.15</v>
+      </c>
+      <c r="G15" s="12" t="n">
+        <v>50.8</v>
       </c>
       <c r="H15" s="3" t="n">
         <v>7.9</v>
@@ -1733,8 +1745,8 @@
       <c r="K15" s="3" t="n">
         <v>21.6</v>
       </c>
-      <c r="L15" s="3" t="n">
-        <v>27.4</v>
+      <c r="L15" s="17" t="n">
+        <v>77.40000000000001</v>
       </c>
       <c r="M15" s="3" t="n">
         <v>11.3</v>
@@ -1751,20 +1763,20 @@
       <c r="Q15" s="3" t="n">
         <v>25.5</v>
       </c>
-      <c r="R15" s="13" t="n">
-        <v>72.59999999999999</v>
-      </c>
-      <c r="S15" s="3" t="n">
-        <v>15.9</v>
+      <c r="R15" s="9" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="S15" s="12" t="n">
+        <v>15.7</v>
       </c>
       <c r="T15" s="3" t="n">
         <v>48</v>
       </c>
-      <c r="U15" s="8" t="n">
-        <v>17</v>
-      </c>
-      <c r="V15" s="13" t="n">
-        <v>2</v>
+      <c r="U15" s="12" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="V15" s="9" t="n">
+        <v>20.7</v>
       </c>
       <c r="W15" s="3" t="n">
         <v>16.3</v>
@@ -1776,7 +1788,7 @@
         <v>67</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>8.699999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1791,77 +1803,75 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C16" s="3" t="n">
-        <v>2227.1</v>
-      </c>
-      <c r="D16" s="11" t="n">
+      <c r="C16" s="3" t="inlineStr"/>
+      <c r="D16" s="9" t="n">
         <v>128</v>
       </c>
-      <c r="E16" s="14" t="n">
-        <v>56.8</v>
-      </c>
-      <c r="F16" s="11" t="n">
+      <c r="E16" s="18" t="n">
+        <v>568.1</v>
+      </c>
+      <c r="F16" s="18" t="n">
         <v>92.5</v>
       </c>
-      <c r="G16" s="11" t="n">
+      <c r="G16" s="3" t="n">
         <v>71.2</v>
       </c>
       <c r="H16" s="3" t="n">
         <v>39.5</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>14.2</v>
+        <v>14.6</v>
       </c>
       <c r="J16" s="3" t="n">
         <v>21.8</v>
       </c>
-      <c r="K16" s="14" t="n">
+      <c r="K16" s="18" t="n">
         <v>39.8</v>
       </c>
-      <c r="L16" s="14" t="n">
+      <c r="L16" s="18" t="n">
         <v>5.9</v>
       </c>
-      <c r="M16" s="14" t="n">
+      <c r="M16" s="18" t="n">
         <v>58.2</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>57.1</v>
+        <v>8.4</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>399</v>
+        <v>489.8</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="Q16" s="14" t="n">
+      <c r="Q16" s="18" t="n">
         <v>1111</v>
       </c>
-      <c r="R16" s="14" t="n">
+      <c r="R16" s="9" t="n">
         <v>82.2</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>78.7</v>
+        <v>77.7</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>310.9</v>
+        <v>310.8</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>60.9</v>
-      </c>
-      <c r="V16" s="14" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="W16" s="14" t="n">
-        <v>801.7</v>
+        <v>603.9</v>
+      </c>
+      <c r="V16" s="18" t="n">
+        <v>958.2</v>
+      </c>
+      <c r="W16" s="18" t="n">
+        <v>801.9</v>
       </c>
       <c r="X16" s="3" t="n">
         <v>82.2</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>33.9</v>
+        <v>33.4</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1879,16 +1889,16 @@
       <c r="C17" s="3" t="n">
         <v>445.9</v>
       </c>
-      <c r="D17" s="11" t="n">
+      <c r="D17" s="9" t="n">
         <v>25.6</v>
       </c>
-      <c r="E17" s="11" t="n">
+      <c r="E17" s="9" t="n">
         <v>11.4</v>
       </c>
-      <c r="F17" s="11" t="n">
+      <c r="F17" s="9" t="n">
         <v>18.5</v>
       </c>
-      <c r="G17" s="11" t="n">
+      <c r="G17" s="9" t="n">
         <v>14.2</v>
       </c>
       <c r="H17" s="3" t="n">
@@ -1897,54 +1907,54 @@
       <c r="I17" s="3" t="n">
         <v>29.4</v>
       </c>
-      <c r="J17" s="8" t="n">
-        <v>871.8</v>
+      <c r="J17" s="3" t="n">
+        <v>97.40000000000001</v>
       </c>
       <c r="K17" s="3" t="inlineStr"/>
-      <c r="L17" s="14" t="n">
+      <c r="L17" s="18" t="n">
         <v>11.8</v>
       </c>
-      <c r="M17" s="14" t="n">
+      <c r="M17" s="18" t="n">
         <v>11.6</v>
       </c>
-      <c r="N17" s="8" t="n">
+      <c r="N17" s="12" t="n">
         <v>13.6</v>
       </c>
       <c r="O17" s="3" t="n">
         <v>97.8</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="Q17" s="14" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="Q17" s="18" t="n">
         <v>22.2</v>
       </c>
-      <c r="R17" s="14" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="S17" s="8" t="n">
+      <c r="R17" s="9" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="S17" s="3" t="n">
         <v>15.5</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>42</v>
+        <v>362</v>
       </c>
       <c r="U17" s="3" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="V17" s="14" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="V17" s="9" t="n">
         <v>19.6</v>
       </c>
-      <c r="W17" s="14" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="X17" s="8" t="n">
+      <c r="W17" s="18" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="X17" s="12" t="n">
         <v>16.5</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>72.8</v>
+        <v>872.8</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>6.8</v>
+        <v>1.8</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1960,25 +1970,25 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>455.5</v>
-      </c>
-      <c r="D18" s="11" t="n">
+        <v>845.5</v>
+      </c>
+      <c r="D18" s="9" t="n">
         <v>25.9</v>
       </c>
-      <c r="E18" s="11" t="n">
+      <c r="E18" s="9" t="n">
         <v>10.9</v>
       </c>
-      <c r="F18" s="11" t="n">
+      <c r="F18" s="9" t="n">
         <v>18.4</v>
       </c>
-      <c r="G18" s="8" t="n">
-        <v>13.8</v>
+      <c r="G18" s="12" t="n">
+        <v>13</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>2.9</v>
+        <v>7.9</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>6.7</v>
+        <v>0.4</v>
       </c>
       <c r="J18" s="3" t="n">
         <v>3.3</v>
@@ -1986,50 +1996,50 @@
       <c r="K18" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="L18" s="13" t="n">
-        <v>166.66</v>
-      </c>
-      <c r="M18" s="13" t="n">
-        <v>81.59999999999999</v>
-      </c>
-      <c r="N18" s="8" t="n">
-        <v>16</v>
+      <c r="L18" s="12" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="M18" s="17" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="N18" s="12" t="n">
+        <v>16.5</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>19</v>
+        <v>99</v>
       </c>
       <c r="P18" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q18" s="11" t="n">
+      <c r="Q18" s="9" t="n">
         <v>25.8</v>
       </c>
-      <c r="R18" s="11" t="n">
-        <v>17.3</v>
-      </c>
-      <c r="S18" s="8" t="n">
-        <v>110.4</v>
+      <c r="R18" s="3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="S18" s="12" t="n">
+        <v>15.4</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="U18" s="8" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="U18" s="12" t="n">
         <v>17.9</v>
       </c>
-      <c r="V18" s="11" t="n">
+      <c r="V18" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="W18" s="3" t="n">
+      <c r="W18" s="12" t="n">
         <v>15.5</v>
       </c>
-      <c r="X18" s="3" t="n">
+      <c r="X18" s="12" t="n">
         <v>19.6</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>110.7</v>
+        <v>10.4</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -2045,19 +2055,19 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>531.9</v>
-      </c>
-      <c r="D19" s="11" t="n">
+        <v>531.1</v>
+      </c>
+      <c r="D19" s="9" t="n">
         <v>28</v>
       </c>
-      <c r="E19" s="11" t="n">
+      <c r="E19" s="9" t="n">
         <v>10.6</v>
       </c>
-      <c r="F19" s="11" t="n">
+      <c r="F19" s="9" t="n">
         <v>19.3</v>
       </c>
-      <c r="G19" s="11" t="n">
-        <v>17.4</v>
+      <c r="G19" s="3" t="n">
+        <v>17.9</v>
       </c>
       <c r="H19" s="3" t="n">
         <v>7.2</v>
@@ -2071,10 +2081,10 @@
       <c r="K19" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L19" s="13" t="n">
-        <v>11.12</v>
-      </c>
-      <c r="M19" s="8" t="n">
+      <c r="L19" s="3" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="M19" s="3" t="n">
         <v>11</v>
       </c>
       <c r="N19" s="3" t="n">
@@ -2083,25 +2093,25 @@
       <c r="O19" s="3" t="n">
         <v>98</v>
       </c>
-      <c r="P19" s="8" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="Q19" s="11" t="n">
+      <c r="P19" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q19" s="9" t="n">
         <v>25.9</v>
       </c>
-      <c r="R19" s="11" t="n">
+      <c r="R19" s="3" t="n">
         <v>18</v>
       </c>
       <c r="S19" s="3" t="n">
         <v>16.2</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="U19" s="8" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="U19" s="12" t="n">
         <v>7.2</v>
       </c>
-      <c r="V19" s="11" t="n">
+      <c r="V19" s="9" t="n">
         <v>21.2</v>
       </c>
       <c r="W19" s="3" t="n">
@@ -2114,7 +2124,7 @@
         <v>74</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>16.6</v>
+        <v>6.6</v>
       </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
@@ -2132,74 +2142,74 @@
       <c r="C20" s="3" t="n">
         <v>542.2</v>
       </c>
-      <c r="D20" s="11" t="n">
+      <c r="D20" s="9" t="n">
         <v>28.2</v>
       </c>
-      <c r="E20" s="11" t="n">
+      <c r="E20" s="9" t="n">
         <v>10.4</v>
       </c>
-      <c r="F20" s="11" t="n">
+      <c r="F20" s="9" t="n">
         <v>19.3</v>
       </c>
-      <c r="G20" s="11" t="n">
+      <c r="G20" s="9" t="n">
         <v>17.8</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>6.9</v>
       </c>
-      <c r="I20" s="8" t="n">
-        <v>33.5</v>
+      <c r="I20" s="12" t="n">
+        <v>33.3</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>4.9</v>
+        <v>5.9</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>10.2</v>
+        <v>0.2</v>
       </c>
       <c r="L20" s="3" t="n">
         <v>11.2</v>
       </c>
-      <c r="M20" s="13" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="N20" s="3" t="n">
+      <c r="M20" s="17" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="N20" s="12" t="n">
         <v>13</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>198</v>
+        <v>28</v>
       </c>
       <c r="P20" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="Q20" s="11" t="n">
+      <c r="Q20" s="9" t="n">
         <v>28</v>
       </c>
-      <c r="R20" s="11" t="n">
+      <c r="R20" s="3" t="n">
         <v>18.9</v>
       </c>
       <c r="S20" s="3" t="n">
-        <v>11.6</v>
+        <v>15.3</v>
       </c>
       <c r="T20" s="3" t="n">
         <v>40.5</v>
       </c>
-      <c r="U20" s="3" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="V20" s="11" t="n">
+      <c r="U20" s="12" t="n">
+        <v>222.4</v>
+      </c>
+      <c r="V20" s="9" t="n">
         <v>22.2</v>
       </c>
-      <c r="W20" s="13" t="n">
-        <v>89.40000000000001</v>
-      </c>
-      <c r="X20" s="8" t="n">
-        <v>299.7</v>
+      <c r="W20" s="12" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="X20" s="12" t="n">
+        <v>19.1</v>
       </c>
       <c r="Y20" s="3" t="n">
         <v>71</v>
       </c>
       <c r="Z20" s="3" t="n">
-        <v>2.6</v>
+        <v>7.6</v>
       </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
@@ -2217,74 +2227,74 @@
       <c r="C21" s="3" t="n">
         <v>382.4</v>
       </c>
-      <c r="D21" s="11" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="E21" s="11" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="F21" s="11" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="G21" s="11" t="n">
+      <c r="D21" s="9" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="E21" s="17" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="F21" s="17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G21" s="3" t="n">
         <v>12.1</v>
       </c>
-      <c r="H21" s="8" t="n">
+      <c r="H21" s="3" t="n">
         <v>10.3</v>
       </c>
       <c r="I21" s="3" t="n">
         <v>2.4</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L21" s="3" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="M21" s="8" t="n">
+      <c r="L21" s="12" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="M21" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="N21" s="8" t="n">
-        <v>15.9</v>
+      <c r="N21" s="3" t="n">
+        <v>14.9</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="P21" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q21" s="11" t="n">
+      <c r="Q21" s="9" t="n">
         <v>25.6</v>
       </c>
-      <c r="R21" s="11" t="n">
+      <c r="R21" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="S21" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="V21" s="11" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V21" s="9" t="n">
         <v>19.8</v>
       </c>
       <c r="W21" s="3" t="n">
         <v>18.2</v>
       </c>
-      <c r="X21" s="3" t="n">
-        <v>20</v>
+      <c r="X21" s="12" t="n">
+        <v>0.9</v>
       </c>
       <c r="Y21" s="3" t="n">
         <v>87</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
@@ -2300,40 +2310,40 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>9489</v>
-      </c>
-      <c r="D22" s="11" t="n">
+        <v>989</v>
+      </c>
+      <c r="D22" s="9" t="n">
         <v>25.2</v>
       </c>
-      <c r="E22" s="11" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="F22" s="11" t="n">
-        <v>18.7</v>
+      <c r="E22" s="17" t="n">
+        <v>-7.8</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>8.699999999999999</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>13.9</v>
+        <v>13.1</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>83.5</v>
       </c>
       <c r="I22" s="3" t="n">
         <v>2.7</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>3.8</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>82.8</v>
-      </c>
-      <c r="L22" s="3" t="n">
-        <v>11.2</v>
+        <v>8</v>
+      </c>
+      <c r="L22" s="12" t="n">
+        <v>12.3</v>
       </c>
       <c r="M22" s="3" t="n">
         <v>12.2</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>1.4</v>
+        <v>14.9</v>
       </c>
       <c r="O22" s="3" t="n">
         <v>99</v>
@@ -2341,29 +2351,29 @@
       <c r="P22" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q22" s="11" t="n">
+      <c r="Q22" s="9" t="n">
         <v>23.6</v>
       </c>
-      <c r="R22" s="11" t="n">
+      <c r="R22" s="3" t="n">
         <v>16.2</v>
       </c>
-      <c r="S22" s="8" t="n">
-        <v>49.7</v>
+      <c r="S22" s="3" t="n">
+        <v>14.4</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>49.5</v>
+        <v>149.5</v>
       </c>
       <c r="U22" s="3" t="n">
         <v>14.8</v>
       </c>
-      <c r="V22" s="11" t="n">
+      <c r="V22" s="9" t="n">
         <v>22.5</v>
       </c>
-      <c r="W22" s="8" t="n">
+      <c r="W22" s="3" t="n">
         <v>15.6</v>
       </c>
-      <c r="X22" s="3" t="n">
-        <v>53.8</v>
+      <c r="X22" s="12" t="n">
+        <v>13.9</v>
       </c>
       <c r="Y22" s="3" t="n">
         <v>50.5</v>
@@ -2385,55 +2395,55 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>12320.3</v>
-      </c>
-      <c r="D23" s="11" t="n">
-        <v>132.1</v>
-      </c>
-      <c r="E23" s="11" t="n">
-        <v>56.7</v>
-      </c>
-      <c r="F23" s="11" t="n">
+        <v>2322.3</v>
+      </c>
+      <c r="D23" s="18" t="n">
+        <v>112.1</v>
+      </c>
+      <c r="E23" s="18" t="n">
+        <v>50.1</v>
+      </c>
+      <c r="F23" s="18" t="n">
         <v>94.40000000000001</v>
       </c>
-      <c r="G23" s="11" t="n">
-        <v>75.40000000000001</v>
+      <c r="G23" s="3" t="n">
+        <v>75.90000000000001</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>40.6</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>1.4</v>
+        <v>14.5</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="K23" s="14" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="K23" s="18" t="n">
         <v>0.3</v>
       </c>
-      <c r="L23" s="14" t="n">
+      <c r="L23" s="18" t="n">
         <v>2.5</v>
       </c>
-      <c r="M23" s="14" t="n">
-        <v>61.8</v>
+      <c r="M23" s="18" t="n">
+        <v>161.8</v>
       </c>
       <c r="N23" s="3" t="n">
         <v>71.5</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>293</v>
+        <v>2493</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="Q23" s="11" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="Q23" s="9" t="n">
         <v>128.9</v>
       </c>
-      <c r="R23" s="14" t="n">
-        <v>8.199999999999999</v>
+      <c r="R23" s="18" t="n">
+        <v>85</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>78.09999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="T23" s="3" t="n">
         <v>235.7</v>
@@ -2441,10 +2451,10 @@
       <c r="U23" s="3" t="n">
         <v>88.5</v>
       </c>
-      <c r="V23" s="11" t="n">
+      <c r="V23" s="9" t="n">
         <v>106.7</v>
       </c>
-      <c r="W23" s="14" t="n">
+      <c r="W23" s="18" t="n">
         <v>85.5</v>
       </c>
       <c r="X23" s="3" t="n">
@@ -2470,38 +2480,40 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>2464.1</v>
-      </c>
-      <c r="D24" s="11" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="E24" s="11" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="F24" s="11" t="n">
+        <v>464.1</v>
+      </c>
+      <c r="D24" s="9" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="E24" s="9" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="F24" s="9" t="n">
         <v>18.9</v>
       </c>
-      <c r="G24" s="8" t="n">
-        <v>57.1</v>
+      <c r="G24" s="9" t="n">
+        <v>15.1</v>
       </c>
       <c r="H24" s="3" t="n">
         <v>8.1</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>29.4</v>
-      </c>
-      <c r="J24" s="8" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="K24" s="3" t="inlineStr"/>
-      <c r="L24" s="14" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J24" s="3" t="n">
+        <v>72.09999999999999</v>
+      </c>
+      <c r="K24" s="3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="L24" s="18" t="n">
         <v>12.5</v>
       </c>
-      <c r="M24" s="14" t="n">
+      <c r="M24" s="18" t="n">
         <v>12.4</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>1.4</v>
+        <v>11.9</v>
       </c>
       <c r="O24" s="3" t="n">
         <v>98.59999999999999</v>
@@ -2509,32 +2521,32 @@
       <c r="P24" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q24" s="11" t="n">
+      <c r="Q24" s="9" t="n">
         <v>25.8</v>
       </c>
-      <c r="R24" s="11" t="n">
+      <c r="R24" s="18" t="n">
         <v>17.6</v>
       </c>
       <c r="S24" s="3" t="n">
         <v>15.6</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>27.1</v>
-      </c>
-      <c r="U24" s="8" t="n">
-        <v>177.1</v>
-      </c>
-      <c r="V24" s="11" t="n">
+        <v>47.9</v>
+      </c>
+      <c r="U24" s="3" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="V24" s="9" t="n">
         <v>21.3</v>
       </c>
-      <c r="W24" s="14" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="X24" s="8" t="n">
+      <c r="W24" s="18" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="X24" s="3" t="n">
         <v>17.2</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>68.3</v>
+        <v>58.3</v>
       </c>
       <c r="Z24" s="3" t="n">
         <v>8.199999999999999</v>
@@ -2553,69 +2565,69 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>1488.9</v>
-      </c>
-      <c r="D25" s="11" t="n">
-        <v>32.7</v>
-      </c>
-      <c r="E25" s="13" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="F25" s="11" t="n">
+        <v>488.9</v>
+      </c>
+      <c r="D25" s="9" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="E25" s="9" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="F25" s="9" t="n">
         <v>17.8</v>
       </c>
-      <c r="G25" s="3" t="n">
-        <v>13.6</v>
+      <c r="G25" s="12" t="n">
+        <v>10.9</v>
       </c>
       <c r="H25" s="3" t="n">
         <v>5.7</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>2.2</v>
+        <v>3.7</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>49.7</v>
+        <v>4.7</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="L25" s="8" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="L25" s="9" t="n">
         <v>10.7</v>
       </c>
-      <c r="M25" s="13" t="n">
+      <c r="M25" s="17" t="n">
         <v>2.9</v>
       </c>
-      <c r="N25" s="8" t="n">
-        <v>19.4</v>
+      <c r="N25" s="3" t="n">
+        <v>14</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>18</v>
+        <v>0.4</v>
       </c>
       <c r="P25" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="Q25" s="13" t="n">
-        <v>41.5</v>
-      </c>
-      <c r="R25" s="8" t="n">
-        <v>37.6</v>
+      <c r="Q25" s="9" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="R25" s="9" t="n">
+        <v>17.2</v>
       </c>
       <c r="S25" s="3" t="n">
-        <v>1.9</v>
+        <v>13.9</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="U25" s="8" t="n">
-        <v>113.2</v>
-      </c>
-      <c r="V25" s="11" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="U25" s="3" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="V25" s="9" t="n">
         <v>21.3</v>
       </c>
-      <c r="W25" s="13" t="n">
-        <v>21.69</v>
-      </c>
-      <c r="X25" s="8" t="n">
+      <c r="W25" s="9" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="X25" s="12" t="n">
         <v>16.8</v>
       </c>
       <c r="Y25" s="3" t="n">
@@ -2640,23 +2652,23 @@
       <c r="C26" s="3" t="n">
         <v>349.9</v>
       </c>
-      <c r="D26" s="11" t="n">
+      <c r="D26" s="9" t="n">
         <v>24.4</v>
       </c>
-      <c r="E26" s="11" t="n">
+      <c r="E26" s="9" t="n">
         <v>9.6</v>
       </c>
-      <c r="F26" s="11" t="n">
+      <c r="F26" s="9" t="n">
         <v>17</v>
       </c>
-      <c r="G26" s="11" t="n">
+      <c r="G26" s="9" t="n">
         <v>14.8</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="I26" s="3" t="n">
-        <v>2.3</v>
+        <v>6.6</v>
+      </c>
+      <c r="I26" s="12" t="n">
+        <v>23.4</v>
       </c>
       <c r="J26" s="3" t="n">
         <v>8.5</v>
@@ -2664,47 +2676,47 @@
       <c r="K26" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="L26" s="13" t="n">
-        <v>10.94</v>
-      </c>
-      <c r="M26" s="8" t="n">
+      <c r="L26" s="9" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="M26" s="3" t="n">
         <v>10.2</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="O26" s="3" t="n">
         <v>98</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Q26" s="3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="Q26" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="R26" s="8" t="n">
+      <c r="R26" s="9" t="n">
         <v>16.2</v>
       </c>
-      <c r="S26" s="8" t="n">
+      <c r="S26" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="T26" s="3" t="n">
         <v>63.5</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="V26" s="11" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="V26" s="9" t="n">
         <v>21.6</v>
       </c>
-      <c r="W26" s="3" t="n">
+      <c r="W26" s="9" t="n">
         <v>15.5</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>16.2</v>
+        <v>14.2</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>155</v>
+        <v>55</v>
       </c>
       <c r="Z26" s="3" t="n">
         <v>111.8</v>
@@ -2725,16 +2737,16 @@
       <c r="C27" s="3" t="n">
         <v>340.2</v>
       </c>
-      <c r="D27" s="11" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="E27" s="11" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="F27" s="11" t="n">
+      <c r="D27" s="9" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="E27" s="9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="F27" s="9" t="n">
         <v>18.1</v>
       </c>
-      <c r="G27" s="8" t="n">
+      <c r="G27" s="12" t="n">
         <v>24</v>
       </c>
       <c r="H27" s="3" t="n">
@@ -2744,34 +2756,34 @@
         <v>2</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>2.9</v>
+        <v>29.4</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="L27" s="8" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="L27" s="9" t="n">
         <v>12.4</v>
       </c>
       <c r="M27" s="3" t="n">
         <v>12.2</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>14</v>
+        <v>1.4</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="Q27" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q27" s="9" t="n">
         <v>17.6</v>
       </c>
-      <c r="R27" s="13" t="n">
-        <v>161.82</v>
-      </c>
-      <c r="S27" s="3" t="n">
-        <v>11.2</v>
+      <c r="R27" s="9" t="n">
+        <v>16</v>
+      </c>
+      <c r="S27" s="12" t="n">
+        <v>17.3</v>
       </c>
       <c r="T27" s="3" t="n">
         <v>86</v>
@@ -2779,17 +2791,17 @@
       <c r="U27" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="V27" s="11" t="n">
+      <c r="V27" s="9" t="n">
         <v>17.4</v>
       </c>
-      <c r="W27" s="13" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="X27" s="8" t="n">
+      <c r="W27" s="9" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="X27" s="12" t="n">
         <v>18.5</v>
       </c>
       <c r="Y27" s="3" t="n">
-        <v>23</v>
+        <v>1213</v>
       </c>
       <c r="Z27" s="3" t="n">
         <v>1.6</v>
@@ -2810,38 +2822,38 @@
       <c r="C28" s="3" t="n">
         <v>513.3</v>
       </c>
-      <c r="D28" s="11" t="n">
+      <c r="D28" s="9" t="n">
         <v>27</v>
       </c>
-      <c r="E28" s="11" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="F28" s="11" t="n">
+      <c r="E28" s="9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="F28" s="9" t="n">
         <v>19.3</v>
       </c>
-      <c r="G28" s="13" t="n">
-        <v>15.7</v>
+      <c r="G28" s="12" t="n">
+        <v>15.9</v>
       </c>
       <c r="H28" s="3" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="J28" s="3" t="n">
         <v>3.3</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="L28" s="13" t="n">
-        <v>93.53999999999999</v>
-      </c>
-      <c r="M28" s="8" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="L28" s="9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="M28" s="12" t="n">
         <v>13.3</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>14.2</v>
+        <v>1.5</v>
       </c>
       <c r="O28" s="3" t="n">
         <v>99</v>
@@ -2849,10 +2861,10 @@
       <c r="P28" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q28" s="3" t="n">
+      <c r="Q28" s="9" t="n">
         <v>22.9</v>
       </c>
-      <c r="R28" s="8" t="n">
+      <c r="R28" s="9" t="n">
         <v>18.6</v>
       </c>
       <c r="S28" s="3" t="n">
@@ -2864,14 +2876,14 @@
       <c r="U28" s="3" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="V28" s="11" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="W28" s="3" t="n">
+      <c r="V28" s="9" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="W28" s="9" t="n">
         <v>15.5</v>
       </c>
-      <c r="X28" s="8" t="n">
-        <v>817</v>
+      <c r="X28" s="12" t="n">
+        <v>17.8</v>
       </c>
       <c r="Y28" s="3" t="n">
         <v>191</v>
@@ -2893,19 +2905,19 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>323.3</v>
-      </c>
-      <c r="D29" s="11" t="n">
-        <v>28.3</v>
-      </c>
-      <c r="E29" s="11" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="F29" s="11" t="n">
+        <v>523.3</v>
+      </c>
+      <c r="D29" s="9" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="E29" s="9" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="F29" s="9" t="n">
         <v>19.5</v>
       </c>
-      <c r="G29" s="8" t="n">
-        <v>18.1</v>
+      <c r="G29" s="3" t="n">
+        <v>1.8</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>7.2</v>
@@ -2919,29 +2931,29 @@
       <c r="K29" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L29" s="8" t="n">
+      <c r="L29" s="9" t="n">
         <v>10.9</v>
       </c>
       <c r="M29" s="3" t="n">
         <v>10.5</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>13.4</v>
+        <v>12.4</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>196</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="Q29" s="8" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q29" s="9" t="n">
         <v>27</v>
       </c>
-      <c r="R29" s="13" t="n">
-        <v>18.17</v>
-      </c>
-      <c r="S29" s="8" t="n">
-        <v>12</v>
+      <c r="R29" s="9" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="S29" s="3" t="n">
+        <v>17</v>
       </c>
       <c r="T29" s="3" t="n">
         <v>47.8</v>
@@ -2949,20 +2961,20 @@
       <c r="U29" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="V29" s="11" t="n">
+      <c r="V29" s="9" t="n">
         <v>22.8</v>
       </c>
-      <c r="W29" s="3" t="n">
+      <c r="W29" s="9" t="n">
         <v>17.3</v>
       </c>
       <c r="X29" s="3" t="n">
-        <v>1.3</v>
+        <v>22.1</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>60</v>
+        <v>160</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>112.9</v>
+        <v>11.2</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
@@ -2978,49 +2990,51 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>2284.8</v>
-      </c>
-      <c r="D30" s="11" t="n">
-        <v>131.2</v>
-      </c>
-      <c r="E30" s="11" t="n">
-        <v>52.2</v>
-      </c>
-      <c r="F30" s="11" t="n">
+        <v>228.4</v>
+      </c>
+      <c r="D30" s="18" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="E30" s="18" t="n">
+        <v>527.1</v>
+      </c>
+      <c r="F30" s="9" t="n">
         <v>91.7</v>
       </c>
-      <c r="G30" s="11" t="n">
+      <c r="G30" s="3" t="n">
         <v>79.09999999999999</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>113.8</v>
+        <v>13.8</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>119.5</v>
-      </c>
-      <c r="K30" s="14" t="n">
-        <v>113.5</v>
-      </c>
-      <c r="L30" s="14" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="K30" s="18" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="L30" s="18" t="n">
         <v>57.2</v>
       </c>
-      <c r="M30" s="14" t="n">
+      <c r="M30" s="18" t="n">
         <v>56.7</v>
       </c>
-      <c r="N30" s="3" t="inlineStr"/>
+      <c r="N30" s="3" t="n">
+        <v>65.90000000000001</v>
+      </c>
       <c r="O30" s="3" t="n">
         <v>489</v>
       </c>
       <c r="P30" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="Q30" s="14" t="n">
-        <v>113.2</v>
-      </c>
-      <c r="R30" s="14" t="n">
+      <c r="Q30" s="18" t="n">
+        <v>413.2</v>
+      </c>
+      <c r="R30" s="9" t="n">
         <v>86.7</v>
       </c>
       <c r="S30" s="3" t="n">
@@ -3030,12 +3044,12 @@
         <v>314.8</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>55.9</v>
-      </c>
-      <c r="V30" s="14" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="V30" s="9" t="n">
         <v>99.5</v>
       </c>
-      <c r="W30" s="14" t="n">
+      <c r="W30" s="9" t="n">
         <v>81.90000000000001</v>
       </c>
       <c r="X30" s="3" t="n">
@@ -3061,74 +3075,74 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>432</v>
-      </c>
-      <c r="D31" s="11" t="n">
+        <v>452</v>
+      </c>
+      <c r="D31" s="9" t="n">
         <v>26.2</v>
       </c>
-      <c r="E31" s="11" t="n">
+      <c r="E31" s="9" t="n">
         <v>10.4</v>
       </c>
-      <c r="F31" s="11" t="n">
+      <c r="F31" s="9" t="n">
         <v>18.3</v>
       </c>
-      <c r="G31" s="8" t="n">
-        <v>58.4</v>
+      <c r="G31" s="9" t="n">
+        <v>15.8</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>72.09999999999999</v>
+        <v>4.2</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>2.8</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>39.1</v>
+        <v>3.9</v>
       </c>
       <c r="K31" s="3" t="inlineStr"/>
-      <c r="L31" s="14" t="n">
+      <c r="L31" s="9" t="n">
         <v>11.5</v>
       </c>
-      <c r="M31" s="14" t="n">
+      <c r="M31" s="18" t="n">
         <v>11.2</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>13.8</v>
+        <v>12.4</v>
       </c>
       <c r="O31" s="3" t="n">
         <v>97.8</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="Q31" s="14" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q31" s="9" t="n">
         <v>22.6</v>
       </c>
-      <c r="R31" s="14" t="n">
+      <c r="R31" s="18" t="n">
         <v>19.3</v>
       </c>
-      <c r="S31" s="8" t="n">
+      <c r="S31" s="12" t="n">
         <v>16.9</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="U31" s="3" t="n">
-        <v>111.1</v>
-      </c>
-      <c r="V31" s="11" t="n">
+        <v>63</v>
+      </c>
+      <c r="U31" s="12" t="n">
+        <v>111.4</v>
+      </c>
+      <c r="V31" s="9" t="n">
         <v>19.9</v>
       </c>
-      <c r="W31" s="14" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="X31" s="8" t="n">
+      <c r="W31" s="9" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="X31" s="12" t="n">
         <v>16.6</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>73</v>
+        <v>730</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>7</v>
+        <v>165.8</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3144,76 +3158,72 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>5280.8</v>
-      </c>
-      <c r="D32" s="11" t="n">
+        <v>520</v>
+      </c>
+      <c r="D32" s="9" t="n">
         <v>27.9</v>
       </c>
-      <c r="E32" s="11" t="n">
+      <c r="E32" s="9" t="n">
         <v>10.2</v>
       </c>
-      <c r="F32" s="11" t="n">
+      <c r="F32" s="9" t="n">
         <v>19</v>
       </c>
-      <c r="G32" s="11" t="n">
+      <c r="G32" s="9" t="n">
         <v>17.7</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>16.6</v>
+        <v>6.6</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K32" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="L32" s="11" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="M32" s="8" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="N32" s="8" t="n">
-        <v>12.1</v>
+      <c r="L32" s="3" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="M32" s="9" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="N32" s="12" t="n">
+        <v>12.4</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="P32" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="3" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="R32" s="11" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q32" s="9" t="n">
+        <v>26.46</v>
+      </c>
+      <c r="R32" s="9" t="n">
         <v>18.2</v>
       </c>
-      <c r="S32" s="3" t="n">
+      <c r="S32" s="12" t="n">
         <v>18.8</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="U32" s="3" t="n">
-        <v>9.699999999999999</v>
-      </c>
+        <v>62.6</v>
+      </c>
+      <c r="U32" s="3" t="inlineStr"/>
       <c r="V32" s="3" t="n">
         <v>21.4</v>
       </c>
-      <c r="W32" s="3" t="n">
+      <c r="W32" s="9" t="n">
         <v>17.6</v>
       </c>
-      <c r="X32" s="8" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="Y32" s="3" t="n">
-        <v>170</v>
-      </c>
+      <c r="X32" s="12" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="Y32" s="3" t="inlineStr"/>
       <c r="Z32" s="3" t="n">
-        <v>4</v>
+        <v>171.8</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3231,23 +3241,23 @@
       <c r="C33" s="3" t="n">
         <v>349.1</v>
       </c>
-      <c r="D33" s="11" t="n">
+      <c r="D33" s="9" t="n">
         <v>24.2</v>
       </c>
-      <c r="E33" s="11" t="n">
+      <c r="E33" s="9" t="n">
         <v>12.8</v>
       </c>
-      <c r="F33" s="11" t="n">
+      <c r="F33" s="9" t="n">
         <v>18.5</v>
       </c>
-      <c r="G33" s="13" t="n">
-        <v>11.1</v>
+      <c r="G33" s="9" t="n">
+        <v>11.4</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>8.9</v>
+        <v>2.4</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>16.5</v>
+        <v>1.9</v>
       </c>
       <c r="J33" s="3" t="n">
         <v>2.5</v>
@@ -3255,50 +3265,50 @@
       <c r="K33" s="3" t="n">
         <v>6.8</v>
       </c>
-      <c r="L33" s="11" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="M33" s="3" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="N33" s="3" t="n">
-        <v>16.5</v>
+      <c r="L33" s="3" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="M33" s="9" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="N33" s="12" t="n">
+        <v>18.5</v>
       </c>
       <c r="O33" s="3" t="n">
         <v>98</v>
       </c>
       <c r="P33" s="3" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="Q33" s="3" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="R33" s="11" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="Q33" s="9" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="R33" s="9" t="n">
         <v>17.8</v>
       </c>
       <c r="S33" s="3" t="n">
         <v>18.9</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>29.9</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="U33" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="V33" s="8" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="W33" s="3" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="X33" s="3" t="n">
-        <v>1.8</v>
+        <v>3</v>
+      </c>
+      <c r="V33" s="3" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="W33" s="9" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="X33" s="12" t="n">
+        <v>18.7</v>
       </c>
       <c r="Y33" s="3" t="n">
         <v>83</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3316,71 +3326,71 @@
       <c r="C34" s="3" t="n">
         <v>329.9</v>
       </c>
-      <c r="D34" s="11" t="n">
+      <c r="D34" s="9" t="n">
         <v>23.3</v>
       </c>
-      <c r="E34" s="11" t="n">
+      <c r="E34" s="9" t="n">
         <v>14.7</v>
       </c>
-      <c r="F34" s="11" t="n">
+      <c r="F34" s="9" t="n">
         <v>19</v>
       </c>
-      <c r="G34" s="11" t="n">
+      <c r="G34" s="9" t="n">
         <v>8.6</v>
       </c>
-      <c r="H34" s="8" t="n">
-        <v>49.7</v>
+      <c r="H34" s="12" t="n">
+        <v>14.7</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>71.5</v>
+        <v>11.5</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>1.9</v>
+        <v>8.9</v>
       </c>
       <c r="K34" s="3" t="n">
         <v>1.7</v>
       </c>
-      <c r="L34" s="11" t="n">
-        <v>12</v>
-      </c>
-      <c r="M34" s="8" t="n">
+      <c r="L34" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="M34" s="9" t="n">
         <v>15.9</v>
       </c>
-      <c r="N34" s="3" t="n">
-        <v>1.7</v>
+      <c r="N34" s="12" t="n">
+        <v>7.8</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>991</v>
+        <v>99</v>
       </c>
       <c r="P34" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q34" s="3" t="n">
+      <c r="Q34" s="9" t="n">
         <v>21.8</v>
       </c>
-      <c r="R34" s="11" t="n">
+      <c r="R34" s="9" t="n">
         <v>18.1</v>
       </c>
-      <c r="S34" s="8" t="n">
+      <c r="S34" s="3" t="n">
         <v>18.7</v>
       </c>
       <c r="T34" s="3" t="n">
         <v>72</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="V34" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W34" s="3" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="V34" s="12" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="W34" s="9" t="n">
         <v>16.8</v>
       </c>
-      <c r="X34" s="3" t="n">
+      <c r="X34" s="12" t="n">
         <v>18</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>33</v>
+        <v>83</v>
       </c>
       <c r="Z34" s="3" t="n">
         <v>3.8</v>
@@ -3401,16 +3411,16 @@
       <c r="C35" s="3" t="n">
         <v>506.7</v>
       </c>
-      <c r="D35" s="11" t="n">
+      <c r="D35" s="9" t="n">
         <v>26.8</v>
       </c>
-      <c r="E35" s="11" t="n">
+      <c r="E35" s="9" t="n">
         <v>12.8</v>
       </c>
-      <c r="F35" s="11" t="n">
+      <c r="F35" s="9" t="n">
         <v>19.8</v>
       </c>
-      <c r="G35" s="11" t="n">
+      <c r="G35" s="9" t="n">
         <v>14</v>
       </c>
       <c r="H35" s="3" t="n">
@@ -3425,47 +3435,47 @@
       <c r="K35" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L35" s="11" t="n">
+      <c r="L35" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="M35" s="3" t="n">
-        <v>11.2</v>
+      <c r="M35" s="9" t="n">
+        <v>12.9</v>
       </c>
       <c r="N35" s="3" t="n">
         <v>14.8</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>189</v>
+        <v>399</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q35" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q35" s="9" t="n">
         <v>23.8</v>
       </c>
-      <c r="R35" s="11" t="n">
+      <c r="R35" s="9" t="n">
         <v>17.6</v>
       </c>
-      <c r="S35" s="3" t="n">
+      <c r="S35" s="12" t="n">
         <v>16.8</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>52</v>
-      </c>
-      <c r="U35" s="8" t="n">
+        <v>37</v>
+      </c>
+      <c r="U35" s="3" t="n">
         <v>12.8</v>
       </c>
-      <c r="V35" s="3" t="n">
+      <c r="V35" s="12" t="n">
         <v>20.8</v>
       </c>
-      <c r="W35" s="8" t="n">
+      <c r="W35" s="9" t="n">
         <v>16.7</v>
       </c>
-      <c r="X35" s="8" t="n">
+      <c r="X35" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>683.5</v>
+        <v>68.3</v>
       </c>
       <c r="Z35" s="3" t="n">
         <v>8</v>
@@ -3486,73 +3496,75 @@
       <c r="C36" s="3" t="n">
         <v>535.5</v>
       </c>
-      <c r="D36" s="11" t="n">
+      <c r="D36" s="9" t="n">
         <v>26.3</v>
       </c>
-      <c r="E36" s="11" t="n">
-        <v>10.54</v>
-      </c>
-      <c r="F36" s="11" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="G36" s="11" t="n">
+      <c r="E36" s="9" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="F36" s="9" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="G36" s="3" t="n">
         <v>15.9</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>6.4</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>3.9</v>
+        <v>13.9</v>
       </c>
       <c r="J36" s="3" t="n">
         <v>5.9</v>
       </c>
       <c r="K36" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="L36" s="12" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="M36" s="9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="N36" s="3" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="O36" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="P36" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L36" s="11" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="M36" s="3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="N36" s="3" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="O36" s="3" t="n">
-        <v>99</v>
-      </c>
-      <c r="P36" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="Q36" s="3" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="R36" s="11" t="n">
+      <c r="Q36" s="9" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="R36" s="9" t="n">
         <v>17.1</v>
       </c>
-      <c r="S36" s="3" t="n">
-        <v>15.8</v>
+      <c r="S36" s="12" t="n">
+        <v>19.8</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="U36" s="8" t="n">
-        <v>17.9</v>
+        <v>63</v>
+      </c>
+      <c r="U36" s="3" t="n">
+        <v>1.7</v>
       </c>
       <c r="V36" s="3" t="n">
         <v>20.6</v>
       </c>
-      <c r="W36" s="13" t="n">
-        <v>44.6</v>
-      </c>
-      <c r="X36" s="3" t="n">
-        <v>11.3</v>
+      <c r="W36" s="9" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="X36" s="12" t="n">
+        <v>3.3</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="Z36" s="3" t="inlineStr"/>
+        <v>55</v>
+      </c>
+      <c r="Z36" s="3" t="n">
+        <v>11</v>
+      </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
           <t>25</t>
@@ -3567,37 +3579,37 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>2140.4</v>
-      </c>
-      <c r="D37" s="11" t="n">
+        <v>2240.4</v>
+      </c>
+      <c r="D37" s="9" t="n">
         <v>128.5</v>
       </c>
-      <c r="E37" s="11" t="n">
+      <c r="E37" s="9" t="n">
         <v>60.9</v>
       </c>
-      <c r="F37" s="11" t="n">
+      <c r="F37" s="9" t="n">
         <v>94.7</v>
       </c>
-      <c r="G37" s="13" t="n">
-        <v>67.3</v>
+      <c r="G37" s="3" t="n">
+        <v>62.6</v>
       </c>
       <c r="H37" s="3" t="n">
         <v>46</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>141.7</v>
+        <v>14.9</v>
       </c>
       <c r="J37" s="3" t="n">
         <v>20.8</v>
       </c>
-      <c r="K37" s="14" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="L37" s="14" t="n">
-        <v>65</v>
-      </c>
-      <c r="M37" s="14" t="n">
-        <v>6.4</v>
+      <c r="K37" s="18" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="L37" s="18" t="n">
+        <v>63</v>
+      </c>
+      <c r="M37" s="18" t="n">
+        <v>64.2</v>
       </c>
       <c r="N37" s="3" t="n">
         <v>74.2</v>
@@ -3605,14 +3617,12 @@
       <c r="O37" s="3" t="n">
         <v>492</v>
       </c>
-      <c r="P37" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="Q37" s="14" t="n">
-        <v>185.9</v>
-      </c>
-      <c r="R37" s="14" t="n">
-        <v>82.90000000000001</v>
+      <c r="P37" s="3" t="inlineStr"/>
+      <c r="Q37" s="18" t="n">
+        <v>115.5</v>
+      </c>
+      <c r="R37" s="18" t="n">
+        <v>89.90000000000001</v>
       </c>
       <c r="S37" s="3" t="n">
         <v>88</v>
@@ -3623,20 +3633,20 @@
       <c r="U37" s="3" t="n">
         <v>54.5</v>
       </c>
-      <c r="V37" s="14" t="n">
+      <c r="V37" s="18" t="n">
         <v>100.9</v>
       </c>
-      <c r="W37" s="14" t="n">
-        <v>837.1</v>
+      <c r="W37" s="18" t="n">
+        <v>83.09999999999999</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>84.8</v>
+        <v>84.7</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>359.5</v>
+        <v>359.3</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>39.4</v>
+        <v>34.6</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3652,18 +3662,18 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>448.1</v>
-      </c>
-      <c r="D38" s="11" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="D38" s="9" t="n">
         <v>25.7</v>
       </c>
-      <c r="E38" s="11" t="n">
+      <c r="E38" s="9" t="n">
         <v>12.2</v>
       </c>
-      <c r="F38" s="11" t="n">
+      <c r="F38" s="9" t="n">
         <v>18.9</v>
       </c>
-      <c r="G38" s="11" t="n">
+      <c r="G38" s="9" t="n">
         <v>13.5</v>
       </c>
       <c r="H38" s="3" t="n">
@@ -3672,51 +3682,51 @@
       <c r="I38" s="3" t="n">
         <v>28.1</v>
       </c>
-      <c r="J38" s="3" t="n">
-        <v>90.09999999999999</v>
+      <c r="J38" s="12" t="n">
+        <v>92.09999999999999</v>
       </c>
       <c r="K38" s="3" t="inlineStr"/>
-      <c r="L38" s="11" t="n">
+      <c r="L38" s="18" t="n">
         <v>13</v>
       </c>
-      <c r="M38" s="14" t="n">
+      <c r="M38" s="9" t="n">
         <v>12.8</v>
       </c>
       <c r="N38" s="3" t="n">
         <v>14.8</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>98.40000000000001</v>
+        <v>298.9</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="Q38" s="14" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Q38" s="9" t="n">
         <v>23.1</v>
       </c>
-      <c r="R38" s="11" t="n">
+      <c r="R38" s="9" t="n">
         <v>17.9</v>
       </c>
-      <c r="S38" s="8" t="n">
-        <v>127.6</v>
+      <c r="S38" s="12" t="n">
+        <v>17.6</v>
       </c>
       <c r="T38" s="3" t="n">
         <v>23.3</v>
       </c>
-      <c r="U38" s="8" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="V38" s="14" t="n">
+      <c r="U38" s="12" t="n">
+        <v>128.9</v>
+      </c>
+      <c r="V38" s="18" t="n">
         <v>20.2</v>
       </c>
-      <c r="W38" s="14" t="n">
+      <c r="W38" s="9" t="n">
         <v>16.6</v>
       </c>
-      <c r="X38" s="8" t="n">
+      <c r="X38" s="12" t="n">
         <v>16.9</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>71.90000000000001</v>
+        <v>21.9</v>
       </c>
       <c r="Z38" s="3" t="n">
         <v>6.9</v>
@@ -3737,36 +3747,38 @@
       <c r="C39" s="3" t="n">
         <v>579.9</v>
       </c>
-      <c r="D39" s="11" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="E39" s="11" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="F39" s="11" t="n">
+      <c r="D39" s="9" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="E39" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="F39" s="9" t="n">
         <v>18.9</v>
       </c>
-      <c r="G39" s="11" t="n">
+      <c r="G39" s="9" t="n">
         <v>15.9</v>
       </c>
-      <c r="H39" s="3" t="inlineStr"/>
+      <c r="H39" s="3" t="n">
+        <v>1.9</v>
+      </c>
       <c r="I39" s="3" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="J39" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="K39" s="11" t="n">
+      <c r="K39" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L39" s="8" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="M39" s="13" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N39" s="3" t="n">
-        <v>1.7</v>
+      <c r="L39" s="3" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="M39" s="9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="N39" s="12" t="n">
+        <v>14.9</v>
       </c>
       <c r="O39" s="3" t="n">
         <v>98</v>
@@ -3774,35 +3786,33 @@
       <c r="P39" s="3" t="n">
         <v>9.4</v>
       </c>
-      <c r="Q39" s="3" t="n">
+      <c r="Q39" s="9" t="n">
         <v>26.6</v>
       </c>
-      <c r="R39" s="8" t="n">
+      <c r="R39" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="S39" s="3" t="n">
-        <v>4.6</v>
-      </c>
+      <c r="S39" s="3" t="inlineStr"/>
       <c r="T39" s="3" t="n">
-        <v>92.5</v>
-      </c>
-      <c r="U39" s="8" t="n">
-        <v>18</v>
-      </c>
-      <c r="V39" s="3" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="W39" s="11" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="X39" s="8" t="n">
-        <v>12.3</v>
+        <v>45.5</v>
+      </c>
+      <c r="U39" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="V39" s="17" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="W39" s="17" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="X39" s="3" t="n">
+        <v>14.6</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>76</v>
+        <v>56</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>11.6</v>
+        <v>176</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3818,56 +3828,58 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>35.5</v>
-      </c>
-      <c r="D40" s="11" t="n">
-        <v>27.1</v>
-      </c>
-      <c r="E40" s="11" t="n">
+        <v>335.9</v>
+      </c>
+      <c r="D40" s="9" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="E40" s="9" t="n">
         <v>10.7</v>
       </c>
-      <c r="F40" s="11" t="n">
+      <c r="F40" s="9" t="n">
         <v>18.9</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>11.6</v>
+        <v>1.6</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>7.3</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>29.4</v>
-      </c>
-      <c r="J40" s="3" t="inlineStr"/>
-      <c r="K40" s="11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J40" s="3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K40" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L40" s="8" t="n">
+      <c r="L40" s="3" t="n">
         <v>10.6</v>
       </c>
-      <c r="M40" s="3" t="n">
+      <c r="M40" s="9" t="n">
         <v>10.3</v>
       </c>
       <c r="N40" s="3" t="n">
         <v>12.9</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>96</v>
+        <v>196</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="Q40" s="13" t="n">
-        <v>82</v>
+        <v>10.2</v>
+      </c>
+      <c r="Q40" s="9" t="n">
+        <v>22</v>
       </c>
       <c r="R40" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="S40" s="3" t="n">
-        <v>18.5</v>
+      <c r="S40" s="12" t="n">
+        <v>18.4</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>69.5</v>
+        <v>169.5</v>
       </c>
       <c r="U40" s="3" t="n">
         <v>8</v>
@@ -3875,17 +3887,17 @@
       <c r="V40" s="3" t="n">
         <v>12.7</v>
       </c>
-      <c r="W40" s="11" t="n">
-        <v>18.15</v>
-      </c>
-      <c r="X40" s="3" t="n">
+      <c r="W40" s="12" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="X40" s="12" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Y40" s="3" t="n">
         <v>29.3</v>
       </c>
-      <c r="Y40" s="3" t="n">
-        <v>89</v>
-      </c>
       <c r="Z40" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>83</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3903,54 +3915,56 @@
       <c r="C41" s="3" t="n">
         <v>451.2</v>
       </c>
-      <c r="D41" s="3" t="n">
-        <v>28.4</v>
-      </c>
-      <c r="E41" s="11" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="F41" s="11" t="n">
-        <v>18.5</v>
+      <c r="D41" s="9" t="n">
+        <v>28.94</v>
+      </c>
+      <c r="E41" s="9" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="F41" s="9" t="n">
+        <v>18.3</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="H41" s="3" t="inlineStr"/>
+        <v>19.8</v>
+      </c>
+      <c r="H41" s="12" t="n">
+        <v>51</v>
+      </c>
       <c r="I41" s="3" t="n">
         <v>0.3</v>
       </c>
       <c r="J41" s="3" t="n">
         <v>5.7</v>
       </c>
-      <c r="K41" s="11" t="n">
+      <c r="K41" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L41" s="13" t="n">
-        <v>88.3</v>
-      </c>
-      <c r="M41" s="3" t="n">
+      <c r="L41" s="3" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="M41" s="9" t="n">
         <v>8.6</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>98</v>
+        <v>198</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Q41" s="3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="Q41" s="9" t="n">
         <v>23.9</v>
       </c>
-      <c r="R41" s="8" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="S41" s="3" t="n">
+      <c r="R41" s="12" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="S41" s="12" t="n">
         <v>16.6</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>423.5</v>
+        <v>57.9</v>
       </c>
       <c r="U41" s="3" t="n">
         <v>12.9</v>
@@ -3958,17 +3972,17 @@
       <c r="V41" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="W41" s="11" t="n">
+      <c r="W41" s="17" t="n">
+        <v>18.15</v>
+      </c>
+      <c r="X41" s="3" t="n">
         <v>16.3</v>
-      </c>
-      <c r="X41" s="3" t="n">
-        <v>14.8</v>
       </c>
       <c r="Y41" s="3" t="n">
         <v>58</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>19.8</v>
+        <v>15.7</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -3984,37 +3998,37 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>529.4</v>
-      </c>
-      <c r="D42" s="11" t="n">
+        <v>524.4</v>
+      </c>
+      <c r="D42" s="9" t="n">
         <v>27.2</v>
       </c>
-      <c r="E42" s="11" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="F42" s="11" t="n">
+      <c r="E42" s="17" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F42" s="9" t="n">
         <v>19.3</v>
       </c>
-      <c r="G42" s="13" t="n">
-        <v>135.2</v>
+      <c r="G42" s="17" t="n">
+        <v>12.6</v>
       </c>
       <c r="H42" s="3" t="n">
         <v>7.8</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>3.9</v>
+        <v>13.9</v>
       </c>
       <c r="J42" s="3" t="n">
         <v>5.6</v>
       </c>
-      <c r="K42" s="11" t="n">
+      <c r="K42" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="M42" s="13" t="n">
-        <v>0.2</v>
+        <v>11.7</v>
+      </c>
+      <c r="M42" s="9" t="n">
+        <v>11.1</v>
       </c>
       <c r="N42" s="3" t="n">
         <v>13.3</v>
@@ -4025,30 +4039,26 @@
       <c r="P42" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="Q42" s="3" t="n">
+      <c r="Q42" s="9" t="n">
         <v>26.6</v>
       </c>
-      <c r="R42" s="13" t="n">
-        <v>87.59999999999999</v>
-      </c>
-      <c r="S42" s="8" t="n">
-        <v>12.7</v>
+      <c r="R42" s="12" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="S42" s="12" t="n">
+        <v>15.1</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>43.5</v>
-      </c>
-      <c r="U42" s="3" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="U42" s="12" t="n">
         <v>19.6</v>
       </c>
-      <c r="V42" s="8" t="n">
+      <c r="V42" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="W42" s="11" t="n">
-        <v>16.3</v>
-      </c>
-      <c r="X42" s="3" t="n">
-        <v>14.8</v>
-      </c>
+      <c r="W42" s="16" t="inlineStr"/>
+      <c r="X42" s="3" t="inlineStr"/>
       <c r="Y42" s="3" t="inlineStr"/>
       <c r="Z42" s="3" t="inlineStr"/>
       <c r="AA42" s="3" t="inlineStr">
@@ -4067,26 +4077,26 @@
       <c r="C43" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="D43" s="12" t="inlineStr"/>
-      <c r="E43" s="12" t="inlineStr"/>
-      <c r="F43" s="11" t="inlineStr"/>
+      <c r="D43" s="9" t="inlineStr"/>
+      <c r="E43" s="9" t="inlineStr"/>
+      <c r="F43" s="9" t="inlineStr"/>
       <c r="G43" s="3" t="inlineStr"/>
       <c r="H43" s="3" t="inlineStr"/>
       <c r="I43" s="3" t="inlineStr"/>
       <c r="J43" s="3" t="inlineStr"/>
-      <c r="K43" s="11" t="inlineStr"/>
-      <c r="L43" s="12" t="inlineStr"/>
-      <c r="M43" s="12" t="inlineStr"/>
+      <c r="K43" s="16" t="inlineStr"/>
+      <c r="L43" s="16" t="inlineStr"/>
+      <c r="M43" s="9" t="inlineStr"/>
       <c r="N43" s="3" t="inlineStr"/>
       <c r="O43" s="3" t="inlineStr"/>
       <c r="P43" s="3" t="inlineStr"/>
-      <c r="Q43" s="12" t="inlineStr"/>
-      <c r="R43" s="12" t="inlineStr"/>
+      <c r="Q43" s="9" t="inlineStr"/>
+      <c r="R43" s="16" t="inlineStr"/>
       <c r="S43" s="3" t="inlineStr"/>
       <c r="T43" s="3" t="inlineStr"/>
       <c r="U43" s="3" t="inlineStr"/>
-      <c r="V43" s="12" t="inlineStr"/>
-      <c r="W43" s="11" t="inlineStr"/>
+      <c r="V43" s="16" t="inlineStr"/>
+      <c r="W43" s="16" t="inlineStr"/>
       <c r="X43" s="3" t="inlineStr"/>
       <c r="Y43" s="3" t="inlineStr"/>
       <c r="Z43" s="3" t="inlineStr"/>
@@ -4106,26 +4116,26 @@
       <c r="C44" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="D44" s="12" t="inlineStr"/>
-      <c r="E44" s="12" t="inlineStr"/>
-      <c r="F44" s="11" t="inlineStr"/>
+      <c r="D44" s="9" t="inlineStr"/>
+      <c r="E44" s="9" t="inlineStr"/>
+      <c r="F44" s="9" t="inlineStr"/>
       <c r="G44" s="3" t="inlineStr"/>
       <c r="H44" s="3" t="inlineStr"/>
       <c r="I44" s="3" t="inlineStr"/>
       <c r="J44" s="3" t="inlineStr"/>
-      <c r="K44" s="11" t="inlineStr"/>
-      <c r="L44" s="12" t="inlineStr"/>
-      <c r="M44" s="12" t="inlineStr"/>
+      <c r="K44" s="16" t="inlineStr"/>
+      <c r="L44" s="16" t="inlineStr"/>
+      <c r="M44" s="9" t="inlineStr"/>
       <c r="N44" s="3" t="inlineStr"/>
       <c r="O44" s="3" t="inlineStr"/>
       <c r="P44" s="3" t="inlineStr"/>
-      <c r="Q44" s="12" t="inlineStr"/>
-      <c r="R44" s="12" t="inlineStr"/>
+      <c r="Q44" s="9" t="inlineStr"/>
+      <c r="R44" s="16" t="inlineStr"/>
       <c r="S44" s="3" t="inlineStr"/>
       <c r="T44" s="3" t="inlineStr"/>
       <c r="U44" s="3" t="inlineStr"/>
-      <c r="V44" s="12" t="inlineStr"/>
-      <c r="W44" s="11" t="inlineStr"/>
+      <c r="V44" s="16" t="inlineStr"/>
+      <c r="W44" s="16" t="inlineStr"/>
       <c r="X44" s="3" t="inlineStr"/>
       <c r="Y44" s="3" t="inlineStr"/>
       <c r="Z44" s="3" t="inlineStr"/>
@@ -4143,76 +4153,76 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>1911.2</v>
-      </c>
-      <c r="D45" s="14" t="n">
-        <v>1091.7</v>
-      </c>
-      <c r="E45" s="14" t="n">
-        <v>61.8</v>
-      </c>
-      <c r="F45" s="11" t="n">
+        <v>1981.2</v>
+      </c>
+      <c r="D45" s="18" t="n">
+        <v>109.7</v>
+      </c>
+      <c r="E45" s="18" t="n">
+        <v>41.8</v>
+      </c>
+      <c r="F45" s="9" t="n">
         <v>75.59999999999999</v>
       </c>
-      <c r="G45" s="3" t="n">
-        <v>27.9</v>
+      <c r="G45" s="17" t="n">
+        <v>10.8</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>119.9</v>
+        <v>16.4</v>
       </c>
       <c r="J45" s="3" t="n">
         <v>20.9</v>
       </c>
-      <c r="K45" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L45" s="14" t="n">
+      <c r="K45" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="L45" s="18" t="n">
         <v>44</v>
       </c>
-      <c r="M45" s="14" t="n">
-        <v>22.9</v>
+      <c r="M45" s="18" t="n">
+        <v>42.9</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>31.6</v>
+        <v>5.1</v>
       </c>
       <c r="O45" s="3" t="n">
         <v>388</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q45" s="14" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="Q45" s="18" t="n">
         <v>98.59999999999999</v>
       </c>
-      <c r="R45" s="14" t="n">
+      <c r="R45" s="18" t="n">
         <v>71</v>
       </c>
       <c r="S45" s="3" t="n">
         <v>66</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>216.9</v>
+        <v>216.4</v>
       </c>
       <c r="U45" s="3" t="n">
         <v>59</v>
       </c>
-      <c r="V45" s="14" t="n">
+      <c r="V45" s="18" t="n">
         <v>831.9</v>
       </c>
-      <c r="W45" s="14" t="n">
-        <v>67.5</v>
+      <c r="W45" s="18" t="n">
+        <v>67.3</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>200.8</v>
+        <v>62.8</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>1263</v>
+        <v>263</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>2331.8</v>
+        <v>35.7</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4228,35 +4238,37 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>417.8</v>
-      </c>
-      <c r="D46" s="11" t="n">
-        <v>27.3</v>
-      </c>
-      <c r="E46" s="11" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="F46" s="11" t="n">
+        <v>477.8</v>
+      </c>
+      <c r="D46" s="9" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="E46" s="9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="F46" s="9" t="n">
         <v>18.9</v>
       </c>
-      <c r="G46" s="8" t="n">
-        <v>69.40000000000001</v>
+      <c r="G46" s="9" t="n">
+        <v>16.9</v>
       </c>
       <c r="H46" s="3" t="n">
         <v>6.7</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>3.6</v>
+        <v>36.1</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>62.1</v>
-      </c>
-      <c r="K46" s="3" t="inlineStr"/>
-      <c r="L46" s="14" t="n">
-        <v>11181.9</v>
-      </c>
-      <c r="M46" s="14" t="n">
-        <v>1</v>
+        <v>65.2</v>
+      </c>
+      <c r="K46" s="3" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="L46" s="18" t="n">
+        <v>111.7</v>
+      </c>
+      <c r="M46" s="9" t="n">
+        <v>10.7</v>
       </c>
       <c r="N46" s="3" t="n">
         <v>12.8</v>
@@ -4267,30 +4279,32 @@
       <c r="P46" s="3" t="n">
         <v>6.4</v>
       </c>
-      <c r="Q46" s="14" t="n">
+      <c r="Q46" s="9" t="n">
         <v>24.7</v>
       </c>
-      <c r="R46" s="14" t="n">
-        <v>88.59999999999999</v>
-      </c>
-      <c r="S46" s="3" t="n">
-        <v>11.6</v>
+      <c r="R46" s="18" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="S46" s="12" t="n">
+        <v>16.5</v>
       </c>
       <c r="T46" s="3" t="n">
         <v>54.1</v>
       </c>
-      <c r="U46" s="3" t="inlineStr"/>
-      <c r="V46" s="14" t="n">
+      <c r="U46" s="3" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="V46" s="18" t="n">
         <v>21.3</v>
       </c>
-      <c r="W46" s="11" t="n">
+      <c r="W46" s="18" t="n">
         <v>16.8</v>
       </c>
       <c r="X46" s="3" t="n">
-        <v>1.4</v>
+        <v>15.7</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>1862.4</v>
+        <v>265.7</v>
       </c>
       <c r="Z46" s="3" t="n">
         <v>81.90000000000001</v>

--- a/results/05_transient_transcription_output/702/702_196402_SF.JPG_stage_duirnal_temp_range.xlsx
+++ b/results/05_transient_transcription_output/702/702_196402_SF.JPG_stage_duirnal_temp_range.xlsx
@@ -131,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -146,37 +146,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -801,11 +786,11 @@
       <c r="F4" s="9" t="n">
         <v>18.5</v>
       </c>
-      <c r="G4" s="12" t="n">
-        <v>81.7</v>
+      <c r="G4" s="9" t="n">
+        <v>18.7</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>0.5</v>
+        <v>5.6</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>3.5</v>
@@ -813,14 +798,14 @@
       <c r="J4" s="3" t="n">
         <v>4.9</v>
       </c>
-      <c r="K4" s="3" t="n">
-        <v>8</v>
+      <c r="K4" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="L4" s="9" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="M4" s="3" t="n">
-        <v>9.699999999999999</v>
+        <v>9.800000000000001</v>
+      </c>
+      <c r="M4" s="9" t="n">
+        <v>9.1</v>
       </c>
       <c r="N4" s="3" t="n">
         <v>11.4</v>
@@ -829,21 +814,21 @@
         <v>98</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="Q4" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q4" s="9" t="n">
         <v>25.8</v>
       </c>
-      <c r="R4" s="12" t="n">
+      <c r="R4" s="9" t="n">
         <v>16.8</v>
       </c>
-      <c r="S4" s="12" t="n">
-        <v>19.1</v>
+      <c r="S4" s="3" t="n">
+        <v>14.1</v>
       </c>
       <c r="T4" s="3" t="n">
         <v>42.5</v>
       </c>
-      <c r="U4" s="12" t="n">
+      <c r="U4" s="3" t="n">
         <v>19.1</v>
       </c>
       <c r="V4" s="9" t="n">
@@ -852,7 +837,7 @@
       <c r="W4" s="3" t="n">
         <v>18.3</v>
       </c>
-      <c r="X4" s="12" t="n">
+      <c r="X4" s="3" t="n">
         <v>18.9</v>
       </c>
       <c r="Y4" s="3" t="n">
@@ -890,7 +875,7 @@
         <v>15.4</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>7.7</v>
+        <v>7.9</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>1.8</v>
@@ -898,14 +883,14 @@
       <c r="J5" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="K5" s="3" t="n">
+      <c r="K5" s="9" t="n">
         <v>1.2</v>
       </c>
       <c r="L5" s="9" t="n">
         <v>12.3</v>
       </c>
-      <c r="M5" s="17" t="n">
-        <v>11.94</v>
+      <c r="M5" s="9" t="n">
+        <v>11.4</v>
       </c>
       <c r="N5" s="3" t="n">
         <v>12.9</v>
@@ -916,10 +901,10 @@
       <c r="P5" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="Q5" s="3" t="n">
+      <c r="Q5" s="9" t="n">
         <v>19.6</v>
       </c>
-      <c r="R5" s="3" t="n">
+      <c r="R5" s="9" t="n">
         <v>18.6</v>
       </c>
       <c r="S5" s="3" t="n">
@@ -944,7 +929,7 @@
         <v>80.5</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>4.4</v>
+        <v>2.9</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -966,12 +951,12 @@
         <v>25.9</v>
       </c>
       <c r="E6" s="9" t="n">
-        <v>7.9</v>
+        <v>10.9</v>
       </c>
       <c r="F6" s="9" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="G6" s="3" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="G6" s="9" t="n">
         <v>15</v>
       </c>
       <c r="H6" s="3" t="n">
@@ -981,30 +966,30 @@
         <v>1.2</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="K6" s="3" t="n">
-        <v>16.5</v>
+        <v>1.1</v>
+      </c>
+      <c r="K6" s="9" t="n">
+        <v>6.5</v>
       </c>
       <c r="L6" s="9" t="n">
         <v>11.1</v>
       </c>
-      <c r="M6" s="12" t="n">
+      <c r="M6" s="9" t="n">
         <v>11</v>
       </c>
       <c r="N6" s="3" t="n">
         <v>13.1</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="P6" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q6" s="12" t="n">
+      <c r="Q6" s="9" t="n">
         <v>15.4</v>
       </c>
-      <c r="R6" s="3" t="n">
+      <c r="R6" s="9" t="n">
         <v>14.7</v>
       </c>
       <c r="S6" s="3" t="n">
@@ -1014,22 +999,22 @@
         <v>92</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>11.9</v>
+        <v>1.4</v>
       </c>
       <c r="V6" s="9" t="n">
         <v>15.8</v>
       </c>
-      <c r="W6" s="12" t="n">
+      <c r="W6" s="3" t="n">
         <v>15.3</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>17.9</v>
+        <v>17.1</v>
       </c>
       <c r="Y6" s="3" t="n">
         <v>95</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>2.9</v>
+        <v>0.9</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -1066,37 +1051,37 @@
         <v>1.2</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="K7" s="3" t="n">
-        <v>10</v>
+        <v>21.1</v>
+      </c>
+      <c r="K7" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="L7" s="9" t="n">
         <v>13.2</v>
       </c>
-      <c r="M7" s="12" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="N7" s="12" t="n">
+      <c r="M7" s="9" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="N7" s="3" t="n">
         <v>15</v>
       </c>
       <c r="O7" s="3" t="n">
         <v>99</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q7" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q7" s="9" t="n">
         <v>19.3</v>
       </c>
-      <c r="R7" s="3" t="n">
+      <c r="R7" s="9" t="n">
         <v>16.8</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>97.09999999999999</v>
+        <v>17.7</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="U7" s="3" t="n">
         <v>4.8</v>
@@ -1107,14 +1092,14 @@
       <c r="W7" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="X7" s="12" t="n">
+      <c r="X7" s="3" t="n">
         <v>17.9</v>
       </c>
       <c r="Y7" s="3" t="n">
         <v>81</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1136,16 +1121,16 @@
         <v>26.3</v>
       </c>
       <c r="E8" s="9" t="n">
-        <v>10.3</v>
+        <v>10.5</v>
       </c>
       <c r="F8" s="9" t="n">
-        <v>18.3</v>
+        <v>18.4</v>
       </c>
       <c r="G8" s="9" t="n">
         <v>15.8</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>17.7</v>
+        <v>7.7</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>2.2</v>
@@ -1153,13 +1138,13 @@
       <c r="J8" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="K8" s="3" t="n">
+      <c r="K8" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L8" s="9" t="n">
         <v>10.8</v>
       </c>
-      <c r="M8" s="3" t="n">
+      <c r="M8" s="9" t="n">
         <v>10.6</v>
       </c>
       <c r="N8" s="3" t="n">
@@ -1171,17 +1156,17 @@
       <c r="P8" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q8" s="12" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="R8" s="3" t="n">
+      <c r="Q8" s="9" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="R8" s="9" t="n">
         <v>18.4</v>
       </c>
       <c r="S8" s="3" t="n">
         <v>19.5</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>176</v>
+        <v>76</v>
       </c>
       <c r="U8" s="3" t="n">
         <v>6</v>
@@ -1189,10 +1174,10 @@
       <c r="V8" s="9" t="n">
         <v>18.7</v>
       </c>
-      <c r="W8" s="17" t="n">
-        <v>97.3</v>
-      </c>
-      <c r="X8" s="12" t="n">
+      <c r="W8" s="3" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="X8" s="3" t="n">
         <v>18.9</v>
       </c>
       <c r="Y8" s="3" t="n">
@@ -1215,7 +1200,7 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>1749.7</v>
+        <v>174.7</v>
       </c>
       <c r="D9" s="9" t="n">
         <v>128.9</v>
@@ -1226,11 +1211,11 @@
       <c r="F9" s="9" t="n">
         <v>91.90000000000001</v>
       </c>
-      <c r="G9" s="3" t="n">
-        <v>13.9</v>
+      <c r="G9" s="9" t="n">
+        <v>73.90000000000001</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>140.6</v>
+        <v>40.6</v>
       </c>
       <c r="I9" s="3" t="n">
         <v>9.9</v>
@@ -1238,14 +1223,14 @@
       <c r="J9" s="3" t="n">
         <v>13.5</v>
       </c>
-      <c r="K9" s="18" t="n">
+      <c r="K9" s="9" t="n">
         <v>7.7</v>
       </c>
-      <c r="L9" s="18" t="n">
+      <c r="L9" s="10" t="n">
         <v>56.7</v>
       </c>
-      <c r="M9" s="18" t="n">
-        <v>551.2</v>
+      <c r="M9" s="9" t="n">
+        <v>55.2</v>
       </c>
       <c r="N9" s="3" t="n">
         <v>766.1</v>
@@ -1254,14 +1239,14 @@
         <v>484.9</v>
       </c>
       <c r="P9" s="3" t="inlineStr"/>
-      <c r="Q9" s="18" t="n">
+      <c r="Q9" s="9" t="n">
         <v>101.5</v>
       </c>
-      <c r="R9" s="18" t="n">
-        <v>185.3</v>
+      <c r="R9" s="9" t="n">
+        <v>85.3</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>88.5</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>380.5</v>
@@ -1272,14 +1257,14 @@
       <c r="V9" s="9" t="n">
         <v>95</v>
       </c>
-      <c r="W9" s="18" t="n">
+      <c r="W9" s="10" t="n">
         <v>84.90000000000001</v>
       </c>
       <c r="X9" s="3" t="n">
         <v>91.09999999999999</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>414.5</v>
+        <v>14.5</v>
       </c>
       <c r="Z9" s="3" t="n">
         <v>19.8</v>
@@ -1298,7 +1283,7 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>8349.9</v>
+        <v>349.9</v>
       </c>
       <c r="D10" s="9" t="n">
         <v>25.8</v>
@@ -1318,17 +1303,17 @@
       <c r="I10" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="J10" s="12" t="n">
-        <v>9.4</v>
+      <c r="J10" s="3" t="n">
+        <v>27.4</v>
       </c>
       <c r="K10" s="3" t="inlineStr"/>
       <c r="L10" s="9" t="n">
         <v>11.3</v>
       </c>
-      <c r="M10" s="18" t="n">
+      <c r="M10" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="N10" s="12" t="n">
+      <c r="N10" s="3" t="n">
         <v>13</v>
       </c>
       <c r="O10" s="3" t="n">
@@ -1337,17 +1322,17 @@
       <c r="P10" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="Q10" s="18" t="n">
+      <c r="Q10" s="9" t="n">
         <v>20.3</v>
       </c>
-      <c r="R10" s="18" t="n">
-        <v>117.7</v>
+      <c r="R10" s="9" t="n">
+        <v>17.1</v>
       </c>
       <c r="S10" s="3" t="n">
         <v>17.7</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>76.90000000000001</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="U10" s="3" t="n">
         <v>6.7</v>
@@ -1355,7 +1340,7 @@
       <c r="V10" s="9" t="n">
         <v>19</v>
       </c>
-      <c r="W10" s="18" t="n">
+      <c r="W10" s="10" t="n">
         <v>17</v>
       </c>
       <c r="X10" s="3" t="n">
@@ -1379,7 +1364,7 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>509.3</v>
+        <v>509.5</v>
       </c>
       <c r="D11" s="9" t="n">
         <v>27.3</v>
@@ -1390,26 +1375,26 @@
       <c r="F11" s="9" t="n">
         <v>19</v>
       </c>
-      <c r="G11" s="12" t="n">
-        <v>18.6</v>
+      <c r="G11" s="9" t="n">
+        <v>16.6</v>
       </c>
       <c r="H11" s="3" t="n">
         <v>6.7</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="J11" s="3" t="n">
         <v>6</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>11.4</v>
+        <v>11</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>11.8</v>
+        <v>11.9</v>
       </c>
       <c r="N11" s="3" t="n">
         <v>13</v>
@@ -1420,28 +1405,28 @@
       <c r="P11" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q11" s="12" t="n">
+      <c r="Q11" s="9" t="n">
         <v>26.3</v>
       </c>
       <c r="R11" s="9" t="n">
         <v>17.1</v>
       </c>
-      <c r="S11" s="12" t="n">
+      <c r="S11" s="3" t="n">
         <v>14.4</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>62</v>
-      </c>
-      <c r="U11" s="12" t="n">
+        <v>42</v>
+      </c>
+      <c r="U11" s="3" t="n">
         <v>19.9</v>
       </c>
       <c r="V11" s="9" t="n">
         <v>22.1</v>
       </c>
-      <c r="W11" s="3" t="n">
+      <c r="W11" s="9" t="n">
         <v>17.6</v>
       </c>
-      <c r="X11" s="12" t="n">
+      <c r="X11" s="3" t="n">
         <v>17.6</v>
       </c>
       <c r="Y11" s="3" t="n">
@@ -1464,7 +1449,7 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>508.7</v>
+        <v>506.7</v>
       </c>
       <c r="D12" s="9" t="n">
         <v>25.9</v>
@@ -1482,18 +1467,18 @@
         <v>7.1</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J12" s="3" t="n">
         <v>5.9</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="M12" s="12" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="M12" s="3" t="n">
         <v>11.9</v>
       </c>
       <c r="N12" s="3" t="n">
@@ -1505,32 +1490,32 @@
       <c r="P12" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="Q12" s="3" t="n">
+      <c r="Q12" s="9" t="n">
         <v>25.4</v>
       </c>
       <c r="R12" s="9" t="n">
         <v>15.5</v>
       </c>
-      <c r="S12" s="12" t="n">
-        <v>12.9</v>
+      <c r="S12" s="3" t="n">
+        <v>12.1</v>
       </c>
       <c r="T12" s="3" t="n">
         <v>37</v>
       </c>
       <c r="U12" s="3" t="n">
-        <v>20.4</v>
+        <v>20.9</v>
       </c>
       <c r="V12" s="9" t="n">
         <v>21.3</v>
       </c>
-      <c r="W12" s="3" t="n">
-        <v>19.7</v>
+      <c r="W12" s="9" t="n">
+        <v>14.7</v>
       </c>
       <c r="X12" s="3" t="n">
         <v>13.1</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="Z12" s="3" t="n">
         <v>12.2</v>
@@ -1552,25 +1537,25 @@
         <v>357.9</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>25.4</v>
+        <v>25.3</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>11.3</v>
+        <v>11.2</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
       <c r="G13" s="9" t="n">
         <v>14.1</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="I13" s="12" t="n">
-        <v>99.40000000000001</v>
+        <v>7.5</v>
+      </c>
+      <c r="I13" s="3" t="n">
+        <v>1.4</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="K13" s="3" t="n">
         <v>0.5</v>
@@ -1579,9 +1564,9 @@
         <v>11.8</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="N13" s="12" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="N13" s="3" t="n">
         <v>13.6</v>
       </c>
       <c r="O13" s="3" t="n">
@@ -1590,7 +1575,7 @@
       <c r="P13" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="Q13" s="3" t="n">
+      <c r="Q13" s="9" t="n">
         <v>18.9</v>
       </c>
       <c r="R13" s="9" t="n">
@@ -1600,18 +1585,18 @@
         <v>18.9</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>185.4</v>
+        <v>85.5</v>
       </c>
       <c r="U13" s="3" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="V13" s="9" t="n">
         <v>19.6</v>
       </c>
-      <c r="W13" s="12" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="X13" s="12" t="n">
+      <c r="W13" s="9" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="X13" s="3" t="n">
         <v>19.1</v>
       </c>
       <c r="Y13" s="3" t="n">
@@ -1637,13 +1622,13 @@
         <v>227</v>
       </c>
       <c r="D14" s="9" t="n">
-        <v>23.6</v>
+        <v>23.5</v>
       </c>
       <c r="E14" s="9" t="n">
-        <v>13.1</v>
+        <v>13</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
       <c r="G14" s="9" t="n">
         <v>10.5</v>
@@ -1651,19 +1636,19 @@
       <c r="H14" s="3" t="n">
         <v>10.3</v>
       </c>
-      <c r="I14" s="12" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="J14" s="12" t="n">
-        <v>28.5</v>
+      <c r="I14" s="3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J14" s="3" t="n">
+        <v>29.5</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>46.7</v>
-      </c>
-      <c r="L14" s="17" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="M14" s="12" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="L14" s="3" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="M14" s="3" t="n">
         <v>13</v>
       </c>
       <c r="N14" s="3" t="n">
@@ -1673,19 +1658,19 @@
         <v>98</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="Q14" s="17" t="n">
-        <v>84.90000000000001</v>
+        <v>0.9</v>
+      </c>
+      <c r="Q14" s="9" t="n">
+        <v>14.9</v>
       </c>
       <c r="R14" s="9" t="n">
         <v>14.7</v>
       </c>
-      <c r="S14" s="12" t="n">
+      <c r="S14" s="3" t="n">
         <v>16.6</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>197</v>
+        <v>97</v>
       </c>
       <c r="U14" s="3" t="n">
         <v>0.6</v>
@@ -1693,10 +1678,10 @@
       <c r="V14" s="9" t="n">
         <v>14.5</v>
       </c>
-      <c r="W14" s="12" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="X14" s="12" t="n">
+      <c r="W14" s="9" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="X14" s="3" t="n">
         <v>16</v>
       </c>
       <c r="Y14" s="3" t="n">
@@ -1719,19 +1704,19 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>631</v>
+        <v>31</v>
       </c>
       <c r="D15" s="9" t="n">
         <v>26</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>10.3</v>
+        <v>11</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>18.15</v>
-      </c>
-      <c r="G15" s="12" t="n">
-        <v>50.8</v>
+        <v>18.5</v>
+      </c>
+      <c r="G15" s="9" t="n">
+        <v>15</v>
       </c>
       <c r="H15" s="3" t="n">
         <v>7.9</v>
@@ -1740,19 +1725,19 @@
         <v>3.8</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="K15" s="3" t="n">
         <v>21.6</v>
       </c>
-      <c r="L15" s="17" t="n">
-        <v>77.40000000000001</v>
+      <c r="L15" s="3" t="n">
+        <v>27.4</v>
       </c>
       <c r="M15" s="3" t="n">
         <v>11.3</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>1.3</v>
+        <v>13.3</v>
       </c>
       <c r="O15" s="3" t="n">
         <v>99</v>
@@ -1760,25 +1745,25 @@
       <c r="P15" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q15" s="3" t="n">
+      <c r="Q15" s="9" t="n">
         <v>25.5</v>
       </c>
       <c r="R15" s="9" t="n">
         <v>17.6</v>
       </c>
-      <c r="S15" s="12" t="n">
+      <c r="S15" s="3" t="n">
         <v>15.7</v>
       </c>
       <c r="T15" s="3" t="n">
         <v>48</v>
       </c>
-      <c r="U15" s="12" t="n">
-        <v>17.8</v>
+      <c r="U15" s="3" t="n">
+        <v>17</v>
       </c>
       <c r="V15" s="9" t="n">
         <v>20.7</v>
       </c>
-      <c r="W15" s="3" t="n">
+      <c r="W15" s="9" t="n">
         <v>16.3</v>
       </c>
       <c r="X15" s="3" t="n">
@@ -1807,13 +1792,13 @@
       <c r="D16" s="9" t="n">
         <v>128</v>
       </c>
-      <c r="E16" s="18" t="n">
-        <v>568.1</v>
-      </c>
-      <c r="F16" s="18" t="n">
+      <c r="E16" s="9" t="n">
+        <v>56.8</v>
+      </c>
+      <c r="F16" s="9" t="n">
         <v>92.5</v>
       </c>
-      <c r="G16" s="3" t="n">
+      <c r="G16" s="9" t="n">
         <v>71.2</v>
       </c>
       <c r="H16" s="3" t="n">
@@ -1825,26 +1810,26 @@
       <c r="J16" s="3" t="n">
         <v>21.8</v>
       </c>
-      <c r="K16" s="18" t="n">
+      <c r="K16" s="10" t="n">
         <v>39.8</v>
       </c>
-      <c r="L16" s="18" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="M16" s="18" t="n">
+      <c r="L16" s="10" t="n">
+        <v>59.1</v>
+      </c>
+      <c r="M16" s="10" t="n">
         <v>58.2</v>
       </c>
       <c r="N16" s="3" t="n">
         <v>8.4</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>489.8</v>
+        <v>89</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="Q16" s="18" t="n">
-        <v>1111</v>
+      <c r="Q16" s="9" t="n">
+        <v>111</v>
       </c>
       <c r="R16" s="9" t="n">
         <v>82.2</v>
@@ -1853,16 +1838,16 @@
         <v>77.7</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>310.8</v>
+        <v>310</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>603.9</v>
-      </c>
-      <c r="V16" s="18" t="n">
-        <v>958.2</v>
-      </c>
-      <c r="W16" s="18" t="n">
-        <v>801.9</v>
+        <v>60.9</v>
+      </c>
+      <c r="V16" s="9" t="n">
+        <v>98.2</v>
+      </c>
+      <c r="W16" s="10" t="n">
+        <v>80.7</v>
       </c>
       <c r="X16" s="3" t="n">
         <v>82.2</v>
@@ -1905,28 +1890,28 @@
         <v>7.9</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>29.4</v>
+        <v>2.9</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>97.40000000000001</v>
+        <v>27.4</v>
       </c>
       <c r="K17" s="3" t="inlineStr"/>
-      <c r="L17" s="18" t="n">
+      <c r="L17" s="10" t="n">
         <v>11.8</v>
       </c>
-      <c r="M17" s="18" t="n">
+      <c r="M17" s="10" t="n">
         <v>11.6</v>
       </c>
-      <c r="N17" s="12" t="n">
+      <c r="N17" s="3" t="n">
         <v>13.6</v>
       </c>
       <c r="O17" s="3" t="n">
         <v>97.8</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="Q17" s="18" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Q17" s="9" t="n">
         <v>22.2</v>
       </c>
       <c r="R17" s="9" t="n">
@@ -1936,7 +1921,7 @@
         <v>15.5</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>362</v>
+        <v>22</v>
       </c>
       <c r="U17" s="3" t="n">
         <v>18.2</v>
@@ -1944,17 +1929,17 @@
       <c r="V17" s="9" t="n">
         <v>19.6</v>
       </c>
-      <c r="W17" s="18" t="n">
+      <c r="W17" s="9" t="n">
         <v>16.1</v>
       </c>
-      <c r="X17" s="12" t="n">
-        <v>16.5</v>
+      <c r="X17" s="3" t="n">
+        <v>16.4</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>872.8</v>
+        <v>72.8</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1970,7 +1955,7 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>845.5</v>
+        <v>45.5</v>
       </c>
       <c r="D18" s="9" t="n">
         <v>25.9</v>
@@ -1979,30 +1964,30 @@
         <v>10.9</v>
       </c>
       <c r="F18" s="9" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="G18" s="12" t="n">
-        <v>13</v>
+        <v>18.7</v>
+      </c>
+      <c r="G18" s="9" t="n">
+        <v>15</v>
       </c>
       <c r="H18" s="3" t="n">
         <v>7.9</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>0.4</v>
+        <v>2.4</v>
       </c>
       <c r="J18" s="3" t="n">
         <v>3.3</v>
       </c>
-      <c r="K18" s="3" t="n">
+      <c r="K18" s="9" t="n">
         <v>0.1</v>
       </c>
-      <c r="L18" s="12" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="M18" s="17" t="n">
+      <c r="L18" s="9" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="M18" s="11" t="n">
         <v>1.6</v>
       </c>
-      <c r="N18" s="12" t="n">
+      <c r="N18" s="3" t="n">
         <v>16.5</v>
       </c>
       <c r="O18" s="3" t="n">
@@ -2014,26 +1999,26 @@
       <c r="Q18" s="9" t="n">
         <v>25.8</v>
       </c>
-      <c r="R18" s="3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="S18" s="12" t="n">
+      <c r="R18" s="9" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="S18" s="3" t="n">
         <v>15.4</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="U18" s="12" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="U18" s="3" t="n">
         <v>17.9</v>
       </c>
       <c r="V18" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="W18" s="12" t="n">
+      <c r="W18" s="9" t="n">
         <v>15.5</v>
       </c>
-      <c r="X18" s="12" t="n">
-        <v>19.6</v>
+      <c r="X18" s="3" t="n">
+        <v>14.6</v>
       </c>
       <c r="Y18" s="3" t="n">
         <v>59</v>
@@ -2066,8 +2051,8 @@
       <c r="F19" s="9" t="n">
         <v>19.3</v>
       </c>
-      <c r="G19" s="3" t="n">
-        <v>17.9</v>
+      <c r="G19" s="9" t="n">
+        <v>17.4</v>
       </c>
       <c r="H19" s="3" t="n">
         <v>7.2</v>
@@ -2078,10 +2063,10 @@
       <c r="J19" s="3" t="n">
         <v>5.2</v>
       </c>
-      <c r="K19" s="3" t="n">
+      <c r="K19" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L19" s="3" t="n">
+      <c r="L19" s="9" t="n">
         <v>11.2</v>
       </c>
       <c r="M19" s="3" t="n">
@@ -2099,7 +2084,7 @@
       <c r="Q19" s="9" t="n">
         <v>25.9</v>
       </c>
-      <c r="R19" s="3" t="n">
+      <c r="R19" s="9" t="n">
         <v>18</v>
       </c>
       <c r="S19" s="3" t="n">
@@ -2108,13 +2093,13 @@
       <c r="T19" s="3" t="n">
         <v>48.5</v>
       </c>
-      <c r="U19" s="12" t="n">
-        <v>7.2</v>
+      <c r="U19" s="3" t="n">
+        <v>17.2</v>
       </c>
       <c r="V19" s="9" t="n">
         <v>21.2</v>
       </c>
-      <c r="W19" s="3" t="n">
+      <c r="W19" s="9" t="n">
         <v>17.8</v>
       </c>
       <c r="X19" s="3" t="n">
@@ -2157,35 +2142,35 @@
       <c r="H20" s="3" t="n">
         <v>6.9</v>
       </c>
-      <c r="I20" s="12" t="n">
-        <v>33.3</v>
+      <c r="I20" s="3" t="n">
+        <v>23.5</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="K20" s="3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K20" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="L20" s="3" t="n">
+      <c r="L20" s="9" t="n">
         <v>11.2</v>
       </c>
-      <c r="M20" s="17" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="N20" s="12" t="n">
+      <c r="M20" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="N20" s="3" t="n">
         <v>13</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>28</v>
+        <v>98</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="Q20" s="9" t="n">
         <v>28</v>
       </c>
-      <c r="R20" s="3" t="n">
-        <v>18.9</v>
+      <c r="R20" s="9" t="n">
+        <v>18.1</v>
       </c>
       <c r="S20" s="3" t="n">
         <v>15.3</v>
@@ -2193,16 +2178,16 @@
       <c r="T20" s="3" t="n">
         <v>40.5</v>
       </c>
-      <c r="U20" s="12" t="n">
-        <v>222.4</v>
+      <c r="U20" s="3" t="n">
+        <v>22.4</v>
       </c>
       <c r="V20" s="9" t="n">
         <v>22.2</v>
       </c>
-      <c r="W20" s="12" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="X20" s="12" t="n">
+      <c r="W20" s="9" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="X20" s="3" t="n">
         <v>19.1</v>
       </c>
       <c r="Y20" s="3" t="n">
@@ -2230,13 +2215,13 @@
       <c r="D21" s="9" t="n">
         <v>24.8</v>
       </c>
-      <c r="E21" s="17" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="F21" s="17" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="G21" s="3" t="n">
+      <c r="E21" s="9" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="F21" s="9" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="G21" s="9" t="n">
         <v>12.1</v>
       </c>
       <c r="H21" s="3" t="n">
@@ -2248,10 +2233,10 @@
       <c r="J21" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="K21" s="3" t="n">
+      <c r="K21" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L21" s="12" t="n">
+      <c r="L21" s="9" t="n">
         <v>13.1</v>
       </c>
       <c r="M21" s="3" t="n">
@@ -2261,7 +2246,7 @@
         <v>14.9</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="P21" s="3" t="n">
         <v>0.2</v>
@@ -2269,7 +2254,7 @@
       <c r="Q21" s="9" t="n">
         <v>25.6</v>
       </c>
-      <c r="R21" s="3" t="n">
+      <c r="R21" s="9" t="n">
         <v>18.2</v>
       </c>
       <c r="S21" s="3" t="n">
@@ -2279,16 +2264,16 @@
         <v>51</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>1.6</v>
+        <v>16.2</v>
       </c>
       <c r="V21" s="9" t="n">
         <v>19.8</v>
       </c>
-      <c r="W21" s="3" t="n">
+      <c r="W21" s="9" t="n">
         <v>18.2</v>
       </c>
-      <c r="X21" s="12" t="n">
-        <v>0.9</v>
+      <c r="X21" s="3" t="n">
+        <v>20</v>
       </c>
       <c r="Y21" s="3" t="n">
         <v>87</v>
@@ -2310,22 +2295,22 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>989</v>
+        <v>9</v>
       </c>
       <c r="D22" s="9" t="n">
         <v>25.2</v>
       </c>
-      <c r="E22" s="17" t="n">
-        <v>-7.8</v>
-      </c>
-      <c r="F22" s="3" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="G22" s="3" t="n">
+      <c r="E22" s="9" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="F22" s="9" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="G22" s="9" t="n">
         <v>13.1</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>83.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I22" s="3" t="n">
         <v>2.7</v>
@@ -2333,17 +2318,17 @@
       <c r="J22" s="3" t="n">
         <v>3.8</v>
       </c>
-      <c r="K22" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L22" s="12" t="n">
+      <c r="K22" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" s="9" t="n">
         <v>12.3</v>
       </c>
       <c r="M22" s="3" t="n">
         <v>12.2</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>14.9</v>
+        <v>14.1</v>
       </c>
       <c r="O22" s="3" t="n">
         <v>99</v>
@@ -2354,14 +2339,14 @@
       <c r="Q22" s="9" t="n">
         <v>23.6</v>
       </c>
-      <c r="R22" s="3" t="n">
+      <c r="R22" s="9" t="n">
         <v>16.2</v>
       </c>
       <c r="S22" s="3" t="n">
         <v>14.4</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>149.5</v>
+        <v>49.5</v>
       </c>
       <c r="U22" s="3" t="n">
         <v>14.8</v>
@@ -2369,17 +2354,17 @@
       <c r="V22" s="9" t="n">
         <v>22.5</v>
       </c>
-      <c r="W22" s="3" t="n">
+      <c r="W22" s="9" t="n">
         <v>15.6</v>
       </c>
-      <c r="X22" s="12" t="n">
+      <c r="X22" s="3" t="n">
         <v>13.9</v>
       </c>
       <c r="Y22" s="3" t="n">
         <v>50.5</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>139.7</v>
+        <v>13.4</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2395,55 +2380,55 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>2322.3</v>
-      </c>
-      <c r="D23" s="18" t="n">
-        <v>112.1</v>
-      </c>
-      <c r="E23" s="18" t="n">
-        <v>50.1</v>
-      </c>
-      <c r="F23" s="18" t="n">
+        <v>2320.3</v>
+      </c>
+      <c r="D23" s="9" t="n">
+        <v>132.1</v>
+      </c>
+      <c r="E23" s="9" t="n">
+        <v>56.7</v>
+      </c>
+      <c r="F23" s="9" t="n">
         <v>94.40000000000001</v>
       </c>
-      <c r="G23" s="3" t="n">
-        <v>75.90000000000001</v>
+      <c r="G23" s="9" t="n">
+        <v>75.40000000000001</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>40.6</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>28.8</v>
-      </c>
-      <c r="K23" s="18" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="K23" s="9" t="n">
         <v>0.3</v>
       </c>
-      <c r="L23" s="18" t="n">
+      <c r="L23" s="10" t="n">
         <v>2.5</v>
       </c>
-      <c r="M23" s="18" t="n">
-        <v>161.8</v>
+      <c r="M23" s="10" t="n">
+        <v>61.8</v>
       </c>
       <c r="N23" s="3" t="n">
         <v>71.5</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>2493</v>
+        <v>93</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>11.4</v>
+        <v>1.4</v>
       </c>
       <c r="Q23" s="9" t="n">
         <v>128.9</v>
       </c>
-      <c r="R23" s="18" t="n">
-        <v>85</v>
+      <c r="R23" s="9" t="n">
+        <v>88</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>7.8</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="T23" s="3" t="n">
         <v>235.7</v>
@@ -2454,7 +2439,7 @@
       <c r="V23" s="9" t="n">
         <v>106.7</v>
       </c>
-      <c r="W23" s="18" t="n">
+      <c r="W23" s="9" t="n">
         <v>85.5</v>
       </c>
       <c r="X23" s="3" t="n">
@@ -2501,19 +2486,19 @@
         <v>2.9</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>72.09999999999999</v>
+        <v>22.1</v>
       </c>
       <c r="K24" s="3" t="n">
         <v>1.4</v>
       </c>
-      <c r="L24" s="18" t="n">
+      <c r="L24" s="9" t="n">
         <v>12.5</v>
       </c>
-      <c r="M24" s="18" t="n">
+      <c r="M24" s="10" t="n">
         <v>12.4</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>11.9</v>
+        <v>1.1</v>
       </c>
       <c r="O24" s="3" t="n">
         <v>98.59999999999999</v>
@@ -2524,23 +2509,23 @@
       <c r="Q24" s="9" t="n">
         <v>25.8</v>
       </c>
-      <c r="R24" s="18" t="n">
+      <c r="R24" s="9" t="n">
         <v>17.6</v>
       </c>
       <c r="S24" s="3" t="n">
         <v>15.6</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>47.9</v>
+        <v>47.1</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>17.8</v>
+        <v>17.7</v>
       </c>
       <c r="V24" s="9" t="n">
         <v>21.3</v>
       </c>
-      <c r="W24" s="18" t="n">
-        <v>17.7</v>
+      <c r="W24" s="9" t="n">
+        <v>17.1</v>
       </c>
       <c r="X24" s="3" t="n">
         <v>17.2</v>
@@ -2576,8 +2561,8 @@
       <c r="F25" s="9" t="n">
         <v>17.8</v>
       </c>
-      <c r="G25" s="12" t="n">
-        <v>10.9</v>
+      <c r="G25" s="9" t="n">
+        <v>16.2</v>
       </c>
       <c r="H25" s="3" t="n">
         <v>5.7</v>
@@ -2588,23 +2573,23 @@
       <c r="J25" s="3" t="n">
         <v>4.7</v>
       </c>
-      <c r="K25" s="3" t="n">
-        <v>6.4</v>
+      <c r="K25" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="L25" s="9" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="M25" s="17" t="n">
-        <v>2.9</v>
+        <v>10.1</v>
+      </c>
+      <c r="M25" s="9" t="n">
+        <v>9.9</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="O25" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="P25" s="3" t="n">
         <v>0.4</v>
-      </c>
-      <c r="P25" s="3" t="n">
-        <v>0.9</v>
       </c>
       <c r="Q25" s="9" t="n">
         <v>24.7</v>
@@ -2613,7 +2598,7 @@
         <v>17.2</v>
       </c>
       <c r="S25" s="3" t="n">
-        <v>13.9</v>
+        <v>15.4</v>
       </c>
       <c r="T25" s="3" t="n">
         <v>49.5</v>
@@ -2624,10 +2609,10 @@
       <c r="V25" s="9" t="n">
         <v>21.3</v>
       </c>
-      <c r="W25" s="9" t="n">
+      <c r="W25" s="3" t="n">
         <v>16.9</v>
       </c>
-      <c r="X25" s="12" t="n">
+      <c r="X25" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="Y25" s="3" t="n">
@@ -2650,7 +2635,7 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>349.9</v>
+        <v>349.1</v>
       </c>
       <c r="D26" s="9" t="n">
         <v>24.4</v>
@@ -2667,29 +2652,29 @@
       <c r="H26" s="3" t="n">
         <v>6.6</v>
       </c>
-      <c r="I26" s="12" t="n">
-        <v>23.4</v>
+      <c r="I26" s="3" t="n">
+        <v>2.3</v>
       </c>
       <c r="J26" s="3" t="n">
         <v>8.5</v>
       </c>
-      <c r="K26" s="3" t="n">
+      <c r="K26" s="9" t="n">
         <v>0.9</v>
       </c>
       <c r="L26" s="9" t="n">
         <v>10.4</v>
       </c>
-      <c r="M26" s="3" t="n">
+      <c r="M26" s="9" t="n">
         <v>10.2</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>1.8</v>
+        <v>12.3</v>
       </c>
       <c r="O26" s="3" t="n">
         <v>98</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="Q26" s="9" t="n">
         <v>21</v>
@@ -2698,19 +2683,19 @@
         <v>16.2</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>15.8</v>
+        <v>15.7</v>
       </c>
       <c r="T26" s="3" t="n">
         <v>63.5</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>19.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="V26" s="9" t="n">
         <v>21.6</v>
       </c>
-      <c r="W26" s="9" t="n">
-        <v>15.5</v>
+      <c r="W26" s="3" t="n">
+        <v>25.5</v>
       </c>
       <c r="X26" s="3" t="n">
         <v>14.2</v>
@@ -2719,7 +2704,7 @@
         <v>55</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>111.8</v>
+        <v>11.8</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2738,16 +2723,16 @@
         <v>340.2</v>
       </c>
       <c r="D27" s="9" t="n">
-        <v>25.7</v>
+        <v>25.1</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>10.5</v>
+        <v>11.1</v>
       </c>
       <c r="F27" s="9" t="n">
         <v>18.1</v>
       </c>
-      <c r="G27" s="12" t="n">
-        <v>24</v>
+      <c r="G27" s="9" t="n">
+        <v>14</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>8.4</v>
@@ -2756,15 +2741,15 @@
         <v>2</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>29.4</v>
-      </c>
-      <c r="K27" s="3" t="n">
-        <v>7.9</v>
+        <v>2.9</v>
+      </c>
+      <c r="K27" s="9" t="n">
+        <v>7.1</v>
       </c>
       <c r="L27" s="9" t="n">
         <v>12.4</v>
       </c>
-      <c r="M27" s="3" t="n">
+      <c r="M27" s="9" t="n">
         <v>12.2</v>
       </c>
       <c r="N27" s="3" t="n">
@@ -2782,26 +2767,26 @@
       <c r="R27" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="S27" s="12" t="n">
+      <c r="S27" s="3" t="n">
         <v>17.3</v>
       </c>
       <c r="T27" s="3" t="n">
         <v>86</v>
       </c>
       <c r="U27" s="3" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="V27" s="9" t="n">
         <v>17.4</v>
       </c>
-      <c r="W27" s="9" t="n">
+      <c r="W27" s="3" t="n">
         <v>16.7</v>
       </c>
-      <c r="X27" s="12" t="n">
+      <c r="X27" s="3" t="n">
         <v>18.5</v>
       </c>
       <c r="Y27" s="3" t="n">
-        <v>1213</v>
+        <v>23</v>
       </c>
       <c r="Z27" s="3" t="n">
         <v>1.6</v>
@@ -2831,11 +2816,11 @@
       <c r="F28" s="9" t="n">
         <v>19.3</v>
       </c>
-      <c r="G28" s="12" t="n">
-        <v>15.9</v>
+      <c r="G28" s="9" t="n">
+        <v>15.5</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>8.699999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>2.4</v>
@@ -2843,13 +2828,13 @@
       <c r="J28" s="3" t="n">
         <v>3.3</v>
       </c>
-      <c r="K28" s="3" t="n">
+      <c r="K28" s="9" t="n">
         <v>5.5</v>
       </c>
       <c r="L28" s="9" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="M28" s="12" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="M28" s="9" t="n">
         <v>13.3</v>
       </c>
       <c r="N28" s="3" t="n">
@@ -2879,17 +2864,17 @@
       <c r="V28" s="9" t="n">
         <v>16.4</v>
       </c>
-      <c r="W28" s="9" t="n">
+      <c r="W28" s="3" t="n">
         <v>15.5</v>
       </c>
-      <c r="X28" s="12" t="n">
-        <v>17.8</v>
+      <c r="X28" s="3" t="n">
+        <v>17</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>191</v>
+        <v>91</v>
       </c>
       <c r="Z28" s="3" t="n">
-        <v>11.8</v>
+        <v>1.8</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -2905,7 +2890,7 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>523.3</v>
+        <v>593.3</v>
       </c>
       <c r="D29" s="9" t="n">
         <v>28.8</v>
@@ -2916,8 +2901,8 @@
       <c r="F29" s="9" t="n">
         <v>19.5</v>
       </c>
-      <c r="G29" s="3" t="n">
-        <v>1.8</v>
+      <c r="G29" s="9" t="n">
+        <v>18.7</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>7.2</v>
@@ -2928,23 +2913,23 @@
       <c r="J29" s="3" t="n">
         <v>6.2</v>
       </c>
-      <c r="K29" s="3" t="n">
+      <c r="K29" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L29" s="9" t="n">
         <v>10.9</v>
       </c>
-      <c r="M29" s="3" t="n">
+      <c r="M29" s="9" t="n">
         <v>10.5</v>
       </c>
       <c r="N29" s="3" t="n">
         <v>12.4</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>196</v>
+        <v>96</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>2.6</v>
+        <v>0.6</v>
       </c>
       <c r="Q29" s="9" t="n">
         <v>27</v>
@@ -2964,14 +2949,14 @@
       <c r="V29" s="9" t="n">
         <v>22.8</v>
       </c>
-      <c r="W29" s="9" t="n">
+      <c r="W29" s="3" t="n">
         <v>17.3</v>
       </c>
       <c r="X29" s="3" t="n">
-        <v>22.1</v>
+        <v>16.7</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>160</v>
+        <v>60</v>
       </c>
       <c r="Z29" s="3" t="n">
         <v>11.2</v>
@@ -2992,16 +2977,16 @@
       <c r="C30" s="3" t="n">
         <v>228.4</v>
       </c>
-      <c r="D30" s="18" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="E30" s="18" t="n">
-        <v>527.1</v>
+      <c r="D30" s="9" t="n">
+        <v>131.2</v>
+      </c>
+      <c r="E30" s="9" t="n">
+        <v>52.1</v>
       </c>
       <c r="F30" s="9" t="n">
         <v>91.7</v>
       </c>
-      <c r="G30" s="3" t="n">
+      <c r="G30" s="9" t="n">
         <v>79.09999999999999</v>
       </c>
       <c r="H30" s="3" t="n">
@@ -3013,14 +2998,14 @@
       <c r="J30" s="3" t="n">
         <v>19.5</v>
       </c>
-      <c r="K30" s="18" t="n">
+      <c r="K30" s="9" t="n">
         <v>13.5</v>
       </c>
-      <c r="L30" s="18" t="n">
+      <c r="L30" s="9" t="n">
         <v>57.2</v>
       </c>
-      <c r="M30" s="18" t="n">
-        <v>56.7</v>
+      <c r="M30" s="9" t="n">
+        <v>56.1</v>
       </c>
       <c r="N30" s="3" t="n">
         <v>65.90000000000001</v>
@@ -3031,7 +3016,7 @@
       <c r="P30" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="Q30" s="18" t="n">
+      <c r="Q30" s="10" t="n">
         <v>413.2</v>
       </c>
       <c r="R30" s="9" t="n">
@@ -3041,15 +3026,15 @@
         <v>84.40000000000001</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>314.8</v>
+        <v>14.8</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>35.4</v>
+        <v>55.4</v>
       </c>
       <c r="V30" s="9" t="n">
         <v>99.5</v>
       </c>
-      <c r="W30" s="9" t="n">
+      <c r="W30" s="10" t="n">
         <v>81.90000000000001</v>
       </c>
       <c r="X30" s="3" t="n">
@@ -3075,7 +3060,7 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="D31" s="9" t="n">
         <v>26.2</v>
@@ -3099,10 +3084,10 @@
         <v>3.9</v>
       </c>
       <c r="K31" s="3" t="inlineStr"/>
-      <c r="L31" s="9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="M31" s="18" t="n">
+      <c r="L31" s="10" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="M31" s="9" t="n">
         <v>11.2</v>
       </c>
       <c r="N31" s="3" t="n">
@@ -3117,32 +3102,32 @@
       <c r="Q31" s="9" t="n">
         <v>22.6</v>
       </c>
-      <c r="R31" s="18" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="S31" s="12" t="n">
+      <c r="R31" s="9" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="S31" s="3" t="n">
         <v>16.9</v>
       </c>
       <c r="T31" s="3" t="n">
         <v>63</v>
       </c>
-      <c r="U31" s="12" t="n">
-        <v>111.4</v>
+      <c r="U31" s="3" t="n">
+        <v>11.1</v>
       </c>
       <c r="V31" s="9" t="n">
         <v>19.9</v>
       </c>
-      <c r="W31" s="9" t="n">
+      <c r="W31" s="10" t="n">
         <v>16.4</v>
       </c>
-      <c r="X31" s="12" t="n">
+      <c r="X31" s="3" t="n">
         <v>16.6</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>730</v>
+        <v>730.2</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>165.8</v>
+        <v>25.8</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3167,7 +3152,7 @@
         <v>10.2</v>
       </c>
       <c r="F32" s="9" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="G32" s="9" t="n">
         <v>17.7</v>
@@ -3181,16 +3166,16 @@
       <c r="J32" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="K32" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L32" s="3" t="n">
-        <v>20.5</v>
+      <c r="K32" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" s="9" t="n">
+        <v>10.5</v>
       </c>
       <c r="M32" s="9" t="n">
         <v>10.2</v>
       </c>
-      <c r="N32" s="12" t="n">
+      <c r="N32" s="3" t="n">
         <v>12.4</v>
       </c>
       <c r="O32" s="3" t="n">
@@ -3199,31 +3184,31 @@
       <c r="P32" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q32" s="9" t="n">
-        <v>26.46</v>
+      <c r="Q32" s="3" t="n">
+        <v>21.1</v>
       </c>
       <c r="R32" s="9" t="n">
         <v>18.2</v>
       </c>
-      <c r="S32" s="12" t="n">
+      <c r="S32" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>62.6</v>
+        <v>62.2</v>
       </c>
       <c r="U32" s="3" t="inlineStr"/>
-      <c r="V32" s="3" t="n">
+      <c r="V32" s="9" t="n">
         <v>21.4</v>
       </c>
       <c r="W32" s="9" t="n">
         <v>17.6</v>
       </c>
-      <c r="X32" s="12" t="n">
-        <v>17.2</v>
+      <c r="X32" s="3" t="n">
+        <v>17.9</v>
       </c>
       <c r="Y32" s="3" t="inlineStr"/>
       <c r="Z32" s="3" t="n">
-        <v>171.8</v>
+        <v>7.8</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3254,25 +3239,25 @@
         <v>11.4</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>2.4</v>
+        <v>9.4</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J33" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="K33" s="3" t="n">
+      <c r="K33" s="9" t="n">
         <v>6.8</v>
       </c>
-      <c r="L33" s="3" t="n">
+      <c r="L33" s="9" t="n">
         <v>14.9</v>
       </c>
       <c r="M33" s="9" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="N33" s="12" t="n">
-        <v>18.5</v>
+        <v>14.7</v>
+      </c>
+      <c r="N33" s="3" t="n">
+        <v>16.5</v>
       </c>
       <c r="O33" s="3" t="n">
         <v>98</v>
@@ -3280,7 +3265,7 @@
       <c r="P33" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="Q33" s="9" t="n">
+      <c r="Q33" s="3" t="n">
         <v>20.3</v>
       </c>
       <c r="R33" s="9" t="n">
@@ -3293,15 +3278,15 @@
         <v>79.90000000000001</v>
       </c>
       <c r="U33" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="V33" s="3" t="n">
-        <v>19.9</v>
+        <v>5</v>
+      </c>
+      <c r="V33" s="9" t="n">
+        <v>19.4</v>
       </c>
       <c r="W33" s="9" t="n">
         <v>17.9</v>
       </c>
-      <c r="X33" s="12" t="n">
+      <c r="X33" s="3" t="n">
         <v>18.7</v>
       </c>
       <c r="Y33" s="3" t="n">
@@ -3324,7 +3309,7 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>329.9</v>
+        <v>329.1</v>
       </c>
       <c r="D34" s="9" t="n">
         <v>23.3</v>
@@ -3338,26 +3323,26 @@
       <c r="G34" s="9" t="n">
         <v>8.6</v>
       </c>
-      <c r="H34" s="12" t="n">
+      <c r="H34" s="3" t="n">
         <v>14.7</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>11.5</v>
+        <v>1.5</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="K34" s="3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="K34" s="9" t="n">
         <v>1.7</v>
       </c>
-      <c r="L34" s="3" t="n">
+      <c r="L34" s="9" t="n">
         <v>16</v>
       </c>
       <c r="M34" s="9" t="n">
         <v>15.9</v>
       </c>
-      <c r="N34" s="12" t="n">
-        <v>7.8</v>
+      <c r="N34" s="3" t="n">
+        <v>17.9</v>
       </c>
       <c r="O34" s="3" t="n">
         <v>99</v>
@@ -3365,7 +3350,7 @@
       <c r="P34" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q34" s="9" t="n">
+      <c r="Q34" s="3" t="n">
         <v>21.8</v>
       </c>
       <c r="R34" s="9" t="n">
@@ -3378,15 +3363,15 @@
         <v>72</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="V34" s="12" t="n">
-        <v>28.7</v>
+        <v>7.6</v>
+      </c>
+      <c r="V34" s="9" t="n">
+        <v>18.7</v>
       </c>
       <c r="W34" s="9" t="n">
         <v>16.8</v>
       </c>
-      <c r="X34" s="12" t="n">
+      <c r="X34" s="3" t="n">
         <v>18</v>
       </c>
       <c r="Y34" s="3" t="n">
@@ -3432,10 +3417,10 @@
       <c r="J35" s="3" t="n">
         <v>5.5</v>
       </c>
-      <c r="K35" s="3" t="n">
+      <c r="K35" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L35" s="3" t="n">
+      <c r="L35" s="9" t="n">
         <v>13</v>
       </c>
       <c r="M35" s="9" t="n">
@@ -3445,27 +3430,27 @@
         <v>14.8</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>399</v>
+        <v>99</v>
       </c>
       <c r="P35" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q35" s="9" t="n">
+      <c r="Q35" s="3" t="n">
         <v>23.8</v>
       </c>
       <c r="R35" s="9" t="n">
         <v>17.6</v>
       </c>
-      <c r="S35" s="12" t="n">
+      <c r="S35" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="U35" s="3" t="n">
         <v>12.8</v>
       </c>
-      <c r="V35" s="12" t="n">
+      <c r="V35" s="9" t="n">
         <v>20.8</v>
       </c>
       <c r="W35" s="9" t="n">
@@ -3475,7 +3460,7 @@
         <v>16.8</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>68.3</v>
+        <v>68.5</v>
       </c>
       <c r="Z35" s="3" t="n">
         <v>8</v>
@@ -3500,64 +3485,64 @@
         <v>26.3</v>
       </c>
       <c r="E36" s="9" t="n">
-        <v>10.9</v>
+        <v>10.4</v>
       </c>
       <c r="F36" s="9" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="G36" s="3" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="G36" s="9" t="n">
         <v>15.9</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>6.4</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>13.9</v>
+        <v>3.9</v>
       </c>
       <c r="J36" s="3" t="n">
         <v>5.9</v>
       </c>
-      <c r="K36" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L36" s="12" t="n">
-        <v>8.6</v>
+      <c r="K36" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" s="9" t="n">
+        <v>10.6</v>
       </c>
       <c r="M36" s="9" t="n">
         <v>10.5</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>12.8</v>
+        <v>12.6</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>29</v>
+        <v>99</v>
       </c>
       <c r="P36" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q36" s="9" t="n">
+      <c r="Q36" s="3" t="n">
         <v>23.5</v>
       </c>
       <c r="R36" s="9" t="n">
         <v>17.1</v>
       </c>
-      <c r="S36" s="12" t="n">
-        <v>19.8</v>
+      <c r="S36" s="3" t="n">
+        <v>14.8</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="V36" s="3" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="V36" s="9" t="n">
         <v>20.6</v>
       </c>
       <c r="W36" s="9" t="n">
         <v>14.6</v>
       </c>
-      <c r="X36" s="12" t="n">
-        <v>3.3</v>
+      <c r="X36" s="3" t="n">
+        <v>13.3</v>
       </c>
       <c r="Y36" s="3" t="n">
         <v>55</v>
@@ -3579,7 +3564,7 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>2240.4</v>
+        <v>224.4</v>
       </c>
       <c r="D37" s="9" t="n">
         <v>128.5</v>
@@ -3590,60 +3575,60 @@
       <c r="F37" s="9" t="n">
         <v>94.7</v>
       </c>
-      <c r="G37" s="3" t="n">
-        <v>62.6</v>
+      <c r="G37" s="9" t="n">
+        <v>67.59999999999999</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>14.9</v>
+        <v>14.1</v>
       </c>
       <c r="J37" s="3" t="n">
         <v>20.8</v>
       </c>
-      <c r="K37" s="18" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="L37" s="18" t="n">
-        <v>63</v>
-      </c>
-      <c r="M37" s="18" t="n">
+      <c r="K37" s="9" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="L37" s="9" t="n">
+        <v>65</v>
+      </c>
+      <c r="M37" s="9" t="n">
         <v>64.2</v>
       </c>
       <c r="N37" s="3" t="n">
         <v>74.2</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>492</v>
+        <v>92</v>
       </c>
       <c r="P37" s="3" t="inlineStr"/>
-      <c r="Q37" s="18" t="n">
+      <c r="Q37" s="10" t="n">
         <v>115.5</v>
       </c>
-      <c r="R37" s="18" t="n">
-        <v>89.90000000000001</v>
+      <c r="R37" s="10" t="n">
+        <v>89.40000000000001</v>
       </c>
       <c r="S37" s="3" t="n">
         <v>88</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>216.9</v>
+        <v>16.4</v>
       </c>
       <c r="U37" s="3" t="n">
         <v>54.5</v>
       </c>
-      <c r="V37" s="18" t="n">
+      <c r="V37" s="9" t="n">
         <v>100.9</v>
       </c>
-      <c r="W37" s="18" t="n">
+      <c r="W37" s="10" t="n">
         <v>83.09999999999999</v>
       </c>
       <c r="X37" s="3" t="n">
         <v>84.7</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>359.3</v>
+        <v>359.5</v>
       </c>
       <c r="Z37" s="3" t="n">
         <v>34.6</v>
@@ -3662,7 +3647,7 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>44.8</v>
+        <v>448.1</v>
       </c>
       <c r="D38" s="9" t="n">
         <v>25.7</v>
@@ -3682,11 +3667,13 @@
       <c r="I38" s="3" t="n">
         <v>28.1</v>
       </c>
-      <c r="J38" s="12" t="n">
-        <v>92.09999999999999</v>
-      </c>
-      <c r="K38" s="3" t="inlineStr"/>
-      <c r="L38" s="18" t="n">
+      <c r="J38" s="3" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="K38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" s="9" t="n">
         <v>13</v>
       </c>
       <c r="M38" s="9" t="n">
@@ -3696,37 +3683,37 @@
         <v>14.8</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>298.9</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="P38" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q38" s="9" t="n">
+      <c r="Q38" s="10" t="n">
         <v>23.1</v>
       </c>
       <c r="R38" s="9" t="n">
         <v>17.9</v>
       </c>
-      <c r="S38" s="12" t="n">
+      <c r="S38" s="3" t="n">
         <v>17.6</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="U38" s="12" t="n">
-        <v>128.9</v>
-      </c>
-      <c r="V38" s="18" t="n">
+        <v>63.3</v>
+      </c>
+      <c r="U38" s="3" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="V38" s="9" t="n">
         <v>20.2</v>
       </c>
       <c r="W38" s="9" t="n">
         <v>16.6</v>
       </c>
-      <c r="X38" s="12" t="n">
+      <c r="X38" s="3" t="n">
         <v>16.9</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>21.9</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="Z38" s="3" t="n">
         <v>6.9</v>
@@ -3760,50 +3747,50 @@
         <v>15.9</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>1.9</v>
+        <v>2.9</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="J39" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="K39" s="3" t="n">
+      <c r="K39" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L39" s="3" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="M39" s="9" t="n">
+      <c r="L39" s="9" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="M39" s="3" t="n">
         <v>12.5</v>
       </c>
-      <c r="N39" s="12" t="n">
+      <c r="N39" s="3" t="n">
         <v>14.9</v>
       </c>
       <c r="O39" s="3" t="n">
         <v>98</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="Q39" s="9" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q39" s="3" t="n">
         <v>26.6</v>
       </c>
-      <c r="R39" s="3" t="n">
+      <c r="R39" s="9" t="n">
         <v>18</v>
       </c>
       <c r="S39" s="3" t="inlineStr"/>
       <c r="T39" s="3" t="n">
-        <v>45.5</v>
+        <v>45.3</v>
       </c>
       <c r="U39" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="V39" s="17" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="W39" s="17" t="n">
-        <v>51.7</v>
+      <c r="V39" s="9" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="W39" s="9" t="n">
+        <v>15.7</v>
       </c>
       <c r="X39" s="3" t="n">
         <v>14.6</v>
@@ -3812,7 +3799,7 @@
         <v>56</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>176</v>
+        <v>76</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3828,7 +3815,7 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>335.9</v>
+        <v>355.7</v>
       </c>
       <c r="D40" s="9" t="n">
         <v>27.2</v>
@@ -3851,46 +3838,46 @@
       <c r="J40" s="3" t="n">
         <v>3.2</v>
       </c>
-      <c r="K40" s="3" t="n">
+      <c r="K40" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L40" s="3" t="n">
+      <c r="L40" s="9" t="n">
         <v>10.6</v>
       </c>
-      <c r="M40" s="9" t="n">
+      <c r="M40" s="3" t="n">
         <v>10.3</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>12.9</v>
+        <v>12.1</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>196</v>
+        <v>96</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="Q40" s="9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q40" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="R40" s="3" t="n">
+      <c r="R40" s="9" t="n">
         <v>18</v>
       </c>
-      <c r="S40" s="12" t="n">
+      <c r="S40" s="3" t="n">
         <v>18.4</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>169.5</v>
+        <v>69.5</v>
       </c>
       <c r="U40" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="V40" s="3" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="W40" s="12" t="n">
+      <c r="V40" s="9" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="W40" s="9" t="n">
         <v>16.8</v>
       </c>
-      <c r="X40" s="12" t="n">
+      <c r="X40" s="3" t="n">
         <v>17.5</v>
       </c>
       <c r="Y40" s="3" t="n">
@@ -3916,51 +3903,51 @@
         <v>451.2</v>
       </c>
       <c r="D41" s="9" t="n">
-        <v>28.94</v>
+        <v>28.4</v>
       </c>
       <c r="E41" s="9" t="n">
-        <v>18.6</v>
+        <v>8.6</v>
       </c>
       <c r="F41" s="9" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="G41" s="3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="G41" s="9" t="n">
         <v>19.8</v>
       </c>
-      <c r="H41" s="12" t="n">
-        <v>51</v>
+      <c r="H41" s="3" t="n">
+        <v>22</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>0.3</v>
+        <v>3.6</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="K41" s="3" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="K41" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L41" s="3" t="n">
+      <c r="L41" s="9" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="M41" s="9" t="n">
+      <c r="M41" s="3" t="n">
         <v>8.6</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>11.1</v>
+        <v>11</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>198</v>
+        <v>98</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="Q41" s="9" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="R41" s="12" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q41" s="3" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="R41" s="9" t="n">
         <v>17.4</v>
       </c>
-      <c r="S41" s="12" t="n">
+      <c r="S41" s="3" t="n">
         <v>16.6</v>
       </c>
       <c r="T41" s="3" t="n">
@@ -3969,11 +3956,11 @@
       <c r="U41" s="3" t="n">
         <v>12.9</v>
       </c>
-      <c r="V41" s="3" t="n">
+      <c r="V41" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="W41" s="17" t="n">
-        <v>18.15</v>
+      <c r="W41" s="9" t="n">
+        <v>18.5</v>
       </c>
       <c r="X41" s="3" t="n">
         <v>16.3</v>
@@ -4003,32 +3990,32 @@
       <c r="D42" s="9" t="n">
         <v>27.2</v>
       </c>
-      <c r="E42" s="17" t="n">
-        <v>1.1</v>
+      <c r="E42" s="9" t="n">
+        <v>11.4</v>
       </c>
       <c r="F42" s="9" t="n">
         <v>19.3</v>
       </c>
-      <c r="G42" s="17" t="n">
-        <v>12.6</v>
+      <c r="G42" s="9" t="n">
+        <v>15.7</v>
       </c>
       <c r="H42" s="3" t="n">
         <v>7.8</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>13.9</v>
+        <v>3.9</v>
       </c>
       <c r="J42" s="3" t="n">
         <v>5.6</v>
       </c>
-      <c r="K42" s="3" t="n">
+      <c r="K42" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L42" s="3" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="M42" s="9" t="n">
-        <v>11.1</v>
+      <c r="L42" s="9" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="M42" s="11" t="n">
+        <v>1.1</v>
       </c>
       <c r="N42" s="3" t="n">
         <v>13.3</v>
@@ -4039,25 +4026,25 @@
       <c r="P42" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="Q42" s="9" t="n">
-        <v>26.6</v>
-      </c>
-      <c r="R42" s="12" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="S42" s="12" t="n">
+      <c r="Q42" s="11" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R42" s="9" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="S42" s="3" t="n">
         <v>15.1</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>53.2</v>
-      </c>
-      <c r="U42" s="12" t="n">
+        <v>43.3</v>
+      </c>
+      <c r="U42" s="3" t="n">
         <v>19.6</v>
       </c>
-      <c r="V42" s="3" t="n">
+      <c r="V42" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="W42" s="16" t="inlineStr"/>
+      <c r="W42" s="9" t="inlineStr"/>
       <c r="X42" s="3" t="inlineStr"/>
       <c r="Y42" s="3" t="inlineStr"/>
       <c r="Z42" s="3" t="inlineStr"/>
@@ -4078,25 +4065,25 @@
         <v>0.1</v>
       </c>
       <c r="D43" s="9" t="inlineStr"/>
-      <c r="E43" s="9" t="inlineStr"/>
+      <c r="E43" s="13" t="inlineStr"/>
       <c r="F43" s="9" t="inlineStr"/>
       <c r="G43" s="3" t="inlineStr"/>
       <c r="H43" s="3" t="inlineStr"/>
       <c r="I43" s="3" t="inlineStr"/>
       <c r="J43" s="3" t="inlineStr"/>
-      <c r="K43" s="16" t="inlineStr"/>
-      <c r="L43" s="16" t="inlineStr"/>
-      <c r="M43" s="9" t="inlineStr"/>
+      <c r="K43" s="9" t="inlineStr"/>
+      <c r="L43" s="9" t="inlineStr"/>
+      <c r="M43" s="13" t="inlineStr"/>
       <c r="N43" s="3" t="inlineStr"/>
       <c r="O43" s="3" t="inlineStr"/>
       <c r="P43" s="3" t="inlineStr"/>
-      <c r="Q43" s="9" t="inlineStr"/>
-      <c r="R43" s="16" t="inlineStr"/>
+      <c r="Q43" s="13" t="inlineStr"/>
+      <c r="R43" s="9" t="inlineStr"/>
       <c r="S43" s="3" t="inlineStr"/>
       <c r="T43" s="3" t="inlineStr"/>
       <c r="U43" s="3" t="inlineStr"/>
-      <c r="V43" s="16" t="inlineStr"/>
-      <c r="W43" s="16" t="inlineStr"/>
+      <c r="V43" s="9" t="inlineStr"/>
+      <c r="W43" s="9" t="inlineStr"/>
       <c r="X43" s="3" t="inlineStr"/>
       <c r="Y43" s="3" t="inlineStr"/>
       <c r="Z43" s="3" t="inlineStr"/>
@@ -4117,25 +4104,25 @@
         <v>0.1</v>
       </c>
       <c r="D44" s="9" t="inlineStr"/>
-      <c r="E44" s="9" t="inlineStr"/>
+      <c r="E44" s="13" t="inlineStr"/>
       <c r="F44" s="9" t="inlineStr"/>
       <c r="G44" s="3" t="inlineStr"/>
       <c r="H44" s="3" t="inlineStr"/>
       <c r="I44" s="3" t="inlineStr"/>
       <c r="J44" s="3" t="inlineStr"/>
-      <c r="K44" s="16" t="inlineStr"/>
-      <c r="L44" s="16" t="inlineStr"/>
-      <c r="M44" s="9" t="inlineStr"/>
+      <c r="K44" s="9" t="inlineStr"/>
+      <c r="L44" s="9" t="inlineStr"/>
+      <c r="M44" s="13" t="inlineStr"/>
       <c r="N44" s="3" t="inlineStr"/>
       <c r="O44" s="3" t="inlineStr"/>
       <c r="P44" s="3" t="inlineStr"/>
-      <c r="Q44" s="9" t="inlineStr"/>
-      <c r="R44" s="16" t="inlineStr"/>
+      <c r="Q44" s="13" t="inlineStr"/>
+      <c r="R44" s="9" t="inlineStr"/>
       <c r="S44" s="3" t="inlineStr"/>
       <c r="T44" s="3" t="inlineStr"/>
       <c r="U44" s="3" t="inlineStr"/>
-      <c r="V44" s="16" t="inlineStr"/>
-      <c r="W44" s="16" t="inlineStr"/>
+      <c r="V44" s="9" t="inlineStr"/>
+      <c r="W44" s="9" t="inlineStr"/>
       <c r="X44" s="3" t="inlineStr"/>
       <c r="Y44" s="3" t="inlineStr"/>
       <c r="Z44" s="3" t="inlineStr"/>
@@ -4153,36 +4140,36 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>1981.2</v>
-      </c>
-      <c r="D45" s="18" t="n">
+        <v>1911.2</v>
+      </c>
+      <c r="D45" s="9" t="n">
         <v>109.7</v>
       </c>
-      <c r="E45" s="18" t="n">
-        <v>41.8</v>
+      <c r="E45" s="9" t="n">
+        <v>41.5</v>
       </c>
       <c r="F45" s="9" t="n">
         <v>75.59999999999999</v>
       </c>
-      <c r="G45" s="17" t="n">
-        <v>10.8</v>
+      <c r="G45" s="3" t="n">
+        <v>27.9</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>16.4</v>
+        <v>14.4</v>
       </c>
       <c r="J45" s="3" t="n">
         <v>20.9</v>
       </c>
-      <c r="K45" s="18" t="n">
-        <v>10</v>
-      </c>
-      <c r="L45" s="18" t="n">
+      <c r="K45" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" s="9" t="n">
         <v>44</v>
       </c>
-      <c r="M45" s="18" t="n">
+      <c r="M45" s="10" t="n">
         <v>42.9</v>
       </c>
       <c r="N45" s="3" t="n">
@@ -4192,12 +4179,12 @@
         <v>388</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="Q45" s="18" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q45" s="10" t="n">
         <v>98.59999999999999</v>
       </c>
-      <c r="R45" s="18" t="n">
+      <c r="R45" s="9" t="n">
         <v>71</v>
       </c>
       <c r="S45" s="3" t="n">
@@ -4209,14 +4196,14 @@
       <c r="U45" s="3" t="n">
         <v>59</v>
       </c>
-      <c r="V45" s="18" t="n">
-        <v>831.9</v>
-      </c>
-      <c r="W45" s="18" t="n">
+      <c r="V45" s="9" t="n">
+        <v>85.40000000000001</v>
+      </c>
+      <c r="W45" s="10" t="n">
         <v>67.3</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>62.8</v>
+        <v>66.8</v>
       </c>
       <c r="Y45" s="3" t="n">
         <v>263</v>
@@ -4259,33 +4246,33 @@
         <v>36.1</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>65.2</v>
-      </c>
-      <c r="K46" s="3" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="L46" s="18" t="n">
-        <v>111.7</v>
-      </c>
-      <c r="M46" s="9" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="K46" s="8" t="n">
+        <v>111100</v>
+      </c>
+      <c r="L46" s="10" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="M46" s="10" t="n">
         <v>10.7</v>
       </c>
       <c r="N46" s="3" t="n">
         <v>12.8</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>197</v>
+        <v>97</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="Q46" s="9" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q46" s="10" t="n">
         <v>24.7</v>
       </c>
-      <c r="R46" s="18" t="n">
+      <c r="R46" s="9" t="n">
         <v>17.7</v>
       </c>
-      <c r="S46" s="12" t="n">
+      <c r="S46" s="3" t="n">
         <v>16.5</v>
       </c>
       <c r="T46" s="3" t="n">
@@ -4294,20 +4281,20 @@
       <c r="U46" s="3" t="n">
         <v>14.7</v>
       </c>
-      <c r="V46" s="18" t="n">
+      <c r="V46" s="9" t="n">
         <v>21.3</v>
       </c>
-      <c r="W46" s="18" t="n">
+      <c r="W46" s="9" t="n">
         <v>16.8</v>
       </c>
       <c r="X46" s="3" t="n">
         <v>15.7</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>265.7</v>
+        <v>65.7</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>81.90000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/05_transient_transcription_output/702/702_196402_SF.JPG_stage_duirnal_temp_range.xlsx
+++ b/results/05_transient_transcription_output/702/702_196402_SF.JPG_stage_duirnal_temp_range.xlsx
@@ -802,7 +802,7 @@
         <v>0</v>
       </c>
       <c r="L4" s="9" t="n">
-        <v>9.800000000000001</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="M4" s="9" t="n">
         <v>9.1</v>
@@ -834,7 +834,7 @@
       <c r="V4" s="9" t="n">
         <v>22.1</v>
       </c>
-      <c r="W4" s="3" t="n">
+      <c r="W4" s="9" t="n">
         <v>18.3</v>
       </c>
       <c r="X4" s="3" t="n">
@@ -919,8 +919,8 @@
       <c r="V5" s="9" t="n">
         <v>19.5</v>
       </c>
-      <c r="W5" s="3" t="n">
-        <v>13.2</v>
+      <c r="W5" s="9" t="n">
+        <v>17.2</v>
       </c>
       <c r="X5" s="3" t="n">
         <v>18.3</v>
@@ -929,7 +929,7 @@
         <v>80.5</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>2.9</v>
+        <v>6.4</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -960,7 +960,7 @@
         <v>15</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>1.2</v>
@@ -999,12 +999,12 @@
         <v>92</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="V6" s="9" t="n">
         <v>15.8</v>
       </c>
-      <c r="W6" s="3" t="n">
+      <c r="W6" s="9" t="n">
         <v>15.3</v>
       </c>
       <c r="X6" s="3" t="n">
@@ -1051,7 +1051,7 @@
         <v>1.2</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>21.1</v>
+        <v>1.9</v>
       </c>
       <c r="K7" s="9" t="n">
         <v>0</v>
@@ -1089,7 +1089,7 @@
       <c r="V7" s="9" t="n">
         <v>18.9</v>
       </c>
-      <c r="W7" s="3" t="n">
+      <c r="W7" s="9" t="n">
         <v>16.8</v>
       </c>
       <c r="X7" s="3" t="n">
@@ -1133,7 +1133,7 @@
         <v>7.7</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>2.2</v>
+        <v>22.2</v>
       </c>
       <c r="J8" s="3" t="n">
         <v>3.5</v>
@@ -1174,7 +1174,7 @@
       <c r="V8" s="9" t="n">
         <v>18.7</v>
       </c>
-      <c r="W8" s="3" t="n">
+      <c r="W8" s="9" t="n">
         <v>17.3</v>
       </c>
       <c r="X8" s="3" t="n">
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>174.7</v>
+        <v>174.9</v>
       </c>
       <c r="D9" s="9" t="n">
         <v>128.9</v>
@@ -1226,7 +1226,7 @@
       <c r="K9" s="9" t="n">
         <v>7.7</v>
       </c>
-      <c r="L9" s="10" t="n">
+      <c r="L9" s="9" t="n">
         <v>56.7</v>
       </c>
       <c r="M9" s="9" t="n">
@@ -1246,7 +1246,7 @@
         <v>85.3</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>88.5</v>
+        <v>88.3</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>380.5</v>
@@ -1257,14 +1257,14 @@
       <c r="V9" s="9" t="n">
         <v>95</v>
       </c>
-      <c r="W9" s="10" t="n">
+      <c r="W9" s="9" t="n">
         <v>84.90000000000001</v>
       </c>
       <c r="X9" s="3" t="n">
         <v>91.09999999999999</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>14.5</v>
+        <v>414.5</v>
       </c>
       <c r="Z9" s="3" t="n">
         <v>19.8</v>
@@ -1325,8 +1325,8 @@
       <c r="Q10" s="9" t="n">
         <v>20.3</v>
       </c>
-      <c r="R10" s="9" t="n">
-        <v>17.1</v>
+      <c r="R10" s="10" t="n">
+        <v>27.1</v>
       </c>
       <c r="S10" s="3" t="n">
         <v>17.7</v>
@@ -1340,7 +1340,7 @@
       <c r="V10" s="9" t="n">
         <v>19</v>
       </c>
-      <c r="W10" s="10" t="n">
+      <c r="W10" s="9" t="n">
         <v>17</v>
       </c>
       <c r="X10" s="3" t="n">
@@ -1364,7 +1364,7 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>509.5</v>
+        <v>509.3</v>
       </c>
       <c r="D11" s="9" t="n">
         <v>27.3</v>
@@ -1387,7 +1387,7 @@
       <c r="J11" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="K11" s="3" t="n">
+      <c r="K11" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L11" s="3" t="n">
@@ -1412,7 +1412,7 @@
         <v>17.1</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>14.4</v>
+        <v>26.8</v>
       </c>
       <c r="T11" s="3" t="n">
         <v>42</v>
@@ -1423,14 +1423,14 @@
       <c r="V11" s="9" t="n">
         <v>22.1</v>
       </c>
-      <c r="W11" s="9" t="n">
+      <c r="W11" s="3" t="n">
         <v>17.6</v>
       </c>
       <c r="X11" s="3" t="n">
         <v>17.6</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>26</v>
+        <v>66</v>
       </c>
       <c r="Z11" s="3" t="n">
         <v>9</v>
@@ -1472,7 +1472,7 @@
       <c r="J12" s="3" t="n">
         <v>5.9</v>
       </c>
-      <c r="K12" s="3" t="n">
+      <c r="K12" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L12" s="3" t="n">
@@ -1503,19 +1503,19 @@
         <v>37</v>
       </c>
       <c r="U12" s="3" t="n">
-        <v>20.9</v>
+        <v>20.4</v>
       </c>
       <c r="V12" s="9" t="n">
         <v>21.3</v>
       </c>
-      <c r="W12" s="9" t="n">
-        <v>14.7</v>
+      <c r="W12" s="3" t="n">
+        <v>19.7</v>
       </c>
       <c r="X12" s="3" t="n">
         <v>13.1</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="Z12" s="3" t="n">
         <v>12.2</v>
@@ -1552,12 +1552,12 @@
         <v>7.5</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>1.4</v>
+        <v>11.4</v>
       </c>
       <c r="J13" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="K13" s="3" t="n">
+      <c r="K13" s="9" t="n">
         <v>0.5</v>
       </c>
       <c r="L13" s="3" t="n">
@@ -1573,7 +1573,7 @@
         <v>98</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="Q13" s="9" t="n">
         <v>18.9</v>
@@ -1585,7 +1585,7 @@
         <v>18.9</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>85.5</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="U13" s="3" t="n">
         <v>3</v>
@@ -1593,7 +1593,7 @@
       <c r="V13" s="9" t="n">
         <v>19.6</v>
       </c>
-      <c r="W13" s="9" t="n">
+      <c r="W13" s="3" t="n">
         <v>17.7</v>
       </c>
       <c r="X13" s="3" t="n">
@@ -1640,13 +1640,13 @@
         <v>1.3</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>29.5</v>
-      </c>
-      <c r="K14" s="3" t="n">
-        <v>6.7</v>
+        <v>11.5</v>
+      </c>
+      <c r="K14" s="9" t="n">
+        <v>16.7</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>23.5</v>
+        <v>23.2</v>
       </c>
       <c r="M14" s="3" t="n">
         <v>13</v>
@@ -1678,8 +1678,8 @@
       <c r="V14" s="9" t="n">
         <v>14.5</v>
       </c>
-      <c r="W14" s="9" t="n">
-        <v>15.2</v>
+      <c r="W14" s="3" t="n">
+        <v>16.2</v>
       </c>
       <c r="X14" s="3" t="n">
         <v>16</v>
@@ -1704,7 +1704,7 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>31</v>
+        <v>631</v>
       </c>
       <c r="D15" s="9" t="n">
         <v>26</v>
@@ -1727,7 +1727,7 @@
       <c r="J15" s="3" t="n">
         <v>5.9</v>
       </c>
-      <c r="K15" s="3" t="n">
+      <c r="K15" s="9" t="n">
         <v>21.6</v>
       </c>
       <c r="L15" s="3" t="n">
@@ -1763,7 +1763,7 @@
       <c r="V15" s="9" t="n">
         <v>20.7</v>
       </c>
-      <c r="W15" s="9" t="n">
+      <c r="W15" s="3" t="n">
         <v>16.3</v>
       </c>
       <c r="X15" s="3" t="n">
@@ -1793,12 +1793,12 @@
         <v>128</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>56.8</v>
+        <v>57</v>
       </c>
       <c r="F16" s="9" t="n">
         <v>92.5</v>
       </c>
-      <c r="G16" s="9" t="n">
+      <c r="G16" s="3" t="n">
         <v>71.2</v>
       </c>
       <c r="H16" s="3" t="n">
@@ -1810,7 +1810,7 @@
       <c r="J16" s="3" t="n">
         <v>21.8</v>
       </c>
-      <c r="K16" s="10" t="n">
+      <c r="K16" s="9" t="n">
         <v>39.8</v>
       </c>
       <c r="L16" s="10" t="n">
@@ -1823,7 +1823,7 @@
         <v>8.4</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>89</v>
+        <v>289</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>2</v>
@@ -1893,7 +1893,7 @@
         <v>2.9</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>27.4</v>
+        <v>29.4</v>
       </c>
       <c r="K17" s="3" t="inlineStr"/>
       <c r="L17" s="10" t="n">
@@ -1909,7 +1909,7 @@
         <v>97.8</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>2.8</v>
       </c>
       <c r="Q17" s="9" t="n">
         <v>22.2</v>
@@ -1929,7 +1929,7 @@
       <c r="V17" s="9" t="n">
         <v>19.6</v>
       </c>
-      <c r="W17" s="9" t="n">
+      <c r="W17" s="10" t="n">
         <v>16.1</v>
       </c>
       <c r="X17" s="3" t="n">
@@ -1939,7 +1939,7 @@
         <v>72.8</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1973,7 +1973,7 @@
         <v>7.9</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="J18" s="3" t="n">
         <v>3.3</v>
@@ -2024,7 +2024,7 @@
         <v>59</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>10.4</v>
+        <v>10.9</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>98</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="Q20" s="9" t="n">
         <v>28</v>
@@ -2231,7 +2231,7 @@
         <v>2.4</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="K21" s="9" t="n">
         <v>0</v>
@@ -2243,7 +2243,7 @@
         <v>13</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>14.9</v>
+        <v>19.9</v>
       </c>
       <c r="O21" s="3" t="n">
         <v>99</v>
@@ -2295,13 +2295,13 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>9</v>
+        <v>429</v>
       </c>
       <c r="D22" s="9" t="n">
         <v>25.2</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>12.1</v>
+        <v>12.9</v>
       </c>
       <c r="F22" s="9" t="n">
         <v>18.7</v>
@@ -2331,7 +2331,7 @@
         <v>14.1</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>99</v>
+        <v>99.2</v>
       </c>
       <c r="P22" s="3" t="n">
         <v>0.2</v>
@@ -2398,7 +2398,7 @@
         <v>40.6</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>12.5</v>
+        <v>16.5</v>
       </c>
       <c r="J23" s="3" t="n">
         <v>20.8</v>
@@ -2416,10 +2416,10 @@
         <v>71.5</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>93</v>
+        <v>293</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>1.4</v>
+        <v>11.4</v>
       </c>
       <c r="Q23" s="9" t="n">
         <v>128.9</v>
@@ -2486,10 +2486,10 @@
         <v>2.9</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>22.1</v>
+        <v>42.1</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="L24" s="9" t="n">
         <v>12.5</v>
@@ -2498,7 +2498,7 @@
         <v>12.4</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>1.1</v>
+        <v>11.8</v>
       </c>
       <c r="O24" s="3" t="n">
         <v>98.59999999999999</v>
@@ -2568,10 +2568,10 @@
         <v>5.7</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="K25" s="9" t="n">
         <v>0</v>
@@ -2586,7 +2586,7 @@
         <v>19</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="P25" s="3" t="n">
         <v>0.4</v>
@@ -2656,7 +2656,7 @@
         <v>2.3</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>8.5</v>
+        <v>3.5</v>
       </c>
       <c r="K26" s="9" t="n">
         <v>0.9</v>
@@ -2695,10 +2695,10 @@
         <v>21.6</v>
       </c>
       <c r="W26" s="3" t="n">
-        <v>25.5</v>
+        <v>13.5</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>14.2</v>
+        <v>142.2</v>
       </c>
       <c r="Y26" s="3" t="n">
         <v>55</v>
@@ -2741,7 +2741,7 @@
         <v>2</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="K27" s="9" t="n">
         <v>7.1</v>
@@ -2811,13 +2811,13 @@
         <v>27</v>
       </c>
       <c r="E28" s="9" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="F28" s="9" t="n">
         <v>19.3</v>
       </c>
       <c r="G28" s="9" t="n">
-        <v>15.5</v>
+        <v>15.4</v>
       </c>
       <c r="H28" s="3" t="n">
         <v>8.1</v>
@@ -2901,8 +2901,8 @@
       <c r="F29" s="9" t="n">
         <v>19.5</v>
       </c>
-      <c r="G29" s="9" t="n">
-        <v>18.7</v>
+      <c r="G29" s="3" t="n">
+        <v>18.2</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>7.2</v>
@@ -2941,7 +2941,7 @@
         <v>17</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>47.8</v>
+        <v>27.8</v>
       </c>
       <c r="U29" s="3" t="n">
         <v>18.6</v>
@@ -2975,7 +2975,7 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>228.4</v>
+        <v>2284.8</v>
       </c>
       <c r="D30" s="9" t="n">
         <v>131.2</v>
@@ -2990,7 +2990,7 @@
         <v>79.09999999999999</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>13.8</v>
@@ -3026,7 +3026,7 @@
         <v>84.40000000000001</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>14.8</v>
+        <v>314.8</v>
       </c>
       <c r="U30" s="3" t="n">
         <v>55.4</v>
@@ -3091,7 +3091,7 @@
         <v>11.2</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>12.4</v>
+        <v>13.2</v>
       </c>
       <c r="O31" s="3" t="n">
         <v>97.8</v>
@@ -3127,7 +3127,7 @@
         <v>730.2</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>25.8</v>
+        <v>165.8</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3188,7 +3188,7 @@
         <v>21.1</v>
       </c>
       <c r="R32" s="9" t="n">
-        <v>18.2</v>
+        <v>18.8</v>
       </c>
       <c r="S32" s="3" t="n">
         <v>18.8</v>
@@ -3257,7 +3257,7 @@
         <v>14.7</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>16.5</v>
+        <v>16.6</v>
       </c>
       <c r="O33" s="3" t="n">
         <v>98</v>
@@ -3324,7 +3324,7 @@
         <v>8.6</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>14.7</v>
+        <v>14.1</v>
       </c>
       <c r="I34" s="3" t="n">
         <v>1.5</v>
@@ -3342,7 +3342,7 @@
         <v>15.9</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>17.9</v>
+        <v>17.8</v>
       </c>
       <c r="O34" s="3" t="n">
         <v>99</v>
@@ -3375,7 +3375,7 @@
         <v>18</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>83</v>
+        <v>53</v>
       </c>
       <c r="Z34" s="3" t="n">
         <v>3.8</v>
@@ -3445,7 +3445,7 @@
         <v>16.8</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="U35" s="3" t="n">
         <v>12.8</v>
@@ -3518,7 +3518,7 @@
         <v>99</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="Q36" s="3" t="n">
         <v>23.5</v>
@@ -3533,7 +3533,7 @@
         <v>45</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>17.2</v>
+        <v>17.9</v>
       </c>
       <c r="V36" s="9" t="n">
         <v>20.6</v>
@@ -3564,7 +3564,7 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>224.4</v>
+        <v>224</v>
       </c>
       <c r="D37" s="9" t="n">
         <v>128.5</v>
@@ -3579,7 +3579,7 @@
         <v>67.59999999999999</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="I37" s="3" t="n">
         <v>14.1</v>
@@ -3600,20 +3600,20 @@
         <v>74.2</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>92</v>
+        <v>492</v>
       </c>
       <c r="P37" s="3" t="inlineStr"/>
       <c r="Q37" s="10" t="n">
         <v>115.5</v>
       </c>
       <c r="R37" s="10" t="n">
-        <v>89.40000000000001</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="S37" s="3" t="n">
         <v>88</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>16.4</v>
+        <v>316.4</v>
       </c>
       <c r="U37" s="3" t="n">
         <v>54.5</v>
@@ -3625,7 +3625,7 @@
         <v>83.09999999999999</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>84.7</v>
+        <v>82.7</v>
       </c>
       <c r="Y37" s="3" t="n">
         <v>359.5</v>
@@ -3668,7 +3668,7 @@
         <v>28.1</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>42.1</v>
+        <v>22.1</v>
       </c>
       <c r="K38" s="3" t="n">
         <v>0</v>
@@ -3701,7 +3701,7 @@
         <v>63.3</v>
       </c>
       <c r="U38" s="3" t="n">
-        <v>18.9</v>
+        <v>19.9</v>
       </c>
       <c r="V38" s="9" t="n">
         <v>20.2</v>
@@ -3735,7 +3735,7 @@
         <v>579.9</v>
       </c>
       <c r="D39" s="9" t="n">
-        <v>26.9</v>
+        <v>26.92</v>
       </c>
       <c r="E39" s="9" t="n">
         <v>11</v>
@@ -3747,7 +3747,7 @@
         <v>15.9</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>2.9</v>
+        <v>0.9</v>
       </c>
       <c r="I39" s="3" t="n">
         <v>4.5</v>
@@ -3761,11 +3761,11 @@
       <c r="L39" s="9" t="n">
         <v>12.7</v>
       </c>
-      <c r="M39" s="3" t="n">
+      <c r="M39" s="9" t="n">
         <v>12.5</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>14.9</v>
+        <v>14.4</v>
       </c>
       <c r="O39" s="3" t="n">
         <v>98</v>
@@ -3773,7 +3773,7 @@
       <c r="P39" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q39" s="3" t="n">
+      <c r="Q39" s="9" t="n">
         <v>26.6</v>
       </c>
       <c r="R39" s="9" t="n">
@@ -3844,19 +3844,19 @@
       <c r="L40" s="9" t="n">
         <v>10.6</v>
       </c>
-      <c r="M40" s="3" t="n">
+      <c r="M40" s="9" t="n">
         <v>10.3</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>12.1</v>
+        <v>12.4</v>
       </c>
       <c r="O40" s="3" t="n">
         <v>96</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q40" s="3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="Q40" s="9" t="n">
         <v>22</v>
       </c>
       <c r="R40" s="9" t="n">
@@ -3915,7 +3915,7 @@
         <v>19.8</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="I41" s="3" t="n">
         <v>3.6</v>
@@ -3929,7 +3929,7 @@
       <c r="L41" s="9" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="M41" s="3" t="n">
+      <c r="M41" s="9" t="n">
         <v>8.6</v>
       </c>
       <c r="N41" s="3" t="n">
@@ -3941,7 +3941,7 @@
       <c r="P41" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q41" s="3" t="n">
+      <c r="Q41" s="9" t="n">
         <v>23.4</v>
       </c>
       <c r="R41" s="9" t="n">
@@ -3969,7 +3969,7 @@
         <v>58</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>15.7</v>
+        <v>14.9</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -4014,8 +4014,8 @@
       <c r="L42" s="9" t="n">
         <v>11.9</v>
       </c>
-      <c r="M42" s="11" t="n">
-        <v>1.1</v>
+      <c r="M42" s="9" t="n">
+        <v>11.3</v>
       </c>
       <c r="N42" s="3" t="n">
         <v>13.3</v>
@@ -4026,8 +4026,8 @@
       <c r="P42" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="Q42" s="11" t="n">
-        <v>2.6</v>
+      <c r="Q42" s="9" t="n">
+        <v>26.6</v>
       </c>
       <c r="R42" s="9" t="n">
         <v>17.6</v>
@@ -4036,7 +4036,7 @@
         <v>15.1</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>43.3</v>
+        <v>23.2</v>
       </c>
       <c r="U42" s="3" t="n">
         <v>19.6</v>
@@ -4073,11 +4073,11 @@
       <c r="J43" s="3" t="inlineStr"/>
       <c r="K43" s="9" t="inlineStr"/>
       <c r="L43" s="9" t="inlineStr"/>
-      <c r="M43" s="13" t="inlineStr"/>
+      <c r="M43" s="9" t="inlineStr"/>
       <c r="N43" s="3" t="inlineStr"/>
       <c r="O43" s="3" t="inlineStr"/>
       <c r="P43" s="3" t="inlineStr"/>
-      <c r="Q43" s="13" t="inlineStr"/>
+      <c r="Q43" s="9" t="inlineStr"/>
       <c r="R43" s="9" t="inlineStr"/>
       <c r="S43" s="3" t="inlineStr"/>
       <c r="T43" s="3" t="inlineStr"/>
@@ -4112,11 +4112,11 @@
       <c r="J44" s="3" t="inlineStr"/>
       <c r="K44" s="9" t="inlineStr"/>
       <c r="L44" s="9" t="inlineStr"/>
-      <c r="M44" s="13" t="inlineStr"/>
+      <c r="M44" s="9" t="inlineStr"/>
       <c r="N44" s="3" t="inlineStr"/>
       <c r="O44" s="3" t="inlineStr"/>
       <c r="P44" s="3" t="inlineStr"/>
-      <c r="Q44" s="13" t="inlineStr"/>
+      <c r="Q44" s="9" t="inlineStr"/>
       <c r="R44" s="9" t="inlineStr"/>
       <c r="S44" s="3" t="inlineStr"/>
       <c r="T44" s="3" t="inlineStr"/>
@@ -4152,10 +4152,10 @@
         <v>75.59999999999999</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>27.9</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I45" s="3" t="n">
         <v>14.4</v>
@@ -4169,19 +4169,19 @@
       <c r="L45" s="9" t="n">
         <v>44</v>
       </c>
-      <c r="M45" s="10" t="n">
+      <c r="M45" s="9" t="n">
         <v>42.9</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>5.1</v>
+        <v>51.1</v>
       </c>
       <c r="O45" s="3" t="n">
         <v>388</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q45" s="10" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="Q45" s="9" t="n">
         <v>98.59999999999999</v>
       </c>
       <c r="R45" s="9" t="n">
@@ -4246,15 +4246,15 @@
         <v>36.1</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>5.2</v>
+        <v>52.1</v>
       </c>
       <c r="K46" s="8" t="n">
-        <v>111100</v>
+        <v>101.1</v>
       </c>
       <c r="L46" s="10" t="n">
         <v>11.8</v>
       </c>
-      <c r="M46" s="10" t="n">
+      <c r="M46" s="9" t="n">
         <v>10.7</v>
       </c>
       <c r="N46" s="3" t="n">
@@ -4266,7 +4266,7 @@
       <c r="P46" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q46" s="10" t="n">
+      <c r="Q46" s="9" t="n">
         <v>24.7</v>
       </c>
       <c r="R46" s="9" t="n">
@@ -4288,7 +4288,7 @@
         <v>16.8</v>
       </c>
       <c r="X46" s="3" t="n">
-        <v>15.7</v>
+        <v>16.7</v>
       </c>
       <c r="Y46" s="3" t="n">
         <v>65.7</v>

--- a/results/05_transient_transcription_output/702/702_196402_SF.JPG_stage_duirnal_temp_range.xlsx
+++ b/results/05_transient_transcription_output/702/702_196402_SF.JPG_stage_duirnal_temp_range.xlsx
@@ -26,18 +26,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FF9933"/>
-        <bgColor rgb="00FF9933"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -131,7 +125,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -155,13 +149,10 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -777,16 +768,16 @@
       <c r="C4" s="3" t="n">
         <v>391.2</v>
       </c>
-      <c r="D4" s="9" t="n">
+      <c r="D4" s="8" t="n">
         <v>27.9</v>
       </c>
-      <c r="E4" s="9" t="n">
+      <c r="E4" s="8" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="F4" s="9" t="n">
+      <c r="F4" s="8" t="n">
         <v>18.5</v>
       </c>
-      <c r="G4" s="9" t="n">
+      <c r="G4" s="8" t="n">
         <v>18.7</v>
       </c>
       <c r="H4" s="3" t="n">
@@ -798,13 +789,13 @@
       <c r="J4" s="3" t="n">
         <v>4.9</v>
       </c>
-      <c r="K4" s="9" t="n">
+      <c r="K4" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L4" s="9" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="M4" s="9" t="n">
+      <c r="L4" s="8" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="M4" s="8" t="n">
         <v>9.1</v>
       </c>
       <c r="N4" s="3" t="n">
@@ -816,10 +807,10 @@
       <c r="P4" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q4" s="9" t="n">
+      <c r="Q4" s="8" t="n">
         <v>25.8</v>
       </c>
-      <c r="R4" s="9" t="n">
+      <c r="R4" s="8" t="n">
         <v>16.8</v>
       </c>
       <c r="S4" s="3" t="n">
@@ -831,10 +822,10 @@
       <c r="U4" s="3" t="n">
         <v>19.1</v>
       </c>
-      <c r="V4" s="9" t="n">
+      <c r="V4" s="8" t="n">
         <v>22.1</v>
       </c>
-      <c r="W4" s="9" t="n">
+      <c r="W4" s="3" t="n">
         <v>18.3</v>
       </c>
       <c r="X4" s="3" t="n">
@@ -862,16 +853,16 @@
       <c r="C5" s="3" t="n">
         <v>382.4</v>
       </c>
-      <c r="D5" s="9" t="n">
+      <c r="D5" s="8" t="n">
         <v>26.9</v>
       </c>
-      <c r="E5" s="9" t="n">
+      <c r="E5" s="8" t="n">
         <v>11.5</v>
       </c>
-      <c r="F5" s="9" t="n">
+      <c r="F5" s="8" t="n">
         <v>19.2</v>
       </c>
-      <c r="G5" s="9" t="n">
+      <c r="G5" s="8" t="n">
         <v>15.4</v>
       </c>
       <c r="H5" s="3" t="n">
@@ -883,13 +874,13 @@
       <c r="J5" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="K5" s="9" t="n">
+      <c r="K5" s="8" t="n">
         <v>1.2</v>
       </c>
-      <c r="L5" s="9" t="n">
+      <c r="L5" s="8" t="n">
         <v>12.3</v>
       </c>
-      <c r="M5" s="9" t="n">
+      <c r="M5" s="8" t="n">
         <v>11.4</v>
       </c>
       <c r="N5" s="3" t="n">
@@ -901,10 +892,10 @@
       <c r="P5" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="Q5" s="9" t="n">
+      <c r="Q5" s="8" t="n">
         <v>19.6</v>
       </c>
-      <c r="R5" s="9" t="n">
+      <c r="R5" s="8" t="n">
         <v>18.6</v>
       </c>
       <c r="S5" s="3" t="n">
@@ -916,11 +907,11 @@
       <c r="U5" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="V5" s="9" t="n">
+      <c r="V5" s="8" t="n">
         <v>19.5</v>
       </c>
-      <c r="W5" s="9" t="n">
-        <v>17.2</v>
+      <c r="W5" s="3" t="n">
+        <v>19.2</v>
       </c>
       <c r="X5" s="3" t="n">
         <v>18.3</v>
@@ -929,7 +920,7 @@
         <v>80.5</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -947,16 +938,16 @@
       <c r="C6" s="3" t="n">
         <v>309.1</v>
       </c>
-      <c r="D6" s="9" t="n">
+      <c r="D6" s="8" t="n">
         <v>25.9</v>
       </c>
-      <c r="E6" s="9" t="n">
+      <c r="E6" s="8" t="n">
         <v>10.9</v>
       </c>
-      <c r="F6" s="9" t="n">
+      <c r="F6" s="8" t="n">
         <v>18.4</v>
       </c>
-      <c r="G6" s="9" t="n">
+      <c r="G6" s="8" t="n">
         <v>15</v>
       </c>
       <c r="H6" s="3" t="n">
@@ -968,13 +959,13 @@
       <c r="J6" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="K6" s="9" t="n">
+      <c r="K6" s="8" t="n">
         <v>6.5</v>
       </c>
-      <c r="L6" s="9" t="n">
+      <c r="L6" s="8" t="n">
         <v>11.1</v>
       </c>
-      <c r="M6" s="9" t="n">
+      <c r="M6" s="8" t="n">
         <v>11</v>
       </c>
       <c r="N6" s="3" t="n">
@@ -986,10 +977,10 @@
       <c r="P6" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q6" s="9" t="n">
+      <c r="Q6" s="8" t="n">
         <v>15.4</v>
       </c>
-      <c r="R6" s="9" t="n">
+      <c r="R6" s="8" t="n">
         <v>14.7</v>
       </c>
       <c r="S6" s="3" t="n">
@@ -999,12 +990,12 @@
         <v>92</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="V6" s="9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V6" s="8" t="n">
         <v>15.8</v>
       </c>
-      <c r="W6" s="9" t="n">
+      <c r="W6" s="3" t="n">
         <v>15.3</v>
       </c>
       <c r="X6" s="3" t="n">
@@ -1032,16 +1023,16 @@
       <c r="C7" s="3" t="n">
         <v>275.8</v>
       </c>
-      <c r="D7" s="9" t="n">
+      <c r="D7" s="8" t="n">
         <v>21.9</v>
       </c>
-      <c r="E7" s="9" t="n">
+      <c r="E7" s="8" t="n">
         <v>12.9</v>
       </c>
-      <c r="F7" s="9" t="n">
+      <c r="F7" s="8" t="n">
         <v>17.4</v>
       </c>
-      <c r="G7" s="9" t="n">
+      <c r="G7" s="8" t="n">
         <v>9</v>
       </c>
       <c r="H7" s="3" t="n">
@@ -1051,19 +1042,19 @@
         <v>1.2</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="K7" s="9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="K7" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L7" s="9" t="n">
+      <c r="L7" s="8" t="n">
         <v>13.2</v>
       </c>
-      <c r="M7" s="9" t="n">
+      <c r="M7" s="8" t="n">
         <v>13.1</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="O7" s="3" t="n">
         <v>99</v>
@@ -1071,10 +1062,10 @@
       <c r="P7" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q7" s="9" t="n">
+      <c r="Q7" s="8" t="n">
         <v>19.3</v>
       </c>
-      <c r="R7" s="9" t="n">
+      <c r="R7" s="8" t="n">
         <v>16.8</v>
       </c>
       <c r="S7" s="3" t="n">
@@ -1086,10 +1077,10 @@
       <c r="U7" s="3" t="n">
         <v>4.8</v>
       </c>
-      <c r="V7" s="9" t="n">
+      <c r="V7" s="8" t="n">
         <v>18.9</v>
       </c>
-      <c r="W7" s="9" t="n">
+      <c r="W7" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="X7" s="3" t="n">
@@ -1117,34 +1108,34 @@
       <c r="C8" s="3" t="n">
         <v>391.2</v>
       </c>
-      <c r="D8" s="9" t="n">
+      <c r="D8" s="8" t="n">
         <v>26.3</v>
       </c>
-      <c r="E8" s="9" t="n">
+      <c r="E8" s="8" t="n">
         <v>10.5</v>
       </c>
-      <c r="F8" s="9" t="n">
+      <c r="F8" s="8" t="n">
         <v>18.4</v>
       </c>
-      <c r="G8" s="9" t="n">
+      <c r="G8" s="8" t="n">
         <v>15.8</v>
       </c>
       <c r="H8" s="3" t="n">
         <v>7.7</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>22.2</v>
+        <v>2.2</v>
       </c>
       <c r="J8" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="K8" s="9" t="n">
+      <c r="K8" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L8" s="9" t="n">
+      <c r="L8" s="8" t="n">
         <v>10.8</v>
       </c>
-      <c r="M8" s="9" t="n">
+      <c r="M8" s="8" t="n">
         <v>10.6</v>
       </c>
       <c r="N8" s="3" t="n">
@@ -1156,10 +1147,10 @@
       <c r="P8" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q8" s="9" t="n">
+      <c r="Q8" s="8" t="n">
         <v>21.4</v>
       </c>
-      <c r="R8" s="9" t="n">
+      <c r="R8" s="8" t="n">
         <v>18.4</v>
       </c>
       <c r="S8" s="3" t="n">
@@ -1171,10 +1162,10 @@
       <c r="U8" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="V8" s="9" t="n">
+      <c r="V8" s="8" t="n">
         <v>18.7</v>
       </c>
-      <c r="W8" s="9" t="n">
+      <c r="W8" s="3" t="n">
         <v>17.3</v>
       </c>
       <c r="X8" s="3" t="n">
@@ -1200,18 +1191,18 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>174.9</v>
-      </c>
-      <c r="D9" s="9" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="D9" s="8" t="n">
         <v>128.9</v>
       </c>
-      <c r="E9" s="9" t="n">
+      <c r="E9" s="8" t="n">
         <v>55</v>
       </c>
-      <c r="F9" s="9" t="n">
+      <c r="F9" s="8" t="n">
         <v>91.90000000000001</v>
       </c>
-      <c r="G9" s="9" t="n">
+      <c r="G9" s="8" t="n">
         <v>73.90000000000001</v>
       </c>
       <c r="H9" s="3" t="n">
@@ -1223,13 +1214,13 @@
       <c r="J9" s="3" t="n">
         <v>13.5</v>
       </c>
-      <c r="K9" s="9" t="n">
+      <c r="K9" s="8" t="n">
         <v>7.7</v>
       </c>
       <c r="L9" s="9" t="n">
         <v>56.7</v>
       </c>
-      <c r="M9" s="9" t="n">
+      <c r="M9" s="8" t="n">
         <v>55.2</v>
       </c>
       <c r="N9" s="3" t="n">
@@ -1239,14 +1230,14 @@
         <v>484.9</v>
       </c>
       <c r="P9" s="3" t="inlineStr"/>
-      <c r="Q9" s="9" t="n">
+      <c r="Q9" s="8" t="n">
         <v>101.5</v>
       </c>
-      <c r="R9" s="9" t="n">
+      <c r="R9" s="8" t="n">
         <v>85.3</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>88.3</v>
+        <v>88.5</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>380.5</v>
@@ -1254,7 +1245,7 @@
       <c r="U9" s="3" t="n">
         <v>33.3</v>
       </c>
-      <c r="V9" s="9" t="n">
+      <c r="V9" s="8" t="n">
         <v>95</v>
       </c>
       <c r="W9" s="9" t="n">
@@ -1285,16 +1276,16 @@
       <c r="C10" s="3" t="n">
         <v>349.9</v>
       </c>
-      <c r="D10" s="9" t="n">
+      <c r="D10" s="8" t="n">
         <v>25.8</v>
       </c>
-      <c r="E10" s="9" t="n">
+      <c r="E10" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="F10" s="9" t="n">
+      <c r="F10" s="8" t="n">
         <v>18.4</v>
       </c>
-      <c r="G10" s="9" t="n">
+      <c r="G10" s="8" t="n">
         <v>14.8</v>
       </c>
       <c r="H10" s="3" t="n">
@@ -1307,10 +1298,10 @@
         <v>27.4</v>
       </c>
       <c r="K10" s="3" t="inlineStr"/>
-      <c r="L10" s="9" t="n">
+      <c r="L10" s="8" t="n">
         <v>11.3</v>
       </c>
-      <c r="M10" s="9" t="n">
+      <c r="M10" s="8" t="n">
         <v>11</v>
       </c>
       <c r="N10" s="3" t="n">
@@ -1322,11 +1313,11 @@
       <c r="P10" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="Q10" s="9" t="n">
+      <c r="Q10" s="8" t="n">
         <v>20.3</v>
       </c>
-      <c r="R10" s="10" t="n">
-        <v>27.1</v>
+      <c r="R10" s="8" t="n">
+        <v>17.1</v>
       </c>
       <c r="S10" s="3" t="n">
         <v>17.7</v>
@@ -1337,7 +1328,7 @@
       <c r="U10" s="3" t="n">
         <v>6.7</v>
       </c>
-      <c r="V10" s="9" t="n">
+      <c r="V10" s="8" t="n">
         <v>19</v>
       </c>
       <c r="W10" s="9" t="n">
@@ -1364,18 +1355,18 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>509.3</v>
-      </c>
-      <c r="D11" s="9" t="n">
+        <v>504.5</v>
+      </c>
+      <c r="D11" s="8" t="n">
         <v>27.3</v>
       </c>
-      <c r="E11" s="9" t="n">
+      <c r="E11" s="8" t="n">
         <v>10.7</v>
       </c>
-      <c r="F11" s="9" t="n">
+      <c r="F11" s="8" t="n">
         <v>19</v>
       </c>
-      <c r="G11" s="9" t="n">
+      <c r="G11" s="8" t="n">
         <v>16.6</v>
       </c>
       <c r="H11" s="3" t="n">
@@ -1387,14 +1378,14 @@
       <c r="J11" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="K11" s="9" t="n">
+      <c r="K11" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L11" s="3" t="n">
         <v>11</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>11.9</v>
+        <v>19.9</v>
       </c>
       <c r="N11" s="3" t="n">
         <v>13</v>
@@ -1405,14 +1396,14 @@
       <c r="P11" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q11" s="9" t="n">
+      <c r="Q11" s="8" t="n">
         <v>26.3</v>
       </c>
-      <c r="R11" s="9" t="n">
+      <c r="R11" s="8" t="n">
         <v>17.1</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>26.8</v>
+        <v>14.4</v>
       </c>
       <c r="T11" s="3" t="n">
         <v>42</v>
@@ -1420,7 +1411,7 @@
       <c r="U11" s="3" t="n">
         <v>19.9</v>
       </c>
-      <c r="V11" s="9" t="n">
+      <c r="V11" s="8" t="n">
         <v>22.1</v>
       </c>
       <c r="W11" s="3" t="n">
@@ -1451,16 +1442,16 @@
       <c r="C12" s="3" t="n">
         <v>506.7</v>
       </c>
-      <c r="D12" s="9" t="n">
+      <c r="D12" s="8" t="n">
         <v>25.9</v>
       </c>
-      <c r="E12" s="9" t="n">
+      <c r="E12" s="8" t="n">
         <v>10.9</v>
       </c>
-      <c r="F12" s="9" t="n">
+      <c r="F12" s="8" t="n">
         <v>18.4</v>
       </c>
-      <c r="G12" s="9" t="n">
+      <c r="G12" s="8" t="n">
         <v>15</v>
       </c>
       <c r="H12" s="3" t="n">
@@ -1472,7 +1463,7 @@
       <c r="J12" s="3" t="n">
         <v>5.9</v>
       </c>
-      <c r="K12" s="9" t="n">
+      <c r="K12" s="3" t="n">
         <v>1</v>
       </c>
       <c r="L12" s="3" t="n">
@@ -1490,10 +1481,10 @@
       <c r="P12" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="Q12" s="9" t="n">
+      <c r="Q12" s="8" t="n">
         <v>25.4</v>
       </c>
-      <c r="R12" s="9" t="n">
+      <c r="R12" s="8" t="n">
         <v>15.5</v>
       </c>
       <c r="S12" s="3" t="n">
@@ -1503,13 +1494,13 @@
         <v>37</v>
       </c>
       <c r="U12" s="3" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="V12" s="9" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="V12" s="8" t="n">
         <v>21.3</v>
       </c>
       <c r="W12" s="3" t="n">
-        <v>19.7</v>
+        <v>14.7</v>
       </c>
       <c r="X12" s="3" t="n">
         <v>13.1</v>
@@ -1536,35 +1527,35 @@
       <c r="C13" s="3" t="n">
         <v>357.9</v>
       </c>
-      <c r="D13" s="9" t="n">
+      <c r="D13" s="8" t="n">
         <v>25.3</v>
       </c>
-      <c r="E13" s="9" t="n">
+      <c r="E13" s="8" t="n">
         <v>11.2</v>
       </c>
-      <c r="F13" s="9" t="n">
+      <c r="F13" s="8" t="n">
         <v>18.3</v>
       </c>
-      <c r="G13" s="9" t="n">
+      <c r="G13" s="8" t="n">
         <v>14.1</v>
       </c>
       <c r="H13" s="3" t="n">
         <v>7.5</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>11.4</v>
+        <v>1.4</v>
       </c>
       <c r="J13" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="K13" s="9" t="n">
+      <c r="K13" s="3" t="n">
         <v>0.5</v>
       </c>
       <c r="L13" s="3" t="n">
         <v>11.8</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>11.6</v>
+        <v>18.6</v>
       </c>
       <c r="N13" s="3" t="n">
         <v>13.6</v>
@@ -1575,22 +1566,22 @@
       <c r="P13" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q13" s="9" t="n">
+      <c r="Q13" s="8" t="n">
         <v>18.9</v>
       </c>
-      <c r="R13" s="9" t="n">
+      <c r="R13" s="8" t="n">
         <v>17.3</v>
       </c>
       <c r="S13" s="3" t="n">
         <v>18.9</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>86.09999999999999</v>
+        <v>86</v>
       </c>
       <c r="U13" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="V13" s="9" t="n">
+      <c r="V13" s="8" t="n">
         <v>19.6</v>
       </c>
       <c r="W13" s="3" t="n">
@@ -1621,16 +1612,16 @@
       <c r="C14" s="3" t="n">
         <v>227</v>
       </c>
-      <c r="D14" s="9" t="n">
+      <c r="D14" s="8" t="n">
         <v>23.5</v>
       </c>
-      <c r="E14" s="9" t="n">
+      <c r="E14" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="F14" s="9" t="n">
+      <c r="F14" s="8" t="n">
         <v>18.3</v>
       </c>
-      <c r="G14" s="9" t="n">
+      <c r="G14" s="8" t="n">
         <v>10.5</v>
       </c>
       <c r="H14" s="3" t="n">
@@ -1640,13 +1631,13 @@
         <v>1.3</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="K14" s="9" t="n">
-        <v>16.7</v>
+        <v>8.5</v>
+      </c>
+      <c r="K14" s="3" t="n">
+        <v>26.7</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>23.2</v>
+        <v>13.3</v>
       </c>
       <c r="M14" s="3" t="n">
         <v>13</v>
@@ -1660,10 +1651,10 @@
       <c r="P14" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="Q14" s="9" t="n">
+      <c r="Q14" s="8" t="n">
         <v>14.9</v>
       </c>
-      <c r="R14" s="9" t="n">
+      <c r="R14" s="8" t="n">
         <v>14.7</v>
       </c>
       <c r="S14" s="3" t="n">
@@ -1673,9 +1664,9 @@
         <v>97</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="V14" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="8" t="n">
         <v>14.5</v>
       </c>
       <c r="W14" s="3" t="n">
@@ -1706,16 +1697,16 @@
       <c r="C15" s="3" t="n">
         <v>631</v>
       </c>
-      <c r="D15" s="9" t="n">
+      <c r="D15" s="8" t="n">
         <v>26</v>
       </c>
-      <c r="E15" s="9" t="n">
+      <c r="E15" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="F15" s="9" t="n">
+      <c r="F15" s="8" t="n">
         <v>18.5</v>
       </c>
-      <c r="G15" s="9" t="n">
+      <c r="G15" s="8" t="n">
         <v>15</v>
       </c>
       <c r="H15" s="3" t="n">
@@ -1727,7 +1718,7 @@
       <c r="J15" s="3" t="n">
         <v>5.9</v>
       </c>
-      <c r="K15" s="9" t="n">
+      <c r="K15" s="3" t="n">
         <v>21.6</v>
       </c>
       <c r="L15" s="3" t="n">
@@ -1745,10 +1736,10 @@
       <c r="P15" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q15" s="9" t="n">
+      <c r="Q15" s="8" t="n">
         <v>25.5</v>
       </c>
-      <c r="R15" s="9" t="n">
+      <c r="R15" s="8" t="n">
         <v>17.6</v>
       </c>
       <c r="S15" s="3" t="n">
@@ -1760,7 +1751,7 @@
       <c r="U15" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="V15" s="9" t="n">
+      <c r="V15" s="8" t="n">
         <v>20.7</v>
       </c>
       <c r="W15" s="3" t="n">
@@ -1789,13 +1780,13 @@
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr"/>
-      <c r="D16" s="9" t="n">
+      <c r="D16" s="8" t="n">
         <v>128</v>
       </c>
-      <c r="E16" s="9" t="n">
+      <c r="E16" s="8" t="n">
         <v>57</v>
       </c>
-      <c r="F16" s="9" t="n">
+      <c r="F16" s="8" t="n">
         <v>92.5</v>
       </c>
       <c r="G16" s="3" t="n">
@@ -1813,10 +1804,10 @@
       <c r="K16" s="9" t="n">
         <v>39.8</v>
       </c>
-      <c r="L16" s="10" t="n">
+      <c r="L16" s="9" t="n">
         <v>59.1</v>
       </c>
-      <c r="M16" s="10" t="n">
+      <c r="M16" s="9" t="n">
         <v>58.2</v>
       </c>
       <c r="N16" s="3" t="n">
@@ -1828,10 +1819,10 @@
       <c r="P16" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="Q16" s="9" t="n">
+      <c r="Q16" s="8" t="n">
         <v>111</v>
       </c>
-      <c r="R16" s="9" t="n">
+      <c r="R16" s="8" t="n">
         <v>82.2</v>
       </c>
       <c r="S16" s="3" t="n">
@@ -1843,10 +1834,10 @@
       <c r="U16" s="3" t="n">
         <v>60.9</v>
       </c>
-      <c r="V16" s="9" t="n">
+      <c r="V16" s="8" t="n">
         <v>98.2</v>
       </c>
-      <c r="W16" s="10" t="n">
+      <c r="W16" s="9" t="n">
         <v>80.7</v>
       </c>
       <c r="X16" s="3" t="n">
@@ -1874,16 +1865,16 @@
       <c r="C17" s="3" t="n">
         <v>445.9</v>
       </c>
-      <c r="D17" s="9" t="n">
+      <c r="D17" s="8" t="n">
         <v>25.6</v>
       </c>
-      <c r="E17" s="9" t="n">
+      <c r="E17" s="8" t="n">
         <v>11.4</v>
       </c>
-      <c r="F17" s="9" t="n">
+      <c r="F17" s="8" t="n">
         <v>18.5</v>
       </c>
-      <c r="G17" s="9" t="n">
+      <c r="G17" s="8" t="n">
         <v>14.2</v>
       </c>
       <c r="H17" s="3" t="n">
@@ -1896,10 +1887,10 @@
         <v>29.4</v>
       </c>
       <c r="K17" s="3" t="inlineStr"/>
-      <c r="L17" s="10" t="n">
+      <c r="L17" s="9" t="n">
         <v>11.8</v>
       </c>
-      <c r="M17" s="10" t="n">
+      <c r="M17" s="9" t="n">
         <v>11.6</v>
       </c>
       <c r="N17" s="3" t="n">
@@ -1909,12 +1900,12 @@
         <v>97.8</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Q17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="8" t="n">
         <v>22.2</v>
       </c>
-      <c r="R17" s="9" t="n">
+      <c r="R17" s="8" t="n">
         <v>16.4</v>
       </c>
       <c r="S17" s="3" t="n">
@@ -1924,12 +1915,12 @@
         <v>22</v>
       </c>
       <c r="U17" s="3" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="V17" s="9" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="V17" s="8" t="n">
         <v>19.6</v>
       </c>
-      <c r="W17" s="10" t="n">
+      <c r="W17" s="9" t="n">
         <v>16.1</v>
       </c>
       <c r="X17" s="3" t="n">
@@ -1939,7 +1930,7 @@
         <v>72.8</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1957,34 +1948,34 @@
       <c r="C18" s="3" t="n">
         <v>45.5</v>
       </c>
-      <c r="D18" s="9" t="n">
+      <c r="D18" s="8" t="n">
         <v>25.9</v>
       </c>
-      <c r="E18" s="9" t="n">
+      <c r="E18" s="8" t="n">
         <v>10.9</v>
       </c>
-      <c r="F18" s="9" t="n">
+      <c r="F18" s="8" t="n">
         <v>18.7</v>
       </c>
-      <c r="G18" s="9" t="n">
+      <c r="G18" s="8" t="n">
         <v>15</v>
       </c>
       <c r="H18" s="3" t="n">
         <v>7.9</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="J18" s="3" t="n">
         <v>3.3</v>
       </c>
-      <c r="K18" s="9" t="n">
+      <c r="K18" s="8" t="n">
         <v>0.1</v>
       </c>
-      <c r="L18" s="9" t="n">
+      <c r="L18" s="8" t="n">
         <v>14.7</v>
       </c>
-      <c r="M18" s="11" t="n">
+      <c r="M18" s="10" t="n">
         <v>1.6</v>
       </c>
       <c r="N18" s="3" t="n">
@@ -1996,10 +1987,10 @@
       <c r="P18" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q18" s="9" t="n">
+      <c r="Q18" s="8" t="n">
         <v>25.8</v>
       </c>
-      <c r="R18" s="9" t="n">
+      <c r="R18" s="8" t="n">
         <v>17.5</v>
       </c>
       <c r="S18" s="3" t="n">
@@ -2011,10 +2002,10 @@
       <c r="U18" s="3" t="n">
         <v>17.9</v>
       </c>
-      <c r="V18" s="9" t="n">
+      <c r="V18" s="8" t="n">
         <v>21</v>
       </c>
-      <c r="W18" s="9" t="n">
+      <c r="W18" s="8" t="n">
         <v>15.5</v>
       </c>
       <c r="X18" s="3" t="n">
@@ -2024,7 +2015,7 @@
         <v>59</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>10.9</v>
+        <v>0.9</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -2042,16 +2033,16 @@
       <c r="C19" s="3" t="n">
         <v>531.1</v>
       </c>
-      <c r="D19" s="9" t="n">
+      <c r="D19" s="8" t="n">
         <v>28</v>
       </c>
-      <c r="E19" s="9" t="n">
+      <c r="E19" s="8" t="n">
         <v>10.6</v>
       </c>
-      <c r="F19" s="9" t="n">
+      <c r="F19" s="8" t="n">
         <v>19.3</v>
       </c>
-      <c r="G19" s="9" t="n">
+      <c r="G19" s="8" t="n">
         <v>17.4</v>
       </c>
       <c r="H19" s="3" t="n">
@@ -2063,10 +2054,10 @@
       <c r="J19" s="3" t="n">
         <v>5.2</v>
       </c>
-      <c r="K19" s="9" t="n">
+      <c r="K19" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L19" s="9" t="n">
+      <c r="L19" s="8" t="n">
         <v>11.2</v>
       </c>
       <c r="M19" s="3" t="n">
@@ -2081,10 +2072,10 @@
       <c r="P19" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q19" s="9" t="n">
+      <c r="Q19" s="8" t="n">
         <v>25.9</v>
       </c>
-      <c r="R19" s="9" t="n">
+      <c r="R19" s="8" t="n">
         <v>18</v>
       </c>
       <c r="S19" s="3" t="n">
@@ -2096,10 +2087,10 @@
       <c r="U19" s="3" t="n">
         <v>17.2</v>
       </c>
-      <c r="V19" s="9" t="n">
+      <c r="V19" s="8" t="n">
         <v>21.2</v>
       </c>
-      <c r="W19" s="9" t="n">
+      <c r="W19" s="8" t="n">
         <v>17.8</v>
       </c>
       <c r="X19" s="3" t="n">
@@ -2127,16 +2118,16 @@
       <c r="C20" s="3" t="n">
         <v>542.2</v>
       </c>
-      <c r="D20" s="9" t="n">
+      <c r="D20" s="8" t="n">
         <v>28.2</v>
       </c>
-      <c r="E20" s="9" t="n">
+      <c r="E20" s="8" t="n">
         <v>10.4</v>
       </c>
-      <c r="F20" s="9" t="n">
+      <c r="F20" s="8" t="n">
         <v>19.3</v>
       </c>
-      <c r="G20" s="9" t="n">
+      <c r="G20" s="8" t="n">
         <v>17.8</v>
       </c>
       <c r="H20" s="3" t="n">
@@ -2148,10 +2139,10 @@
       <c r="J20" s="3" t="n">
         <v>4.9</v>
       </c>
-      <c r="K20" s="9" t="n">
+      <c r="K20" s="8" t="n">
         <v>0.2</v>
       </c>
-      <c r="L20" s="9" t="n">
+      <c r="L20" s="8" t="n">
         <v>11.2</v>
       </c>
       <c r="M20" s="3" t="n">
@@ -2164,12 +2155,12 @@
         <v>98</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="Q20" s="9" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q20" s="8" t="n">
         <v>28</v>
       </c>
-      <c r="R20" s="9" t="n">
+      <c r="R20" s="8" t="n">
         <v>18.1</v>
       </c>
       <c r="S20" s="3" t="n">
@@ -2181,10 +2172,10 @@
       <c r="U20" s="3" t="n">
         <v>22.4</v>
       </c>
-      <c r="V20" s="9" t="n">
+      <c r="V20" s="8" t="n">
         <v>22.2</v>
       </c>
-      <c r="W20" s="9" t="n">
+      <c r="W20" s="8" t="n">
         <v>18.4</v>
       </c>
       <c r="X20" s="3" t="n">
@@ -2210,18 +2201,18 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>382.4</v>
-      </c>
-      <c r="D21" s="9" t="n">
+        <v>38.2</v>
+      </c>
+      <c r="D21" s="8" t="n">
         <v>24.8</v>
       </c>
-      <c r="E21" s="9" t="n">
+      <c r="E21" s="8" t="n">
         <v>12.7</v>
       </c>
-      <c r="F21" s="9" t="n">
+      <c r="F21" s="8" t="n">
         <v>18.7</v>
       </c>
-      <c r="G21" s="9" t="n">
+      <c r="G21" s="8" t="n">
         <v>12.1</v>
       </c>
       <c r="H21" s="3" t="n">
@@ -2231,12 +2222,12 @@
         <v>2.4</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K21" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="K21" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L21" s="9" t="n">
+      <c r="L21" s="8" t="n">
         <v>13.1</v>
       </c>
       <c r="M21" s="3" t="n">
@@ -2251,10 +2242,10 @@
       <c r="P21" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q21" s="9" t="n">
+      <c r="Q21" s="8" t="n">
         <v>25.6</v>
       </c>
-      <c r="R21" s="9" t="n">
+      <c r="R21" s="8" t="n">
         <v>18.2</v>
       </c>
       <c r="S21" s="3" t="n">
@@ -2266,10 +2257,10 @@
       <c r="U21" s="3" t="n">
         <v>16.2</v>
       </c>
-      <c r="V21" s="9" t="n">
+      <c r="V21" s="8" t="n">
         <v>19.8</v>
       </c>
-      <c r="W21" s="9" t="n">
+      <c r="W21" s="8" t="n">
         <v>18.2</v>
       </c>
       <c r="X21" s="3" t="n">
@@ -2295,18 +2286,18 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>429</v>
-      </c>
-      <c r="D22" s="9" t="n">
+        <v>309</v>
+      </c>
+      <c r="D22" s="8" t="n">
         <v>25.2</v>
       </c>
-      <c r="E22" s="9" t="n">
+      <c r="E22" s="8" t="n">
         <v>12.9</v>
       </c>
-      <c r="F22" s="9" t="n">
+      <c r="F22" s="8" t="n">
         <v>18.7</v>
       </c>
-      <c r="G22" s="9" t="n">
+      <c r="G22" s="8" t="n">
         <v>13.1</v>
       </c>
       <c r="H22" s="3" t="n">
@@ -2318,10 +2309,10 @@
       <c r="J22" s="3" t="n">
         <v>3.8</v>
       </c>
-      <c r="K22" s="9" t="n">
+      <c r="K22" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L22" s="9" t="n">
+      <c r="L22" s="8" t="n">
         <v>12.3</v>
       </c>
       <c r="M22" s="3" t="n">
@@ -2331,15 +2322,15 @@
         <v>14.1</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>99.2</v>
+        <v>99</v>
       </c>
       <c r="P22" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q22" s="9" t="n">
+      <c r="Q22" s="8" t="n">
         <v>23.6</v>
       </c>
-      <c r="R22" s="9" t="n">
+      <c r="R22" s="8" t="n">
         <v>16.2</v>
       </c>
       <c r="S22" s="3" t="n">
@@ -2351,10 +2342,10 @@
       <c r="U22" s="3" t="n">
         <v>14.8</v>
       </c>
-      <c r="V22" s="9" t="n">
+      <c r="V22" s="8" t="n">
         <v>22.5</v>
       </c>
-      <c r="W22" s="9" t="n">
+      <c r="W22" s="8" t="n">
         <v>15.6</v>
       </c>
       <c r="X22" s="3" t="n">
@@ -2380,18 +2371,18 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>2320.3</v>
-      </c>
-      <c r="D23" s="9" t="n">
+        <v>232</v>
+      </c>
+      <c r="D23" s="8" t="n">
         <v>132.1</v>
       </c>
-      <c r="E23" s="9" t="n">
+      <c r="E23" s="8" t="n">
         <v>56.7</v>
       </c>
-      <c r="F23" s="9" t="n">
+      <c r="F23" s="8" t="n">
         <v>94.40000000000001</v>
       </c>
-      <c r="G23" s="9" t="n">
+      <c r="G23" s="8" t="n">
         <v>75.40000000000001</v>
       </c>
       <c r="H23" s="3" t="n">
@@ -2403,13 +2394,13 @@
       <c r="J23" s="3" t="n">
         <v>20.8</v>
       </c>
-      <c r="K23" s="9" t="n">
+      <c r="K23" s="8" t="n">
         <v>0.3</v>
       </c>
-      <c r="L23" s="10" t="n">
+      <c r="L23" s="9" t="n">
         <v>2.5</v>
       </c>
-      <c r="M23" s="10" t="n">
+      <c r="M23" s="9" t="n">
         <v>61.8</v>
       </c>
       <c r="N23" s="3" t="n">
@@ -2419,12 +2410,12 @@
         <v>293</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="Q23" s="9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Q23" s="8" t="n">
         <v>128.9</v>
       </c>
-      <c r="R23" s="9" t="n">
+      <c r="R23" s="8" t="n">
         <v>88</v>
       </c>
       <c r="S23" s="3" t="n">
@@ -2436,10 +2427,10 @@
       <c r="U23" s="3" t="n">
         <v>88.5</v>
       </c>
-      <c r="V23" s="9" t="n">
+      <c r="V23" s="8" t="n">
         <v>106.7</v>
       </c>
-      <c r="W23" s="9" t="n">
+      <c r="W23" s="8" t="n">
         <v>85.5</v>
       </c>
       <c r="X23" s="3" t="n">
@@ -2467,16 +2458,16 @@
       <c r="C24" s="3" t="n">
         <v>464.1</v>
       </c>
-      <c r="D24" s="9" t="n">
+      <c r="D24" s="8" t="n">
         <v>26.4</v>
       </c>
-      <c r="E24" s="9" t="n">
+      <c r="E24" s="8" t="n">
         <v>11.3</v>
       </c>
-      <c r="F24" s="9" t="n">
+      <c r="F24" s="8" t="n">
         <v>18.9</v>
       </c>
-      <c r="G24" s="9" t="n">
+      <c r="G24" s="8" t="n">
         <v>15.1</v>
       </c>
       <c r="H24" s="3" t="n">
@@ -2489,16 +2480,16 @@
         <v>42.1</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="L24" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="8" t="n">
         <v>12.5</v>
       </c>
-      <c r="M24" s="10" t="n">
+      <c r="M24" s="9" t="n">
         <v>12.4</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>11.8</v>
+        <v>10.3</v>
       </c>
       <c r="O24" s="3" t="n">
         <v>98.59999999999999</v>
@@ -2506,10 +2497,10 @@
       <c r="P24" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q24" s="9" t="n">
+      <c r="Q24" s="8" t="n">
         <v>25.8</v>
       </c>
-      <c r="R24" s="9" t="n">
+      <c r="R24" s="8" t="n">
         <v>17.6</v>
       </c>
       <c r="S24" s="3" t="n">
@@ -2521,10 +2512,10 @@
       <c r="U24" s="3" t="n">
         <v>17.7</v>
       </c>
-      <c r="V24" s="9" t="n">
+      <c r="V24" s="8" t="n">
         <v>21.3</v>
       </c>
-      <c r="W24" s="9" t="n">
+      <c r="W24" s="8" t="n">
         <v>17.1</v>
       </c>
       <c r="X24" s="3" t="n">
@@ -2552,16 +2543,16 @@
       <c r="C25" s="3" t="n">
         <v>488.9</v>
       </c>
-      <c r="D25" s="9" t="n">
+      <c r="D25" s="8" t="n">
         <v>25.9</v>
       </c>
-      <c r="E25" s="9" t="n">
+      <c r="E25" s="8" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="F25" s="9" t="n">
+      <c r="F25" s="8" t="n">
         <v>17.8</v>
       </c>
-      <c r="G25" s="9" t="n">
+      <c r="G25" s="8" t="n">
         <v>16.2</v>
       </c>
       <c r="H25" s="3" t="n">
@@ -2573,28 +2564,28 @@
       <c r="J25" s="3" t="n">
         <v>4.1</v>
       </c>
-      <c r="K25" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" s="9" t="n">
+      <c r="K25" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L25" s="8" t="n">
         <v>10.1</v>
       </c>
-      <c r="M25" s="9" t="n">
+      <c r="M25" s="8" t="n">
         <v>9.9</v>
       </c>
       <c r="N25" s="3" t="n">
         <v>19</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>28</v>
+        <v>98</v>
       </c>
       <c r="P25" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q25" s="9" t="n">
+      <c r="Q25" s="8" t="n">
         <v>24.7</v>
       </c>
-      <c r="R25" s="9" t="n">
+      <c r="R25" s="8" t="n">
         <v>17.2</v>
       </c>
       <c r="S25" s="3" t="n">
@@ -2606,10 +2597,10 @@
       <c r="U25" s="3" t="n">
         <v>13.8</v>
       </c>
-      <c r="V25" s="9" t="n">
+      <c r="V25" s="8" t="n">
         <v>21.3</v>
       </c>
-      <c r="W25" s="3" t="n">
+      <c r="W25" s="8" t="n">
         <v>16.9</v>
       </c>
       <c r="X25" s="3" t="n">
@@ -2637,16 +2628,16 @@
       <c r="C26" s="3" t="n">
         <v>349.1</v>
       </c>
-      <c r="D26" s="9" t="n">
+      <c r="D26" s="8" t="n">
         <v>24.4</v>
       </c>
-      <c r="E26" s="9" t="n">
+      <c r="E26" s="8" t="n">
         <v>9.6</v>
       </c>
-      <c r="F26" s="9" t="n">
+      <c r="F26" s="8" t="n">
         <v>17</v>
       </c>
-      <c r="G26" s="9" t="n">
+      <c r="G26" s="8" t="n">
         <v>14.8</v>
       </c>
       <c r="H26" s="3" t="n">
@@ -2658,13 +2649,13 @@
       <c r="J26" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="K26" s="9" t="n">
+      <c r="K26" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="L26" s="9" t="n">
+      <c r="L26" s="8" t="n">
         <v>10.4</v>
       </c>
-      <c r="M26" s="9" t="n">
+      <c r="M26" s="8" t="n">
         <v>10.2</v>
       </c>
       <c r="N26" s="3" t="n">
@@ -2676,10 +2667,10 @@
       <c r="P26" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q26" s="9" t="n">
+      <c r="Q26" s="8" t="n">
         <v>21</v>
       </c>
-      <c r="R26" s="9" t="n">
+      <c r="R26" s="8" t="n">
         <v>16.2</v>
       </c>
       <c r="S26" s="3" t="n">
@@ -2691,14 +2682,14 @@
       <c r="U26" s="3" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="V26" s="9" t="n">
+      <c r="V26" s="8" t="n">
         <v>21.6</v>
       </c>
-      <c r="W26" s="3" t="n">
-        <v>13.5</v>
+      <c r="W26" s="8" t="n">
+        <v>15.5</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>142.2</v>
+        <v>14.2</v>
       </c>
       <c r="Y26" s="3" t="n">
         <v>55</v>
@@ -2722,16 +2713,16 @@
       <c r="C27" s="3" t="n">
         <v>340.2</v>
       </c>
-      <c r="D27" s="9" t="n">
+      <c r="D27" s="8" t="n">
         <v>25.1</v>
       </c>
-      <c r="E27" s="9" t="n">
+      <c r="E27" s="8" t="n">
         <v>11.1</v>
       </c>
-      <c r="F27" s="9" t="n">
+      <c r="F27" s="8" t="n">
         <v>18.1</v>
       </c>
-      <c r="G27" s="9" t="n">
+      <c r="G27" s="8" t="n">
         <v>14</v>
       </c>
       <c r="H27" s="3" t="n">
@@ -2743,13 +2734,13 @@
       <c r="J27" s="3" t="n">
         <v>2.4</v>
       </c>
-      <c r="K27" s="9" t="n">
+      <c r="K27" s="3" t="n">
         <v>7.1</v>
       </c>
-      <c r="L27" s="9" t="n">
+      <c r="L27" s="8" t="n">
         <v>12.4</v>
       </c>
-      <c r="M27" s="9" t="n">
+      <c r="M27" s="8" t="n">
         <v>12.2</v>
       </c>
       <c r="N27" s="3" t="n">
@@ -2761,10 +2752,10 @@
       <c r="P27" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q27" s="9" t="n">
+      <c r="Q27" s="8" t="n">
         <v>17.6</v>
       </c>
-      <c r="R27" s="9" t="n">
+      <c r="R27" s="8" t="n">
         <v>16</v>
       </c>
       <c r="S27" s="3" t="n">
@@ -2776,17 +2767,17 @@
       <c r="U27" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="V27" s="9" t="n">
+      <c r="V27" s="8" t="n">
         <v>17.4</v>
       </c>
-      <c r="W27" s="3" t="n">
+      <c r="W27" s="8" t="n">
         <v>16.7</v>
       </c>
       <c r="X27" s="3" t="n">
         <v>18.5</v>
       </c>
       <c r="Y27" s="3" t="n">
-        <v>23</v>
+        <v>93</v>
       </c>
       <c r="Z27" s="3" t="n">
         <v>1.6</v>
@@ -2807,16 +2798,16 @@
       <c r="C28" s="3" t="n">
         <v>513.3</v>
       </c>
-      <c r="D28" s="9" t="n">
+      <c r="D28" s="8" t="n">
         <v>27</v>
       </c>
-      <c r="E28" s="9" t="n">
+      <c r="E28" s="8" t="n">
         <v>11.6</v>
       </c>
-      <c r="F28" s="9" t="n">
+      <c r="F28" s="8" t="n">
         <v>19.3</v>
       </c>
-      <c r="G28" s="9" t="n">
+      <c r="G28" s="8" t="n">
         <v>15.4</v>
       </c>
       <c r="H28" s="3" t="n">
@@ -2828,13 +2819,13 @@
       <c r="J28" s="3" t="n">
         <v>3.3</v>
       </c>
-      <c r="K28" s="9" t="n">
+      <c r="K28" s="3" t="n">
         <v>5.5</v>
       </c>
-      <c r="L28" s="9" t="n">
+      <c r="L28" s="8" t="n">
         <v>13.4</v>
       </c>
-      <c r="M28" s="9" t="n">
+      <c r="M28" s="8" t="n">
         <v>13.3</v>
       </c>
       <c r="N28" s="3" t="n">
@@ -2846,10 +2837,10 @@
       <c r="P28" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q28" s="9" t="n">
+      <c r="Q28" s="8" t="n">
         <v>22.9</v>
       </c>
-      <c r="R28" s="9" t="n">
+      <c r="R28" s="8" t="n">
         <v>18.6</v>
       </c>
       <c r="S28" s="3" t="n">
@@ -2861,10 +2852,10 @@
       <c r="U28" s="3" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="V28" s="9" t="n">
+      <c r="V28" s="8" t="n">
         <v>16.4</v>
       </c>
-      <c r="W28" s="3" t="n">
+      <c r="W28" s="8" t="n">
         <v>15.5</v>
       </c>
       <c r="X28" s="3" t="n">
@@ -2892,17 +2883,17 @@
       <c r="C29" s="3" t="n">
         <v>593.3</v>
       </c>
-      <c r="D29" s="9" t="n">
+      <c r="D29" s="8" t="n">
         <v>28.8</v>
       </c>
-      <c r="E29" s="9" t="n">
+      <c r="E29" s="8" t="n">
         <v>10.1</v>
       </c>
-      <c r="F29" s="9" t="n">
+      <c r="F29" s="8" t="n">
         <v>19.5</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>7.2</v>
@@ -2913,13 +2904,13 @@
       <c r="J29" s="3" t="n">
         <v>6.2</v>
       </c>
-      <c r="K29" s="9" t="n">
+      <c r="K29" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L29" s="9" t="n">
+      <c r="L29" s="8" t="n">
         <v>10.9</v>
       </c>
-      <c r="M29" s="9" t="n">
+      <c r="M29" s="8" t="n">
         <v>10.5</v>
       </c>
       <c r="N29" s="3" t="n">
@@ -2931,25 +2922,25 @@
       <c r="P29" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q29" s="9" t="n">
+      <c r="Q29" s="8" t="n">
         <v>27</v>
       </c>
-      <c r="R29" s="9" t="n">
+      <c r="R29" s="8" t="n">
         <v>18.7</v>
       </c>
       <c r="S29" s="3" t="n">
         <v>17</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>27.8</v>
+        <v>47.8</v>
       </c>
       <c r="U29" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="V29" s="9" t="n">
+      <c r="V29" s="8" t="n">
         <v>22.8</v>
       </c>
-      <c r="W29" s="3" t="n">
+      <c r="W29" s="8" t="n">
         <v>17.3</v>
       </c>
       <c r="X29" s="3" t="n">
@@ -2975,22 +2966,22 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>2284.8</v>
-      </c>
-      <c r="D30" s="9" t="n">
+        <v>228.4</v>
+      </c>
+      <c r="D30" s="8" t="n">
         <v>131.2</v>
       </c>
-      <c r="E30" s="9" t="n">
+      <c r="E30" s="8" t="n">
         <v>52.1</v>
       </c>
-      <c r="F30" s="9" t="n">
+      <c r="F30" s="8" t="n">
         <v>91.7</v>
       </c>
-      <c r="G30" s="9" t="n">
+      <c r="G30" s="8" t="n">
         <v>79.09999999999999</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>13.8</v>
@@ -3001,10 +2992,10 @@
       <c r="K30" s="9" t="n">
         <v>13.5</v>
       </c>
-      <c r="L30" s="9" t="n">
+      <c r="L30" s="8" t="n">
         <v>57.2</v>
       </c>
-      <c r="M30" s="9" t="n">
+      <c r="M30" s="8" t="n">
         <v>56.1</v>
       </c>
       <c r="N30" s="3" t="n">
@@ -3016,10 +3007,10 @@
       <c r="P30" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="Q30" s="10" t="n">
+      <c r="Q30" s="9" t="n">
         <v>413.2</v>
       </c>
-      <c r="R30" s="9" t="n">
+      <c r="R30" s="8" t="n">
         <v>86.7</v>
       </c>
       <c r="S30" s="3" t="n">
@@ -3031,10 +3022,10 @@
       <c r="U30" s="3" t="n">
         <v>55.4</v>
       </c>
-      <c r="V30" s="9" t="n">
+      <c r="V30" s="8" t="n">
         <v>99.5</v>
       </c>
-      <c r="W30" s="10" t="n">
+      <c r="W30" s="8" t="n">
         <v>81.90000000000001</v>
       </c>
       <c r="X30" s="3" t="n">
@@ -3062,16 +3053,16 @@
       <c r="C31" s="3" t="n">
         <v>457</v>
       </c>
-      <c r="D31" s="9" t="n">
+      <c r="D31" s="8" t="n">
         <v>26.2</v>
       </c>
-      <c r="E31" s="9" t="n">
+      <c r="E31" s="8" t="n">
         <v>10.4</v>
       </c>
-      <c r="F31" s="9" t="n">
+      <c r="F31" s="8" t="n">
         <v>18.3</v>
       </c>
-      <c r="G31" s="9" t="n">
+      <c r="G31" s="8" t="n">
         <v>15.8</v>
       </c>
       <c r="H31" s="3" t="n">
@@ -3084,14 +3075,14 @@
         <v>3.9</v>
       </c>
       <c r="K31" s="3" t="inlineStr"/>
-      <c r="L31" s="10" t="n">
+      <c r="L31" s="9" t="n">
         <v>11.9</v>
       </c>
-      <c r="M31" s="9" t="n">
+      <c r="M31" s="8" t="n">
         <v>11.2</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>13.2</v>
+        <v>13.8</v>
       </c>
       <c r="O31" s="3" t="n">
         <v>97.8</v>
@@ -3099,10 +3090,10 @@
       <c r="P31" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q31" s="9" t="n">
+      <c r="Q31" s="8" t="n">
         <v>22.6</v>
       </c>
-      <c r="R31" s="9" t="n">
+      <c r="R31" s="8" t="n">
         <v>17.3</v>
       </c>
       <c r="S31" s="3" t="n">
@@ -3114,10 +3105,10 @@
       <c r="U31" s="3" t="n">
         <v>11.1</v>
       </c>
-      <c r="V31" s="9" t="n">
+      <c r="V31" s="8" t="n">
         <v>19.9</v>
       </c>
-      <c r="W31" s="10" t="n">
+      <c r="W31" s="8" t="n">
         <v>16.4</v>
       </c>
       <c r="X31" s="3" t="n">
@@ -3127,7 +3118,7 @@
         <v>730.2</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>165.8</v>
+        <v>10.8</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3145,16 +3136,16 @@
       <c r="C32" s="3" t="n">
         <v>520</v>
       </c>
-      <c r="D32" s="9" t="n">
+      <c r="D32" s="8" t="n">
         <v>27.9</v>
       </c>
-      <c r="E32" s="9" t="n">
+      <c r="E32" s="8" t="n">
         <v>10.2</v>
       </c>
-      <c r="F32" s="9" t="n">
+      <c r="F32" s="8" t="n">
         <v>19.1</v>
       </c>
-      <c r="G32" s="9" t="n">
+      <c r="G32" s="8" t="n">
         <v>17.7</v>
       </c>
       <c r="H32" s="3" t="n">
@@ -3166,17 +3157,17 @@
       <c r="J32" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="K32" s="9" t="n">
+      <c r="K32" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L32" s="9" t="n">
+      <c r="L32" s="8" t="n">
         <v>10.5</v>
       </c>
-      <c r="M32" s="9" t="n">
+      <c r="M32" s="8" t="n">
         <v>10.2</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>12.4</v>
+        <v>12</v>
       </c>
       <c r="O32" s="3" t="n">
         <v>97</v>
@@ -3187,20 +3178,20 @@
       <c r="Q32" s="3" t="n">
         <v>21.1</v>
       </c>
-      <c r="R32" s="9" t="n">
+      <c r="R32" s="8" t="n">
         <v>18.8</v>
       </c>
       <c r="S32" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>62.2</v>
+        <v>62.5</v>
       </c>
       <c r="U32" s="3" t="inlineStr"/>
-      <c r="V32" s="9" t="n">
+      <c r="V32" s="8" t="n">
         <v>21.4</v>
       </c>
-      <c r="W32" s="9" t="n">
+      <c r="W32" s="8" t="n">
         <v>17.6</v>
       </c>
       <c r="X32" s="3" t="n">
@@ -3226,16 +3217,16 @@
       <c r="C33" s="3" t="n">
         <v>349.1</v>
       </c>
-      <c r="D33" s="9" t="n">
+      <c r="D33" s="8" t="n">
         <v>24.2</v>
       </c>
-      <c r="E33" s="9" t="n">
+      <c r="E33" s="8" t="n">
         <v>12.8</v>
       </c>
-      <c r="F33" s="9" t="n">
+      <c r="F33" s="8" t="n">
         <v>18.5</v>
       </c>
-      <c r="G33" s="9" t="n">
+      <c r="G33" s="8" t="n">
         <v>11.4</v>
       </c>
       <c r="H33" s="3" t="n">
@@ -3247,17 +3238,17 @@
       <c r="J33" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="K33" s="9" t="n">
+      <c r="K33" s="8" t="n">
         <v>6.8</v>
       </c>
-      <c r="L33" s="9" t="n">
+      <c r="L33" s="8" t="n">
         <v>14.9</v>
       </c>
-      <c r="M33" s="9" t="n">
+      <c r="M33" s="8" t="n">
         <v>14.7</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>16.6</v>
+        <v>10.6</v>
       </c>
       <c r="O33" s="3" t="n">
         <v>98</v>
@@ -3268,7 +3259,7 @@
       <c r="Q33" s="3" t="n">
         <v>20.3</v>
       </c>
-      <c r="R33" s="9" t="n">
+      <c r="R33" s="8" t="n">
         <v>17.8</v>
       </c>
       <c r="S33" s="3" t="n">
@@ -3280,10 +3271,10 @@
       <c r="U33" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="V33" s="9" t="n">
+      <c r="V33" s="8" t="n">
         <v>19.4</v>
       </c>
-      <c r="W33" s="9" t="n">
+      <c r="W33" s="8" t="n">
         <v>17.9</v>
       </c>
       <c r="X33" s="3" t="n">
@@ -3311,16 +3302,16 @@
       <c r="C34" s="3" t="n">
         <v>329.1</v>
       </c>
-      <c r="D34" s="9" t="n">
+      <c r="D34" s="8" t="n">
         <v>23.3</v>
       </c>
-      <c r="E34" s="9" t="n">
+      <c r="E34" s="8" t="n">
         <v>14.7</v>
       </c>
-      <c r="F34" s="9" t="n">
+      <c r="F34" s="8" t="n">
         <v>19</v>
       </c>
-      <c r="G34" s="9" t="n">
+      <c r="G34" s="8" t="n">
         <v>8.6</v>
       </c>
       <c r="H34" s="3" t="n">
@@ -3332,13 +3323,13 @@
       <c r="J34" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="K34" s="9" t="n">
+      <c r="K34" s="8" t="n">
         <v>1.7</v>
       </c>
-      <c r="L34" s="9" t="n">
+      <c r="L34" s="8" t="n">
         <v>16</v>
       </c>
-      <c r="M34" s="9" t="n">
+      <c r="M34" s="8" t="n">
         <v>15.9</v>
       </c>
       <c r="N34" s="3" t="n">
@@ -3353,7 +3344,7 @@
       <c r="Q34" s="3" t="n">
         <v>21.8</v>
       </c>
-      <c r="R34" s="9" t="n">
+      <c r="R34" s="8" t="n">
         <v>18.1</v>
       </c>
       <c r="S34" s="3" t="n">
@@ -3365,17 +3356,17 @@
       <c r="U34" s="3" t="n">
         <v>7.6</v>
       </c>
-      <c r="V34" s="9" t="n">
+      <c r="V34" s="8" t="n">
         <v>18.7</v>
       </c>
-      <c r="W34" s="9" t="n">
+      <c r="W34" s="8" t="n">
         <v>16.8</v>
       </c>
       <c r="X34" s="3" t="n">
         <v>18</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>53</v>
+        <v>83</v>
       </c>
       <c r="Z34" s="3" t="n">
         <v>3.8</v>
@@ -3396,16 +3387,16 @@
       <c r="C35" s="3" t="n">
         <v>506.7</v>
       </c>
-      <c r="D35" s="9" t="n">
+      <c r="D35" s="8" t="n">
         <v>26.8</v>
       </c>
-      <c r="E35" s="9" t="n">
+      <c r="E35" s="8" t="n">
         <v>12.8</v>
       </c>
-      <c r="F35" s="9" t="n">
+      <c r="F35" s="8" t="n">
         <v>19.8</v>
       </c>
-      <c r="G35" s="9" t="n">
+      <c r="G35" s="8" t="n">
         <v>14</v>
       </c>
       <c r="H35" s="3" t="n">
@@ -3417,13 +3408,13 @@
       <c r="J35" s="3" t="n">
         <v>5.5</v>
       </c>
-      <c r="K35" s="9" t="n">
+      <c r="K35" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L35" s="9" t="n">
+      <c r="L35" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="M35" s="9" t="n">
+      <c r="M35" s="8" t="n">
         <v>12.9</v>
       </c>
       <c r="N35" s="3" t="n">
@@ -3438,22 +3429,22 @@
       <c r="Q35" s="3" t="n">
         <v>23.8</v>
       </c>
-      <c r="R35" s="9" t="n">
+      <c r="R35" s="8" t="n">
         <v>17.6</v>
       </c>
       <c r="S35" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="U35" s="3" t="n">
         <v>12.8</v>
       </c>
-      <c r="V35" s="9" t="n">
+      <c r="V35" s="8" t="n">
         <v>20.8</v>
       </c>
-      <c r="W35" s="9" t="n">
+      <c r="W35" s="8" t="n">
         <v>16.7</v>
       </c>
       <c r="X35" s="3" t="n">
@@ -3481,16 +3472,16 @@
       <c r="C36" s="3" t="n">
         <v>535.5</v>
       </c>
-      <c r="D36" s="9" t="n">
+      <c r="D36" s="8" t="n">
         <v>26.3</v>
       </c>
-      <c r="E36" s="9" t="n">
+      <c r="E36" s="8" t="n">
         <v>10.4</v>
       </c>
-      <c r="F36" s="9" t="n">
+      <c r="F36" s="8" t="n">
         <v>18.3</v>
       </c>
-      <c r="G36" s="9" t="n">
+      <c r="G36" s="8" t="n">
         <v>15.9</v>
       </c>
       <c r="H36" s="3" t="n">
@@ -3502,13 +3493,13 @@
       <c r="J36" s="3" t="n">
         <v>5.9</v>
       </c>
-      <c r="K36" s="9" t="n">
+      <c r="K36" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L36" s="9" t="n">
+      <c r="L36" s="8" t="n">
         <v>10.6</v>
       </c>
-      <c r="M36" s="9" t="n">
+      <c r="M36" s="8" t="n">
         <v>10.5</v>
       </c>
       <c r="N36" s="3" t="n">
@@ -3518,27 +3509,27 @@
         <v>99</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="Q36" s="3" t="n">
         <v>23.5</v>
       </c>
-      <c r="R36" s="9" t="n">
+      <c r="R36" s="8" t="n">
         <v>17.1</v>
       </c>
       <c r="S36" s="3" t="n">
         <v>14.8</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="U36" s="3" t="n">
         <v>17.9</v>
       </c>
-      <c r="V36" s="9" t="n">
+      <c r="V36" s="8" t="n">
         <v>20.6</v>
       </c>
-      <c r="W36" s="9" t="n">
+      <c r="W36" s="8" t="n">
         <v>14.6</v>
       </c>
       <c r="X36" s="3" t="n">
@@ -3566,16 +3557,16 @@
       <c r="C37" s="3" t="n">
         <v>224</v>
       </c>
-      <c r="D37" s="9" t="n">
+      <c r="D37" s="8" t="n">
         <v>128.5</v>
       </c>
-      <c r="E37" s="9" t="n">
+      <c r="E37" s="8" t="n">
         <v>60.9</v>
       </c>
-      <c r="F37" s="9" t="n">
+      <c r="F37" s="8" t="n">
         <v>94.7</v>
       </c>
-      <c r="G37" s="9" t="n">
+      <c r="G37" s="8" t="n">
         <v>67.59999999999999</v>
       </c>
       <c r="H37" s="3" t="n">
@@ -3587,13 +3578,13 @@
       <c r="J37" s="3" t="n">
         <v>20.8</v>
       </c>
-      <c r="K37" s="9" t="n">
+      <c r="K37" s="8" t="n">
         <v>8.5</v>
       </c>
-      <c r="L37" s="9" t="n">
+      <c r="L37" s="8" t="n">
         <v>65</v>
       </c>
-      <c r="M37" s="9" t="n">
+      <c r="M37" s="8" t="n">
         <v>64.2</v>
       </c>
       <c r="N37" s="3" t="n">
@@ -3603,10 +3594,10 @@
         <v>492</v>
       </c>
       <c r="P37" s="3" t="inlineStr"/>
-      <c r="Q37" s="10" t="n">
+      <c r="Q37" s="9" t="n">
         <v>115.5</v>
       </c>
-      <c r="R37" s="10" t="n">
+      <c r="R37" s="9" t="n">
         <v>82.40000000000001</v>
       </c>
       <c r="S37" s="3" t="n">
@@ -3618,14 +3609,14 @@
       <c r="U37" s="3" t="n">
         <v>54.5</v>
       </c>
-      <c r="V37" s="9" t="n">
+      <c r="V37" s="8" t="n">
         <v>100.9</v>
       </c>
-      <c r="W37" s="10" t="n">
+      <c r="W37" s="9" t="n">
         <v>83.09999999999999</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>82.7</v>
+        <v>84.7</v>
       </c>
       <c r="Y37" s="3" t="n">
         <v>359.5</v>
@@ -3649,23 +3640,23 @@
       <c r="C38" s="3" t="n">
         <v>448.1</v>
       </c>
-      <c r="D38" s="9" t="n">
+      <c r="D38" s="8" t="n">
         <v>25.7</v>
       </c>
-      <c r="E38" s="9" t="n">
+      <c r="E38" s="8" t="n">
         <v>12.2</v>
       </c>
-      <c r="F38" s="9" t="n">
+      <c r="F38" s="8" t="n">
         <v>18.9</v>
       </c>
-      <c r="G38" s="9" t="n">
+      <c r="G38" s="8" t="n">
         <v>13.5</v>
       </c>
       <c r="H38" s="3" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>28.1</v>
+        <v>2.8</v>
       </c>
       <c r="J38" s="3" t="n">
         <v>22.1</v>
@@ -3673,10 +3664,10 @@
       <c r="K38" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L38" s="9" t="n">
+      <c r="L38" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="M38" s="9" t="n">
+      <c r="M38" s="8" t="n">
         <v>12.8</v>
       </c>
       <c r="N38" s="3" t="n">
@@ -3688,10 +3679,10 @@
       <c r="P38" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q38" s="10" t="n">
+      <c r="Q38" s="9" t="n">
         <v>23.1</v>
       </c>
-      <c r="R38" s="9" t="n">
+      <c r="R38" s="8" t="n">
         <v>17.9</v>
       </c>
       <c r="S38" s="3" t="n">
@@ -3703,10 +3694,10 @@
       <c r="U38" s="3" t="n">
         <v>19.9</v>
       </c>
-      <c r="V38" s="9" t="n">
+      <c r="V38" s="8" t="n">
         <v>20.2</v>
       </c>
-      <c r="W38" s="9" t="n">
+      <c r="W38" s="8" t="n">
         <v>16.6</v>
       </c>
       <c r="X38" s="3" t="n">
@@ -3734,16 +3725,16 @@
       <c r="C39" s="3" t="n">
         <v>579.9</v>
       </c>
-      <c r="D39" s="9" t="n">
-        <v>26.92</v>
-      </c>
-      <c r="E39" s="9" t="n">
+      <c r="D39" s="8" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="E39" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="F39" s="9" t="n">
+      <c r="F39" s="8" t="n">
         <v>18.9</v>
       </c>
-      <c r="G39" s="9" t="n">
+      <c r="G39" s="8" t="n">
         <v>15.9</v>
       </c>
       <c r="H39" s="3" t="n">
@@ -3755,13 +3746,13 @@
       <c r="J39" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="K39" s="9" t="n">
+      <c r="K39" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L39" s="9" t="n">
+      <c r="L39" s="8" t="n">
         <v>12.7</v>
       </c>
-      <c r="M39" s="9" t="n">
+      <c r="M39" s="8" t="n">
         <v>12.5</v>
       </c>
       <c r="N39" s="3" t="n">
@@ -3773,10 +3764,10 @@
       <c r="P39" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q39" s="9" t="n">
+      <c r="Q39" s="8" t="n">
         <v>26.6</v>
       </c>
-      <c r="R39" s="9" t="n">
+      <c r="R39" s="8" t="n">
         <v>18</v>
       </c>
       <c r="S39" s="3" t="inlineStr"/>
@@ -3786,10 +3777,10 @@
       <c r="U39" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="V39" s="9" t="n">
+      <c r="V39" s="8" t="n">
         <v>21.7</v>
       </c>
-      <c r="W39" s="9" t="n">
+      <c r="W39" s="8" t="n">
         <v>15.7</v>
       </c>
       <c r="X39" s="3" t="n">
@@ -3817,13 +3808,13 @@
       <c r="C40" s="3" t="n">
         <v>355.7</v>
       </c>
-      <c r="D40" s="9" t="n">
+      <c r="D40" s="8" t="n">
         <v>27.2</v>
       </c>
-      <c r="E40" s="9" t="n">
+      <c r="E40" s="8" t="n">
         <v>10.7</v>
       </c>
-      <c r="F40" s="9" t="n">
+      <c r="F40" s="8" t="n">
         <v>18.9</v>
       </c>
       <c r="G40" s="3" t="n">
@@ -3838,13 +3829,13 @@
       <c r="J40" s="3" t="n">
         <v>3.2</v>
       </c>
-      <c r="K40" s="9" t="n">
+      <c r="K40" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L40" s="9" t="n">
+      <c r="L40" s="8" t="n">
         <v>10.6</v>
       </c>
-      <c r="M40" s="9" t="n">
+      <c r="M40" s="8" t="n">
         <v>10.3</v>
       </c>
       <c r="N40" s="3" t="n">
@@ -3856,10 +3847,10 @@
       <c r="P40" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="Q40" s="9" t="n">
+      <c r="Q40" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="R40" s="9" t="n">
+      <c r="R40" s="8" t="n">
         <v>18</v>
       </c>
       <c r="S40" s="3" t="n">
@@ -3871,10 +3862,10 @@
       <c r="U40" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="V40" s="9" t="n">
+      <c r="V40" s="8" t="n">
         <v>19.7</v>
       </c>
-      <c r="W40" s="9" t="n">
+      <c r="W40" s="8" t="n">
         <v>16.8</v>
       </c>
       <c r="X40" s="3" t="n">
@@ -3902,16 +3893,16 @@
       <c r="C41" s="3" t="n">
         <v>451.2</v>
       </c>
-      <c r="D41" s="9" t="n">
+      <c r="D41" s="8" t="n">
         <v>28.4</v>
       </c>
-      <c r="E41" s="9" t="n">
+      <c r="E41" s="8" t="n">
         <v>8.6</v>
       </c>
-      <c r="F41" s="9" t="n">
+      <c r="F41" s="8" t="n">
         <v>18.5</v>
       </c>
-      <c r="G41" s="9" t="n">
+      <c r="G41" s="8" t="n">
         <v>19.8</v>
       </c>
       <c r="H41" s="3" t="n">
@@ -3923,13 +3914,13 @@
       <c r="J41" s="3" t="n">
         <v>5.1</v>
       </c>
-      <c r="K41" s="9" t="n">
+      <c r="K41" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L41" s="9" t="n">
+      <c r="L41" s="8" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="M41" s="9" t="n">
+      <c r="M41" s="8" t="n">
         <v>8.6</v>
       </c>
       <c r="N41" s="3" t="n">
@@ -3941,10 +3932,10 @@
       <c r="P41" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q41" s="9" t="n">
+      <c r="Q41" s="8" t="n">
         <v>23.4</v>
       </c>
-      <c r="R41" s="9" t="n">
+      <c r="R41" s="8" t="n">
         <v>17.4</v>
       </c>
       <c r="S41" s="3" t="n">
@@ -3954,12 +3945,12 @@
         <v>57.9</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="V41" s="9" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="V41" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="W41" s="9" t="n">
+      <c r="W41" s="8" t="n">
         <v>18.5</v>
       </c>
       <c r="X41" s="3" t="n">
@@ -3969,7 +3960,7 @@
         <v>58</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>14.9</v>
+        <v>15.4</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -3987,16 +3978,16 @@
       <c r="C42" s="3" t="n">
         <v>524.4</v>
       </c>
-      <c r="D42" s="9" t="n">
+      <c r="D42" s="8" t="n">
         <v>27.2</v>
       </c>
-      <c r="E42" s="9" t="n">
+      <c r="E42" s="8" t="n">
         <v>11.4</v>
       </c>
-      <c r="F42" s="9" t="n">
+      <c r="F42" s="8" t="n">
         <v>19.3</v>
       </c>
-      <c r="G42" s="9" t="n">
+      <c r="G42" s="8" t="n">
         <v>15.7</v>
       </c>
       <c r="H42" s="3" t="n">
@@ -4008,13 +3999,13 @@
       <c r="J42" s="3" t="n">
         <v>5.6</v>
       </c>
-      <c r="K42" s="9" t="n">
+      <c r="K42" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L42" s="9" t="n">
+      <c r="L42" s="8" t="n">
         <v>11.9</v>
       </c>
-      <c r="M42" s="9" t="n">
+      <c r="M42" s="8" t="n">
         <v>11.3</v>
       </c>
       <c r="N42" s="3" t="n">
@@ -4026,25 +4017,25 @@
       <c r="P42" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="Q42" s="9" t="n">
+      <c r="Q42" s="8" t="n">
         <v>26.6</v>
       </c>
-      <c r="R42" s="9" t="n">
+      <c r="R42" s="8" t="n">
         <v>17.6</v>
       </c>
       <c r="S42" s="3" t="n">
         <v>15.1</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>23.2</v>
+        <v>23.5</v>
       </c>
       <c r="U42" s="3" t="n">
         <v>19.6</v>
       </c>
-      <c r="V42" s="9" t="n">
+      <c r="V42" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="W42" s="9" t="inlineStr"/>
+      <c r="W42" s="8" t="inlineStr"/>
       <c r="X42" s="3" t="inlineStr"/>
       <c r="Y42" s="3" t="inlineStr"/>
       <c r="Z42" s="3" t="inlineStr"/>
@@ -4062,28 +4053,28 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D43" s="9" t="inlineStr"/>
-      <c r="E43" s="13" t="inlineStr"/>
-      <c r="F43" s="9" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="D43" s="8" t="inlineStr"/>
+      <c r="E43" s="12" t="inlineStr"/>
+      <c r="F43" s="8" t="inlineStr"/>
       <c r="G43" s="3" t="inlineStr"/>
       <c r="H43" s="3" t="inlineStr"/>
       <c r="I43" s="3" t="inlineStr"/>
       <c r="J43" s="3" t="inlineStr"/>
-      <c r="K43" s="9" t="inlineStr"/>
-      <c r="L43" s="9" t="inlineStr"/>
-      <c r="M43" s="9" t="inlineStr"/>
+      <c r="K43" s="8" t="inlineStr"/>
+      <c r="L43" s="8" t="inlineStr"/>
+      <c r="M43" s="8" t="inlineStr"/>
       <c r="N43" s="3" t="inlineStr"/>
       <c r="O43" s="3" t="inlineStr"/>
       <c r="P43" s="3" t="inlineStr"/>
-      <c r="Q43" s="9" t="inlineStr"/>
-      <c r="R43" s="9" t="inlineStr"/>
+      <c r="Q43" s="8" t="inlineStr"/>
+      <c r="R43" s="8" t="inlineStr"/>
       <c r="S43" s="3" t="inlineStr"/>
       <c r="T43" s="3" t="inlineStr"/>
       <c r="U43" s="3" t="inlineStr"/>
-      <c r="V43" s="9" t="inlineStr"/>
-      <c r="W43" s="9" t="inlineStr"/>
+      <c r="V43" s="8" t="inlineStr"/>
+      <c r="W43" s="8" t="inlineStr"/>
       <c r="X43" s="3" t="inlineStr"/>
       <c r="Y43" s="3" t="inlineStr"/>
       <c r="Z43" s="3" t="inlineStr"/>
@@ -4101,28 +4092,28 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D44" s="9" t="inlineStr"/>
-      <c r="E44" s="13" t="inlineStr"/>
-      <c r="F44" s="9" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="D44" s="8" t="inlineStr"/>
+      <c r="E44" s="12" t="inlineStr"/>
+      <c r="F44" s="8" t="inlineStr"/>
       <c r="G44" s="3" t="inlineStr"/>
       <c r="H44" s="3" t="inlineStr"/>
       <c r="I44" s="3" t="inlineStr"/>
       <c r="J44" s="3" t="inlineStr"/>
-      <c r="K44" s="9" t="inlineStr"/>
-      <c r="L44" s="9" t="inlineStr"/>
-      <c r="M44" s="9" t="inlineStr"/>
+      <c r="K44" s="8" t="inlineStr"/>
+      <c r="L44" s="8" t="inlineStr"/>
+      <c r="M44" s="8" t="inlineStr"/>
       <c r="N44" s="3" t="inlineStr"/>
       <c r="O44" s="3" t="inlineStr"/>
       <c r="P44" s="3" t="inlineStr"/>
-      <c r="Q44" s="9" t="inlineStr"/>
-      <c r="R44" s="9" t="inlineStr"/>
+      <c r="Q44" s="8" t="inlineStr"/>
+      <c r="R44" s="8" t="inlineStr"/>
       <c r="S44" s="3" t="inlineStr"/>
       <c r="T44" s="3" t="inlineStr"/>
       <c r="U44" s="3" t="inlineStr"/>
-      <c r="V44" s="9" t="inlineStr"/>
-      <c r="W44" s="9" t="inlineStr"/>
+      <c r="V44" s="8" t="inlineStr"/>
+      <c r="W44" s="8" t="inlineStr"/>
       <c r="X44" s="3" t="inlineStr"/>
       <c r="Y44" s="3" t="inlineStr"/>
       <c r="Z44" s="3" t="inlineStr"/>
@@ -4140,22 +4131,22 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>1911.2</v>
-      </c>
-      <c r="D45" s="9" t="n">
+        <v>191.1</v>
+      </c>
+      <c r="D45" s="8" t="n">
         <v>109.7</v>
       </c>
-      <c r="E45" s="9" t="n">
+      <c r="E45" s="8" t="n">
         <v>41.5</v>
       </c>
-      <c r="F45" s="9" t="n">
+      <c r="F45" s="8" t="n">
         <v>75.59999999999999</v>
       </c>
       <c r="G45" s="3" t="n">
         <v>67.90000000000001</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I45" s="3" t="n">
         <v>14.4</v>
@@ -4163,13 +4154,13 @@
       <c r="J45" s="3" t="n">
         <v>20.9</v>
       </c>
-      <c r="K45" s="9" t="n">
+      <c r="K45" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L45" s="9" t="n">
+      <c r="L45" s="8" t="n">
         <v>44</v>
       </c>
-      <c r="M45" s="9" t="n">
+      <c r="M45" s="8" t="n">
         <v>42.9</v>
       </c>
       <c r="N45" s="3" t="n">
@@ -4179,12 +4170,12 @@
         <v>388</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="Q45" s="9" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q45" s="8" t="n">
         <v>98.59999999999999</v>
       </c>
-      <c r="R45" s="9" t="n">
+      <c r="R45" s="8" t="n">
         <v>71</v>
       </c>
       <c r="S45" s="3" t="n">
@@ -4196,14 +4187,14 @@
       <c r="U45" s="3" t="n">
         <v>59</v>
       </c>
-      <c r="V45" s="9" t="n">
+      <c r="V45" s="8" t="n">
         <v>85.40000000000001</v>
       </c>
-      <c r="W45" s="10" t="n">
+      <c r="W45" s="9" t="n">
         <v>67.3</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>66.8</v>
+        <v>60.8</v>
       </c>
       <c r="Y45" s="3" t="n">
         <v>263</v>
@@ -4227,16 +4218,16 @@
       <c r="C46" s="3" t="n">
         <v>477.8</v>
       </c>
-      <c r="D46" s="9" t="n">
+      <c r="D46" s="8" t="n">
         <v>27.4</v>
       </c>
-      <c r="E46" s="9" t="n">
+      <c r="E46" s="8" t="n">
         <v>10.5</v>
       </c>
-      <c r="F46" s="9" t="n">
+      <c r="F46" s="8" t="n">
         <v>18.9</v>
       </c>
-      <c r="G46" s="9" t="n">
+      <c r="G46" s="8" t="n">
         <v>16.9</v>
       </c>
       <c r="H46" s="3" t="n">
@@ -4246,15 +4237,15 @@
         <v>36.1</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>52.1</v>
-      </c>
-      <c r="K46" s="8" t="n">
-        <v>101.1</v>
-      </c>
-      <c r="L46" s="10" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="K46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" s="9" t="n">
         <v>11.8</v>
       </c>
-      <c r="M46" s="9" t="n">
+      <c r="M46" s="8" t="n">
         <v>10.7</v>
       </c>
       <c r="N46" s="3" t="n">
@@ -4266,10 +4257,10 @@
       <c r="P46" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q46" s="9" t="n">
+      <c r="Q46" s="8" t="n">
         <v>24.7</v>
       </c>
-      <c r="R46" s="9" t="n">
+      <c r="R46" s="8" t="n">
         <v>17.7</v>
       </c>
       <c r="S46" s="3" t="n">
@@ -4281,17 +4272,17 @@
       <c r="U46" s="3" t="n">
         <v>14.7</v>
       </c>
-      <c r="V46" s="9" t="n">
+      <c r="V46" s="8" t="n">
         <v>21.3</v>
       </c>
-      <c r="W46" s="9" t="n">
+      <c r="W46" s="8" t="n">
         <v>16.8</v>
       </c>
       <c r="X46" s="3" t="n">
         <v>16.7</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>65.7</v>
+        <v>265.7</v>
       </c>
       <c r="Z46" s="3" t="n">
         <v>8.9</v>

--- a/results/05_transient_transcription_output/702/702_196402_SF.JPG_stage_duirnal_temp_range.xlsx
+++ b/results/05_transient_transcription_output/702/702_196402_SF.JPG_stage_duirnal_temp_range.xlsx
@@ -59,14 +59,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
+        <fgColor rgb="00FFC0CB"/>
+        <bgColor rgb="00FFC0CB"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC0CB"/>
-        <bgColor rgb="00FFC0CB"/>
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -1224,7 +1224,7 @@
       <c r="J9" s="3" t="n">
         <v>13.3</v>
       </c>
-      <c r="K9" s="3" t="n">
+      <c r="K9" s="9" t="n">
         <v>7.7</v>
       </c>
       <c r="L9" s="3" t="n">
@@ -1802,7 +1802,7 @@
       <c r="J16" s="3" t="n">
         <v>139.8</v>
       </c>
-      <c r="K16" s="3" t="n"/>
+      <c r="K16" s="13" t="n"/>
       <c r="L16" s="3" t="n">
         <v>59.9</v>
       </c>
@@ -1945,7 +1945,7 @@
       <c r="C18" s="3" t="n">
         <v>455.6</v>
       </c>
-      <c r="D18" s="13" t="n"/>
+      <c r="D18" s="14" t="n"/>
       <c r="E18" s="12" t="n">
         <v>0.1</v>
       </c>
@@ -2132,7 +2132,7 @@
       <c r="J20" s="3" t="n">
         <v>4.9</v>
       </c>
-      <c r="K20" s="3" t="n"/>
+      <c r="K20" s="14" t="n"/>
       <c r="L20" s="3" t="n">
         <v>0.2</v>
       </c>
@@ -2280,7 +2280,7 @@
       <c r="D22" s="3" t="n">
         <v>24.8</v>
       </c>
-      <c r="E22" s="13" t="n"/>
+      <c r="E22" s="14" t="n"/>
       <c r="F22" s="12" t="n">
         <v>81.7</v>
       </c>
@@ -2379,7 +2379,7 @@
       <c r="J23" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="K23" s="3" t="n">
+      <c r="K23" s="9" t="n">
         <v>0.3</v>
       </c>
       <c r="L23" s="3" t="n">
@@ -2622,7 +2622,7 @@
       <c r="J26" s="3" t="n">
         <v>18.5</v>
       </c>
-      <c r="K26" s="3" t="n"/>
+      <c r="K26" s="14" t="n"/>
       <c r="L26" s="3" t="n">
         <v>10.4</v>
       </c>
@@ -2956,7 +2956,7 @@
       <c r="J30" s="3" t="n">
         <v>119.5</v>
       </c>
-      <c r="K30" s="3" t="n">
+      <c r="K30" s="9" t="n">
         <v>13.5</v>
       </c>
       <c r="L30" s="3" t="n">
@@ -3543,7 +3543,7 @@
       <c r="J37" s="3" t="n">
         <v>5.9</v>
       </c>
-      <c r="K37" s="3" t="n"/>
+      <c r="K37" s="13" t="n"/>
       <c r="L37" s="3" t="n">
         <v>10.6</v>
       </c>
@@ -3792,7 +3792,7 @@
       <c r="J40" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="K40" s="3" t="n"/>
+      <c r="K40" s="14" t="n"/>
       <c r="L40" s="3" t="n">
         <v>12.7</v>
       </c>
@@ -4105,8 +4105,8 @@
       <c r="D44" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="E44" s="13" t="n"/>
-      <c r="F44" s="13" t="n"/>
+      <c r="E44" s="14" t="n"/>
+      <c r="F44" s="14" t="n"/>
       <c r="G44" s="3" t="n"/>
       <c r="H44" s="3" t="n">
         <v>0.1</v>
@@ -4188,7 +4188,7 @@
       <c r="J45" s="3" t="n">
         <v>221.9</v>
       </c>
-      <c r="K45" s="3" t="n">
+      <c r="K45" s="9" t="n">
         <v>1.1</v>
       </c>
       <c r="L45" s="3" t="n"/>
@@ -4244,8 +4244,8 @@
       <c r="C46" s="3" t="n">
         <v>477.8</v>
       </c>
-      <c r="D46" s="14" t="n"/>
-      <c r="E46" s="14" t="n"/>
+      <c r="D46" s="13" t="n"/>
+      <c r="E46" s="13" t="n"/>
       <c r="F46" s="9" t="n">
         <v>18.9</v>
       </c>
